--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -4126,7 +4126,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>🟠</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="B29" s="3" t="str">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 08:19:03</t>
+          <t>22/07/2026 10:19:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>🟠</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="B30" s="3" t="str">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA NORTE</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 08:23:49</t>
+          <t>22/07/2026 10:23:49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>🟠</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="B31" s="3" t="str">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 08:25:50</t>
+          <t>22/07/2026 10:25:50</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>🟠</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="B46" s="3" t="str">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 08:21:17</t>
+          <t>22/07/2026 10:21:17</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>SANTIAGO PERDOMO ACERO</t>
+          <t>KEVIN ALEXIS GARCIA GUARACA</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>SANTIAGO PERDOMO ACERO</t>
+          <t>GERLYN RENTERIA OROZCO</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 09:55:48</t>
+          <t>22/07/2026 11:55:48</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>🟠</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="B24" s="3" t="str">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>ZONA CENTRO</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026 13:05</t>
+          <t>27/07/2026 14:43</t>
         </is>
       </c>
     </row>
@@ -12312,21 +12312,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SANTIAGO PERDOMO ACERO</t>
+          <t>MIGUEL JOSE NUÑEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL JOSE NUÑEZ MARQUEZ</t>
+          <t>SANTIAGO PERDOMO ACERO</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -12336,13 +12336,13 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MICHAEL STEVEN FRAILE GOMEZ</t>
+          <t>KEVIN ALEXIS GARCIA GUARACA</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -12352,17 +12352,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO BORDA MESTIZO</t>
+          <t>MICHAEL STEVEN FRAILE GOMEZ</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KEVIN ALEXIS GARCIA GUARACA</t>
+          <t>DANIEL ALEJANDRO BORDA MESTIZO</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -12506,7 +12506,7 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -12522,47 +12522,47 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA CENTRO</t>
+          <t>SPT ZONA SURORIENTE</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SPT ZONA SURORIENTE</t>
+          <t>ZONA SURORIENTE</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ZONA SURORIENTE</t>
+          <t>ZONA OCCIDENTE</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ZONA OCCIDENTE</t>
+          <t>SPT CABECERA CALLE 42</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SPT CABECERA CALLE 42</t>
+          <t>SPT ESCRITORIO VIRTUAL</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -12572,7 +12572,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SPT ESCRITORIO VIRTUAL</t>
+          <t>SPT REGIONALES</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -12582,7 +12582,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SPT REGIONALES</t>
+          <t>SPT ZONA CENTRO</t>
         </is>
       </c>
       <c r="B11" s="2">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -742,7 +742,7 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G11" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
         <v>2026-07-15T20:17:14.000Z</v>
@@ -1914,7 +1914,7 @@
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D48" t="str">
         <v>Baja</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153044</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,27 +2144,27 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T06:31:39.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>21/07/2026 14:31:24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2176,27 +2176,27 @@
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T06:38:35.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 10:07:52</v>
+        <v>21/07/2026 14:38:19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,33 +2208,33 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-21T06:37:37.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 14:37:21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
@@ -2249,18 +2249,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>-</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2272,7 +2272,7 @@
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F59" t="str">
         <v>ZONA CENTRO</v>
@@ -2281,7 +2281,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153128</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,7 +2304,7 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F60" t="str">
         <v>ZONA CENTRO</v>
@@ -2313,7 +2313,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-20T15:51:44.000Z</v>
+        <v>2026-07-19T09:48:32.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2336,178 +2336,187 @@
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I61" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-19T12:11:08.000Z</v>
+      </c>
+      <c r="I61" t="str">
+        <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>-</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I62" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
+      </c>
+      <c r="I62" t="str">
+        <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000153128</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D63" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
-      </c>
-      <c r="I63" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-20T15:51:44.000Z</v>
+      </c>
+      <c r="I63" t="str">
+        <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153133</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D64" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-21T06:44:50.000Z</v>
+      </c>
+      <c r="I64" t="str">
+        <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 14:44:34</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D65" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I65" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G66" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I66" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>-</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2516,210 +2525,213 @@
         <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E67" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="I67" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E68" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I68" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D69" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E69" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I69" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G70" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G71" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G72" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G73" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I73" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2740,27 +2752,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J74" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F75" t="str">
         <v>ZONA CENTRO</v>
@@ -2769,30 +2781,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I75" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000308081</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F76" t="str">
         <v>ZONA CENTRO</v>
@@ -2801,91 +2810,85 @@
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-15T10:58:15.999Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>21/07/2026 10:58</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I78" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F79" t="str">
         <v>ZONA CENTRO</v>
@@ -2894,15 +2897,18 @@
         <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I79" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308081</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2914,7 +2920,7 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
@@ -2923,15 +2929,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-15T10:58:15.999Z</v>
       </c>
       <c r="J80" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>21/07/2026 10:58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
@@ -2943,27 +2949,27 @@
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G81" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I81" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2975,56 +2981,56 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
       </c>
       <c r="I82" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F83" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3036,82 +3042,88 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F85" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-16T10:59:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I85" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 12:59</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I86" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3120,27 +3132,27 @@
         <v>Asignado</v>
       </c>
       <c r="D87" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E87" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3155,21 +3167,21 @@
         <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3181,24 +3193,24 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T10:59:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>21/07/2026 12:59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3210,53 +3222,53 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J91" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3268,24 +3280,24 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3297,24 +3309,24 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3326,82 +3338,82 @@
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F94" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J94" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3413,24 +3425,24 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3445,21 +3457,21 @@
         <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3471,7 +3483,7 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
@@ -3480,44 +3492,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J100" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3529,24 +3541,24 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3558,53 +3570,53 @@
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3616,24 +3628,24 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J104" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3645,24 +3657,198 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+      </c>
+      <c r="F105" t="str">
+        <v>SPT ZONA NORTE</v>
+      </c>
+      <c r="G105" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H105" s="1" t="d">
+        <v>2026-07-17T16:59:16.000Z</v>
+      </c>
+      <c r="J105" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>WO0000000309615</v>
+      </c>
+      <c r="B106" t="str">
+        <v>No</v>
+      </c>
+      <c r="C106" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E106" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F106" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G106" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H106" s="1" t="d">
+        <v>2026-07-17T15:11:16.000Z</v>
+      </c>
+      <c r="J106" t="str">
+        <v>23/07/2026 15:17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>WO0000000309641</v>
+      </c>
+      <c r="B107" t="str">
+        <v>No</v>
+      </c>
+      <c r="C107" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E107" t="str">
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+      </c>
+      <c r="F107" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G107" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H107" s="1" t="d">
+        <v>2026-07-17T16:32:15.999Z</v>
+      </c>
+      <c r="J107" t="str">
+        <v>23/07/2026 16:49</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>WO0000000309657</v>
+      </c>
+      <c r="B108" t="str">
+        <v>No</v>
+      </c>
+      <c r="C108" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E108" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F108" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G108" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H108" s="1" t="d">
+        <v>2026-07-17T17:33:15.999Z</v>
+      </c>
+      <c r="J108" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>WO0000000309779</v>
+      </c>
+      <c r="B109" t="str">
+        <v>No</v>
+      </c>
+      <c r="C109" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E109" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F109" t="str">
+        <v>SPT ZONA ORIENTE</v>
+      </c>
+      <c r="G109" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H109" s="1" t="d">
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="J109" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>WO0000000309799</v>
+      </c>
+      <c r="B110" t="str">
+        <v>No</v>
+      </c>
+      <c r="C110" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E110" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F110" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G110" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H110" s="1" t="d">
+        <v>2026-07-21T05:56:16.000Z</v>
+      </c>
+      <c r="J110" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>WO0000000309834</v>
+      </c>
+      <c r="B111" t="str">
+        <v>No</v>
+      </c>
+      <c r="C111" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E111" t="str">
         <v>GERLYN RENTERIA OROZCO</v>
       </c>
-      <c r="F105" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G105" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H105" s="1" t="d">
+      <c r="F111" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G111" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H111" s="1" t="d">
         <v>2026-07-19T11:09:15.999Z</v>
       </c>
-      <c r="J105" t="str">
+      <c r="J111" t="str">
         <v>27/07/2026 12:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -724,39 +724,39 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152417</v>
+        <v>INC000000152450</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
       </c>
       <c r="C11" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D11" t="str">
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F11" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G11" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-15T20:17:14.000Z</v>
+        <v>2026-07-16T08:45:20.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>-</v>
+        <v>21/07/2026 17:00:00</v>
       </c>
       <c r="J11" t="str">
-        <v>21/07/2026 09:09:42</v>
+        <v>-</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152450</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-16T08:45:20.000Z</v>
+        <v>2026-07-16T13:20:36.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-16T13:20:36.000Z</v>
+        <v>2026-07-16T09:06:34.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152653</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,19 +832,19 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-16T09:06:34.000Z</v>
+        <v>2026-07-17T07:13:25.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>21/07/2026 16:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152653</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,7 +864,7 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F15" t="str">
         <v>ZONA SURORIENTE</v>
@@ -873,10 +873,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T07:13:25.000Z</v>
+        <v>2026-07-17T08:33:20.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>21/07/2026 16:00:00</v>
+        <v>22/07/2026 17:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,19 +896,19 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-17T08:33:20.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>22/07/2026 17:00:00</v>
+        <v>21/07/2026 20:00:00</v>
       </c>
       <c r="J16" t="str">
         <v>-</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,19 +928,19 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F17" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>21/07/2026 20:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,19 +960,19 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T09:29:00.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000152679</v>
+        <v>INC000000152694</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,16 +992,16 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F19" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-17T09:29:00.000Z</v>
+        <v>2026-07-17T10:42:22.000Z</v>
       </c>
       <c r="I19" t="str">
         <v>21/07/2026 18:00:00</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000152694</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,7 +1024,7 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F20" t="str">
         <v>ZONA CENTRO</v>
@@ -1033,10 +1033,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-17T10:42:22.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J20" t="str">
         <v>-</v>
@@ -1044,19 +1044,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F21" t="str">
         <v>ZONA CENTRO</v>
@@ -1065,30 +1065,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>21/07/2026 09:39:44</v>
+        <v>21/07/2026 10:13:38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F22" t="str">
         <v>ZONA CENTRO</v>
@@ -1097,30 +1097,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>21/07/2026 10:13:38</v>
+        <v>21/07/2026 10:27:47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F23" t="str">
         <v>ZONA CENTRO</v>
@@ -1129,30 +1129,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>21/07/2026 10:27:47</v>
+        <v>21/07/2026 11:37:23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152863</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D24" t="str">
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F24" t="str">
         <v>ZONA CENTRO</v>
@@ -1161,82 +1161,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T06:34:52.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>21/07/2026 11:37:23</v>
+        <v>22/07/2026 06:34:36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-18T06:34:52.000Z</v>
+        <v>2026-07-18T06:51:32.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>-</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J25" t="str">
-        <v>22/07/2026 06:34:36</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152878</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F26" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-18T06:51:32.000Z</v>
+        <v>2026-07-18T07:52:05.999Z</v>
       </c>
       <c r="I26" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>-</v>
+        <v>22/07/2026 07:51:50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000152878</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1257,18 +1257,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-18T07:52:05.999Z</v>
+        <v>2026-07-18T10:01:52.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 07:51:50</v>
+        <v>22/07/2026 10:01:36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1280,27 +1280,27 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-18T10:01:52.000Z</v>
+        <v>2026-07-18T10:19:19.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>21/07/2026 08:01:36</v>
+        <v>22/07/2026 10:19:03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1321,18 +1321,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-18T10:19:19.000Z</v>
+        <v>2026-07-18T10:24:05.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 10:19:03</v>
+        <v>22/07/2026 10:23:49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1353,18 +1353,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-18T10:24:05.000Z</v>
+        <v>2026-07-18T10:26:05.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 10:23:49</v>
+        <v>22/07/2026 10:25:50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,27 +1376,27 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-18T10:26:05.999Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>22/07/2026 10:25:50</v>
+        <v>22/07/2026 10:43:40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1411,24 +1411,24 @@
         <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F32" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-18T10:50:35.999Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>21/07/2026 08:43:40</v>
+        <v>22/07/2026 10:50:20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,155 +1440,155 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F33" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-18T10:50:35.999Z</v>
+        <v>2026-07-17T13:27:34.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>21/07/2026 08:50:20</v>
+        <v>21/07/2026 13:27:18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000152913</v>
+        <v>INC000000152915</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-17T13:27:34.000Z</v>
+        <v>2026-07-17T13:57:28.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>21/07/2026 13:27:18</v>
+        <v>21/07/2026 13:57:12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000152915</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-17T13:57:28.000Z</v>
+        <v>2026-07-17T14:11:12.999Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>21/07/2026 13:57:12</v>
+        <v>21/07/2026 14:10:57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000152919</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-17T14:11:12.999Z</v>
+        <v>2026-07-17T16:39:06.999Z</v>
       </c>
       <c r="I36" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J36" t="str">
-        <v>21/07/2026 14:10:57</v>
+        <v>-</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000152934</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-17T15:39:39.000Z</v>
+        <v>2026-07-17T16:40:08.000Z</v>
       </c>
       <c r="I37" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J37" t="str">
-        <v>21/07/2026 15:39:23</v>
+        <v>-</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,19 +1600,19 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-17T19:08:56.000Z</v>
       </c>
       <c r="I38" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>21/07/2026 17:00:00</v>
       </c>
       <c r="J38" t="str">
         <v>-</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000152958</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,19 +1632,19 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-17T20:26:05.000Z</v>
       </c>
       <c r="I39" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J39" t="str">
         <v>-</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1664,19 +1664,19 @@
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-17T19:08:56.000Z</v>
+        <v>2026-07-18T08:30:58.000Z</v>
       </c>
       <c r="I40" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>21/07/2026 22:00:00</v>
       </c>
       <c r="J40" t="str">
         <v>-</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000152958</v>
+        <v>INC000000152980</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,19 +1696,19 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-17T20:26:05.000Z</v>
+        <v>2026-07-18T08:51:30.999Z</v>
       </c>
       <c r="I41" t="str">
-        <v>-</v>
+        <v>21/07/2026 16:00:00</v>
       </c>
       <c r="J41" t="str">
         <v>-</v>
@@ -1716,71 +1716,71 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-18T08:30:58.000Z</v>
+        <v>2026-07-18T09:34:34.000Z</v>
       </c>
       <c r="I42" t="str">
-        <v>21/07/2026 22:00:00</v>
+        <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>-</v>
+        <v>22/07/2026 09:34:18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000152980</v>
+        <v>INC000000152990</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-18T08:51:30.999Z</v>
+        <v>2026-07-18T09:44:00.000Z</v>
       </c>
       <c r="I43" t="str">
-        <v>21/07/2026 16:00:00</v>
+        <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>-</v>
+        <v>22/07/2026 09:43:44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,27 +1792,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-18T10:21:32.999Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>22/07/2026 10:21:17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000152990</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1827,132 +1827,132 @@
         <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-18T09:44:00.000Z</v>
+        <v>2026-07-18T10:48:25.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>21/07/2026 07:43:44</v>
+        <v>22/07/2026 10:48:09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-18T10:48:25.000Z</v>
+        <v>2026-07-19T10:15:16.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>21/07/2026 08:48:09</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D48" t="str">
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-19T10:13:27.999Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F49" t="str">
         <v>ZONA CENTRO</v>
@@ -1961,18 +1961,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-19T10:15:16.000Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1993,7 +1993,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-19T10:13:27.999Z</v>
+        <v>2026-07-19T12:25:49.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,7 +2016,7 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F51" t="str">
         <v>ZONA CENTRO</v>
@@ -2025,7 +2025,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-19T12:32:26.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
@@ -2036,71 +2036,71 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-19T12:25:49.000Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153029</v>
+        <v>INC000000153044</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-19T12:32:26.000Z</v>
+        <v>2026-07-21T06:31:39.999Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 14:31:24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2112,33 +2112,33 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T06:38:35.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 14:38:19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153044</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
@@ -2153,114 +2153,114 @@
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T06:31:39.999Z</v>
+        <v>2026-07-21T06:37:37.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>21/07/2026 14:31:24</v>
+        <v>21/07/2026 14:37:21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T06:38:35.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 14:38:19</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153047</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T06:37:37.000Z</v>
+        <v>2026-07-21T07:41:35.999Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 14:37:21</v>
+        <v>21/07/2026 15:41:20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153063</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T08:01:34.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>21/07/2026 16:01:18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2272,27 +2272,27 @@
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153066</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,91 +2304,91 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-21T08:32:32.999Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 16:32:17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-21T08:33:01.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>-</v>
+        <v>21/07/2026 16:32:45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-21T08:35:04.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 16:34:48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153128</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,27 +2400,27 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-20T15:51:44.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153133</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2432,91 +2432,91 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T06:44:50.000Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 14:44:34</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G65" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I65" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
+      </c>
+      <c r="I65" t="str">
+        <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F66" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I66" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-19T09:48:32.000Z</v>
+      </c>
+      <c r="I66" t="str">
+        <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2525,39 +2525,39 @@
         <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
-      </c>
-      <c r="I67" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-19T12:11:08.000Z</v>
+      </c>
+      <c r="I67" t="str">
+        <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>-</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E68" t="str">
         <v>GERLYN RENTERIA OROZCO</v>
@@ -2566,18 +2566,21 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
+      </c>
+      <c r="I68" t="str">
+        <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
@@ -2586,27 +2589,30 @@
         <v>En curso</v>
       </c>
       <c r="D69" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-21T06:40:50.000Z</v>
+      </c>
+      <c r="I69" t="str">
+        <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 14:40:34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2618,120 +2624,123 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G70" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-21T07:32:50.000Z</v>
+      </c>
+      <c r="I70" t="str">
+        <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>21/07/2026 15:32:34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G71" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T07:56:44.999Z</v>
+      </c>
+      <c r="I71" t="str">
+        <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 15:56:29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G72" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-21T08:03:00.000Z</v>
+      </c>
+      <c r="I72" t="str">
+        <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 16:02:44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000306908</v>
+        <v>INC000000153148</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G73" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I73" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-21T08:14:41.000Z</v>
+      </c>
+      <c r="I73" t="str">
+        <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>21/07/2026 16:14:25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000307604</v>
+        <v>INC000000153152</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2743,24 +2752,27 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G74" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-21T08:22:38.999Z</v>
+      </c>
+      <c r="I74" t="str">
+        <v>-</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>21/07/2026 16:22:23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000307613</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2772,123 +2784,135 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G75" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-21T08:37:39.000Z</v>
+      </c>
+      <c r="I75" t="str">
+        <v>-</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>21/07/2026 16:37:23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G76" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I76" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G77" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>-</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D78" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E78" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F78" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
+      </c>
+      <c r="I78" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E79" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F79" t="str">
         <v>ZONA CENTRO</v>
@@ -2897,18 +2921,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I79" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000308081</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2917,59 +2938,56 @@
         <v>En curso</v>
       </c>
       <c r="D80" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E80" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-15T10:58:15.999Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>21/07/2026 10:58</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G81" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2981,97 +2999,103 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G82" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I82" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G83" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I83" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G84" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F85" t="str">
         <v>ZONA CENTRO</v>
@@ -3080,50 +3104,44 @@
         <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I85" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I86" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3132,56 +3150,56 @@
         <v>Asignado</v>
       </c>
       <c r="D87" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F87" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3193,111 +3211,120 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F89" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-16T10:59:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 12:59</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I90" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G91" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I91" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G92" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
+      </c>
+      <c r="I92" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3309,24 +3336,24 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3338,111 +3365,117 @@
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G94" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I95" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G96" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I96" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D97" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E97" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3454,36 +3487,36 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
@@ -3492,73 +3525,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-16T10:59:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>21/07/2026 12:59</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F100" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J101" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3570,53 +3603,53 @@
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F103" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3628,24 +3661,24 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J104" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3657,24 +3690,24 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3686,24 +3719,24 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3715,24 +3748,24 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3744,82 +3777,82 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J109" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309799</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F110" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-21T05:56:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J110" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3840,15 +3873,392 @@
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>23/07/2026 11:10</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WO0000000309424</v>
+      </c>
+      <c r="B112" t="str">
+        <v>No</v>
+      </c>
+      <c r="C112" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E112" t="str">
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+      </c>
+      <c r="F112" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G112" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H112" s="1" t="d">
+        <v>2026-07-17T11:13:16.000Z</v>
+      </c>
+      <c r="J112" t="str">
+        <v>23/07/2026 11:15</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>WO0000000309436</v>
+      </c>
+      <c r="B113" t="str">
+        <v>No</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E113" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F113" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G113" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H113" s="1" t="d">
+        <v>2026-07-17T11:38:16.000Z</v>
+      </c>
+      <c r="J113" t="str">
+        <v>24/07/2026 15:38</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>WO0000000309459</v>
+      </c>
+      <c r="B114" t="str">
+        <v>No</v>
+      </c>
+      <c r="C114" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E114" t="str">
+        <v>GERLYN RENTERIA OROZCO</v>
+      </c>
+      <c r="F114" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G114" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H114" s="1" t="d">
+        <v>2026-07-17T12:09:15.999Z</v>
+      </c>
+      <c r="J114" t="str">
+        <v>23/07/2026 12:11</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>WO0000000309582</v>
+      </c>
+      <c r="B115" t="str">
+        <v>No</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E115" t="str">
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
+      </c>
+      <c r="F115" t="str">
+        <v>SPT CABECERA SUBA</v>
+      </c>
+      <c r="G115" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H115" s="1" t="d">
+        <v>2026-07-17T16:24:15.999Z</v>
+      </c>
+      <c r="J115" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>WO0000000309593</v>
+      </c>
+      <c r="B116" t="str">
+        <v>No</v>
+      </c>
+      <c r="C116" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E116" t="str">
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+      </c>
+      <c r="F116" t="str">
+        <v>SPT ZONA NORTE</v>
+      </c>
+      <c r="G116" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H116" s="1" t="d">
+        <v>2026-07-17T16:59:16.000Z</v>
+      </c>
+      <c r="J116" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>WO0000000309615</v>
+      </c>
+      <c r="B117" t="str">
+        <v>No</v>
+      </c>
+      <c r="C117" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E117" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F117" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G117" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H117" s="1" t="d">
+        <v>2026-07-17T15:11:16.000Z</v>
+      </c>
+      <c r="J117" t="str">
+        <v>23/07/2026 15:17</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>WO0000000309641</v>
+      </c>
+      <c r="B118" t="str">
+        <v>No</v>
+      </c>
+      <c r="C118" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E118" t="str">
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+      </c>
+      <c r="F118" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G118" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H118" s="1" t="d">
+        <v>2026-07-17T16:32:15.999Z</v>
+      </c>
+      <c r="J118" t="str">
+        <v>23/07/2026 16:49</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>WO0000000309657</v>
+      </c>
+      <c r="B119" t="str">
+        <v>No</v>
+      </c>
+      <c r="C119" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E119" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F119" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G119" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H119" s="1" t="d">
+        <v>2026-07-17T17:33:15.999Z</v>
+      </c>
+      <c r="J119" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>WO0000000309779</v>
+      </c>
+      <c r="B120" t="str">
+        <v>No</v>
+      </c>
+      <c r="C120" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E120" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F120" t="str">
+        <v>SPT ZONA ORIENTE</v>
+      </c>
+      <c r="G120" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H120" s="1" t="d">
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="J120" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>WO0000000309799</v>
+      </c>
+      <c r="B121" t="str">
+        <v>No</v>
+      </c>
+      <c r="C121" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E121" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F121" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G121" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H121" s="1" t="d">
+        <v>2026-07-21T05:56:16.000Z</v>
+      </c>
+      <c r="J121" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>WO0000000309875</v>
+      </c>
+      <c r="B122" t="str">
+        <v>No</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E122" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F122" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G122" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H122" s="1" t="d">
+        <v>2026-07-21T08:11:16.000Z</v>
+      </c>
+      <c r="J122" t="str">
+        <v>24/07/2026 08:19</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>WO0000000309901</v>
+      </c>
+      <c r="B123" t="str">
+        <v>No</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E123" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F123" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G123" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H123" s="1" t="d">
+        <v>2026-07-21T06:12:16.000Z</v>
+      </c>
+      <c r="J123" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>WO0000000309931</v>
+      </c>
+      <c r="B124" t="str">
+        <v>No</v>
+      </c>
+      <c r="C124" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E124" t="str">
+        <v>ALLISSON MAURICIO MORENO PABON</v>
+      </c>
+      <c r="F124" t="str">
+        <v>SPT CABECERA KENNEDY</v>
+      </c>
+      <c r="G124" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H124" s="1" t="d">
+        <v>2026-07-21T07:46:16.000Z</v>
+      </c>
+      <c r="J124" t="str">
+        <v>24/07/2026 08:32</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J128"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,7 +806,7 @@
         <v>ZONA NORTE</v>
       </c>
       <c r="G13" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H13" s="1" t="d">
         <v>2026-07-16T09:06:34.000Z</v>
@@ -1754,7 +1754,7 @@
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
@@ -2292,66 +2292,66 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153066</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T08:32:32.999Z</v>
+        <v>2026-07-21T08:33:01.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 16:32:17</v>
+        <v>21/07/2026 16:32:45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T08:33:01.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>21/07/2026 16:32:45</v>
+        <v>21/07/2026 16:35:57</v>
       </c>
     </row>
     <row r="62">
@@ -2394,7 +2394,7 @@
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
@@ -2420,39 +2420,39 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2464,27 +2464,27 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T09:01:46.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 15:01:30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2496,7 +2496,7 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2505,30 +2505,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F67" t="str">
         <v>ZONA CENTRO</v>
@@ -2537,18 +2537,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2560,7 +2560,7 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F68" t="str">
         <v>ZONA CENTRO</v>
@@ -2569,7 +2569,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-19T09:48:32.000Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
@@ -2580,39 +2580,39 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T06:40:50.000Z</v>
+        <v>2026-07-19T12:11:08.000Z</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>21/07/2026 14:40:34</v>
+        <v>-</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2624,91 +2624,91 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T07:32:50.000Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
       </c>
       <c r="I70" t="str">
         <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 15:32:34</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T07:56:44.999Z</v>
+        <v>2026-07-21T06:40:50.000Z</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 15:56:29</v>
+        <v>21/07/2026 14:40:34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T08:03:00.000Z</v>
+        <v>2026-07-21T07:32:50.000Z</v>
       </c>
       <c r="I72" t="str">
         <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 16:02:44</v>
+        <v>21/07/2026 15:32:34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153148</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2720,27 +2720,27 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T08:14:41.000Z</v>
+        <v>2026-07-21T07:56:44.999Z</v>
       </c>
       <c r="I73" t="str">
         <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>21/07/2026 16:14:25</v>
+        <v>21/07/2026 15:56:29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>INC000000153152</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2761,233 +2761,242 @@
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T08:22:38.999Z</v>
+        <v>2026-07-21T08:03:00.000Z</v>
       </c>
       <c r="I74" t="str">
         <v>-</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 16:22:23</v>
+        <v>21/07/2026 16:02:44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>INC000000153156</v>
+        <v>INC000000153148</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T08:37:39.000Z</v>
+        <v>2026-07-21T08:14:41.000Z</v>
       </c>
       <c r="I75" t="str">
         <v>-</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 16:37:23</v>
+        <v>21/07/2026 16:14:25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153152</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G76" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I76" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T08:22:38.999Z</v>
+      </c>
+      <c r="I76" t="str">
+        <v>-</v>
       </c>
       <c r="J76" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>21/07/2026 16:22:23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T08:37:39.000Z</v>
+      </c>
+      <c r="I77" t="str">
+        <v>-</v>
       </c>
       <c r="J77" t="str">
-        <v>-</v>
+        <v>21/07/2026 16:37:23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D78" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
-      </c>
-      <c r="I78" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
+      </c>
+      <c r="I78" t="str">
+        <v>-</v>
       </c>
       <c r="J78" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>21/07/2026 16:45:35</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153158</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G79" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-21T08:53:58.000Z</v>
+      </c>
+      <c r="I79" t="str">
+        <v>-</v>
       </c>
       <c r="J79" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 16:53:42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D80" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G80" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I80" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G81" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>-</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2996,210 +3005,213 @@
         <v>Pendiente</v>
       </c>
       <c r="D82" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E82" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="I82" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E83" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I83" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E84" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I84" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G85" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I86" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G87" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I87" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G88" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I88" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3220,27 +3232,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J89" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F90" t="str">
         <v>ZONA CENTRO</v>
@@ -3249,82 +3261,73 @@
         <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I90" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I91" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I92" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3336,7 +3339,7 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F93" t="str">
         <v>ZONA CENTRO</v>
@@ -3345,27 +3348,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F94" t="str">
         <v>ZONA CENTRO</v>
@@ -3374,15 +3377,18 @@
         <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I94" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3394,27 +3400,27 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G95" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I95" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3426,56 +3432,56 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G96" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
       </c>
       <c r="I96" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F97" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3487,82 +3493,88 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G99" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-16T10:59:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I99" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>21/07/2026 12:59</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F100" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G100" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I100" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3571,27 +3583,27 @@
         <v>Asignado</v>
       </c>
       <c r="D101" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E101" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3606,21 +3618,21 @@
         <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3632,24 +3644,24 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T10:59:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>21/07/2026 12:59</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3661,53 +3673,53 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F105" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J105" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3719,24 +3731,24 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3748,24 +3760,24 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3777,82 +3789,82 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F108" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J108" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F109" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F110" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3864,24 +3876,24 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F111" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G111" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
@@ -3896,21 +3908,21 @@
         <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F112" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
@@ -3922,7 +3934,7 @@
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F113" t="str">
         <v>ZONA CENTRO</v>
@@ -3931,73 +3943,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J113" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
       </c>
       <c r="C114" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D114" t="str">
         <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F114" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G114" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J114" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000309582</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F115" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G115" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-17T16:24:15.999Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J115" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4009,53 +4021,53 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F116" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
@@ -4067,7 +4079,7 @@
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F118" t="str">
         <v>SPT ZONA CENTRO</v>
@@ -4076,36 +4088,36 @@
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J118" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309582</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
       </c>
       <c r="C119" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D119" t="str">
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F119" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T16:24:15.999Z</v>
       </c>
       <c r="J119" t="str">
         <v>24/07/2026 08:00</v>
@@ -4113,7 +4125,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4125,16 +4137,16 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J120" t="str">
         <v>24/07/2026 08:00</v>
@@ -4142,7 +4154,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309799</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4154,74 +4166,74 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-21T05:56:16.000Z</v>
+        <v>2026-07-17T15:11:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 15:17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309875</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
       </c>
       <c r="C122" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D122" t="str">
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F122" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-21T08:11:16.000Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J122" t="str">
-        <v>24/07/2026 08:19</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
       </c>
       <c r="C123" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D123" t="str">
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F123" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J123" t="str">
         <v>24/07/2026 08:00</v>
@@ -4229,36 +4241,152 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
+        <v>WO0000000309779</v>
+      </c>
+      <c r="B124" t="str">
+        <v>No</v>
+      </c>
+      <c r="C124" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E124" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F124" t="str">
+        <v>SPT ZONA ORIENTE</v>
+      </c>
+      <c r="G124" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H124" s="1" t="d">
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="J124" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>WO0000000309799</v>
+      </c>
+      <c r="B125" t="str">
+        <v>No</v>
+      </c>
+      <c r="C125" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E125" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F125" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G125" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H125" s="1" t="d">
+        <v>2026-07-21T05:56:16.000Z</v>
+      </c>
+      <c r="J125" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>WO0000000309875</v>
+      </c>
+      <c r="B126" t="str">
+        <v>No</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E126" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F126" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G126" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H126" s="1" t="d">
+        <v>2026-07-21T08:11:16.000Z</v>
+      </c>
+      <c r="J126" t="str">
+        <v>24/07/2026 08:19</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>WO0000000309901</v>
+      </c>
+      <c r="B127" t="str">
+        <v>No</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E127" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F127" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G127" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H127" s="1" t="d">
+        <v>2026-07-21T06:12:16.000Z</v>
+      </c>
+      <c r="J127" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
         <v>WO0000000309931</v>
       </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-      <c r="C124" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E124" t="str">
+      <c r="B128" t="str">
+        <v>No</v>
+      </c>
+      <c r="C128" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E128" t="str">
         <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
-      <c r="F124" t="str">
+      <c r="F128" t="str">
         <v>SPT CABECERA KENNEDY</v>
       </c>
-      <c r="G124" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H124" s="1" t="d">
+      <c r="G128" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H128" s="1" t="d">
         <v>2026-07-21T07:46:16.000Z</v>
       </c>
-      <c r="J124" t="str">
+      <c r="J128" t="str">
         <v>24/07/2026 08:32</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -2906,7 +2906,7 @@
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
@@ -2932,39 +2932,39 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I80" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T09:13:30.000Z</v>
+      </c>
+      <c r="I80" t="str">
+        <v>-</v>
       </c>
       <c r="J80" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>22/07/2026 15:13:14</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
@@ -2976,27 +2976,27 @@
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G81" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
       </c>
       <c r="I81" s="1" t="d">
         <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>-</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -3005,59 +3005,62 @@
         <v>Pendiente</v>
       </c>
       <c r="D82" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E82" t="str">
         <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
       </c>
       <c r="I82" s="1" t="d">
         <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>-</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D83" t="str">
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E83" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
+      </c>
+      <c r="I83" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3075,79 +3078,76 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E85" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G86" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I86" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3159,27 +3159,27 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I87" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3191,56 +3191,59 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G88" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I88" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G89" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I89" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3252,7 +3255,7 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F90" t="str">
         <v>ZONA CENTRO</v>
@@ -3261,27 +3264,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F91" t="str">
         <v>ZONA CENTRO</v>
@@ -3290,15 +3293,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3310,7 +3313,7 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F92" t="str">
         <v>ZONA CENTRO</v>
@@ -3319,27 +3322,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F93" t="str">
         <v>ZONA CENTRO</v>
@@ -3348,27 +3351,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F94" t="str">
         <v>ZONA CENTRO</v>
@@ -3377,18 +3380,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I94" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3400,27 +3400,27 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I95" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3432,56 +3432,59 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G96" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I96" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G97" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
+      </c>
+      <c r="I97" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3502,27 +3505,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
@@ -3531,18 +3534,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I99" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3554,71 +3554,74 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G100" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
       </c>
       <c r="I100" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D101" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G101" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I101" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D102" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E102" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F102" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
@@ -3627,12 +3630,12 @@
         <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3644,24 +3647,24 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F103" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-16T10:59:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>21/07/2026 12:59</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308808</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3673,82 +3676,82 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-16T10:59:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 12:59</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J106" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3760,24 +3763,24 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3789,24 +3792,24 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3818,24 +3821,24 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F109" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J109" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
@@ -3847,24 +3850,24 @@
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F110" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3876,24 +3879,24 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F111" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G111" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
@@ -3905,36 +3908,36 @@
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F112" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D113" t="str">
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F113" t="str">
         <v>ZONA CENTRO</v>
@@ -3943,15 +3946,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
@@ -3972,27 +3975,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J114" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F115" t="str">
         <v>ZONA CENTRO</v>
@@ -4001,15 +4004,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J115" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4021,111 +4024,111 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F116" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F117" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
       </c>
       <c r="C118" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D118" t="str">
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F118" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G118" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J118" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000309582</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
       </c>
       <c r="C119" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D119" t="str">
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F119" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-17T16:24:15.999Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J119" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309582</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4137,16 +4140,16 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T16:24:15.999Z</v>
       </c>
       <c r="J120" t="str">
         <v>24/07/2026 08:00</v>
@@ -4154,7 +4157,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4166,24 +4169,24 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4195,24 +4198,24 @@
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F122" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T15:11:16.000Z</v>
       </c>
       <c r="J122" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>23/07/2026 15:17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
@@ -4224,24 +4227,24 @@
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F123" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J123" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B124" t="str">
         <v>No</v>
@@ -4253,16 +4256,16 @@
         <v>Baja</v>
       </c>
       <c r="E124" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F124" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G124" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H124" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J124" t="str">
         <v>24/07/2026 08:00</v>
@@ -4270,7 +4273,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WO0000000309799</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B125" t="str">
         <v>No</v>
@@ -4282,16 +4285,16 @@
         <v>Baja</v>
       </c>
       <c r="E125" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F125" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G125" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H125" s="1" t="d">
-        <v>2026-07-21T05:56:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="J125" t="str">
         <v>24/07/2026 08:00</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1050,7 +1050,7 @@
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
@@ -1068,10 +1068,10 @@
         <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I21" t="str">
-        <v>-</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J21" t="str">
-        <v>21/07/2026 10:13:38</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22">
@@ -1082,7 +1082,7 @@
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
@@ -1100,10 +1100,10 @@
         <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I22" t="str">
-        <v>-</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J22" t="str">
-        <v>21/07/2026 10:27:47</v>
+        <v>-</v>
       </c>
     </row>
     <row r="23">
@@ -2010,7 +2010,7 @@
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
@@ -2068,71 +2068,71 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153044</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T06:31:39.999Z</v>
+        <v>2026-07-21T06:38:35.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>21/07/2026 14:31:24</v>
+        <v>21/07/2026 14:38:19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T06:38:35.000Z</v>
+        <v>2026-07-21T06:37:37.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>21/07/2026 14:38:19</v>
+        <v>21/07/2026 14:37:21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153047</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,59 +2144,59 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T06:37:37.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>21/07/2026 14:37:21</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T07:41:35.999Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>21/07/2026 15:41:20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153063</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2217,24 +2217,24 @@
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T07:41:35.999Z</v>
+        <v>2026-07-21T08:01:34.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 15:41:20</v>
+        <v>21/07/2026 16:01:18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153063</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
@@ -2243,120 +2243,120 @@
         <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T08:01:34.000Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>21/07/2026 16:01:18</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T08:33:01.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>21/07/2026 16:32:45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T08:33:01.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 16:32:45</v>
+        <v>21/07/2026 16:35:57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T08:35:04.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>21/07/2026 16:35:57</v>
+        <v>21/07/2026 16:34:48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153070</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2377,18 +2377,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T08:35:04.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>21/07/2026 16:34:48</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153071</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2420,39 +2420,39 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T09:01:46.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>22/07/2026 15:01:30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153074</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2464,27 +2464,27 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T09:01:46.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 15:01:30</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2496,7 +2496,7 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2505,18 +2505,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2528,7 +2528,7 @@
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F67" t="str">
         <v>ZONA CENTRO</v>
@@ -2537,30 +2537,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F68" t="str">
         <v>ZONA CENTRO</v>
@@ -2569,7 +2569,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
@@ -2580,13 +2580,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
@@ -2601,30 +2601,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-19T09:48:32.000Z</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F70" t="str">
         <v>ZONA CENTRO</v>
@@ -2633,18 +2633,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-19T12:11:08.000Z</v>
       </c>
       <c r="I70" t="str">
         <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2656,59 +2656,59 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T06:40:50.000Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 14:40:34</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T07:32:50.000Z</v>
+        <v>2026-07-21T06:40:50.000Z</v>
       </c>
       <c r="I72" t="str">
         <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 15:32:34</v>
+        <v>21/07/2026 14:40:34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2720,27 +2720,27 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T07:56:44.999Z</v>
+        <v>2026-07-21T07:12:13.999Z</v>
       </c>
       <c r="I73" t="str">
         <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>21/07/2026 15:56:29</v>
+        <v>21/07/2026 17:40:24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2752,27 +2752,27 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T08:03:00.000Z</v>
+        <v>2026-07-21T07:32:50.000Z</v>
       </c>
       <c r="I74" t="str">
         <v>-</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 16:02:44</v>
+        <v>21/07/2026 15:32:34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>INC000000153148</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2784,27 +2784,27 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T08:14:41.000Z</v>
+        <v>2026-07-21T07:56:44.999Z</v>
       </c>
       <c r="I75" t="str">
         <v>-</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 16:14:25</v>
+        <v>21/07/2026 15:56:29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>INC000000153152</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2825,13 +2825,13 @@
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T08:22:38.999Z</v>
+        <v>2026-07-21T08:03:00.000Z</v>
       </c>
       <c r="I76" t="str">
         <v>-</v>
       </c>
       <c r="J76" t="str">
-        <v>21/07/2026 16:22:23</v>
+        <v>21/07/2026 16:02:44</v>
       </c>
     </row>
     <row r="77">
@@ -2900,39 +2900,39 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>INC000000153158</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T08:53:58.000Z</v>
+        <v>2026-07-21T08:49:14.000Z</v>
       </c>
       <c r="I79" t="str">
         <v>-</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 16:53:42</v>
+        <v>22/07/2026 14:48:58</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>INC000000153164</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2944,7 +2944,7 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
@@ -2953,143 +2953,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T09:13:30.000Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I80" t="str">
         <v>-</v>
       </c>
       <c r="J80" t="str">
-        <v>22/07/2026 15:13:14</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T09:13:30.000Z</v>
+      </c>
+      <c r="I81" t="str">
+        <v>-</v>
       </c>
       <c r="J81" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>22/07/2026 15:13:14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I82" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T09:24:42.999Z</v>
+      </c>
+      <c r="I82" t="str">
+        <v>-</v>
       </c>
       <c r="J82" t="str">
-        <v>-</v>
+        <v>21/07/2026 17:24:27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000153169</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
-      </c>
-      <c r="I83" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T09:19:11.000Z</v>
+      </c>
+      <c r="I83" t="str">
+        <v>-</v>
       </c>
       <c r="J83" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>21/07/2026 17:18:55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153170</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D84" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G84" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-21T09:18:59.000Z</v>
+      </c>
+      <c r="I84" t="str">
+        <v>-</v>
       </c>
       <c r="J84" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 17:18:43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3098,27 +3101,30 @@
         <v>En curso</v>
       </c>
       <c r="D85" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-21T09:25:31.000Z</v>
+      </c>
+      <c r="I85" t="str">
+        <v>-</v>
       </c>
       <c r="J85" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 17:25:15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3130,213 +3136,225 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-21T09:33:54.000Z</v>
+      </c>
+      <c r="I86" t="str">
+        <v>-</v>
       </c>
       <c r="J86" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>22/07/2026 15:33:38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G87" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I87" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T09:30:31.000Z</v>
+      </c>
+      <c r="I87" t="str">
+        <v>-</v>
       </c>
       <c r="J87" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 17:30:15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G88" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I88" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-21T09:41:10.000Z</v>
+      </c>
+      <c r="I88" t="str">
+        <v>-</v>
       </c>
       <c r="J88" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 17:40:54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000306908</v>
+        <v>INC000000153180</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G89" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I89" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-21T09:39:08.000Z</v>
+      </c>
+      <c r="I89" t="str">
+        <v>-</v>
       </c>
       <c r="J89" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>21/07/2026 17:38:52</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000307604</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G90" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
+      </c>
+      <c r="I90" t="str">
+        <v>-</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>21/07/2026 17:54:20</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000307613</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-21T10:02:00.000Z</v>
+      </c>
+      <c r="I91" t="str">
+        <v>-</v>
       </c>
       <c r="J91" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>21/07/2026 18:01:44</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000307614</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G92" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-21T10:24:30.000Z</v>
+      </c>
+      <c r="I92" t="str">
+        <v>-</v>
       </c>
       <c r="J92" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 18:24:14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
@@ -3345,50 +3363,56 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G93" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I93" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F94" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G94" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I94" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>-</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3397,152 +3421,149 @@
         <v>Pendiente</v>
       </c>
       <c r="D95" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E95" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="I95" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D96" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E96" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I96" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E97" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I97" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G98" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F99" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G99" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I99" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3554,27 +3575,27 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F100" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G100" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I100" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3586,36 +3607,36 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G101" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
       </c>
       <c r="I101" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D102" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E102" t="str">
         <v>SANTIAGO PERDOMO ACERO</v>
@@ -3624,18 +3645,18 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G102" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J102" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3647,30 +3668,30 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F103" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G103" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000308808</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
@@ -3682,24 +3703,24 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-16T10:59:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>21/07/2026 12:59</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
@@ -3708,137 +3729,146 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F105" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G105" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G106" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
       </c>
       <c r="C107" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D107" t="str">
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G107" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I107" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G108" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I108" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G109" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
+      </c>
+      <c r="I109" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
@@ -3850,24 +3880,24 @@
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F110" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G110" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3879,82 +3909,88 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F111" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G111" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
       </c>
       <c r="C112" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D112" t="str">
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F112" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G112" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I112" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D113" t="str">
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F113" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G113" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I113" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
@@ -3963,10 +3999,10 @@
         <v>Asignado</v>
       </c>
       <c r="D114" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E114" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F114" t="str">
         <v>ZONA CENTRO</v>
@@ -3975,27 +4011,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J114" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F115" t="str">
         <v>ZONA CENTRO</v>
@@ -4004,15 +4040,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I115" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J115" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4024,82 +4063,82 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F116" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J117" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
       </c>
       <c r="C118" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D118" t="str">
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F118" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G118" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J118" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
@@ -4111,24 +4150,24 @@
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F119" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J119" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309582</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4140,24 +4179,24 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-17T16:24:15.999Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J120" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4169,24 +4208,24 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4198,24 +4237,24 @@
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F122" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J122" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
@@ -4227,24 +4266,24 @@
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F123" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J123" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B124" t="str">
         <v>No</v>
@@ -4256,53 +4295,53 @@
         <v>Baja</v>
       </c>
       <c r="E124" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F124" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G124" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H124" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J124" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B125" t="str">
         <v>No</v>
       </c>
       <c r="C125" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D125" t="str">
         <v>Baja</v>
       </c>
       <c r="E125" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F125" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G125" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H125" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J125" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>WO0000000309875</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B126" t="str">
         <v>No</v>
@@ -4314,82 +4353,804 @@
         <v>Baja</v>
       </c>
       <c r="E126" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F126" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G126" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H126" s="1" t="d">
-        <v>2026-07-21T08:11:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J126" t="str">
-        <v>24/07/2026 08:19</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B127" t="str">
         <v>No</v>
       </c>
       <c r="C127" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D127" t="str">
         <v>Baja</v>
       </c>
       <c r="E127" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F127" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G127" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H127" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J127" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>WO0000000309424</v>
+      </c>
+      <c r="B128" t="str">
+        <v>No</v>
+      </c>
+      <c r="C128" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E128" t="str">
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+      </c>
+      <c r="F128" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G128" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H128" s="1" t="d">
+        <v>2026-07-17T11:13:16.000Z</v>
+      </c>
+      <c r="J128" t="str">
+        <v>23/07/2026 11:15</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>WO0000000309436</v>
+      </c>
+      <c r="B129" t="str">
+        <v>No</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E129" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F129" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G129" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H129" s="1" t="d">
+        <v>2026-07-17T11:38:16.000Z</v>
+      </c>
+      <c r="J129" t="str">
+        <v>24/07/2026 15:38</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>WO0000000309459</v>
+      </c>
+      <c r="B130" t="str">
+        <v>No</v>
+      </c>
+      <c r="C130" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E130" t="str">
+        <v>GERLYN RENTERIA OROZCO</v>
+      </c>
+      <c r="F130" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G130" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H130" s="1" t="d">
+        <v>2026-07-17T12:09:15.999Z</v>
+      </c>
+      <c r="J130" t="str">
+        <v>23/07/2026 12:11</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>WO0000000309593</v>
+      </c>
+      <c r="B131" t="str">
+        <v>No</v>
+      </c>
+      <c r="C131" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E131" t="str">
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+      </c>
+      <c r="F131" t="str">
+        <v>SPT ZONA NORTE</v>
+      </c>
+      <c r="G131" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H131" s="1" t="d">
+        <v>2026-07-17T16:59:16.000Z</v>
+      </c>
+      <c r="J131" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>WO0000000309615</v>
+      </c>
+      <c r="B132" t="str">
+        <v>No</v>
+      </c>
+      <c r="C132" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E132" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F132" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G132" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H132" s="1" t="d">
+        <v>2026-07-17T15:11:16.000Z</v>
+      </c>
+      <c r="J132" t="str">
+        <v>23/07/2026 15:17</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>WO0000000309641</v>
+      </c>
+      <c r="B133" t="str">
+        <v>No</v>
+      </c>
+      <c r="C133" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E133" t="str">
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+      </c>
+      <c r="F133" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G133" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H133" s="1" t="d">
+        <v>2026-07-17T16:32:15.999Z</v>
+      </c>
+      <c r="J133" t="str">
+        <v>23/07/2026 16:49</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>WO0000000309657</v>
+      </c>
+      <c r="B134" t="str">
+        <v>No</v>
+      </c>
+      <c r="C134" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E134" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F134" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G134" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H134" s="1" t="d">
+        <v>2026-07-17T17:33:15.999Z</v>
+      </c>
+      <c r="J134" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>WO0000000309779</v>
+      </c>
+      <c r="B135" t="str">
+        <v>No</v>
+      </c>
+      <c r="C135" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E135" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F135" t="str">
+        <v>SPT ZONA ORIENTE</v>
+      </c>
+      <c r="G135" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H135" s="1" t="d">
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="J135" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>WO0000000309875</v>
+      </c>
+      <c r="B136" t="str">
+        <v>No</v>
+      </c>
+      <c r="C136" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E136" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F136" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G136" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H136" s="1" t="d">
+        <v>2026-07-21T08:11:16.000Z</v>
+      </c>
+      <c r="J136" t="str">
+        <v>24/07/2026 08:19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>WO0000000309901</v>
+      </c>
+      <c r="B137" t="str">
+        <v>No</v>
+      </c>
+      <c r="C137" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E137" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F137" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G137" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H137" s="1" t="d">
+        <v>2026-07-21T06:12:16.000Z</v>
+      </c>
+      <c r="J137" t="str">
+        <v>24/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
         <v>WO0000000309931</v>
       </c>
-      <c r="B128" t="str">
-        <v>No</v>
-      </c>
-      <c r="C128" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D128" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E128" t="str">
+      <c r="B138" t="str">
+        <v>No</v>
+      </c>
+      <c r="C138" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E138" t="str">
         <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
-      <c r="F128" t="str">
+      <c r="F138" t="str">
         <v>SPT CABECERA KENNEDY</v>
       </c>
-      <c r="G128" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H128" s="1" t="d">
+      <c r="G138" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H138" s="1" t="d">
         <v>2026-07-21T07:46:16.000Z</v>
       </c>
-      <c r="J128" t="str">
+      <c r="J138" t="str">
         <v>24/07/2026 08:32</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>WO0000000309985</v>
+      </c>
+      <c r="B139" t="str">
+        <v>No</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E139" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F139" t="str">
+        <v>SPT ZONA ORIENTE</v>
+      </c>
+      <c r="G139" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H139" s="1" t="d">
+        <v>2026-07-21T09:27:16.000Z</v>
+      </c>
+      <c r="J139" t="str">
+        <v>24/07/2026 09:27</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>WO0000000309987</v>
+      </c>
+      <c r="B140" t="str">
+        <v>No</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E140" t="str">
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+      </c>
+      <c r="F140" t="str">
+        <v>SPT ZONA SURORIENTE</v>
+      </c>
+      <c r="G140" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H140" s="1" t="d">
+        <v>2026-07-21T09:30:16.000Z</v>
+      </c>
+      <c r="J140" t="str">
+        <v>24/07/2026 09:30</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>WO0000000309990</v>
+      </c>
+      <c r="B141" t="str">
+        <v>No</v>
+      </c>
+      <c r="C141" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E141" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F141" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G141" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H141" s="1" t="d">
+        <v>2026-07-21T09:34:16.000Z</v>
+      </c>
+      <c r="J141" t="str">
+        <v>24/07/2026 09:34</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>WO0000000309996</v>
+      </c>
+      <c r="B142" t="str">
+        <v>No</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E142" t="str">
+        <v>JUAN CAMILO RINCON BLANCO</v>
+      </c>
+      <c r="F142" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G142" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H142" s="1" t="d">
+        <v>2026-07-21T09:48:16.000Z</v>
+      </c>
+      <c r="J142" t="str">
+        <v>24/07/2026 09:48</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>WO0000000310024</v>
+      </c>
+      <c r="B143" t="str">
+        <v>No</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E143" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F143" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G143" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H143" s="1" t="d">
+        <v>2026-07-21T09:49:16.000Z</v>
+      </c>
+      <c r="J143" t="str">
+        <v>24/07/2026 09:49</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>WO0000000310026</v>
+      </c>
+      <c r="B144" t="str">
+        <v>No</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E144" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F144" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G144" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H144" s="1" t="d">
+        <v>2026-07-21T09:37:16.000Z</v>
+      </c>
+      <c r="J144" t="str">
+        <v>24/07/2026 09:37</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>WO0000000310028</v>
+      </c>
+      <c r="B145" t="str">
+        <v>No</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E145" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F145" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G145" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H145" s="1" t="d">
+        <v>2026-07-21T09:40:16.000Z</v>
+      </c>
+      <c r="J145" t="str">
+        <v>24/07/2026 09:40</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>WO0000000310030</v>
+      </c>
+      <c r="B146" t="str">
+        <v>No</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E146" t="str">
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+      </c>
+      <c r="F146" t="str">
+        <v>SPT CABECERA CALLE 94</v>
+      </c>
+      <c r="G146" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H146" s="1" t="d">
+        <v>2026-07-21T09:41:16.000Z</v>
+      </c>
+      <c r="J146" t="str">
+        <v>24/07/2026 09:41</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>WO0000000310040</v>
+      </c>
+      <c r="B147" t="str">
+        <v>No</v>
+      </c>
+      <c r="C147" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E147" t="str">
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+      </c>
+      <c r="F147" t="str">
+        <v>SPT CABECERA CENTRO MAYOR</v>
+      </c>
+      <c r="G147" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H147" s="1" t="d">
+        <v>2026-07-21T10:03:15.999Z</v>
+      </c>
+      <c r="J147" t="str">
+        <v>24/07/2026 10:03</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>WO0000000310060</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E148" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F148" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G148" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H148" s="1" t="d">
+        <v>2026-07-21T10:46:16.000Z</v>
+      </c>
+      <c r="J148" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>WO0000000310105</v>
+      </c>
+      <c r="B149" t="str">
+        <v>No</v>
+      </c>
+      <c r="C149" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E149" t="str">
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+      </c>
+      <c r="F149" t="str">
+        <v>SPT CABECERA CENTRO MAYOR</v>
+      </c>
+      <c r="G149" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H149" s="1" t="d">
+        <v>2026-07-21T09:56:16.000Z</v>
+      </c>
+      <c r="J149" t="str">
+        <v>24/07/2026 09:56</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>WO0000000310111</v>
+      </c>
+      <c r="B150" t="str">
+        <v>No</v>
+      </c>
+      <c r="C150" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E150" t="str">
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
+      </c>
+      <c r="F150" t="str">
+        <v>SPT CABECERA SUBA</v>
+      </c>
+      <c r="G150" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H150" s="1" t="d">
+        <v>2026-07-21T10:05:16.000Z</v>
+      </c>
+      <c r="J150" t="str">
+        <v>24/07/2026 10:05</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>WO0000000310112</v>
+      </c>
+      <c r="B151" t="str">
+        <v>No</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E151" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F151" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G151" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H151" s="1" t="d">
+        <v>2026-07-21T10:07:16.000Z</v>
+      </c>
+      <c r="J151" t="str">
+        <v>24/07/2026 10:07</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>WO0000000310113</v>
+      </c>
+      <c r="B152" t="str">
+        <v>No</v>
+      </c>
+      <c r="C152" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E152" t="str">
+        <v>JUAN CAMILO RINCON BLANCO</v>
+      </c>
+      <c r="F152" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G152" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H152" s="1" t="d">
+        <v>2026-07-21T10:12:16.000Z</v>
+      </c>
+      <c r="J152" t="str">
+        <v>24/07/2026 10:16</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>WO0000000310124</v>
+      </c>
+      <c r="B153" t="str">
+        <v>No</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E153" t="str">
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+      </c>
+      <c r="F153" t="str">
+        <v>SPT CABECERA CALLE 26</v>
+      </c>
+      <c r="G153" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H153" s="1" t="d">
+        <v>2026-07-21T10:33:16.000Z</v>
+      </c>
+      <c r="J153" t="str">
+        <v>24/07/2026 10:33</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J153"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J152"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1114,7 +1114,7 @@
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
@@ -1132,10 +1132,10 @@
         <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I23" t="str">
-        <v>-</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J23" t="str">
-        <v>21/07/2026 11:37:23</v>
+        <v>-</v>
       </c>
     </row>
     <row r="24">
@@ -1460,71 +1460,71 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000152915</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-17T13:57:28.000Z</v>
+        <v>2026-07-17T14:11:12.999Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>21/07/2026 13:57:12</v>
+        <v>21/07/2026 14:10:57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000152919</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-17T14:11:12.999Z</v>
+        <v>2026-07-17T16:39:06.999Z</v>
       </c>
       <c r="I35" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J35" t="str">
-        <v>21/07/2026 14:10:57</v>
+        <v>-</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1545,7 +1545,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-17T16:40:08.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>21/07/2026 21:00:00</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,19 +1568,19 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-17T19:08:56.000Z</v>
       </c>
       <c r="I37" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>21/07/2026 17:00:00</v>
       </c>
       <c r="J37" t="str">
         <v>-</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,19 +1600,19 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-17T19:08:56.000Z</v>
+        <v>2026-07-18T08:30:58.000Z</v>
       </c>
       <c r="I38" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>21/07/2026 22:00:00</v>
       </c>
       <c r="J38" t="str">
         <v>-</v>
@@ -1620,179 +1620,179 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000152958</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-17T20:26:05.000Z</v>
+        <v>2026-07-18T09:34:34.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>-</v>
+        <v>22/07/2026 09:34:18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-18T08:30:58.000Z</v>
+        <v>2026-07-18T10:21:32.999Z</v>
       </c>
       <c r="I40" t="str">
-        <v>21/07/2026 22:00:00</v>
+        <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:21:17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000152980</v>
+        <v>INC000000153000</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-18T08:51:30.999Z</v>
+        <v>2026-07-18T10:48:25.000Z</v>
       </c>
       <c r="I41" t="str">
-        <v>21/07/2026 16:00:00</v>
+        <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:48:09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F42" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000152990</v>
+        <v>INC000000153024</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-18T09:44:00.000Z</v>
+        <v>2026-07-19T10:15:16.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>22/07/2026 09:43:44</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153025</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F44" t="str">
         <v>ZONA CENTRO</v>
@@ -1801,18 +1801,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-19T10:13:27.999Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>-</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,71 +1824,71 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-18T10:48:25.000Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>22/07/2026 10:48:09</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153028</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-19T12:25:49.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153029</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F47" t="str">
         <v>ZONA CENTRO</v>
@@ -1897,50 +1897,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-19T10:15:16.000Z</v>
+        <v>2026-07-19T12:32:26.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D48" t="str">
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-19T10:13:27.999Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,59 +1952,59 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T06:38:35.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 14:38:19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153047</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-19T12:25:49.000Z</v>
+        <v>2026-07-21T06:37:37.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>-</v>
+        <v>21/07/2026 14:37:21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153029</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,7 +2016,7 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F51" t="str">
         <v>ZONA CENTRO</v>
@@ -2025,18 +2025,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-19T12:32:26.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,59 +2048,59 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T07:41:35.999Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 15:41:20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T06:38:35.000Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>21/07/2026 14:38:19</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153047</v>
+        <v>INC000000153068</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2121,82 +2121,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T06:37:37.000Z</v>
+        <v>2026-07-21T08:33:01.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>21/07/2026 14:37:21</v>
+        <v>21/07/2026 16:32:45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>21/07/2026 16:35:57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153070</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T07:41:35.999Z</v>
+        <v>2026-07-21T08:35:04.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 15:41:20</v>
+        <v>21/07/2026 16:34:48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153063</v>
+        <v>INC000000153071</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,91 +2208,91 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T08:01:34.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 16:01:18</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T08:33:01.000Z</v>
+        <v>2026-07-21T09:01:46.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>21/07/2026 16:32:45</v>
+        <v>22/07/2026 15:01:30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,91 +2304,91 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 16:35:57</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153070</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T08:35:04.000Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>21/07/2026 16:34:48</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153071</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,27 +2400,27 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153074</v>
+        <v>INC000000153110</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2432,33 +2432,33 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T09:01:46.000Z</v>
+        <v>2026-07-19T09:48:32.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 15:01:30</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153114</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
@@ -2473,30 +2473,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-19T12:11:08.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>-</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2505,146 +2505,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153134</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F67" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T06:40:50.000Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>21/07/2026 14:40:34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153138</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T07:12:13.999Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 17:40:24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153140</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-21T07:32:50.000Z</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 15:32:34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-21T07:56:44.999Z</v>
       </c>
       <c r="I70" t="str">
         <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>-</v>
+        <v>21/07/2026 15:56:29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2656,27 +2656,27 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-21T08:03:00.000Z</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 16:02:44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153156</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
@@ -2697,18 +2697,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T06:40:50.000Z</v>
+        <v>2026-07-21T08:37:39.000Z</v>
       </c>
       <c r="I72" t="str">
         <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 14:40:34</v>
+        <v>21/07/2026 16:37:23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153157</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2729,50 +2729,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T07:12:13.999Z</v>
+        <v>2026-07-21T08:45:51.000Z</v>
       </c>
       <c r="I73" t="str">
         <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>21/07/2026 17:40:24</v>
+        <v>21/07/2026 16:45:35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T07:32:50.000Z</v>
+        <v>2026-07-21T08:49:14.000Z</v>
       </c>
       <c r="I74" t="str">
         <v>-</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 15:32:34</v>
+        <v>22/07/2026 14:48:58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2784,59 +2784,59 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T07:56:44.999Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I75" t="str">
         <v>-</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 15:56:29</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153164</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G76" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T08:03:00.000Z</v>
+        <v>2026-07-21T09:13:30.000Z</v>
       </c>
       <c r="I76" t="str">
         <v>-</v>
       </c>
       <c r="J76" t="str">
-        <v>21/07/2026 16:02:44</v>
+        <v>22/07/2026 15:13:14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>INC000000153156</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
@@ -2848,27 +2848,27 @@
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T08:37:39.000Z</v>
+        <v>2026-07-21T09:24:42.999Z</v>
       </c>
       <c r="I77" t="str">
         <v>-</v>
       </c>
       <c r="J77" t="str">
-        <v>21/07/2026 16:37:23</v>
+        <v>21/07/2026 17:24:27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>INC000000153157</v>
+        <v>INC000000153170</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2880,59 +2880,59 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T09:18:59.000Z</v>
       </c>
       <c r="I78" t="str">
         <v>-</v>
       </c>
       <c r="J78" t="str">
-        <v>21/07/2026 16:45:35</v>
+        <v>21/07/2026 17:18:43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>INC000000153159</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T08:49:14.000Z</v>
+        <v>2026-07-21T09:25:31.000Z</v>
       </c>
       <c r="I79" t="str">
         <v>-</v>
       </c>
       <c r="J79" t="str">
-        <v>22/07/2026 14:48:58</v>
+        <v>21/07/2026 17:25:15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2944,7 +2944,7 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
@@ -2953,50 +2953,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-21T09:33:54.000Z</v>
       </c>
       <c r="I80" t="str">
         <v>-</v>
       </c>
       <c r="J80" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>22/07/2026 15:33:38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>INC000000153164</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T09:13:30.000Z</v>
+        <v>2026-07-21T09:30:31.000Z</v>
       </c>
       <c r="I81" t="str">
         <v>-</v>
       </c>
       <c r="J81" t="str">
-        <v>22/07/2026 15:13:14</v>
+        <v>21/07/2026 17:30:15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>INC000000153167</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -3008,27 +3008,27 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T09:24:42.999Z</v>
+        <v>2026-07-21T09:41:10.000Z</v>
       </c>
       <c r="I82" t="str">
         <v>-</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 17:24:27</v>
+        <v>21/07/2026 17:40:54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>INC000000153169</v>
+        <v>INC000000153180</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -3040,27 +3040,27 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T09:19:11.000Z</v>
+        <v>2026-07-21T09:39:08.000Z</v>
       </c>
       <c r="I83" t="str">
         <v>-</v>
       </c>
       <c r="J83" t="str">
-        <v>21/07/2026 17:18:55</v>
+        <v>21/07/2026 17:38:52</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>INC000000153170</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3072,155 +3072,155 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T09:18:59.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
       <c r="I84" t="str">
         <v>-</v>
       </c>
       <c r="J84" t="str">
-        <v>21/07/2026 17:18:43</v>
+        <v>21/07/2026 17:54:20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>INC000000153175</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T09:25:31.000Z</v>
+        <v>2026-07-21T10:02:00.000Z</v>
       </c>
       <c r="I85" t="str">
         <v>-</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 17:25:15</v>
+        <v>21/07/2026 18:01:44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>INC000000153176</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T09:33:54.000Z</v>
+        <v>2026-07-21T10:24:30.000Z</v>
       </c>
       <c r="I86" t="str">
         <v>-</v>
       </c>
       <c r="J86" t="str">
-        <v>22/07/2026 15:33:38</v>
+        <v>21/07/2026 18:24:14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>INC000000153177</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T09:30:31.000Z</v>
+        <v>2026-07-21T10:28:08.000Z</v>
       </c>
       <c r="I87" t="str">
         <v>-</v>
       </c>
       <c r="J87" t="str">
-        <v>21/07/2026 17:30:15</v>
+        <v>22/07/2026 16:27:52</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>INC000000153178</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-21T09:41:10.000Z</v>
+        <v>2026-07-21T10:47:17.000Z</v>
       </c>
       <c r="I88" t="str">
         <v>-</v>
       </c>
       <c r="J88" t="str">
-        <v>21/07/2026 17:40:54</v>
+        <v>-</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>INC000000153180</v>
+        <v>INC000000153214</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3232,27 +3232,27 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-21T09:39:08.000Z</v>
+        <v>2026-07-21T10:57:18.999Z</v>
       </c>
       <c r="I89" t="str">
         <v>-</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 17:38:52</v>
+        <v>21/07/2026 18:57:03</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153215</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3264,91 +3264,91 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T11:00:35.000Z</v>
       </c>
       <c r="I90" t="str">
         <v>-</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 17:54:20</v>
+        <v>21/07/2026 19:00:19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>INC000000153184</v>
+        <v>INC000000153301</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-21T10:02:00.000Z</v>
+        <v>2026-07-21T10:55:15.000Z</v>
       </c>
       <c r="I91" t="str">
         <v>-</v>
       </c>
       <c r="J91" t="str">
-        <v>21/07/2026 18:01:44</v>
+        <v>21/07/2026 18:54:59</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>INC000000153193</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G92" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-21T10:24:30.000Z</v>
-      </c>
-      <c r="I92" t="str">
-        <v>-</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I92" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>21/07/2026 18:24:14</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3360,178 +3360,178 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
       </c>
       <c r="I93" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>-</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E94" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G94" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I94" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>-</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D95" t="str">
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E95" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
-      </c>
-      <c r="I95" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D96" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G96" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D97" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G97" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I97" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G98" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I98" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3543,103 +3543,97 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G99" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
       </c>
       <c r="I99" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000307604</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G100" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I100" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-14T11:54:15.999Z</v>
       </c>
       <c r="J100" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 15:00</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I101" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F102" t="str">
         <v>ZONA CENTRO</v>
@@ -3648,27 +3642,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F103" t="str">
         <v>ZONA CENTRO</v>
@@ -3677,27 +3671,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F104" t="str">
         <v>ZONA CENTRO</v>
@@ -3706,27 +3700,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F105" t="str">
         <v>ZONA CENTRO</v>
@@ -3735,44 +3729,50 @@
         <v>b) 5-10</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I105" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F106" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G106" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I106" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3784,33 +3784,33 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F107" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G107" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
       </c>
       <c r="I107" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
@@ -3819,68 +3819,62 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F108" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I108" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I109" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F110" t="str">
         <v>ZONA CENTRO</v>
@@ -3889,56 +3883,62 @@
         <v>b) 5-10</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I110" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
       </c>
       <c r="C111" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D111" t="str">
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F111" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G111" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I111" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
       </c>
       <c r="C112" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D112" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E112" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F112" t="str">
         <v>ZONA CENTRO</v>
@@ -3947,18 +3947,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I112" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
@@ -3970,88 +3967,85 @@
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F113" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G113" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="I113" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
       </c>
       <c r="C114" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D114" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F114" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G114" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J114" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F115" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G115" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I115" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J115" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4063,53 +4057,53 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F116" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
@@ -4130,15 +4124,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J118" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
@@ -4150,24 +4144,24 @@
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F119" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J119" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4179,24 +4173,24 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J120" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4208,24 +4202,24 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F121" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4237,65 +4231,65 @@
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F122" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J122" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
       </c>
       <c r="C123" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D123" t="str">
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F123" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J123" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B124" t="str">
         <v>No</v>
       </c>
       <c r="C124" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D124" t="str">
         <v>Baja</v>
       </c>
       <c r="E124" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F124" t="str">
         <v>ZONA CENTRO</v>
@@ -4304,27 +4298,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H124" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J124" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B125" t="str">
         <v>No</v>
       </c>
       <c r="C125" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D125" t="str">
         <v>Baja</v>
       </c>
       <c r="E125" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F125" t="str">
         <v>ZONA CENTRO</v>
@@ -4333,56 +4327,56 @@
         <v>a) 0-4</v>
       </c>
       <c r="H125" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J125" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B126" t="str">
         <v>No</v>
       </c>
       <c r="C126" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D126" t="str">
         <v>Baja</v>
       </c>
       <c r="E126" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F126" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G126" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H126" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J126" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B127" t="str">
         <v>No</v>
       </c>
       <c r="C127" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D127" t="str">
         <v>Baja</v>
       </c>
       <c r="E127" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F127" t="str">
         <v>ZONA CENTRO</v>
@@ -4391,15 +4385,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H127" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J127" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B128" t="str">
         <v>No</v>
@@ -4411,7 +4405,7 @@
         <v>Baja</v>
       </c>
       <c r="E128" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F128" t="str">
         <v>SPT ZONA CENTRO</v>
@@ -4420,44 +4414,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H128" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J128" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B129" t="str">
         <v>No</v>
       </c>
       <c r="C129" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D129" t="str">
         <v>Baja</v>
       </c>
       <c r="E129" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F129" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G129" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H129" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J129" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B130" t="str">
         <v>No</v>
@@ -4469,24 +4463,24 @@
         <v>Baja</v>
       </c>
       <c r="E130" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F130" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G130" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H130" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-17T15:11:16.000Z</v>
       </c>
       <c r="J130" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>23/07/2026 15:17</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B131" t="str">
         <v>No</v>
@@ -4498,24 +4492,24 @@
         <v>Baja</v>
       </c>
       <c r="E131" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F131" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G131" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H131" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J131" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B132" t="str">
         <v>No</v>
@@ -4536,15 +4530,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H132" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J132" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B133" t="str">
         <v>No</v>
@@ -4556,53 +4550,53 @@
         <v>Baja</v>
       </c>
       <c r="E133" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F133" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G133" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H133" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="J133" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B134" t="str">
         <v>No</v>
       </c>
       <c r="C134" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D134" t="str">
         <v>Baja</v>
       </c>
       <c r="E134" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F134" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G134" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H134" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-18T10:37:16.000Z</v>
       </c>
       <c r="J134" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309875</v>
       </c>
       <c r="B135" t="str">
         <v>No</v>
@@ -4614,24 +4608,24 @@
         <v>Baja</v>
       </c>
       <c r="E135" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F135" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G135" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H135" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-21T08:11:16.000Z</v>
       </c>
       <c r="J135" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 08:19</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>WO0000000309875</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B136" t="str">
         <v>No</v>
@@ -4652,15 +4646,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H136" s="1" t="d">
-        <v>2026-07-21T08:11:16.000Z</v>
+        <v>2026-07-21T06:12:16.000Z</v>
       </c>
       <c r="J136" t="str">
-        <v>24/07/2026 08:19</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B137" t="str">
         <v>No</v>
@@ -4672,53 +4666,53 @@
         <v>Baja</v>
       </c>
       <c r="E137" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F137" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G137" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H137" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
+        <v>2026-07-21T07:46:16.000Z</v>
       </c>
       <c r="J137" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 08:32</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B138" t="str">
         <v>No</v>
       </c>
       <c r="C138" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D138" t="str">
         <v>Baja</v>
       </c>
       <c r="E138" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F138" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G138" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H138" s="1" t="d">
-        <v>2026-07-21T07:46:16.000Z</v>
+        <v>2026-07-21T09:27:16.000Z</v>
       </c>
       <c r="J138" t="str">
-        <v>24/07/2026 08:32</v>
+        <v>24/07/2026 09:27</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>WO0000000309985</v>
+        <v>WO0000000309987</v>
       </c>
       <c r="B139" t="str">
         <v>No</v>
@@ -4730,82 +4724,82 @@
         <v>Baja</v>
       </c>
       <c r="E139" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F139" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G139" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H139" s="1" t="d">
-        <v>2026-07-21T09:27:16.000Z</v>
+        <v>2026-07-21T09:30:16.000Z</v>
       </c>
       <c r="J139" t="str">
-        <v>24/07/2026 09:27</v>
+        <v>24/07/2026 09:30</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>WO0000000309987</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B140" t="str">
         <v>No</v>
       </c>
       <c r="C140" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D140" t="str">
         <v>Baja</v>
       </c>
       <c r="E140" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F140" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G140" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H140" s="1" t="d">
-        <v>2026-07-21T09:30:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J140" t="str">
-        <v>24/07/2026 09:30</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B141" t="str">
         <v>No</v>
       </c>
       <c r="C141" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D141" t="str">
         <v>Baja</v>
       </c>
       <c r="E141" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F141" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G141" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H141" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-21T09:48:16.000Z</v>
       </c>
       <c r="J141" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 09:48</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>WO0000000309996</v>
+        <v>WO0000000310024</v>
       </c>
       <c r="B142" t="str">
         <v>No</v>
@@ -4817,7 +4811,7 @@
         <v>Baja</v>
       </c>
       <c r="E142" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F142" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -4826,44 +4820,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H142" s="1" t="d">
-        <v>2026-07-21T09:48:16.000Z</v>
+        <v>2026-07-21T09:49:16.000Z</v>
       </c>
       <c r="J142" t="str">
-        <v>24/07/2026 09:48</v>
+        <v>24/07/2026 09:49</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WO0000000310024</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B143" t="str">
         <v>No</v>
       </c>
       <c r="C143" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D143" t="str">
         <v>Baja</v>
       </c>
       <c r="E143" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F143" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G143" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H143" s="1" t="d">
-        <v>2026-07-21T09:49:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J143" t="str">
-        <v>24/07/2026 09:49</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B144" t="str">
         <v>No</v>
@@ -4875,24 +4869,24 @@
         <v>Baja</v>
       </c>
       <c r="E144" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F144" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G144" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H144" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J144" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B145" t="str">
         <v>No</v>
@@ -4913,99 +4907,102 @@
         <v>a) 0-4</v>
       </c>
       <c r="H145" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J145" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B146" t="str">
         <v>No</v>
       </c>
       <c r="C146" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D146" t="str">
         <v>Baja</v>
       </c>
       <c r="E146" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F146" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G146" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H146" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T10:03:15.999Z</v>
       </c>
       <c r="J146" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>24/07/2026 10:03</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>WO0000000310040</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B147" t="str">
         <v>No</v>
       </c>
       <c r="C147" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D147" t="str">
         <v>Baja</v>
       </c>
       <c r="E147" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F147" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G147" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H147" s="1" t="d">
-        <v>2026-07-21T10:03:15.999Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J147" t="str">
-        <v>24/07/2026 10:03</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310105</v>
+      </c>
+      <c r="B148" t="str">
+        <v>No</v>
       </c>
       <c r="C148" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D148" t="str">
         <v>Baja</v>
       </c>
       <c r="E148" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F148" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G148" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H148" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T09:56:16.000Z</v>
       </c>
       <c r="J148" t="str">
-        <v>-</v>
+        <v>24/07/2026 09:56</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>WO0000000310105</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B149" t="str">
         <v>No</v>
@@ -5017,65 +5014,65 @@
         <v>Baja</v>
       </c>
       <c r="E149" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F149" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G149" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H149" s="1" t="d">
-        <v>2026-07-21T09:56:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J149" t="str">
-        <v>24/07/2026 09:56</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B150" t="str">
         <v>No</v>
       </c>
       <c r="C150" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D150" t="str">
         <v>Baja</v>
       </c>
       <c r="E150" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F150" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G150" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H150" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J150" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B151" t="str">
         <v>No</v>
       </c>
       <c r="C151" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D151" t="str">
         <v>Baja</v>
       </c>
       <c r="E151" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F151" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -5084,15 +5081,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H151" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T10:12:16.000Z</v>
       </c>
       <c r="J151" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 10:16</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>WO0000000310113</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B152" t="str">
         <v>No</v>
@@ -5104,53 +5101,24 @@
         <v>Baja</v>
       </c>
       <c r="E152" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F152" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G152" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H152" s="1" t="d">
-        <v>2026-07-21T10:12:16.000Z</v>
+        <v>2026-07-21T10:33:16.000Z</v>
       </c>
       <c r="J152" t="str">
-        <v>24/07/2026 10:16</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>WO0000000310124</v>
-      </c>
-      <c r="B153" t="str">
-        <v>No</v>
-      </c>
-      <c r="C153" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D153" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E153" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
-      </c>
-      <c r="F153" t="str">
-        <v>SPT CABECERA CALLE 26</v>
-      </c>
-      <c r="G153" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H153" s="1" t="d">
-        <v>2026-07-21T10:33:16.000Z</v>
-      </c>
-      <c r="J153" t="str">
         <v>24/07/2026 10:33</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J153"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J152"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J143"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152653</v>
+        <v>INC000000152663</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,7 +832,7 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F14" t="str">
         <v>ZONA SURORIENTE</v>
@@ -841,10 +841,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T07:13:25.000Z</v>
+        <v>2026-07-17T08:33:20.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>21/07/2026 16:00:00</v>
+        <v>22/07/2026 17:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,19 +864,19 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T08:33:20.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>22/07/2026 17:00:00</v>
+        <v>21/07/2026 20:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,19 +896,19 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F16" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>21/07/2026 20:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J16" t="str">
         <v>-</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152679</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,19 +928,19 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F17" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T09:29:00.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000152679</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,19 +960,19 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F18" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-17T09:29:00.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000152694</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,7 +992,7 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F19" t="str">
         <v>ZONA CENTRO</v>
@@ -1001,10 +1001,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-17T10:42:22.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I19" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J19" t="str">
         <v>-</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1033,10 +1033,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J20" t="str">
         <v>-</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1065,10 +1065,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I21" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J21" t="str">
         <v>-</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1088,19 +1088,19 @@
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-18T06:51:32.000Z</v>
       </c>
       <c r="I22" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J22" t="str">
         <v>-</v>
@@ -1108,39 +1108,39 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T10:01:52.000Z</v>
       </c>
       <c r="I23" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:01:36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000152863</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1161,50 +1161,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-18T06:34:52.000Z</v>
+        <v>2026-07-18T10:19:19.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 06:34:36</v>
+        <v>22/07/2026 10:19:03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F25" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-18T06:51:32.000Z</v>
+        <v>2026-07-18T10:24:05.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:23:49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000152878</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1216,27 +1216,27 @@
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F26" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-18T07:52:05.999Z</v>
+        <v>2026-07-18T10:26:05.999Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>22/07/2026 07:51:50</v>
+        <v>22/07/2026 10:25:50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1257,18 +1257,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-18T10:01:52.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 10:01:36</v>
+        <v>22/07/2026 10:43:40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1280,27 +1280,27 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-18T10:19:19.000Z</v>
+        <v>2026-07-18T10:50:35.999Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 10:19:03</v>
+        <v>22/07/2026 10:50:20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152913</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,27 +1312,27 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-18T10:24:05.000Z</v>
+        <v>2026-07-17T13:27:34.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 10:23:49</v>
+        <v>21/07/2026 13:27:18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000152919</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,199 +1344,199 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-18T10:26:05.999Z</v>
+        <v>2026-07-17T14:11:12.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 10:25:50</v>
+        <v>21/07/2026 14:10:57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-17T16:39:06.999Z</v>
       </c>
       <c r="I31" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J31" t="str">
-        <v>22/07/2026 10:43:40</v>
+        <v>-</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F32" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-18T10:50:35.999Z</v>
+        <v>2026-07-17T16:40:08.000Z</v>
       </c>
       <c r="I32" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 10:50:20</v>
+        <v>-</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000152913</v>
+        <v>INC000000152956</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-17T13:27:34.000Z</v>
+        <v>2026-07-17T19:08:56.000Z</v>
       </c>
       <c r="I33" t="str">
-        <v>-</v>
+        <v>21/07/2026 17:00:00</v>
       </c>
       <c r="J33" t="str">
-        <v>21/07/2026 13:27:18</v>
+        <v>-</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000152919</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-17T14:11:12.999Z</v>
+        <v>2026-07-18T08:30:58.000Z</v>
       </c>
       <c r="I34" t="str">
-        <v>-</v>
+        <v>21/07/2026 22:00:00</v>
       </c>
       <c r="J34" t="str">
-        <v>21/07/2026 14:10:57</v>
+        <v>-</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-18T09:34:34.000Z</v>
       </c>
       <c r="I35" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>-</v>
+        <v>22/07/2026 09:34:18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F36" t="str">
         <v>ZONA CENTRO</v>
@@ -1545,82 +1545,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-18T10:21:32.999Z</v>
       </c>
       <c r="I36" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:21:17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-17T19:08:56.000Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I37" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-18T08:30:58.000Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I38" t="str">
-        <v>21/07/2026 22:00:00</v>
+        <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,7 +1632,7 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F39" t="str">
         <v>ZONA NORTE</v>
@@ -1641,18 +1641,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153046</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1664,251 +1664,251 @@
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F40" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-21T06:38:35.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>21/07/2026 14:38:19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153000</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-18T10:48:25.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 10:48:09</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F42" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-21T07:41:35.999Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 15:41:20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153024</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-19T10:15:16.000Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>-</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153025</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-19T10:13:27.999Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>-</v>
+        <v>21/07/2026 16:35:57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153072</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D45" t="str">
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T08:45:29.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 16:45:13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153028</v>
+        <v>INC000000153074</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-19T12:25:49.000Z</v>
+        <v>2026-07-21T09:01:46.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>-</v>
+        <v>22/07/2026 15:01:30</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153029</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F47" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-19T12:32:26.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1923,24 +1923,24 @@
         <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153101</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,27 +1952,27 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F49" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-21T06:38:35.000Z</v>
+        <v>2026-07-18T11:56:04.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>21/07/2026 14:38:19</v>
+        <v>22/07/2026 11:55:48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153047</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,27 +1984,27 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-21T06:37:37.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>21/07/2026 14:37:21</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153120</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,7 +2016,7 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F51" t="str">
         <v>ZONA CENTRO</v>
@@ -2025,18 +2025,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-19T14:30:15.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153144</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,27 +2048,27 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-21T07:41:35.999Z</v>
+        <v>2026-07-21T07:56:44.999Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 15:41:20</v>
+        <v>21/07/2026 15:56:29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153145</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2083,88 +2083,88 @@
         <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T08:03:00.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>21/07/2026 16:02:44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153068</v>
+        <v>INC000000153159</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T08:33:01.000Z</v>
+        <v>2026-07-21T08:49:14.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>21/07/2026 16:32:45</v>
+        <v>22/07/2026 14:48:58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>21/07/2026 16:35:57</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153070</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2176,27 +2176,27 @@
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T08:35:04.000Z</v>
+        <v>2026-07-21T09:24:42.999Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 16:34:48</v>
+        <v>21/07/2026 17:24:27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153071</v>
+        <v>INC000000153175</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,123 +2208,123 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T09:25:31.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>21/07/2026 17:25:15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153176</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T09:33:54.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>22/07/2026 15:33:38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153074</v>
+        <v>INC000000153177</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T09:01:46.000Z</v>
+        <v>2026-07-21T09:30:31.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 15:01:30</v>
+        <v>21/07/2026 17:30:15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153178</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T09:41:10.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>21/07/2026 17:40:54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2336,27 +2336,27 @@
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>21/07/2026 17:54:20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2368,27 +2368,27 @@
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T10:02:00.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>21/07/2026 18:01:44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153193</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,27 +2400,27 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T10:24:30.000Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 18:24:14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153110</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2432,39 +2432,39 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-19T09:48:32.000Z</v>
+        <v>2026-07-21T10:28:08.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:27:52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153114</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F65" t="str">
         <v>ZONA CENTRO</v>
@@ -2473,114 +2473,114 @@
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-19T12:11:08.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>-</v>
+        <v>22/07/2026 16:51:52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-21T10:47:17.000Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153134</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T06:40:50.000Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>21/07/2026 14:40:34</v>
+        <v>21/07/2026 18:47:31</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153138</v>
+        <v>INC000000153214</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-21T07:12:13.999Z</v>
+        <v>2026-07-21T10:57:18.999Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 17:40:24</v>
+        <v>21/07/2026 18:57:03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153140</v>
+        <v>INC000000153217</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
@@ -2592,27 +2592,27 @@
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T07:32:50.000Z</v>
+        <v>2026-07-21T11:06:41.000Z</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>21/07/2026 15:32:34</v>
+        <v>21/07/2026 19:06:25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153219</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2624,27 +2624,27 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T07:56:44.999Z</v>
+        <v>2026-07-21T11:32:16.000Z</v>
       </c>
       <c r="I70" t="str">
         <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 15:56:29</v>
+        <v>21/07/2026 19:32:00</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153225</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2656,59 +2656,59 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T08:03:00.000Z</v>
+        <v>2026-07-21T11:41:27.000Z</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 16:02:44</v>
+        <v>21/07/2026 19:41:11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153156</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T08:37:39.000Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I72" t="str">
         <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 16:37:23</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153157</v>
+        <v>INC000000153227</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2720,59 +2720,59 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T08:45:51.000Z</v>
+        <v>2026-07-21T11:51:20.000Z</v>
       </c>
       <c r="I73" t="str">
         <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>21/07/2026 16:45:35</v>
+        <v>21/07/2026 19:51:04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>INC000000153159</v>
+        <v>INC000000153301</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T08:49:14.000Z</v>
+        <v>2026-07-21T10:55:15.000Z</v>
       </c>
       <c r="I74" t="str">
         <v>-</v>
       </c>
       <c r="J74" t="str">
-        <v>22/07/2026 14:48:58</v>
+        <v>21/07/2026 18:54:59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153303</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2784,27 +2784,27 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-21T10:59:42.999Z</v>
       </c>
       <c r="I75" t="str">
         <v>-</v>
       </c>
       <c r="J75" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>21/07/2026 18:59:27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>INC000000153164</v>
+        <v>INC000000153307</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2816,27 +2816,27 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G76" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T09:13:30.000Z</v>
+        <v>2026-07-21T11:09:38.000Z</v>
       </c>
       <c r="I76" t="str">
         <v>-</v>
       </c>
       <c r="J76" t="str">
-        <v>22/07/2026 15:13:14</v>
+        <v>22/07/2026 17:09:22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>INC000000153167</v>
+        <v>INC000000153308</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
@@ -2848,27 +2848,27 @@
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T09:24:42.999Z</v>
+        <v>2026-07-21T11:10:59.999Z</v>
       </c>
       <c r="I77" t="str">
         <v>-</v>
       </c>
       <c r="J77" t="str">
-        <v>21/07/2026 17:24:27</v>
+        <v>21/07/2026 19:10:44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>INC000000153170</v>
+        <v>INC000000153309</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2880,59 +2880,59 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T09:18:59.000Z</v>
+        <v>2026-07-21T11:15:37.999Z</v>
       </c>
       <c r="I78" t="str">
         <v>-</v>
       </c>
       <c r="J78" t="str">
-        <v>21/07/2026 17:18:43</v>
+        <v>21/07/2026 19:15:22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>INC000000153175</v>
+        <v>INC000000153318</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T09:25:31.000Z</v>
+        <v>2026-07-21T11:45:03.000Z</v>
       </c>
       <c r="I79" t="str">
         <v>-</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 17:25:15</v>
+        <v>21/07/2026 19:44:47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>INC000000153176</v>
+        <v>INC000000153320</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2944,187 +2944,184 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T09:33:54.000Z</v>
+        <v>2026-07-21T11:50:35.000Z</v>
       </c>
       <c r="I80" t="str">
         <v>-</v>
       </c>
       <c r="J80" t="str">
-        <v>22/07/2026 15:33:38</v>
+        <v>21/07/2026 19:50:19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>INC000000153177</v>
+        <v>INC000000153324</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T09:30:31.000Z</v>
+        <v>2026-07-21T11:57:50.000Z</v>
       </c>
       <c r="I81" t="str">
         <v>-</v>
       </c>
       <c r="J81" t="str">
-        <v>21/07/2026 17:30:15</v>
+        <v>21/07/2026 19:57:34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>INC000000153178</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G82" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T09:41:10.000Z</v>
-      </c>
-      <c r="I82" t="str">
-        <v>-</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I82" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 17:40:54</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>INC000000153180</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G83" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T09:39:08.000Z</v>
-      </c>
-      <c r="I83" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I83" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>21/07/2026 17:38:52</v>
+        <v>-</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>INC000000153183</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E84" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
-      </c>
-      <c r="I84" t="str">
-        <v>-</v>
+        <v>2026-07-16T12:39:15.999Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>21/07/2026 17:54:20</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>INC000000153184</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E85" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T10:02:00.000Z</v>
-      </c>
-      <c r="I85" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 18:01:44</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>INC000000153193</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3133,30 +3130,27 @@
         <v>En curso</v>
       </c>
       <c r="D86" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E86" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T10:24:30.000Z</v>
-      </c>
-      <c r="I86" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 18:24:14</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>INC000000153195</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3168,27 +3162,24 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G87" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T10:28:08.000Z</v>
-      </c>
-      <c r="I87" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>22/07/2026 16:27:52</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>INC000000153205</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3200,91 +3191,91 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G88" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-21T10:47:17.000Z</v>
-      </c>
-      <c r="I88" t="str">
-        <v>-</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I88" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>-</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>INC000000153214</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G89" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-21T10:57:18.999Z</v>
-      </c>
-      <c r="I89" t="str">
-        <v>-</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I89" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 18:57:03</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>INC000000153215</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G90" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-21T11:00:35.000Z</v>
-      </c>
-      <c r="I90" t="str">
-        <v>-</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I90" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 19:00:19</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>INC000000153301</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3296,91 +3287,82 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-21T10:55:15.000Z</v>
-      </c>
-      <c r="I91" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>21/07/2026 18:54:59</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I92" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I93" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>-</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3389,10 +3371,10 @@
         <v>En curso</v>
       </c>
       <c r="D94" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F94" t="str">
         <v>ZONA CENTRO</v>
@@ -3401,27 +3383,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D95" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F95" t="str">
         <v>ZONA CENTRO</v>
@@ -3430,44 +3412,50 @@
         <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I95" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G96" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I96" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3479,103 +3467,97 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G97" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
       </c>
       <c r="I97" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I98" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G99" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I99" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000307604</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F100" t="str">
         <v>ZONA CENTRO</v>
@@ -3584,44 +3566,50 @@
         <v>b) 5-10</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-14T11:54:15.999Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I100" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>21/07/2026 15:00</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G101" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I101" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3630,10 +3618,10 @@
         <v>Asignado</v>
       </c>
       <c r="D102" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E102" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F102" t="str">
         <v>ZONA CENTRO</v>
@@ -3642,27 +3630,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F103" t="str">
         <v>ZONA CENTRO</v>
@@ -3671,15 +3659,18 @@
         <v>b) 5-10</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I103" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3691,120 +3682,111 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G104" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F105" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G105" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I105" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J105" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F106" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G106" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I106" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
       </c>
       <c r="C107" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D107" t="str">
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G107" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I107" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3816,24 +3798,24 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F108" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G108" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3845,207 +3827,198 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F109" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G109" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F110" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G110" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I110" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
       </c>
       <c r="C111" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D111" t="str">
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F111" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G111" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I111" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
       </c>
       <c r="C112" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D112" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F112" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G112" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D113" t="str">
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F113" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G113" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I113" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J113" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
       </c>
       <c r="C114" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D114" t="str">
         <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F114" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G114" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J114" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F115" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G115" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J115" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4057,53 +4030,53 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F116" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
@@ -4115,24 +4088,24 @@
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F118" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G118" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J118" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
@@ -4144,24 +4117,24 @@
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F119" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J119" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4173,24 +4146,24 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T15:11:16.000Z</v>
       </c>
       <c r="J120" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>23/07/2026 15:17</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4202,24 +4175,24 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J121" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4231,82 +4204,82 @@
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F122" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J122" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
       </c>
       <c r="C123" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D123" t="str">
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F123" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="J123" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B124" t="str">
         <v>No</v>
       </c>
       <c r="C124" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D124" t="str">
         <v>Baja</v>
       </c>
       <c r="E124" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F124" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G124" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H124" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-18T10:37:16.000Z</v>
       </c>
       <c r="J124" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>24/07/2026 09:33</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B125" t="str">
         <v>No</v>
@@ -4318,24 +4291,24 @@
         <v>Baja</v>
       </c>
       <c r="E125" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F125" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G125" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H125" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-21T06:12:16.000Z</v>
       </c>
       <c r="J125" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B126" t="str">
         <v>No</v>
@@ -4347,24 +4320,24 @@
         <v>Baja</v>
       </c>
       <c r="E126" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F126" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G126" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H126" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-21T07:46:16.000Z</v>
       </c>
       <c r="J126" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>24/07/2026 08:32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B127" t="str">
         <v>No</v>
@@ -4376,53 +4349,53 @@
         <v>Baja</v>
       </c>
       <c r="E127" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F127" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G127" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H127" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T09:27:16.000Z</v>
       </c>
       <c r="J127" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 09:27</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309987</v>
       </c>
       <c r="B128" t="str">
         <v>No</v>
       </c>
       <c r="C128" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D128" t="str">
         <v>Baja</v>
       </c>
       <c r="E128" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F128" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G128" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H128" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-21T09:30:16.000Z</v>
       </c>
       <c r="J128" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>24/07/2026 09:30</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B129" t="str">
         <v>No</v>
@@ -4434,53 +4407,53 @@
         <v>Baja</v>
       </c>
       <c r="E129" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F129" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G129" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H129" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J129" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309996</v>
       </c>
       <c r="B130" t="str">
         <v>No</v>
       </c>
       <c r="C130" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D130" t="str">
         <v>Baja</v>
       </c>
       <c r="E130" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F130" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G130" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H130" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-21T09:48:16.000Z</v>
       </c>
       <c r="J130" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>24/07/2026 09:48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B131" t="str">
         <v>No</v>
@@ -4492,30 +4465,30 @@
         <v>Baja</v>
       </c>
       <c r="E131" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F131" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G131" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H131" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J131" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B132" t="str">
         <v>No</v>
       </c>
       <c r="C132" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D132" t="str">
         <v>Baja</v>
@@ -4530,131 +4503,131 @@
         <v>a) 0-4</v>
       </c>
       <c r="H132" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J132" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B133" t="str">
         <v>No</v>
       </c>
       <c r="C133" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D133" t="str">
         <v>Baja</v>
       </c>
       <c r="E133" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F133" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G133" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H133" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J133" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>WO0000000309805</v>
+        <v>WO0000000310040</v>
       </c>
       <c r="B134" t="str">
         <v>No</v>
       </c>
       <c r="C134" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D134" t="str">
         <v>Baja</v>
       </c>
       <c r="E134" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F134" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G134" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H134" s="1" t="d">
-        <v>2026-07-18T10:37:16.000Z</v>
+        <v>2026-07-21T10:03:15.999Z</v>
       </c>
       <c r="J134" t="str">
-        <v>24/07/2026 09:33</v>
+        <v>24/07/2026 10:03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>WO0000000309875</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B135" t="str">
         <v>No</v>
       </c>
       <c r="C135" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D135" t="str">
         <v>Baja</v>
       </c>
       <c r="E135" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F135" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G135" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H135" s="1" t="d">
-        <v>2026-07-21T08:11:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J135" t="str">
-        <v>24/07/2026 08:19</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B136" t="str">
         <v>No</v>
       </c>
       <c r="C136" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D136" t="str">
         <v>Baja</v>
       </c>
       <c r="E136" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F136" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G136" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H136" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J136" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 12:03</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B137" t="str">
         <v>No</v>
@@ -4666,82 +4639,82 @@
         <v>Baja</v>
       </c>
       <c r="E137" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F137" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G137" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H137" s="1" t="d">
-        <v>2026-07-21T07:46:16.000Z</v>
+        <v>2026-07-21T09:56:16.000Z</v>
       </c>
       <c r="J137" t="str">
-        <v>24/07/2026 08:32</v>
+        <v>24/07/2026 09:56</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>WO0000000309985</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B138" t="str">
         <v>No</v>
       </c>
       <c r="C138" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D138" t="str">
         <v>Baja</v>
       </c>
       <c r="E138" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F138" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G138" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H138" s="1" t="d">
-        <v>2026-07-21T09:27:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J138" t="str">
-        <v>24/07/2026 09:27</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>WO0000000309987</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B139" t="str">
         <v>No</v>
       </c>
       <c r="C139" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D139" t="str">
         <v>Baja</v>
       </c>
       <c r="E139" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F139" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G139" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H139" s="1" t="d">
-        <v>2026-07-21T09:30:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J139" t="str">
-        <v>24/07/2026 09:30</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310113</v>
       </c>
       <c r="B140" t="str">
         <v>No</v>
@@ -4753,53 +4726,53 @@
         <v>Baja</v>
       </c>
       <c r="E140" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F140" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G140" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H140" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-21T10:12:16.000Z</v>
       </c>
       <c r="J140" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 10:16</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>WO0000000309996</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B141" t="str">
         <v>No</v>
       </c>
       <c r="C141" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D141" t="str">
         <v>Baja</v>
       </c>
       <c r="E141" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F141" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G141" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H141" s="1" t="d">
-        <v>2026-07-21T09:48:16.000Z</v>
+        <v>2026-07-21T10:33:16.000Z</v>
       </c>
       <c r="J141" t="str">
-        <v>24/07/2026 09:48</v>
+        <v>24/07/2026 10:33</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>WO0000000310024</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B142" t="str">
         <v>No</v>
@@ -4811,314 +4784,53 @@
         <v>Baja</v>
       </c>
       <c r="E142" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F142" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G142" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H142" s="1" t="d">
-        <v>2026-07-21T09:49:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J142" t="str">
-        <v>24/07/2026 09:49</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310171</v>
       </c>
       <c r="B143" t="str">
         <v>No</v>
       </c>
       <c r="C143" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D143" t="str">
         <v>Baja</v>
       </c>
       <c r="E143" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F143" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G143" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H143" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-21T11:50:15.999Z</v>
       </c>
       <c r="J143" t="str">
-        <v>24/07/2026 09:37</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>WO0000000310028</v>
-      </c>
-      <c r="B144" t="str">
-        <v>No</v>
-      </c>
-      <c r="C144" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D144" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E144" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F144" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G144" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H144" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
-      </c>
-      <c r="J144" t="str">
-        <v>24/07/2026 09:40</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>WO0000000310030</v>
-      </c>
-      <c r="B145" t="str">
-        <v>No</v>
-      </c>
-      <c r="C145" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D145" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E145" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F145" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G145" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H145" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
-      </c>
-      <c r="J145" t="str">
-        <v>24/07/2026 09:41</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>WO0000000310040</v>
-      </c>
-      <c r="B146" t="str">
-        <v>No</v>
-      </c>
-      <c r="C146" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D146" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E146" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
-      </c>
-      <c r="F146" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
-      </c>
-      <c r="G146" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H146" s="1" t="d">
-        <v>2026-07-21T10:03:15.999Z</v>
-      </c>
-      <c r="J146" t="str">
-        <v>24/07/2026 10:03</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>WO0000000310060</v>
-      </c>
-      <c r="B147" t="str">
-        <v>No</v>
-      </c>
-      <c r="C147" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D147" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E147" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F147" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G147" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H147" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
-      </c>
-      <c r="J147" t="str">
-        <v>20/08/2026 10:46</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>WO0000000310105</v>
-      </c>
-      <c r="B148" t="str">
-        <v>No</v>
-      </c>
-      <c r="C148" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D148" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E148" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
-      </c>
-      <c r="F148" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
-      </c>
-      <c r="G148" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H148" s="1" t="d">
-        <v>2026-07-21T09:56:16.000Z</v>
-      </c>
-      <c r="J148" t="str">
-        <v>24/07/2026 09:56</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>WO0000000310111</v>
-      </c>
-      <c r="B149" t="str">
-        <v>No</v>
-      </c>
-      <c r="C149" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D149" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E149" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
-      </c>
-      <c r="F149" t="str">
-        <v>SPT CABECERA SUBA</v>
-      </c>
-      <c r="G149" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H149" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
-      </c>
-      <c r="J149" t="str">
-        <v>24/07/2026 10:05</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>WO0000000310112</v>
-      </c>
-      <c r="B150" t="str">
-        <v>No</v>
-      </c>
-      <c r="C150" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D150" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E150" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F150" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G150" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H150" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
-      </c>
-      <c r="J150" t="str">
-        <v>24/07/2026 10:07</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>WO0000000310113</v>
-      </c>
-      <c r="B151" t="str">
-        <v>No</v>
-      </c>
-      <c r="C151" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D151" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E151" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
-      </c>
-      <c r="F151" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G151" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H151" s="1" t="d">
-        <v>2026-07-21T10:12:16.000Z</v>
-      </c>
-      <c r="J151" t="str">
-        <v>24/07/2026 10:16</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>WO0000000310124</v>
-      </c>
-      <c r="B152" t="str">
-        <v>No</v>
-      </c>
-      <c r="C152" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D152" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E152" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
-      </c>
-      <c r="F152" t="str">
-        <v>SPT CABECERA CALLE 26</v>
-      </c>
-      <c r="G152" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H152" s="1" t="d">
-        <v>2026-07-21T10:33:16.000Z</v>
-      </c>
-      <c r="J152" t="str">
-        <v>24/07/2026 10:33</v>
+        <v>20/08/2026 11:56</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J143"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -704,7 +704,7 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F10" t="str">
         <v>ZONA CENTRO</v>
@@ -2996,39 +2996,39 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153327</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G82" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I82" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-21T12:02:55.000Z</v>
+      </c>
+      <c r="I82" t="str">
+        <v>-</v>
       </c>
       <c r="J82" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>21/07/2026 20:02:39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -3040,27 +3040,27 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G83" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
       </c>
       <c r="I83" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>-</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3069,59 +3069,62 @@
         <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E84" t="str">
         <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G84" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
       </c>
       <c r="I84" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>-</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D85" t="str">
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E85" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G85" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
+      </c>
+      <c r="I85" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 15:12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3142,76 +3145,73 @@
         <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E87" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G88" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I88" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3223,27 +3223,27 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G89" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I89" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3255,68 +3255,71 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G90" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I90" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G91" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I91" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000307613</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F92" t="str">
         <v>ZONA CENTRO</v>
@@ -3325,15 +3328,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-14T12:04:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 14:05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3345,7 +3348,7 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F93" t="str">
         <v>ZONA CENTRO</v>
@@ -3354,27 +3357,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F94" t="str">
         <v>ZONA CENTRO</v>
@@ -3383,27 +3386,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F95" t="str">
         <v>ZONA CENTRO</v>
@@ -3412,18 +3415,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I95" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3435,27 +3435,27 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I96" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3467,56 +3467,59 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G97" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I97" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000308271</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G98" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-15T13:58:15.999Z</v>
+      </c>
+      <c r="I98" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>21/07/2026 14:00</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3537,27 +3540,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F100" t="str">
         <v>ZONA CENTRO</v>
@@ -3566,18 +3569,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I100" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3589,68 +3589,71 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
       </c>
       <c r="I101" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D102" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F102" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G102" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I102" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D103" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E103" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F103" t="str">
         <v>ZONA CENTRO</v>
@@ -3661,103 +3664,103 @@
       <c r="H103" s="1" t="d">
         <v>2026-07-16T10:49:16.000Z</v>
       </c>
-      <c r="I103" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
-      </c>
       <c r="J103" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I104" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J106" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308965</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3769,24 +3772,24 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T16:18:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>22/07/2026 16:18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3798,24 +3801,24 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309051</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3827,24 +3830,24 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F109" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-16T16:48:15.999Z</v>
       </c>
       <c r="J109" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 08:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
@@ -3856,24 +3859,24 @@
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F110" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3885,24 +3888,24 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F111" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G111" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
@@ -3914,36 +3917,36 @@
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F112" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D113" t="str">
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F113" t="str">
         <v>ZONA CENTRO</v>
@@ -3952,15 +3955,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
@@ -3981,27 +3984,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J114" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F115" t="str">
         <v>ZONA CENTRO</v>
@@ -4010,15 +4013,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J115" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309422</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -4030,82 +4033,82 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F116" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T11:10:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>23/07/2026 11:10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F117" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000309459</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
       </c>
       <c r="C118" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D118" t="str">
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F118" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G118" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J118" t="str">
-        <v>23/07/2026 12:11</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309459</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
@@ -4117,24 +4120,24 @@
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F119" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T12:09:15.999Z</v>
       </c>
       <c r="J119" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 12:11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000309615</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4146,24 +4149,24 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J120" t="str">
-        <v>23/07/2026 15:17</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000309615</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
@@ -4175,24 +4178,24 @@
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-17T15:11:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>23/07/2026 15:17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4204,24 +4207,24 @@
         <v>Baja</v>
       </c>
       <c r="E122" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F122" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G122" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J122" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B123" t="str">
         <v>No</v>
@@ -4233,16 +4236,16 @@
         <v>Baja</v>
       </c>
       <c r="E123" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F123" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G123" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H123" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J123" t="str">
         <v>24/07/2026 08:00</v>
@@ -4250,7 +4253,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>WO0000000309805</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B124" t="str">
         <v>No</v>
@@ -4262,24 +4265,24 @@
         <v>Baja</v>
       </c>
       <c r="E124" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F124" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G124" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H124" s="1" t="d">
-        <v>2026-07-18T10:37:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="J124" t="str">
-        <v>24/07/2026 09:33</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WO0000000309901</v>
+        <v>WO0000000309805</v>
       </c>
       <c r="B125" t="str">
         <v>No</v>
@@ -4291,24 +4294,24 @@
         <v>Baja</v>
       </c>
       <c r="E125" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F125" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G125" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H125" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
+        <v>2026-07-18T10:37:16.000Z</v>
       </c>
       <c r="J125" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:33</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000309901</v>
       </c>
       <c r="B126" t="str">
         <v>No</v>
@@ -4320,53 +4323,53 @@
         <v>Baja</v>
       </c>
       <c r="E126" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F126" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G126" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H126" s="1" t="d">
-        <v>2026-07-21T07:46:16.000Z</v>
+        <v>2026-07-21T06:12:16.000Z</v>
       </c>
       <c r="J126" t="str">
-        <v>24/07/2026 08:32</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>WO0000000309985</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B127" t="str">
         <v>No</v>
       </c>
       <c r="C127" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D127" t="str">
         <v>Baja</v>
       </c>
       <c r="E127" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F127" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G127" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H127" s="1" t="d">
-        <v>2026-07-21T09:27:16.000Z</v>
+        <v>2026-07-21T07:46:16.000Z</v>
       </c>
       <c r="J127" t="str">
-        <v>24/07/2026 09:27</v>
+        <v>24/07/2026 08:32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>WO0000000309987</v>
+        <v>WO0000000309985</v>
       </c>
       <c r="B128" t="str">
         <v>No</v>
@@ -4378,19 +4381,19 @@
         <v>Baja</v>
       </c>
       <c r="E128" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F128" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G128" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H128" s="1" t="d">
-        <v>2026-07-21T09:30:16.000Z</v>
+        <v>2026-07-21T09:27:16.000Z</v>
       </c>
       <c r="J128" t="str">
-        <v>24/07/2026 09:30</v>
+        <v>24/07/2026 09:27</v>
       </c>
     </row>
     <row r="129">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J117"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152450</v>
+        <v>INC000000152496</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,19 +736,19 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F11" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G11" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-16T08:45:20.000Z</v>
+        <v>2026-07-16T13:20:36.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G12" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-16T13:20:36.000Z</v>
+        <v>2026-07-16T09:06:34.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G13" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-16T09:06:34.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>21/07/2026 20:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152663</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,19 +832,19 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T08:33:20.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>22/07/2026 17:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,19 +864,19 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F15" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>21/07/2026 20:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,7 +896,7 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F16" t="str">
         <v>ZONA CENTRO</v>
@@ -905,10 +905,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I16" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J16" t="str">
         <v>-</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000152679</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,19 +928,19 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F17" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-17T09:29:00.000Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,7 +960,7 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F18" t="str">
         <v>ZONA CENTRO</v>
@@ -969,10 +969,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,19 +992,19 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-18T06:51:32.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J19" t="str">
         <v>-</v>
@@ -1012,51 +1012,51 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F20" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-18T10:01:52.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:01:36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F21" t="str">
         <v>ZONA CENTRO</v>
@@ -1065,50 +1065,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T10:19:19.000Z</v>
       </c>
       <c r="I21" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:19:03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F22" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-18T06:51:32.000Z</v>
+        <v>2026-07-18T10:24:05.000Z</v>
       </c>
       <c r="I22" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:23:49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,27 +1120,27 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-18T10:01:52.000Z</v>
+        <v>2026-07-18T10:26:05.999Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>22/07/2026 10:01:36</v>
+        <v>22/07/2026 10:25:50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,27 +1152,27 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-18T10:19:19.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 10:19:03</v>
+        <v>22/07/2026 10:43:40</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
@@ -1184,39 +1184,39 @@
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-18T10:24:05.000Z</v>
+        <v>2026-07-18T10:50:35.999Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>22/07/2026 10:23:49</v>
+        <v>22/07/2026 10:50:20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F26" t="str">
         <v>ZONA CENTRO</v>
@@ -1225,82 +1225,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-18T10:26:05.999Z</v>
+        <v>2026-07-17T16:39:06.999Z</v>
       </c>
       <c r="I26" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J26" t="str">
-        <v>22/07/2026 10:25:50</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-17T16:40:08.000Z</v>
       </c>
       <c r="I27" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 10:43:40</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000152978</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-18T10:50:35.999Z</v>
+        <v>2026-07-18T08:30:58.000Z</v>
       </c>
       <c r="I28" t="str">
-        <v>-</v>
+        <v>21/07/2026 22:00:00</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 10:50:20</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000152913</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,27 +1312,27 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-17T13:27:34.000Z</v>
+        <v>2026-07-18T09:34:34.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>21/07/2026 13:27:18</v>
+        <v>22/07/2026 09:34:18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000152919</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,71 +1344,71 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-17T14:11:12.999Z</v>
+        <v>2026-07-18T10:21:32.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>21/07/2026 14:10:57</v>
+        <v>22/07/2026 10:21:17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I31" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F32" t="str">
         <v>ZONA CENTRO</v>
@@ -1417,82 +1417,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I32" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000152956</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F33" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-17T19:08:56.000Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I33" t="str">
-        <v>21/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-18T08:30:58.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I34" t="str">
-        <v>21/07/2026 22:00:00</v>
+        <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>-</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153056</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,91 +1504,91 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-21T07:41:35.999Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>21/07/2026 15:41:20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 14:35:57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,27 +1600,27 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,59 +1632,59 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153046</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-21T06:38:35.000Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>21/07/2026 14:38:19</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,7 +1696,7 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F41" t="str">
         <v>ZONA CENTRO</v>
@@ -1705,146 +1705,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153167</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-21T07:41:35.999Z</v>
+        <v>2026-07-21T09:24:42.999Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>21/07/2026 15:41:20</v>
+        <v>21/07/2026 17:24:27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>21/07/2026 17:54:20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153184</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T10:02:00.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>21/07/2026 16:35:57</v>
+        <v>21/07/2026 18:01:44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153072</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D45" t="str">
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-21T08:45:29.000Z</v>
+        <v>2026-07-21T10:28:08.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>21/07/2026 16:45:13</v>
+        <v>22/07/2026 16:27:52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153074</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1856,33 +1856,33 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-21T09:01:46.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 15:01:30</v>
+        <v>22/07/2026 16:51:52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
@@ -1891,24 +1891,24 @@
         <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F47" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T10:47:17.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,27 +1920,27 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>21/07/2026 18:47:31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153101</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,7 +1952,7 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F49" t="str">
         <v>ZONA CENTRO</v>
@@ -1961,18 +1961,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-18T11:56:04.000Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>22/07/2026 11:55:48</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153239</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,27 +1984,27 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T12:37:27.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 18:37:11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153120</v>
+        <v>INC000000153240</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,27 +2016,27 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F51" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-19T14:30:15.000Z</v>
+        <v>2026-07-21T12:47:42.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>21/07/2026 20:47:26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153144</v>
+        <v>INC000000153243</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,7 +2048,7 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F52" t="str">
         <v>SPT ZONA SURORIENTE</v>
@@ -2057,18 +2057,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-21T07:56:44.999Z</v>
+        <v>2026-07-21T12:58:05.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 15:56:29</v>
+        <v>21/07/2026 20:57:49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153145</v>
+        <v>INC000000153246</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2080,27 +2080,27 @@
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T08:03:00.000Z</v>
+        <v>2026-07-21T13:07:55.999Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>21/07/2026 16:02:44</v>
+        <v>22/07/2026 06:07:40</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153159</v>
+        <v>INC000000153247</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2112,91 +2112,91 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T08:49:14.000Z</v>
+        <v>2026-07-21T13:21:11.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 14:48:58</v>
+        <v>22/07/2026 06:20:55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153251</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-21T13:44:21.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>22/07/2026 06:44:06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153167</v>
+        <v>INC000000153255</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T09:24:42.999Z</v>
+        <v>2026-07-21T14:20:26.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 17:24:27</v>
+        <v>22/07/2026 07:20:10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153175</v>
+        <v>INC000000153309</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,27 +2208,27 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T09:25:31.000Z</v>
+        <v>2026-07-21T11:15:37.999Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 17:25:15</v>
+        <v>21/07/2026 19:15:22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153176</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2249,18 +2249,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T09:33:54.000Z</v>
+        <v>2026-07-21T11:57:35.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>22/07/2026 15:33:38</v>
+        <v>22/07/2026 17:57:19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153177</v>
+        <v>INC000000153326</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2272,59 +2272,59 @@
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JUAN DAVID GIL SALAMANCA</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T09:30:31.000Z</v>
+        <v>2026-07-21T12:11:56.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>21/07/2026 17:30:15</v>
+        <v>21/07/2026 20:11:40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153178</v>
+        <v>INC000000153329</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T09:41:10.000Z</v>
+        <v>2026-07-21T12:12:36.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 17:40:54</v>
+        <v>21/07/2026 20:12:20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2336,27 +2336,27 @@
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T12:13:44.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>21/07/2026 17:54:20</v>
+        <v>22/07/2026 18:13:28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153184</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2368,59 +2368,59 @@
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T10:02:00.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>21/07/2026 18:01:44</v>
+        <v>21/07/2026 20:16:47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153193</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T10:24:30.000Z</v>
+        <v>2026-07-21T12:36:32.999Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>21/07/2026 18:24:14</v>
+        <v>22/07/2026 18:36:17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153195</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2432,27 +2432,27 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T10:28:08.000Z</v>
+        <v>2026-07-21T12:47:19.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 16:27:52</v>
+        <v>22/07/2026 18:47:03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153200</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2473,50 +2473,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 16:51:52</v>
+        <v>22/07/2026 18:40:06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153205</v>
+        <v>INC000000153352</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F66" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-21T10:47:17.000Z</v>
+        <v>2026-07-21T13:48:52.000Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>-</v>
+        <v>22/07/2026 19:48:36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2528,347 +2528,338 @@
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-21T13:59:41.000Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>21/07/2026 18:47:31</v>
+        <v>22/07/2026 19:59:25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153214</v>
+        <v>INC000000153357</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-21T10:57:18.999Z</v>
+        <v>2026-07-21T14:16:50.000Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 18:57:03</v>
+        <v>22/07/2026 07:16:34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153217</v>
+        <v>INC000000153362</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T11:06:41.000Z</v>
+        <v>2026-07-21T14:37:17.999Z</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>21/07/2026 19:06:25</v>
+        <v>22/07/2026 07:37:02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153219</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G70" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T11:32:16.000Z</v>
-      </c>
-      <c r="I70" t="str">
-        <v>-</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I70" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 19:32:00</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153225</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G71" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T11:41:27.000Z</v>
-      </c>
-      <c r="I71" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 19:41:11</v>
+        <v>-</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153226</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E72" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F72" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
-      </c>
-      <c r="I72" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153227</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D73" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E73" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G73" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T11:51:20.000Z</v>
-      </c>
-      <c r="I73" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>21/07/2026 19:51:04</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>INC000000153301</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G74" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T10:55:15.000Z</v>
-      </c>
-      <c r="I74" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 18:54:59</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>INC000000153303</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F75" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T10:59:42.999Z</v>
-      </c>
-      <c r="I75" t="str">
-        <v>-</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I75" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 18:59:27</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>INC000000153307</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G76" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T11:09:38.000Z</v>
-      </c>
-      <c r="I76" t="str">
-        <v>-</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I76" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>22/07/2026 17:09:22</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>INC000000153308</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G77" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T11:10:59.999Z</v>
-      </c>
-      <c r="I77" t="str">
-        <v>-</v>
+        <v>2026-07-10T14:58:16.000Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>21/07/2026 19:10:44</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>INC000000153309</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2880,27 +2871,24 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T11:15:37.999Z</v>
-      </c>
-      <c r="I78" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>21/07/2026 19:15:22</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>INC000000153318</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
@@ -2912,187 +2900,175 @@
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G79" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T11:45:03.000Z</v>
-      </c>
-      <c r="I79" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 19:44:47</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>INC000000153320</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T11:50:35.000Z</v>
-      </c>
-      <c r="I80" t="str">
-        <v>-</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>21/07/2026 19:50:19</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>INC000000153324</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T11:57:50.000Z</v>
-      </c>
-      <c r="I81" t="str">
-        <v>-</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>21/07/2026 19:57:34</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>INC000000153327</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G82" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T12:02:55.000Z</v>
-      </c>
-      <c r="I82" t="str">
-        <v>-</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I82" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 20:02:39</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I83" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I84" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>-</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3101,71 +3077,74 @@
         <v>Pendiente</v>
       </c>
       <c r="D85" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
       </c>
       <c r="I85" s="1" t="d">
         <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 15:12</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D86" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I86" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D87" t="str">
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E87" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F87" t="str">
         <v>ZONA CENTRO</v>
@@ -3174,82 +3153,82 @@
         <v>b) 5-10</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I88" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G89" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I89" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
@@ -3258,56 +3237,50 @@
         <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G90" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I90" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G91" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I91" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000307613</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3319,82 +3292,82 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G92" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-14T12:04:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>21/07/2026 14:05</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G93" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F94" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G94" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3406,149 +3379,140 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F95" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F96" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I96" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J96" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I97" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J97" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000308271</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-15T13:58:15.999Z</v>
-      </c>
-      <c r="I98" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>21/07/2026 14:00</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G99" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3560,149 +3524,140 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F100" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G100" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000309641</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I101" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-17T16:32:15.999Z</v>
       </c>
       <c r="J101" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>23/07/2026 16:49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G102" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I102" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J102" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D103" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F103" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G103" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G104" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I104" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J104" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000309931</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3714,53 +3669,53 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F105" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-21T07:46:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>24/07/2026 08:32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000308965</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3772,111 +3727,111 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-16T16:18:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>22/07/2026 16:18</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000309051</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-16T16:48:15.999Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>23/07/2026 08:00</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F110" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000310105</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3888,24 +3843,24 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F111" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G111" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-21T09:56:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>24/07/2026 09:56</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
@@ -3917,24 +3872,24 @@
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F112" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
@@ -3946,53 +3901,53 @@
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F113" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G113" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
       </c>
       <c r="C114" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D114" t="str">
         <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F114" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G114" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-21T10:33:16.000Z</v>
       </c>
       <c r="J114" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>24/07/2026 10:33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000310189</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
@@ -4003,9 +3958,6 @@
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
-      <c r="E115" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
-      </c>
       <c r="F115" t="str">
         <v>ZONA CENTRO</v>
       </c>
@@ -4013,827 +3965,70 @@
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T12:24:16.000Z</v>
       </c>
       <c r="J115" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 14:24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000309422</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
       </c>
       <c r="C116" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D116" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E116" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F116" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-17T11:10:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>23/07/2026 11:10</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
-      <c r="E117" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
-      </c>
       <c r="F117" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>23/07/2026 11:15</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>WO0000000309436</v>
-      </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-      <c r="C118" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E118" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F118" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G118" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H118" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
-      </c>
-      <c r="J118" t="str">
-        <v>24/07/2026 15:38</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>WO0000000309459</v>
-      </c>
-      <c r="B119" t="str">
-        <v>No</v>
-      </c>
-      <c r="C119" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D119" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E119" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
-      </c>
-      <c r="F119" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G119" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H119" s="1" t="d">
-        <v>2026-07-17T12:09:15.999Z</v>
-      </c>
-      <c r="J119" t="str">
-        <v>23/07/2026 12:11</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>WO0000000309593</v>
-      </c>
-      <c r="B120" t="str">
-        <v>No</v>
-      </c>
-      <c r="C120" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D120" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E120" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
-      </c>
-      <c r="F120" t="str">
-        <v>SPT ZONA NORTE</v>
-      </c>
-      <c r="G120" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H120" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
-      </c>
-      <c r="J120" t="str">
-        <v>24/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>WO0000000309615</v>
-      </c>
-      <c r="B121" t="str">
-        <v>No</v>
-      </c>
-      <c r="C121" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D121" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E121" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F121" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G121" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H121" s="1" t="d">
-        <v>2026-07-17T15:11:16.000Z</v>
-      </c>
-      <c r="J121" t="str">
-        <v>23/07/2026 15:17</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>WO0000000309641</v>
-      </c>
-      <c r="B122" t="str">
-        <v>No</v>
-      </c>
-      <c r="C122" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D122" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E122" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F122" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G122" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H122" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
-      </c>
-      <c r="J122" t="str">
-        <v>23/07/2026 16:49</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>WO0000000309657</v>
-      </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-      <c r="C123" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D123" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E123" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F123" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G123" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H123" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
-      </c>
-      <c r="J123" t="str">
-        <v>24/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>WO0000000309779</v>
-      </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-      <c r="C124" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E124" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
-      </c>
-      <c r="F124" t="str">
-        <v>SPT ZONA ORIENTE</v>
-      </c>
-      <c r="G124" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H124" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="J124" t="str">
-        <v>24/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>WO0000000309805</v>
-      </c>
-      <c r="B125" t="str">
-        <v>No</v>
-      </c>
-      <c r="C125" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D125" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E125" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
-      </c>
-      <c r="F125" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G125" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H125" s="1" t="d">
-        <v>2026-07-18T10:37:16.000Z</v>
-      </c>
-      <c r="J125" t="str">
-        <v>24/07/2026 09:33</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>WO0000000309901</v>
-      </c>
-      <c r="B126" t="str">
-        <v>No</v>
-      </c>
-      <c r="C126" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D126" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E126" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F126" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G126" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H126" s="1" t="d">
-        <v>2026-07-21T06:12:16.000Z</v>
-      </c>
-      <c r="J126" t="str">
-        <v>24/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>WO0000000309931</v>
-      </c>
-      <c r="B127" t="str">
-        <v>No</v>
-      </c>
-      <c r="C127" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D127" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E127" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
-      </c>
-      <c r="F127" t="str">
-        <v>SPT CABECERA KENNEDY</v>
-      </c>
-      <c r="G127" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H127" s="1" t="d">
-        <v>2026-07-21T07:46:16.000Z</v>
-      </c>
-      <c r="J127" t="str">
-        <v>24/07/2026 08:32</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>WO0000000309985</v>
-      </c>
-      <c r="B128" t="str">
-        <v>No</v>
-      </c>
-      <c r="C128" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D128" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E128" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
-      </c>
-      <c r="F128" t="str">
-        <v>SPT ZONA ORIENTE</v>
-      </c>
-      <c r="G128" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H128" s="1" t="d">
-        <v>2026-07-21T09:27:16.000Z</v>
-      </c>
-      <c r="J128" t="str">
-        <v>24/07/2026 09:27</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>WO0000000309990</v>
-      </c>
-      <c r="B129" t="str">
-        <v>No</v>
-      </c>
-      <c r="C129" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D129" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E129" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F129" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G129" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H129" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
-      </c>
-      <c r="J129" t="str">
-        <v>24/07/2026 09:34</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>WO0000000309996</v>
-      </c>
-      <c r="B130" t="str">
-        <v>No</v>
-      </c>
-      <c r="C130" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D130" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E130" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
-      </c>
-      <c r="F130" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G130" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H130" s="1" t="d">
-        <v>2026-07-21T09:48:16.000Z</v>
-      </c>
-      <c r="J130" t="str">
-        <v>24/07/2026 09:48</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>WO0000000310026</v>
-      </c>
-      <c r="B131" t="str">
-        <v>No</v>
-      </c>
-      <c r="C131" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D131" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E131" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F131" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G131" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H131" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
-      </c>
-      <c r="J131" t="str">
-        <v>24/07/2026 09:37</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>WO0000000310028</v>
-      </c>
-      <c r="B132" t="str">
-        <v>No</v>
-      </c>
-      <c r="C132" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D132" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E132" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F132" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G132" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H132" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
-      </c>
-      <c r="J132" t="str">
-        <v>24/07/2026 09:40</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>WO0000000310030</v>
-      </c>
-      <c r="B133" t="str">
-        <v>No</v>
-      </c>
-      <c r="C133" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D133" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E133" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
-      </c>
-      <c r="F133" t="str">
-        <v>SPT CABECERA CALLE 94</v>
-      </c>
-      <c r="G133" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H133" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
-      </c>
-      <c r="J133" t="str">
-        <v>24/07/2026 09:41</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>WO0000000310040</v>
-      </c>
-      <c r="B134" t="str">
-        <v>No</v>
-      </c>
-      <c r="C134" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D134" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E134" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
-      </c>
-      <c r="F134" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
-      </c>
-      <c r="G134" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H134" s="1" t="d">
-        <v>2026-07-21T10:03:15.999Z</v>
-      </c>
-      <c r="J134" t="str">
-        <v>24/07/2026 10:03</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>WO0000000310060</v>
-      </c>
-      <c r="B135" t="str">
-        <v>No</v>
-      </c>
-      <c r="C135" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D135" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E135" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F135" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G135" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H135" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
-      </c>
-      <c r="J135" t="str">
-        <v>20/08/2026 10:46</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>WO0000000310097</v>
-      </c>
-      <c r="B136" t="str">
-        <v>No</v>
-      </c>
-      <c r="C136" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D136" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E136" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F136" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G136" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H136" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
-      </c>
-      <c r="J136" t="str">
-        <v>24/07/2026 12:03</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>WO0000000310105</v>
-      </c>
-      <c r="B137" t="str">
-        <v>No</v>
-      </c>
-      <c r="C137" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D137" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E137" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
-      </c>
-      <c r="F137" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
-      </c>
-      <c r="G137" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H137" s="1" t="d">
-        <v>2026-07-21T09:56:16.000Z</v>
-      </c>
-      <c r="J137" t="str">
-        <v>24/07/2026 09:56</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>WO0000000310111</v>
-      </c>
-      <c r="B138" t="str">
-        <v>No</v>
-      </c>
-      <c r="C138" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D138" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E138" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
-      </c>
-      <c r="F138" t="str">
-        <v>SPT CABECERA SUBA</v>
-      </c>
-      <c r="G138" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H138" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
-      </c>
-      <c r="J138" t="str">
-        <v>24/07/2026 10:05</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>WO0000000310112</v>
-      </c>
-      <c r="B139" t="str">
-        <v>No</v>
-      </c>
-      <c r="C139" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D139" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E139" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F139" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G139" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H139" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
-      </c>
-      <c r="J139" t="str">
-        <v>24/07/2026 10:07</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>WO0000000310113</v>
-      </c>
-      <c r="B140" t="str">
-        <v>No</v>
-      </c>
-      <c r="C140" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D140" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E140" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
-      </c>
-      <c r="F140" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G140" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H140" s="1" t="d">
-        <v>2026-07-21T10:12:16.000Z</v>
-      </c>
-      <c r="J140" t="str">
-        <v>24/07/2026 10:16</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>WO0000000310124</v>
-      </c>
-      <c r="B141" t="str">
-        <v>No</v>
-      </c>
-      <c r="C141" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D141" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E141" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
-      </c>
-      <c r="F141" t="str">
-        <v>SPT CABECERA CALLE 26</v>
-      </c>
-      <c r="G141" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H141" s="1" t="d">
-        <v>2026-07-21T10:33:16.000Z</v>
-      </c>
-      <c r="J141" t="str">
-        <v>24/07/2026 10:33</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>WO0000000310164</v>
-      </c>
-      <c r="B142" t="str">
-        <v>No</v>
-      </c>
-      <c r="C142" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D142" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E142" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F142" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G142" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H142" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
-      </c>
-      <c r="J142" t="str">
-        <v>24/07/2026 11:38</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>WO0000000310171</v>
-      </c>
-      <c r="B143" t="str">
-        <v>No</v>
-      </c>
-      <c r="C143" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D143" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E143" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
-      </c>
-      <c r="F143" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G143" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H143" s="1" t="d">
-        <v>2026-07-21T11:50:15.999Z</v>
-      </c>
-      <c r="J143" t="str">
-        <v>20/08/2026 11:56</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J117"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -550,7 +550,7 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G5" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H5" s="1" t="d">
         <v>2026-07-10T15:10:06.999Z</v>
@@ -628,31 +628,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>INC000000152308</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B8" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C8" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D8" t="str">
         <v>Baja</v>
       </c>
       <c r="E8" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F8" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G8" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H8" s="1" t="d">
-        <v>2026-07-15T09:06:35.000Z</v>
+        <v>2026-07-15T09:19:18.000Z</v>
       </c>
       <c r="I8" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J8" t="str">
         <v>-</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000152320</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B9" t="str">
         <v>No</v>
@@ -672,7 +672,7 @@
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F9" t="str">
         <v>ZONA CENTRO</v>
@@ -681,10 +681,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-15T09:19:18.000Z</v>
+        <v>2026-07-15T12:30:33.000Z</v>
       </c>
       <c r="I9" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J9" t="str">
         <v>-</v>
@@ -692,7 +692,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152537</v>
       </c>
       <c r="B10" t="str">
         <v>No</v>
@@ -704,16 +704,16 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F10" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G10" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-15T12:30:33.000Z</v>
+        <v>2026-07-16T09:06:34.000Z</v>
       </c>
       <c r="I10" t="str">
         <v>21/07/2026 18:00:00</v>
@@ -724,19 +724,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152496</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B11" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C11" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D11" t="str">
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
@@ -745,10 +745,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-16T13:20:36.000Z</v>
+        <v>2026-07-16T11:12:30.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G12" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-16T09:06:34.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>21/07/2026 20:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F13" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>21/07/2026 20:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,7 +832,7 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F14" t="str">
         <v>ZONA CENTRO</v>
@@ -841,7 +841,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I14" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,7 +864,7 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F15" t="str">
         <v>ZONA CENTRO</v>
@@ -873,10 +873,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I15" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,7 +896,7 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F16" t="str">
         <v>ZONA CENTRO</v>
@@ -905,7 +905,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I16" t="str">
         <v>22/07/2026 18:00:00</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,7 +928,7 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F17" t="str">
         <v>ZONA CENTRO</v>
@@ -937,10 +937,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>21/07/2026 18:00:00</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152866</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,16 +960,16 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T06:51:32.000Z</v>
       </c>
       <c r="I18" t="str">
         <v>21/07/2026 18:00:00</v>
@@ -980,39 +980,39 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000152890</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F19" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-18T06:51:32.000Z</v>
+        <v>2026-07-18T10:01:52.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:01:36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000152891</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,27 +1024,27 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F20" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-18T10:01:52.000Z</v>
+        <v>2026-07-18T10:19:19.000Z</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>22/07/2026 10:01:36</v>
+        <v>22/07/2026 10:19:03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000152892</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1065,18 +1065,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-18T10:19:19.000Z</v>
+        <v>2026-07-18T10:24:05.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>22/07/2026 10:19:03</v>
+        <v>22/07/2026 10:23:49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000152893</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1097,18 +1097,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-18T10:24:05.000Z</v>
+        <v>2026-07-18T10:26:05.999Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>22/07/2026 10:23:49</v>
+        <v>22/07/2026 10:25:50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,27 +1120,27 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-18T10:26:05.999Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>22/07/2026 10:25:50</v>
+        <v>22/07/2026 10:43:40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000152897</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1161,50 +1161,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-18T10:50:35.999Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 10:43:40</v>
+        <v>22/07/2026 10:50:20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000152939</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-18T10:50:35.999Z</v>
+        <v>2026-07-17T16:39:06.999Z</v>
       </c>
       <c r="I25" t="str">
-        <v>-</v>
+        <v>21/07/2026 21:00:00</v>
       </c>
       <c r="J25" t="str">
-        <v>22/07/2026 10:50:20</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000152944</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1225,7 +1225,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-17T16:40:08.000Z</v>
       </c>
       <c r="I26" t="str">
         <v>21/07/2026 21:00:00</v>
@@ -1236,103 +1236,103 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000152987</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-18T09:34:34.000Z</v>
       </c>
       <c r="I27" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>-</v>
+        <v>22/07/2026 09:34:18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000152978</v>
+        <v>INC000000152994</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-18T08:30:58.000Z</v>
+        <v>2026-07-18T10:21:32.999Z</v>
       </c>
       <c r="I28" t="str">
-        <v>21/07/2026 22:00:00</v>
+        <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>-</v>
+        <v>22/07/2026 10:21:17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,7 +1344,7 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F30" t="str">
         <v>ZONA CENTRO</v>
@@ -1353,18 +1353,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,16 +1376,16 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
@@ -1396,19 +1396,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F32" t="str">
         <v>ZONA CENTRO</v>
@@ -1417,18 +1417,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,59 +1440,59 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>22/07/2026 14:35:57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153056</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,123 +1504,123 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-21T07:41:35.999Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>21/07/2026 15:41:20</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>EXT SON ANDERSON CAMILO JAIMES GUTIERREZ</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 14:35:57</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153183</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,71 +1632,71 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-21T09:54:36.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>21/07/2026 17:54:20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F40" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-21T10:28:08.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:27:52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F41" t="str">
         <v>ZONA CENTRO</v>
@@ -1705,50 +1705,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>22/07/2026 16:51:52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153167</v>
+        <v>INC000000153205</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-21T09:24:42.999Z</v>
+        <v>2026-07-21T10:47:17.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>21/07/2026 17:24:27</v>
+        <v>22/07/2026 08:45:57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
@@ -1760,59 +1760,59 @@
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>21/07/2026 17:54:20</v>
+        <v>21/07/2026 18:47:31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153184</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-21T10:02:00.000Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>21/07/2026 18:01:44</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153195</v>
+        <v>INC000000153243</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,27 +1824,27 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-21T10:28:08.000Z</v>
+        <v>2026-07-21T12:58:05.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>22/07/2026 16:27:52</v>
+        <v>21/07/2026 20:57:49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153200</v>
+        <v>INC000000153247</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1856,33 +1856,33 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T13:21:11.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 16:51:52</v>
+        <v>22/07/2026 06:20:55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153205</v>
+        <v>INC000000153251</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
@@ -1897,18 +1897,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-21T10:47:17.000Z</v>
+        <v>2026-07-21T13:44:21.999Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>-</v>
+        <v>22/07/2026 06:44:06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153258</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,27 +1920,27 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-21T15:00:43.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>21/07/2026 18:47:31</v>
+        <v>22/07/2026 08:00:27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1961,178 +1961,178 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
+        <v>2026-07-21T11:57:35.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>22/07/2026 17:57:19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153239</v>
+        <v>INC000000153329</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-21T12:37:27.000Z</v>
+        <v>2026-07-21T12:12:36.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>22/07/2026 18:37:11</v>
+        <v>21/07/2026 20:12:20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153240</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-21T12:47:42.000Z</v>
+        <v>2026-07-21T12:13:44.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>21/07/2026 20:47:26</v>
+        <v>22/07/2026 18:13:28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153243</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-21T12:58:05.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 20:57:49</v>
+        <v>21/07/2026 20:16:47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153246</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T13:07:55.999Z</v>
+        <v>2026-07-21T12:36:32.999Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 06:07:40</v>
+        <v>22/07/2026 18:36:17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153247</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T13:21:11.000Z</v>
+        <v>2026-07-21T12:47:19.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 06:20:55</v>
+        <v>22/07/2026 18:47:03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153251</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,91 +2144,91 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T13:44:21.999Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 06:44:06</v>
+        <v>22/07/2026 18:40:06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153255</v>
+        <v>INC000000153352</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T14:20:26.000Z</v>
+        <v>2026-07-21T13:48:52.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>22/07/2026 07:20:10</v>
+        <v>22/07/2026 19:48:36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153309</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T11:15:37.999Z</v>
+        <v>2026-07-21T13:59:41.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>21/07/2026 19:15:22</v>
+        <v>22/07/2026 19:59:25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153323</v>
+        <v>INC000000153357</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2240,123 +2240,123 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T11:57:35.000Z</v>
+        <v>2026-07-21T14:16:50.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>22/07/2026 17:57:19</v>
+        <v>22/07/2026 07:16:34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153326</v>
+        <v>INC000000153360</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>JUAN DAVID GIL SALAMANCA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T12:11:56.000Z</v>
+        <v>2026-07-21T14:25:11.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>21/07/2026 20:11:40</v>
+        <v>23/07/2026 16:24:55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153329</v>
+        <v>INC000000153362</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T12:12:36.000Z</v>
+        <v>2026-07-21T14:37:17.999Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 20:12:20</v>
+        <v>22/07/2026 07:37:02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153332</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T12:13:44.000Z</v>
+        <v>2026-07-21T14:56:44.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>22/07/2026 18:13:28</v>
+        <v>23/07/2026 06:56:28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153371</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2368,27 +2368,27 @@
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-21T15:11:39.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>21/07/2026 20:16:47</v>
+        <v>22/07/2026 08:11:23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153376</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,91 +2400,91 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T12:36:32.999Z</v>
+        <v>2026-07-21T15:43:00.999Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>22/07/2026 18:36:17</v>
+        <v>23/07/2026 07:42:45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153343</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G64" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T12:47:19.000Z</v>
-      </c>
-      <c r="I64" t="str">
-        <v>-</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I64" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 18:47:03</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153344</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
-      </c>
-      <c r="I65" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I65" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 18:40:06</v>
+        <v>-</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153352</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2493,62 +2493,56 @@
         <v>En curso</v>
       </c>
       <c r="D66" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E66" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-21T13:48:52.000Z</v>
-      </c>
-      <c r="I66" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 19:48:36</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153353</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E67" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F67" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T13:59:41.000Z</v>
-      </c>
-      <c r="I67" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>22/07/2026 19:59:25</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153357</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2560,59 +2554,56 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G68" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-21T14:16:50.000Z</v>
-      </c>
-      <c r="I68" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>22/07/2026 07:16:34</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153362</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G69" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T14:37:17.999Z</v>
-      </c>
-      <c r="I69" t="str">
-        <v>-</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I69" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>22/07/2026 07:37:02</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2624,27 +2615,27 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G70" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I70" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000306908</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2656,36 +2647,36 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G71" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
+        <v>2026-07-10T14:58:16.000Z</v>
       </c>
       <c r="I71" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-21T17:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>-</v>
+        <v>16/07/2026 15:26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D72" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E72" t="str">
         <v>GERLYN RENTERIA OROZCO</v>
@@ -2697,27 +2688,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D73" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F73" t="str">
         <v>ZONA CENTRO</v>
@@ -2726,44 +2717,44 @@
         <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000307665</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-14T14:03:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>13/08/2026 14:03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2775,27 +2766,27 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I75" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2807,71 +2798,68 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G76" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I76" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000308306</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-15T13:18:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>23/07/2026 16:42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000308327</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F78" t="str">
         <v>ZONA CENTRO</v>
@@ -2880,27 +2868,27 @@
         <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-15T14:41:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>22/07/2026 14:41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308420</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F79" t="str">
         <v>ZONA CENTRO</v>
@@ -2909,56 +2897,62 @@
         <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:02:15.999Z</v>
+      </c>
+      <c r="I79" s="1" t="d">
+        <v>2026-07-21T18:00:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 08:02</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G80" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I80" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308722</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E81" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F81" t="str">
         <v>ZONA CENTRO</v>
@@ -2967,18 +2961,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>27/07/2026 14:43</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2993,24 +2984,24 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="I82" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000308952</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -3022,178 +3013,169 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G83" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-16T15:59:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>22/07/2026 08:59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000308961</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G84" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-16T16:06:15.999Z</v>
       </c>
       <c r="J84" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>23/07/2026 14:40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G85" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I85" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G86" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I86" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G87" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G88" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I88" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3205,24 +3187,24 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3234,53 +3216,53 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J91" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3292,53 +3274,53 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3350,16 +3332,16 @@
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J94" t="str">
         <v>24/07/2026 08:00</v>
@@ -3367,7 +3349,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3379,65 +3361,68 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J95" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="I96" s="1" t="d">
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F97" t="str">
         <v>ZONA CENTRO</v>
@@ -3446,15 +3431,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J97" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3466,169 +3451,169 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F99" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000309641</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-17T16:32:15.999Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>23/07/2026 16:49</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 14:35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3640,24 +3625,24 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000309931</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3669,24 +3654,24 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-21T07:46:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 08:32</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310124</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3698,53 +3683,53 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-21T10:33:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 10:33</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
       </c>
       <c r="C107" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D107" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E107" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3756,24 +3741,24 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3785,250 +3770,24 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J109" t="str">
-        <v>24/07/2026 09:41</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>WO0000000310060</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E110" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F110" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G110" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H110" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
-      </c>
-      <c r="J110" t="str">
-        <v>20/08/2026 10:46</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>WO0000000310105</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-      <c r="C111" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E111" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
-      </c>
-      <c r="F111" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
-      </c>
-      <c r="G111" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H111" s="1" t="d">
-        <v>2026-07-21T09:56:16.000Z</v>
-      </c>
-      <c r="J111" t="str">
-        <v>24/07/2026 09:56</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>WO0000000310111</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-      <c r="C112" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E112" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
-      </c>
-      <c r="F112" t="str">
-        <v>SPT CABECERA SUBA</v>
-      </c>
-      <c r="G112" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H112" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
-      </c>
-      <c r="J112" t="str">
-        <v>24/07/2026 10:05</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>WO0000000310112</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-      <c r="C113" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E113" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F113" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G113" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H113" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
-      </c>
-      <c r="J113" t="str">
-        <v>24/07/2026 10:07</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>WO0000000310124</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-      <c r="C114" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E114" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
-      </c>
-      <c r="F114" t="str">
-        <v>SPT CABECERA CALLE 26</v>
-      </c>
-      <c r="G114" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H114" s="1" t="d">
-        <v>2026-07-21T10:33:16.000Z</v>
-      </c>
-      <c r="J114" t="str">
-        <v>24/07/2026 10:33</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>WO0000000310189</v>
-      </c>
-      <c r="B115" t="str">
-        <v>No</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="F115" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G115" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H115" s="1" t="d">
-        <v>2026-07-21T12:24:16.000Z</v>
-      </c>
-      <c r="J115" t="str">
-        <v>23/07/2026 14:24</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>WO0000000310240</v>
-      </c>
-      <c r="B116" t="str">
-        <v>No</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Media</v>
-      </c>
-      <c r="E116" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
-      </c>
-      <c r="F116" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G116" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H116" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="J116" t="str">
-        <v>23/07/2026 14:41</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>WO0000000310328</v>
-      </c>
-      <c r="B117" t="str">
-        <v>No</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D117" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="F117" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G117" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H117" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
-      </c>
-      <c r="J117" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -532,7 +532,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>INC000000151527</v>
+        <v>INC000000152002</v>
       </c>
       <c r="B5" t="str">
         <v>No</v>
@@ -544,19 +544,19 @@
         <v>Baja</v>
       </c>
       <c r="E5" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F5" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G5" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H5" s="1" t="d">
-        <v>2026-07-10T15:10:06.999Z</v>
+        <v>2026-07-14T10:57:48.999Z</v>
       </c>
       <c r="I5" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>22/07/2026 16:00:00</v>
       </c>
       <c r="J5" t="str">
         <v>-</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>INC000000152002</v>
+        <v>INC000000152155</v>
       </c>
       <c r="B6" t="str">
         <v>No</v>
@@ -576,19 +576,19 @@
         <v>Baja</v>
       </c>
       <c r="E6" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F6" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G6" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H6" s="1" t="d">
-        <v>2026-07-14T10:57:48.999Z</v>
+        <v>2026-07-14T16:38:07.000Z</v>
       </c>
       <c r="I6" t="str">
-        <v>22/07/2026 16:00:00</v>
+        <v>24/07/2026 18:00:00</v>
       </c>
       <c r="J6" t="str">
         <v>-</v>
@@ -596,7 +596,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>INC000000152155</v>
+        <v>INC000000152320</v>
       </c>
       <c r="B7" t="str">
         <v>No</v>
@@ -608,19 +608,19 @@
         <v>Baja</v>
       </c>
       <c r="E7" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F7" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G7" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H7" s="1" t="d">
-        <v>2026-07-14T16:38:07.000Z</v>
+        <v>2026-07-15T09:19:18.000Z</v>
       </c>
       <c r="I7" t="str">
-        <v>24/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J7" t="str">
         <v>-</v>
@@ -628,7 +628,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>INC000000152320</v>
+        <v>INC000000152361</v>
       </c>
       <c r="B8" t="str">
         <v>No</v>
@@ -640,7 +640,7 @@
         <v>Baja</v>
       </c>
       <c r="E8" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F8" t="str">
         <v>ZONA CENTRO</v>
@@ -649,10 +649,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H8" s="1" t="d">
-        <v>2026-07-15T09:19:18.000Z</v>
+        <v>2026-07-15T12:30:33.000Z</v>
       </c>
       <c r="I8" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 21:00:00</v>
       </c>
       <c r="J8" t="str">
         <v>-</v>
@@ -660,19 +660,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152566</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C9" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D9" t="str">
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F9" t="str">
         <v>ZONA CENTRO</v>
@@ -681,10 +681,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-15T12:30:33.000Z</v>
+        <v>2026-07-16T11:12:30.000Z</v>
       </c>
       <c r="I9" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J9" t="str">
         <v>-</v>
@@ -692,31 +692,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000152537</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B10" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C10" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D10" t="str">
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F10" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G10" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-16T09:06:34.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I10" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -724,31 +724,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152566</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B11" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C11" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D11" t="str">
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G11" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-16T11:12:30.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F12" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>21/07/2026 20:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,7 +800,7 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F13" t="str">
         <v>ZONA CENTRO</v>
@@ -809,10 +809,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I13" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -841,10 +841,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -873,10 +873,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,19 +896,19 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J16" t="str">
         <v>-</v>
@@ -916,83 +916,83 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000153021</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F17" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-19T07:53:56.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J17" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000152866</v>
+        <v>INC000000153027</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F18" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-18T06:51:32.000Z</v>
+        <v>2026-07-19T10:26:14.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>21/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J18" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000152890</v>
+        <v>INC000000153038</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F19" t="str">
         <v>ZONA NORTE</v>
@@ -1001,30 +1001,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-18T10:01:52.000Z</v>
+        <v>2026-07-20T08:41:31.999Z</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>22/07/2026 10:01:36</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000152891</v>
+        <v>INC000000153052</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F20" t="str">
         <v>ZONA CENTRO</v>
@@ -1033,50 +1033,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-18T10:19:19.000Z</v>
+        <v>2026-07-21T07:17:50.000Z</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>22/07/2026 10:19:03</v>
+        <v>22/07/2026 13:17:34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000152892</v>
+        <v>INC000000153065</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-18T10:24:05.000Z</v>
+        <v>2026-07-21T08:21:34.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>22/07/2026 10:23:49</v>
+        <v>22/07/2026 14:21:18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000152893</v>
+        <v>INC000000153069</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1088,59 +1088,59 @@
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-18T10:26:05.999Z</v>
+        <v>2026-07-21T08:36:12.999Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>22/07/2026 10:25:50</v>
+        <v>22/07/2026 14:35:57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>22/07/2026 10:43:40</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000152897</v>
+        <v>INC000000153093</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,39 +1152,39 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-18T10:50:35.999Z</v>
+        <v>2026-07-21T10:11:52.999Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 10:50:20</v>
+        <v>22/07/2026 16:11:37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000152939</v>
+        <v>INC000000153102</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F25" t="str">
         <v>ZONA CENTRO</v>
@@ -1193,30 +1193,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-17T16:39:06.999Z</v>
+        <v>2026-07-18T12:08:07.999Z</v>
       </c>
       <c r="I25" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>-</v>
+        <v>22/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000152944</v>
+        <v>INC000000153163</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F26" t="str">
         <v>ZONA CENTRO</v>
@@ -1225,18 +1225,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-17T16:40:08.000Z</v>
+        <v>2026-07-21T09:14:25.000Z</v>
       </c>
       <c r="I26" t="str">
-        <v>21/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>-</v>
+        <v>22/07/2026 15:14:09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000152987</v>
+        <v>INC000000153195</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1248,27 +1248,27 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-18T09:34:34.000Z</v>
+        <v>2026-07-21T10:28:08.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 09:34:18</v>
+        <v>22/07/2026 16:27:52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000152994</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1280,7 +1280,7 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F28" t="str">
         <v>ZONA CENTRO</v>
@@ -1289,50 +1289,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-18T10:21:32.999Z</v>
+        <v>2026-07-21T10:34:43.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 10:21:17</v>
+        <v>22/07/2026 16:34:27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153200</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-21T10:52:08.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:51:52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,7 +1344,7 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F30" t="str">
         <v>ZONA CENTRO</v>
@@ -1353,114 +1353,111 @@
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:47:31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
-      <c r="E32" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
-      </c>
       <c r="F32" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T17:06:23.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>22/07/2026 10:06:07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>23/07/2026 09:04:44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1472,91 +1469,91 @@
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>22/07/2026 14:35:57</v>
+        <v>23/07/2026 11:00:53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-22T06:27:48.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>22/07/2026 14:27:32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153281</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>EXT SON ANDERSON CAMILO JAIMES GUTIERREZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-22T06:43:05.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>22/07/2026 14:42:49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153285</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,27 +1565,27 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-22T07:30:20.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 15:30:05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153286</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,91 +1597,91 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-22T07:30:22.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>22/07/2026 15:30:06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153183</v>
+        <v>INC000000153287</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-21T09:54:36.000Z</v>
+        <v>2026-07-22T07:30:22.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>21/07/2026 17:54:20</v>
+        <v>22/07/2026 15:30:06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153195</v>
+        <v>INC000000153288</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F40" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-21T10:28:08.000Z</v>
+        <v>2026-07-22T07:30:22.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 16:27:52</v>
+        <v>22/07/2026 15:30:06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153200</v>
+        <v>INC000000153290</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,27 +1693,27 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-22T07:33:08.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 16:51:52</v>
+        <v>22/07/2026 15:32:52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153205</v>
+        <v>INC000000153291</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
@@ -1728,27 +1725,27 @@
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-21T10:47:17.000Z</v>
+        <v>2026-07-22T07:33:08.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 08:45:57</v>
+        <v>22/07/2026 15:32:52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153292</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
@@ -1760,27 +1757,27 @@
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-22T07:33:08.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>21/07/2026 18:47:31</v>
+        <v>23/07/2026 13:32:52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153293</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,27 +1789,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
+        <v>2026-07-22T07:47:23.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>22/07/2026 15:47:07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153243</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1827,56 +1824,56 @@
         <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-21T12:58:05.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>21/07/2026 20:57:49</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153247</v>
+        <v>INC000000153300</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-21T13:21:11.000Z</v>
+        <v>2026-07-22T08:31:33.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 06:20:55</v>
+        <v>22/07/2026 16:31:17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153251</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1888,27 +1885,27 @@
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-21T13:44:21.999Z</v>
+        <v>2026-07-21T11:57:35.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>22/07/2026 06:44:06</v>
+        <v>22/07/2026 17:57:19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153258</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,59 +1917,59 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-21T15:00:43.000Z</v>
+        <v>2026-07-21T12:13:44.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 08:00:27</v>
+        <v>22/07/2026 18:13:28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153323</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-21T11:57:35.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I49" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J49" t="str">
-        <v>22/07/2026 17:57:19</v>
+        <v>-</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153329</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,135 +1981,135 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-21T12:12:36.000Z</v>
+        <v>2026-07-21T12:36:32.999Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>21/07/2026 20:12:20</v>
+        <v>22/07/2026 18:36:17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153332</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F51" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-21T12:13:44.000Z</v>
+        <v>2026-07-21T12:47:19.000Z</v>
       </c>
       <c r="I51" t="str">
-        <v>-</v>
+        <v>22/07/2026 21:00:00</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 18:13:28</v>
+        <v>-</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 20:16:47</v>
+        <v>22/07/2026 18:40:06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153352</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T12:36:32.999Z</v>
+        <v>2026-07-21T13:48:52.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 18:36:17</v>
+        <v>22/07/2026 19:48:36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153343</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F54" t="str">
         <v>ZONA CENTRO</v>
@@ -2121,24 +2118,24 @@
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T12:47:19.000Z</v>
+        <v>2026-07-21T13:59:41.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 18:47:03</v>
+        <v>22/07/2026 19:59:25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
@@ -2153,18 +2150,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-21T14:56:44.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 18:40:06</v>
+        <v>23/07/2026 06:56:28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153352</v>
+        <v>INC000000153382</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2176,27 +2173,27 @@
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T13:48:52.000Z</v>
+        <v>2026-07-21T16:32:55.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>22/07/2026 19:48:36</v>
+        <v>23/07/2026 08:32:39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153353</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,7 +2205,7 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F57" t="str">
         <v>ZONA CENTRO</v>
@@ -2217,18 +2214,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T13:59:41.000Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>22/07/2026 19:59:25</v>
+        <v>23/07/2026 09:01:06</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153357</v>
+        <v>INC000000153404</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2240,59 +2237,59 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-21T14:16:50.000Z</v>
+        <v>2026-07-22T05:25:20.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>22/07/2026 07:16:34</v>
+        <v>23/07/2026 12:00:00</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153360</v>
+        <v>INC000000153406</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-21T14:25:11.000Z</v>
+        <v>2026-07-22T06:39:06.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>23/07/2026 16:24:55</v>
+        <v>22/07/2026 14:38:50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153362</v>
+        <v>INC000000153407</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,91 +2301,91 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T14:37:17.999Z</v>
+        <v>2026-07-22T06:51:53.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 07:37:02</v>
+        <v>22/07/2026 14:51:37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153368</v>
+        <v>INC000000153410</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T14:56:44.000Z</v>
+        <v>2026-07-22T07:02:26.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>23/07/2026 06:56:28</v>
+        <v>22/07/2026 15:02:10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153371</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T15:11:39.000Z</v>
+        <v>2026-07-22T07:32:32.999Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>22/07/2026 08:11:23</v>
+        <v>22/07/2026 15:32:17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153376</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,129 +2397,132 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T15:43:00.999Z</v>
+        <v>2026-07-22T08:15:11.000Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>23/07/2026 07:42:45</v>
+        <v>23/07/2026 14:14:55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153426</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G64" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I64" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T08:28:32.000Z</v>
+      </c>
+      <c r="I64" t="str">
+        <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>22/07/2026 16:28:16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F65" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G65" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I65" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T08:42:28.000Z</v>
+      </c>
+      <c r="I65" t="str">
+        <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>-</v>
+        <v>22/07/2026 16:42:12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153503</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D66" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-22T08:50:19.000Z</v>
+      </c>
+      <c r="I66" t="str">
+        <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>23/07/2026 14:50:03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E67" t="str">
         <v>GERLYN RENTERIA OROZCO</v>
@@ -2531,24 +2531,27 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
+      </c>
+      <c r="I67" t="str">
+        <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
@@ -2563,15 +2566,18 @@
         <v>c) 11-30</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I68" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
@@ -2583,100 +2589,94 @@
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F69" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G69" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
       </c>
       <c r="I69" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>-</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D70" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E70" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G70" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I70" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>22/07/2026 15:12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000306908</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E71" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-10T14:58:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-21T17:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>16/07/2026 15:26</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E72" t="str">
         <v>GERLYN RENTERIA OROZCO</v>
@@ -2688,21 +2688,21 @@
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
@@ -2711,50 +2711,53 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G73" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000307665</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-14T14:03:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I74" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>13/08/2026 14:03</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2766,71 +2769,68 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G75" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I75" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-22T19:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I76" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000308306</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F77" t="str">
         <v>ZONA CENTRO</v>
@@ -2839,15 +2839,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-15T13:18:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>23/07/2026 16:42</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000308327</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2859,7 +2859,7 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F78" t="str">
         <v>ZONA CENTRO</v>
@@ -2868,47 +2868,44 @@
         <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-15T14:41:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>22/07/2026 14:41</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000308420</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G79" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-15T15:02:15.999Z</v>
-      </c>
-      <c r="I79" s="1" t="d">
-        <v>2026-07-21T18:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 08:02</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2920,56 +2917,59 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I80" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000308722</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G81" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>27/07/2026 14:43</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2981,85 +2981,88 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
       </c>
       <c r="I82" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000308952</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-16T15:59:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I83" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>22/07/2026 08:59</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000308961</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G84" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T16:06:15.999Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>23/07/2026 14:40</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3071,24 +3074,24 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G85" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3100,24 +3103,24 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G86" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3129,65 +3132,68 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I88" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F89" t="str">
         <v>ZONA CENTRO</v>
@@ -3196,15 +3202,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J89" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3225,44 +3231,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 11:15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3274,53 +3280,53 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3332,16 +3338,16 @@
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J94" t="str">
         <v>24/07/2026 08:00</v>
@@ -3349,28 +3355,31 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="I95" s="1" t="d">
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
         <v>24/07/2026 08:00</v>
@@ -3378,39 +3387,36 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I96" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J96" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3422,24 +3428,24 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3460,44 +3466,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3518,15 +3524,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3538,24 +3544,24 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3567,53 +3573,53 @@
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F102" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>24/07/2026 14:35</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3625,24 +3631,24 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3654,53 +3660,56 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000310124</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D106" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E106" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-21T10:33:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I106" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>24/07/2026 10:33</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3709,27 +3718,27 @@
         <v>Asignado</v>
       </c>
       <c r="D107" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3741,24 +3750,24 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F108" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J108" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3770,24 +3779,285 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+      </c>
+      <c r="F109" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G109" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H109" s="1" t="d">
+        <v>2026-07-21T15:38:16.000Z</v>
+      </c>
+      <c r="J109" t="str">
+        <v>24/07/2026 08:38</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>WO0000000310425</v>
+      </c>
+      <c r="B110" t="str">
+        <v>No</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E110" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F110" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G110" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H110" s="1" t="d">
+        <v>2026-07-21T17:12:16.000Z</v>
+      </c>
+      <c r="J110" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>WO0000000310452</v>
+      </c>
+      <c r="B111" t="str">
+        <v>No</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E111" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F111" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G111" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H111" s="1" t="d">
+        <v>2026-07-21T22:40:16.000Z</v>
+      </c>
+      <c r="J111" t="str">
+        <v>24/07/2026 10:00</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WO0000000310476</v>
+      </c>
+      <c r="B112" t="str">
+        <v>No</v>
+      </c>
+      <c r="C112" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E112" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F112" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G112" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H112" s="1" t="d">
+        <v>2026-07-22T08:10:16.000Z</v>
+      </c>
+      <c r="J112" t="str">
+        <v>27/07/2026 08:11</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>WO0000000310478</v>
+      </c>
+      <c r="B113" t="str">
+        <v>No</v>
+      </c>
+      <c r="C113" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E113" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F113" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G113" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H113" s="1" t="d">
+        <v>2026-07-22T08:12:16.000Z</v>
+      </c>
+      <c r="J113" t="str">
+        <v>27/07/2026 08:13</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>WO0000000310521</v>
+      </c>
+      <c r="B114" t="str">
+        <v>No</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E114" t="str">
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
-      <c r="F109" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G109" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H109" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="J109" t="str">
-        <v>24/07/2026 14:55</v>
+      <c r="F114" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G114" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H114" s="1" t="d">
+        <v>2026-07-21T22:31:16.000Z</v>
+      </c>
+      <c r="J114" t="str">
+        <v>24/07/2026 10:00</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>WO0000000310530</v>
+      </c>
+      <c r="B115" t="str">
+        <v>No</v>
+      </c>
+      <c r="C115" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E115" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F115" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G115" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H115" s="1" t="d">
+        <v>2026-07-22T06:09:15.999Z</v>
+      </c>
+      <c r="J115" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>WO0000000310533</v>
+      </c>
+      <c r="B116" t="str">
+        <v>No</v>
+      </c>
+      <c r="C116" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E116" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F116" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G116" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H116" s="1" t="d">
+        <v>2026-07-22T06:14:16.000Z</v>
+      </c>
+      <c r="J116" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>WO0000000310543</v>
+      </c>
+      <c r="B117" t="str">
+        <v>No</v>
+      </c>
+      <c r="C117" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E117" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F117" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G117" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H117" s="1" t="d">
+        <v>2026-07-22T07:27:16.000Z</v>
+      </c>
+      <c r="J117" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>WO0000000310577</v>
+      </c>
+      <c r="B118" t="str">
+        <v>No</v>
+      </c>
+      <c r="C118" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E118" t="str">
+        <v>SANTIAGO PERDOMO ACERO</v>
+      </c>
+      <c r="F118" t="str">
+        <v>SPT CABECERA CARRERA 60</v>
+      </c>
+      <c r="G118" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H118" s="1" t="d">
+        <v>2026-07-22T08:38:16.000Z</v>
+      </c>
+      <c r="J118" t="str">
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -742,7 +742,7 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G11" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
         <v>2026-07-17T09:17:43.000Z</v>
@@ -774,7 +774,7 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G12" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H12" s="1" t="d">
         <v>2026-07-17T09:40:00.000Z</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153200</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,7 +1312,7 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F29" t="str">
         <v>ZONA CENTRO</v>
@@ -1321,18 +1321,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-21T10:52:08.000Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 16:51:52</v>
+        <v>22/07/2026 16:47:31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,7 +1344,7 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F30" t="str">
         <v>ZONA CENTRO</v>
@@ -1353,50 +1353,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 16:47:31</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
+        <v>2026-07-21T17:06:23.000Z</v>
       </c>
       <c r="I31" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J31" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>-</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1407,25 +1407,28 @@
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
+      <c r="E32" t="str">
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+      </c>
       <c r="F32" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-21T17:06:23.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 10:06:07</v>
+        <v>23/07/2026 09:04:44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1437,7 +1440,7 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F33" t="str">
         <v>ZONA CENTRO</v>
@@ -1446,50 +1449,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>23/07/2026 09:04:44</v>
+        <v>23/07/2026 11:00:53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-22T06:27:48.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 11:00:53</v>
+        <v>22/07/2026 14:27:32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153281</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1501,27 +1504,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T06:27:48.000Z</v>
+        <v>2026-07-22T06:43:05.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>22/07/2026 14:27:32</v>
+        <v>22/07/2026 14:42:49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153281</v>
+        <v>INC000000153285</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1542,18 +1545,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-22T06:43:05.000Z</v>
+        <v>2026-07-22T07:30:20.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 14:42:49</v>
+        <v>22/07/2026 15:30:05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153285</v>
+        <v>INC000000153286</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1574,18 +1577,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T07:30:20.999Z</v>
+        <v>2026-07-22T07:30:22.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 15:30:05</v>
+        <v>22/07/2026 15:30:06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153286</v>
+        <v>INC000000153287</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1617,7 +1620,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153287</v>
+        <v>INC000000153288</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1649,7 +1652,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153288</v>
+        <v>INC000000153289</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1670,13 +1673,13 @@
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T07:30:22.000Z</v>
+        <v>2026-07-22T07:33:08.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 15:30:06</v>
+        <v>22/07/2026 15:32:52</v>
       </c>
     </row>
     <row r="41">
@@ -2417,39 +2420,39 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153426</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-22T08:28:32.000Z</v>
+        <v>2026-07-22T08:42:28.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 16:28:16</v>
+        <v>22/07/2026 16:42:12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153427</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2461,27 +2464,27 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-22T08:42:28.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 16:42:12</v>
+        <v>22/07/2026 16:46:27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153503</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2493,7 +2496,7 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2502,18 +2505,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-22T08:50:19.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>23/07/2026 14:50:03</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153502</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2525,271 +2528,277 @@
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F67" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T08:44:57.999Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>22/07/2026 16:44:42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153503</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I68" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T08:50:19.000Z</v>
+      </c>
+      <c r="I68" t="str">
+        <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>23/07/2026 14:50:03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I69" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
+      </c>
+      <c r="I69" t="str">
+        <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000304757</v>
+        <v>INC000000153506</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D70" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G70" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-22T09:01:19.000Z</v>
+      </c>
+      <c r="I70" t="str">
+        <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>22/07/2026 15:12</v>
+        <v>22/07/2026 17:01:03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153517</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D71" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G71" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-22T09:42:26.000Z</v>
+      </c>
+      <c r="I71" t="str">
+        <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>22/07/2026 17:42:10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G72" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G73" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I73" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>-</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E74" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G74" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I74" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="J74" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>22/07/2026 15:12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D75" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E75" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I75" s="1" t="d">
-        <v>2026-07-22T19:00:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2798,91 +2807,94 @@
         <v>En curso</v>
       </c>
       <c r="D76" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E76" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G77" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F78" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G78" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I78" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
@@ -2894,352 +2906,352 @@
         <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G79" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I79" s="1" t="d">
+        <v>2026-07-22T19:00:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G80" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I80" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I82" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G83" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I83" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G85" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I85" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I86" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I87" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G88" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I88" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G89" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G90" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3251,36 +3263,36 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>23/07/2026 11:15</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F92" t="str">
         <v>ZONA CENTRO</v>
@@ -3289,105 +3301,105 @@
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I92" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D93" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E93" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J94" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I95" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J95" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3399,7 +3411,7 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F96" t="str">
         <v>ZONA CENTRO</v>
@@ -3408,15 +3420,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 11:25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3428,24 +3440,24 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3457,30 +3469,30 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
@@ -3495,56 +3507,59 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="I100" s="1" t="d">
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F101" t="str">
         <v>ZONA CENTRO</v>
@@ -3553,44 +3568,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J101" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3602,114 +3617,111 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 11:38</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D106" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I106" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3721,198 +3733,201 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F107" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F109" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F110" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J110" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
       </c>
       <c r="C111" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D111" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E111" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F111" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G111" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I111" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000310476</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
       </c>
       <c r="C112" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D112" t="str">
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F112" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-22T08:10:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J112" t="str">
-        <v>27/07/2026 08:11</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000310478</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D113" t="str">
         <v>Baja</v>
       </c>
       <c r="E113" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F113" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G113" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-22T08:12:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J113" t="str">
-        <v>27/07/2026 08:13</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000310521</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
@@ -3924,7 +3939,7 @@
         <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F114" t="str">
         <v>ZONA CENTRO</v>
@@ -3933,36 +3948,36 @@
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-21T22:31:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J114" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000310530</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
       </c>
       <c r="C115" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D115" t="str">
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F115" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G115" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-22T06:09:15.999Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J115" t="str">
         <v>27/07/2026 08:00</v>
@@ -3970,36 +3985,36 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000310533</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
       </c>
       <c r="C116" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D116" t="str">
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F116" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G116" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-22T06:14:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000310543</v>
+        <v>WO0000000310476</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
@@ -4011,53 +4026,198 @@
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-22T07:27:16.000Z</v>
+        <v>2026-07-22T08:10:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 08:11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
+        <v>WO0000000310478</v>
+      </c>
+      <c r="B118" t="str">
+        <v>No</v>
+      </c>
+      <c r="C118" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E118" t="str">
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+      </c>
+      <c r="F118" t="str">
+        <v>SPT CABECERA 1 MAYO</v>
+      </c>
+      <c r="G118" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H118" s="1" t="d">
+        <v>2026-07-22T08:12:16.000Z</v>
+      </c>
+      <c r="J118" t="str">
+        <v>27/07/2026 08:13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>WO0000000310521</v>
+      </c>
+      <c r="B119" t="str">
+        <v>No</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E119" t="str">
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+      </c>
+      <c r="F119" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G119" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H119" s="1" t="d">
+        <v>2026-07-21T22:31:16.000Z</v>
+      </c>
+      <c r="J119" t="str">
+        <v>24/07/2026 10:00</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>WO0000000310530</v>
+      </c>
+      <c r="B120" t="str">
+        <v>No</v>
+      </c>
+      <c r="C120" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E120" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F120" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G120" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H120" s="1" t="d">
+        <v>2026-07-22T06:09:15.999Z</v>
+      </c>
+      <c r="J120" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>WO0000000310533</v>
+      </c>
+      <c r="B121" t="str">
+        <v>No</v>
+      </c>
+      <c r="C121" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E121" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F121" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G121" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H121" s="1" t="d">
+        <v>2026-07-22T06:14:16.000Z</v>
+      </c>
+      <c r="J121" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>WO0000000310543</v>
+      </c>
+      <c r="B122" t="str">
+        <v>No</v>
+      </c>
+      <c r="C122" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E122" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F122" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G122" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H122" s="1" t="d">
+        <v>2026-07-22T07:27:16.000Z</v>
+      </c>
+      <c r="J122" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
         <v>WO0000000310577</v>
       </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-      <c r="C118" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E118" t="str">
+      <c r="B123" t="str">
+        <v>No</v>
+      </c>
+      <c r="C123" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E123" t="str">
         <v>SANTIAGO PERDOMO ACERO</v>
       </c>
-      <c r="F118" t="str">
+      <c r="F123" t="str">
         <v>SPT CABECERA CARRERA 60</v>
       </c>
-      <c r="G118" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H118" s="1" t="d">
+      <c r="G123" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H123" s="1" t="d">
         <v>2026-07-22T08:38:16.000Z</v>
       </c>
-      <c r="J118" t="str">
+      <c r="J123" t="str">
         <v>27/07/2026 08:40</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J123"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J127"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,7 +806,7 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G13" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H13" s="1" t="d">
         <v>2026-07-17T10:13:53.999Z</v>
@@ -1690,7 +1690,7 @@
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
@@ -1722,7 +1722,7 @@
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
@@ -1754,7 +1754,7 @@
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
@@ -1763,7 +1763,7 @@
         <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
@@ -1775,7 +1775,7 @@
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 13:32:52</v>
+        <v>22/07/2026 15:32:52</v>
       </c>
     </row>
     <row r="44">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153406</v>
+        <v>INC000000153407</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2281,18 +2281,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-22T06:39:06.000Z</v>
+        <v>2026-07-22T06:51:53.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 14:38:50</v>
+        <v>22/07/2026 14:51:37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153407</v>
+        <v>INC000000153410</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,91 +2304,91 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-22T06:51:53.000Z</v>
+        <v>2026-07-22T07:02:26.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 14:51:37</v>
+        <v>22/07/2026 15:02:10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153410</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-22T07:02:26.000Z</v>
+        <v>2026-07-22T07:32:32.999Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>22/07/2026 15:02:10</v>
+        <v>22/07/2026 15:32:17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153415</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-22T07:32:32.999Z</v>
+        <v>2026-07-22T08:15:11.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>22/07/2026 15:32:17</v>
+        <v>23/07/2026 14:14:55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153422</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2400,27 +2400,27 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-22T08:15:11.000Z</v>
+        <v>2026-07-22T08:42:28.000Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>23/07/2026 14:14:55</v>
+        <v>22/07/2026 16:42:12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153427</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2432,27 +2432,27 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-22T08:42:28.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 16:42:12</v>
+        <v>22/07/2026 16:46:27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2464,27 +2464,27 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>22/07/2026 16:46:27</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153438</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2496,22 +2496,22 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T10:11:27.999Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>22/07/2026 18:11:12</v>
       </c>
     </row>
     <row r="67">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153517</v>
+        <v>INC000000153509</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2656,149 +2656,155 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-22T09:42:26.000Z</v>
+        <v>2026-07-22T09:00:48.000Z</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>22/07/2026 17:42:10</v>
+        <v>22/07/2026 17:00:32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000304422</v>
+        <v>INC000000153517</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G72" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T09:42:26.000Z</v>
+      </c>
+      <c r="I72" t="str">
+        <v>-</v>
       </c>
       <c r="J72" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>22/07/2026 17:42:10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000304756</v>
+        <v>INC000000153521</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DIEGO ARTURO ROMERO CALDERON</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA LAGOSOL</v>
       </c>
       <c r="G73" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I73" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-22T10:09:30.000Z</v>
+      </c>
+      <c r="I73" t="str">
+        <v>-</v>
       </c>
       <c r="J73" t="str">
-        <v>-</v>
+        <v>23/07/2026 16:09:14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D74" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G74" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I74" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>22/07/2026 15:12</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D75" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I75" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2807,27 +2813,27 @@
         <v>En curso</v>
       </c>
       <c r="D76" t="str">
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E76" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="J76" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>22/07/2026 15:12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
@@ -2836,149 +2842,149 @@
         <v>En curso</v>
       </c>
       <c r="D77" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E77" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E78" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I78" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G79" t="str">
         <v>c) 11-30</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I79" s="1" t="d">
-        <v>2026-07-22T19:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G80" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I80" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G81" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-22T19:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2990,65 +2996,65 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F84" t="str">
         <v>ZONA CENTRO</v>
@@ -3057,50 +3063,44 @@
         <v>b) 5-10</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I84" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G85" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I85" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3112,27 +3112,27 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I86" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3147,82 +3147,88 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G87" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I87" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G88" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I88" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I89" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3234,24 +3240,24 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G90" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3263,97 +3269,94 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G91" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G92" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I92" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D93" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F94" t="str">
         <v>ZONA CENTRO</v>
@@ -3362,15 +3365,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I94" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3379,7 +3385,7 @@
         <v>Asignado</v>
       </c>
       <c r="D95" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E95" t="str">
         <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
@@ -3391,27 +3397,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F96" t="str">
         <v>ZONA CENTRO</v>
@@ -3420,27 +3426,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J96" t="str">
-        <v>24/07/2026 11:25</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F97" t="str">
         <v>ZONA CENTRO</v>
@@ -3449,15 +3455,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J97" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3469,24 +3475,24 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 11:25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3498,48 +3504,45 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000309593</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I100" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-17T16:59:16.000Z</v>
       </c>
       <c r="J100" t="str">
         <v>24/07/2026 08:00</v>
@@ -3547,7 +3550,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3559,53 +3562,56 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J101" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="I102" s="1" t="d">
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3617,82 +3623,82 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J103" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3704,24 +3710,24 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F106" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3733,59 +3739,59 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
@@ -3800,15 +3806,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
@@ -3820,36 +3826,36 @@
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F110" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>24/07/2026 11:38</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
       </c>
       <c r="C111" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D111" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F111" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3858,76 +3864,76 @@
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I111" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J111" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B112" t="str">
         <v>No</v>
       </c>
       <c r="C112" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D112" t="str">
         <v>Baja</v>
       </c>
       <c r="E112" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F112" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G112" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H112" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J112" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B113" t="str">
         <v>No</v>
       </c>
       <c r="C113" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D113" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E113" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F113" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G113" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H113" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I113" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J113" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B114" t="str">
         <v>No</v>
@@ -3939,7 +3945,7 @@
         <v>Baja</v>
       </c>
       <c r="E114" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F114" t="str">
         <v>ZONA CENTRO</v>
@@ -3948,15 +3954,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H114" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J114" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B115" t="str">
         <v>No</v>
@@ -3968,24 +3974,24 @@
         <v>Baja</v>
       </c>
       <c r="E115" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F115" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G115" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H115" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J115" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B116" t="str">
         <v>No</v>
@@ -3997,7 +4003,7 @@
         <v>Baja</v>
       </c>
       <c r="E116" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F116" t="str">
         <v>ZONA CENTRO</v>
@@ -4006,102 +4012,102 @@
         <v>a) 0-4</v>
       </c>
       <c r="H116" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J116" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WO0000000310476</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B117" t="str">
         <v>No</v>
       </c>
       <c r="C117" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D117" t="str">
         <v>Baja</v>
       </c>
       <c r="E117" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F117" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G117" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H117" s="1" t="d">
-        <v>2026-07-22T08:10:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J117" t="str">
-        <v>27/07/2026 08:11</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WO0000000310478</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B118" t="str">
         <v>No</v>
       </c>
       <c r="C118" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D118" t="str">
         <v>Baja</v>
       </c>
       <c r="E118" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F118" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G118" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H118" s="1" t="d">
-        <v>2026-07-22T08:12:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J118" t="str">
-        <v>27/07/2026 08:13</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WO0000000310521</v>
+        <v>WO0000000310476</v>
       </c>
       <c r="B119" t="str">
         <v>No</v>
       </c>
       <c r="C119" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D119" t="str">
         <v>Baja</v>
       </c>
       <c r="E119" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F119" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G119" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H119" s="1" t="d">
-        <v>2026-07-21T22:31:16.000Z</v>
+        <v>2026-07-22T08:10:16.000Z</v>
       </c>
       <c r="J119" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 08:11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>WO0000000310530</v>
+        <v>WO0000000310478</v>
       </c>
       <c r="B120" t="str">
         <v>No</v>
@@ -4113,53 +4119,53 @@
         <v>Baja</v>
       </c>
       <c r="E120" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F120" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G120" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H120" s="1" t="d">
-        <v>2026-07-22T06:09:15.999Z</v>
+        <v>2026-07-22T08:12:16.000Z</v>
       </c>
       <c r="J120" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 08:13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>WO0000000310533</v>
+        <v>WO0000000310521</v>
       </c>
       <c r="B121" t="str">
         <v>No</v>
       </c>
       <c r="C121" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D121" t="str">
         <v>Baja</v>
       </c>
       <c r="E121" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F121" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G121" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H121" s="1" t="d">
-        <v>2026-07-22T06:14:16.000Z</v>
+        <v>2026-07-21T22:31:16.000Z</v>
       </c>
       <c r="J121" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>WO0000000310543</v>
+        <v>WO0000000310530</v>
       </c>
       <c r="B122" t="str">
         <v>No</v>
@@ -4180,7 +4186,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H122" s="1" t="d">
-        <v>2026-07-22T07:27:16.000Z</v>
+        <v>2026-07-22T06:09:15.999Z</v>
       </c>
       <c r="J122" t="str">
         <v>27/07/2026 08:00</v>
@@ -4188,36 +4194,149 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
+        <v>WO0000000310533</v>
+      </c>
+      <c r="B123" t="str">
+        <v>No</v>
+      </c>
+      <c r="C123" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E123" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F123" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G123" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H123" s="1" t="d">
+        <v>2026-07-22T06:14:16.000Z</v>
+      </c>
+      <c r="J123" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>WO0000000310543</v>
+      </c>
+      <c r="B124" t="str">
+        <v>No</v>
+      </c>
+      <c r="C124" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E124" t="str">
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+      </c>
+      <c r="F124" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G124" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H124" s="1" t="d">
+        <v>2026-07-22T07:27:16.000Z</v>
+      </c>
+      <c r="J124" t="str">
+        <v>27/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
         <v>WO0000000310577</v>
       </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-      <c r="C123" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D123" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E123" t="str">
+      <c r="B125" t="str">
+        <v>No</v>
+      </c>
+      <c r="C125" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E125" t="str">
         <v>SANTIAGO PERDOMO ACERO</v>
       </c>
-      <c r="F123" t="str">
+      <c r="F125" t="str">
         <v>SPT CABECERA CARRERA 60</v>
       </c>
-      <c r="G123" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H123" s="1" t="d">
+      <c r="G125" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H125" s="1" t="d">
         <v>2026-07-22T08:38:16.000Z</v>
       </c>
-      <c r="J123" t="str">
+      <c r="J125" t="str">
         <v>27/07/2026 08:40</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>WO0000000310630</v>
+      </c>
+      <c r="B126" t="str">
+        <v>No</v>
+      </c>
+      <c r="C126" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E126" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F126" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G126" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H126" s="1" t="d">
+        <v>2026-07-22T09:58:16.000Z</v>
+      </c>
+      <c r="J126" t="str">
+        <v>27/07/2026 09:59</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>WO0000000310725</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E127" t="str">
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+      </c>
+      <c r="F127" t="str">
+        <v>ZONA NORTE</v>
+      </c>
+      <c r="G127" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H127" s="1" t="d">
+        <v>2026-07-22T09:58:16.000Z</v>
+      </c>
+      <c r="J127" t="str">
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J123"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J127"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -660,28 +660,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000152566</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B9" t="str">
         <v>Si</v>
       </c>
       <c r="C9" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D9" t="str">
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F9" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G9" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-16T11:12:30.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I9" t="str">
         <v>-</v>
@@ -692,31 +692,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B10" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C10" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D10" t="str">
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F10" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G10" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I10" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,7 +736,7 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
@@ -745,7 +745,7 @@
         <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I11" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152768</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,7 +768,7 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F12" t="str">
         <v>ZONA CENTRO</v>
@@ -777,10 +777,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T10:13:53.999Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 18:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152774</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,7 +800,7 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F13" t="str">
         <v>ZONA CENTRO</v>
@@ -809,7 +809,7 @@
         <v>b) 5-10</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T10:28:03.000Z</v>
       </c>
       <c r="I13" t="str">
         <v>22/07/2026 18:00:00</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,19 +832,19 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F14" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G14" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,16 +864,16 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I15" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -884,83 +884,83 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J16" t="str">
-        <v>-</v>
+        <v>22/07/2026 16:16:33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153021</v>
+        <v>INC000000153196</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F17" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-19T07:53:56.000Z</v>
+        <v>2026-07-21T10:34:43.000Z</v>
       </c>
       <c r="I17" t="str">
         <v>-</v>
       </c>
       <c r="J17" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:34:27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153027</v>
+        <v>INC000000153206</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F18" t="str">
         <v>ZONA CENTRO</v>
@@ -969,146 +969,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-19T10:26:14.000Z</v>
+        <v>2026-07-21T10:47:47.000Z</v>
       </c>
       <c r="I18" t="str">
         <v>-</v>
       </c>
       <c r="J18" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 16:47:31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153038</v>
+        <v>INC000000153226</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-20T08:41:31.999Z</v>
+        <v>2026-07-21T11:48:55.000Z</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>22/07/2026 17:48:39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153052</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F20" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-21T07:17:50.000Z</v>
+        <v>2026-07-21T17:06:23.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J20" t="str">
-        <v>22/07/2026 13:17:34</v>
+        <v>-</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153065</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-21T08:21:34.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>22/07/2026 14:21:18</v>
+        <v>23/07/2026 09:04:44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153069</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-21T08:36:12.999Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>22/07/2026 14:35:57</v>
+        <v>23/07/2026 11:00:53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,27 +1120,27 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-22T06:27:48.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>22/07/2026 14:27:32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153093</v>
+        <v>INC000000153293</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,27 +1152,27 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-21T10:11:52.999Z</v>
+        <v>2026-07-22T07:47:23.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 16:11:37</v>
+        <v>22/07/2026 15:47:07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153102</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
@@ -1184,27 +1184,27 @@
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-18T12:08:07.999Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>22/07/2026 12:00:00</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153163</v>
+        <v>INC000000153300</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1216,27 +1216,27 @@
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F26" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-21T09:14:25.000Z</v>
+        <v>2026-07-22T08:31:33.000Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>22/07/2026 15:14:09</v>
+        <v>22/07/2026 16:31:17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153195</v>
+        <v>INC000000153323</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1248,27 +1248,27 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-21T10:28:08.000Z</v>
+        <v>2026-07-21T11:57:35.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 16:27:52</v>
+        <v>22/07/2026 17:57:19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153196</v>
+        <v>INC000000153332</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1280,59 +1280,59 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-21T10:34:43.000Z</v>
+        <v>2026-07-21T12:13:44.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 16:34:27</v>
+        <v>22/07/2026 18:13:28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I29" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J29" t="str">
-        <v>22/07/2026 16:47:31</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,27 +1344,27 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
+        <v>2026-07-21T12:36:32.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>22/07/2026 18:36:17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,19 +1376,19 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F31" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-21T17:06:23.000Z</v>
+        <v>2026-07-21T12:47:19.000Z</v>
       </c>
       <c r="I31" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>22/07/2026 21:00:00</v>
       </c>
       <c r="J31" t="str">
         <v>-</v>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1417,30 +1417,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>23/07/2026 09:04:44</v>
+        <v>22/07/2026 18:40:06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153353</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F33" t="str">
         <v>ZONA CENTRO</v>
@@ -1449,18 +1449,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T13:59:41.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>23/07/2026 11:00:53</v>
+        <v>22/07/2026 19:59:25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1472,27 +1472,27 @@
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T06:27:48.000Z</v>
+        <v>2026-07-21T14:56:44.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>22/07/2026 14:27:32</v>
+        <v>23/07/2026 06:56:28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153281</v>
+        <v>INC000000153382</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,59 +1504,59 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T06:43:05.000Z</v>
+        <v>2026-07-21T16:32:55.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>22/07/2026 14:42:49</v>
+        <v>23/07/2026 08:32:39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153285</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F36" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-22T07:30:20.999Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 15:30:05</v>
+        <v>23/07/2026 09:01:06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153286</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,187 +1568,187 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T07:30:22.000Z</v>
+        <v>2026-07-22T07:32:32.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 15:30:06</v>
+        <v>22/07/2026 15:32:17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153287</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T07:30:22.000Z</v>
+        <v>2026-07-22T08:15:11.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>22/07/2026 15:30:06</v>
+        <v>23/07/2026 14:14:55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153288</v>
+        <v>INC000000153427</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-22T07:30:22.000Z</v>
+        <v>2026-07-22T08:42:28.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 15:30:06</v>
+        <v>22/07/2026 16:42:12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153289</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T07:33:08.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 15:32:52</v>
+        <v>22/07/2026 16:46:27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153290</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T07:33:08.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 15:32:52</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153291</v>
+        <v>INC000000153435</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T07:33:08.000Z</v>
+        <v>2026-07-22T09:50:01.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 15:32:52</v>
+        <v>22/07/2026 17:49:45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153292</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
@@ -1760,27 +1760,27 @@
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-22T07:33:08.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>22/07/2026 15:32:52</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153293</v>
+        <v>INC000000153443</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,27 +1792,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-22T07:47:23.000Z</v>
+        <v>2026-07-22T10:45:27.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>22/07/2026 15:47:07</v>
+        <v>23/07/2026 16:45:11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153446</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,59 +1824,59 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-22T10:56:30.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>22/07/2026 18:56:14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153300</v>
+        <v>INC000000153449</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-22T08:31:33.000Z</v>
+        <v>2026-07-22T10:59:55.999Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 16:31:17</v>
+        <v>22/07/2026 18:59:40</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153323</v>
+        <v>INC000000153452</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1887,28 +1887,25 @@
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
-      <c r="E47" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
-      </c>
       <c r="F47" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-21T11:57:35.000Z</v>
+        <v>2026-07-22T11:37:57.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>22/07/2026 17:57:19</v>
+        <v>22/07/2026 19:37:41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153332</v>
+        <v>INC000000153454</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,59 +1917,59 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-21T12:13:44.000Z</v>
+        <v>2026-07-22T11:38:33.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 18:13:28</v>
+        <v>23/07/2026 17:38:17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153458</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F49" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-22T11:51:14.000Z</v>
       </c>
       <c r="I49" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>-</v>
+        <v>22/07/2026 19:50:58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153459</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,59 +1981,59 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-21T12:36:32.999Z</v>
+        <v>2026-07-22T11:47:41.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>22/07/2026 18:36:17</v>
+        <v>22/07/2026 19:47:25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153343</v>
+        <v>INC000000153460</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F51" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-21T12:47:19.000Z</v>
+        <v>2026-07-22T11:49:50.000Z</v>
       </c>
       <c r="I51" t="str">
-        <v>22/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>-</v>
+        <v>22/07/2026 19:49:34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,7 +2045,7 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F52" t="str">
         <v>ZONA CENTRO</v>
@@ -2057,210 +2054,210 @@
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>22/07/2026 18:40:06</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153352</v>
+        <v>INC000000153506</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-21T13:48:52.000Z</v>
+        <v>2026-07-22T09:01:19.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 19:48:36</v>
+        <v>22/07/2026 17:01:03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153353</v>
+        <v>INC000000153517</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-21T13:59:41.000Z</v>
+        <v>2026-07-22T09:42:26.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 19:59:25</v>
+        <v>22/07/2026 17:42:10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153368</v>
+        <v>INC000000153527</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T14:56:44.000Z</v>
+        <v>2026-07-22T11:08:27.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>23/07/2026 06:56:28</v>
+        <v>22/07/2026 19:08:11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153382</v>
+        <v>INC000000153535</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-21T16:32:55.000Z</v>
+        <v>2026-07-22T11:44:00.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 08:32:39</v>
+        <v>22/07/2026 19:43:44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153385</v>
+        <v>WO0000000304422</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G57" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
-      </c>
-      <c r="I57" t="str">
-        <v>-</v>
+        <v>2026-07-06T12:24:16.000Z</v>
+      </c>
+      <c r="I57" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 09:01:06</v>
+        <v>16/07/2026 12:55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153404</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G58" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-22T05:25:20.000Z</v>
-      </c>
-      <c r="I58" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I58" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>23/07/2026 12:00:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153407</v>
+        <v>WO0000000304757</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2269,132 +2266,126 @@
         <v>En curso</v>
       </c>
       <c r="D59" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E59" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G59" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-22T06:51:53.000Z</v>
-      </c>
-      <c r="I59" t="str">
-        <v>-</v>
+        <v>2026-07-16T12:39:15.999Z</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 14:51:37</v>
+        <v>22/07/2026 15:12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153410</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D60" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E60" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-22T07:02:26.000Z</v>
-      </c>
-      <c r="I60" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I60" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 15:02:10</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153415</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D61" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E61" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-22T07:32:32.999Z</v>
-      </c>
-      <c r="I61" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I61" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>22/07/2026 15:32:17</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153422</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G62" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-22T08:15:11.000Z</v>
-      </c>
-      <c r="I62" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>23/07/2026 14:14:55</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153427</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
@@ -2406,85 +2397,82 @@
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-22T08:42:28.000Z</v>
-      </c>
-      <c r="I63" t="str">
-        <v>-</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I63" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>22/07/2026 16:42:12</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153431</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G64" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
-      </c>
-      <c r="I64" t="str">
-        <v>-</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I64" s="1" t="d">
+        <v>2026-07-22T19:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 16:46:27</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153433</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
-      </c>
-      <c r="I65" t="str">
-        <v>-</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153438</v>
+        <v>WO0000000307614</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2496,219 +2484,210 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F66" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-22T10:11:27.999Z</v>
-      </c>
-      <c r="I66" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:13:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 18:11:12</v>
+        <v>13/08/2026 13:14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153502</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-22T08:44:57.999Z</v>
-      </c>
-      <c r="I67" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>22/07/2026 16:44:42</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153503</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G68" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-22T08:50:19.000Z</v>
-      </c>
-      <c r="I68" t="str">
-        <v>-</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>23/07/2026 14:50:03</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153505</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F69" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
-      </c>
-      <c r="I69" t="str">
-        <v>-</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I69" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153506</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G70" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-22T09:01:19.000Z</v>
-      </c>
-      <c r="I70" t="str">
-        <v>-</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I70" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>22/07/2026 17:01:03</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153509</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G71" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-22T09:00:48.000Z</v>
-      </c>
-      <c r="I71" t="str">
-        <v>-</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>22/07/2026 17:00:32</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>INC000000153517</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-22T09:42:26.000Z</v>
-      </c>
-      <c r="I72" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>22/07/2026 17:42:10</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>INC000000153521</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2720,91 +2699,82 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>DIEGO ARTURO ROMERO CALDERON</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA LAGOSOL</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G73" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-22T10:09:30.000Z</v>
-      </c>
-      <c r="I73" t="str">
-        <v>-</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>23/07/2026 16:09:14</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G74" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
-      </c>
-      <c r="I74" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G75" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
-      </c>
-      <c r="I75" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>-</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2813,39 +2783,39 @@
         <v>En curso</v>
       </c>
       <c r="D76" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>22/07/2026 15:12</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F77" t="str">
         <v>ZONA CENTRO</v>
@@ -2854,137 +2824,134 @@
         <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D78" t="str">
         <v>Alta</v>
       </c>
       <c r="E78" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F78" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G79" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
       </c>
       <c r="J79" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I80" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J80" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000309424</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-22T19:00:16.000Z</v>
+        <v>2026-07-17T11:13:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>24/07/2026 11:25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2996,82 +2963,85 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G83" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J83" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G84" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3083,210 +3053,198 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J85" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000309990</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G86" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I86" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-21T09:34:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>24/07/2026 09:34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000310026</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G87" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I87" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-21T09:37:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>24/07/2026 09:37</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G88" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I88" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G89" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I89" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3298,24 +3256,24 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G92" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3327,85 +3285,85 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F93" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F94" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I94" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J94" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D95" t="str">
-        <v>Alta</v>
+        <v>Media</v>
       </c>
       <c r="E95" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I95" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3417,7 +3375,7 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F96" t="str">
         <v>ZONA CENTRO</v>
@@ -3426,15 +3384,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3446,36 +3404,36 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J97" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F98" t="str">
         <v>ZONA CENTRO</v>
@@ -3484,21 +3442,21 @@
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>24/07/2026 11:25</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
@@ -3513,105 +3471,102 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000309593</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-17T16:59:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310521</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
       </c>
       <c r="C101" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D101" t="str">
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F101" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G101" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T22:31:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000310530</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I102" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-22T06:09:15.999Z</v>
       </c>
       <c r="J102" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310533</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3623,24 +3578,24 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F103" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-22T06:14:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3652,24 +3607,24 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3681,24 +3636,24 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310640</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3710,24 +3665,24 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-22T10:26:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>27/07/2026 10:28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310684</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3736,607 +3691,85 @@
         <v>Asignado</v>
       </c>
       <c r="D107" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E107" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>24/07/2026 11:46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310748</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F108" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-22T10:39:15.999Z</v>
       </c>
       <c r="J108" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>27/07/2026 10:40</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>24/07/2026 14:55</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>WO0000000310111</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-      <c r="C110" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E110" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
-      </c>
-      <c r="F110" t="str">
-        <v>SPT CABECERA SUBA</v>
-      </c>
-      <c r="G110" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H110" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
-      </c>
-      <c r="J110" t="str">
-        <v>24/07/2026 10:05</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>WO0000000310112</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-      <c r="C111" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E111" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F111" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G111" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H111" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
-      </c>
-      <c r="J111" t="str">
-        <v>24/07/2026 10:07</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>WO0000000310164</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-      <c r="C112" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E112" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F112" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G112" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H112" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
-      </c>
-      <c r="J112" t="str">
-        <v>24/07/2026 11:38</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>WO0000000310240</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Media</v>
-      </c>
-      <c r="E113" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
-      </c>
-      <c r="F113" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G113" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H113" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I113" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
-      </c>
-      <c r="J113" t="str">
-        <v>23/07/2026 14:41</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>WO0000000310328</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E114" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
-      </c>
-      <c r="F114" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G114" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H114" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
-      </c>
-      <c r="J114" t="str">
-        <v>23/07/2026 16:08</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>WO0000000310343</v>
-      </c>
-      <c r="B115" t="str">
-        <v>No</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E115" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F115" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G115" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H115" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="J115" t="str">
-        <v>24/07/2026 14:55</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>WO0000000310376</v>
-      </c>
-      <c r="B116" t="str">
-        <v>No</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E116" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
-      </c>
-      <c r="F116" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G116" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H116" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
-      </c>
-      <c r="J116" t="str">
-        <v>24/07/2026 08:38</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>WO0000000310425</v>
-      </c>
-      <c r="B117" t="str">
-        <v>No</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D117" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E117" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F117" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G117" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H117" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
-      </c>
-      <c r="J117" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>WO0000000310452</v>
-      </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-      <c r="C118" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E118" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F118" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G118" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H118" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
-      </c>
-      <c r="J118" t="str">
-        <v>24/07/2026 10:00</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>WO0000000310476</v>
-      </c>
-      <c r="B119" t="str">
-        <v>No</v>
-      </c>
-      <c r="C119" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D119" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E119" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
-      </c>
-      <c r="F119" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
-      </c>
-      <c r="G119" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H119" s="1" t="d">
-        <v>2026-07-22T08:10:16.000Z</v>
-      </c>
-      <c r="J119" t="str">
-        <v>27/07/2026 08:11</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>WO0000000310478</v>
-      </c>
-      <c r="B120" t="str">
-        <v>No</v>
-      </c>
-      <c r="C120" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D120" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E120" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
-      </c>
-      <c r="F120" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
-      </c>
-      <c r="G120" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H120" s="1" t="d">
-        <v>2026-07-22T08:12:16.000Z</v>
-      </c>
-      <c r="J120" t="str">
-        <v>27/07/2026 08:13</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>WO0000000310521</v>
-      </c>
-      <c r="B121" t="str">
-        <v>No</v>
-      </c>
-      <c r="C121" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D121" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E121" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F121" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G121" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H121" s="1" t="d">
-        <v>2026-07-21T22:31:16.000Z</v>
-      </c>
-      <c r="J121" t="str">
-        <v>24/07/2026 10:00</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>WO0000000310530</v>
-      </c>
-      <c r="B122" t="str">
-        <v>No</v>
-      </c>
-      <c r="C122" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D122" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E122" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F122" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G122" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H122" s="1" t="d">
-        <v>2026-07-22T06:09:15.999Z</v>
-      </c>
-      <c r="J122" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>WO0000000310533</v>
-      </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-      <c r="C123" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D123" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E123" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F123" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G123" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H123" s="1" t="d">
-        <v>2026-07-22T06:14:16.000Z</v>
-      </c>
-      <c r="J123" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>WO0000000310543</v>
-      </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-      <c r="C124" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E124" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F124" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G124" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H124" s="1" t="d">
-        <v>2026-07-22T07:27:16.000Z</v>
-      </c>
-      <c r="J124" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>WO0000000310577</v>
-      </c>
-      <c r="B125" t="str">
-        <v>No</v>
-      </c>
-      <c r="C125" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D125" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E125" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
-      </c>
-      <c r="F125" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
-      </c>
-      <c r="G125" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H125" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
-      </c>
-      <c r="J125" t="str">
-        <v>27/07/2026 08:40</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>WO0000000310630</v>
-      </c>
-      <c r="B126" t="str">
-        <v>No</v>
-      </c>
-      <c r="C126" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D126" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E126" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F126" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G126" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H126" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
-      </c>
-      <c r="J126" t="str">
-        <v>27/07/2026 09:59</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>WO0000000310725</v>
-      </c>
-      <c r="C127" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D127" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E127" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
-      </c>
-      <c r="F127" t="str">
-        <v>ZONA NORTE</v>
-      </c>
-      <c r="G127" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H127" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
-      </c>
-      <c r="J127" t="str">
-        <v>-</v>
+        <v>27/07/2026 11:33</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -948,39 +948,39 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153206</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-21T10:47:47.000Z</v>
+        <v>2026-07-21T17:06:23.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J18" t="str">
-        <v>22/07/2026 16:47:31</v>
+        <v>-</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153226</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -1001,18 +1001,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-21T11:48:55.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>22/07/2026 17:48:39</v>
+        <v>23/07/2026 09:04:44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,19 +1024,19 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F20" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-21T17:06:23.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J20" t="str">
         <v>-</v>
@@ -1044,39 +1044,39 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-22T06:27:48.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>23/07/2026 09:04:44</v>
+        <v>22/07/2026 14:27:32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1088,59 +1088,59 @@
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 11:00:53</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F23" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T06:27:48.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I23" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J23" t="str">
-        <v>22/07/2026 14:27:32</v>
+        <v>-</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153293</v>
+        <v>INC000000153342</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,97 +1152,97 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F24" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T07:47:23.000Z</v>
+        <v>2026-07-21T12:36:32.999Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 15:47:07</v>
+        <v>22/07/2026 18:36:17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153343</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-21T12:47:19.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>-</v>
+        <v>22/07/2026 21:00:00</v>
       </c>
       <c r="J25" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153300</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F26" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T08:31:33.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>22/07/2026 16:31:17</v>
+        <v>22/07/2026 18:40:06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153323</v>
+        <v>INC000000153368</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
@@ -1257,126 +1257,126 @@
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-21T11:57:35.000Z</v>
+        <v>2026-07-21T14:56:44.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 17:57:19</v>
+        <v>23/07/2026 06:56:28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153332</v>
+        <v>INC000000153382</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-21T12:13:44.000Z</v>
+        <v>2026-07-21T16:32:55.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 18:13:28</v>
+        <v>23/07/2026 08:32:39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F29" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I29" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>-</v>
+        <v>23/07/2026 09:01:06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153415</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-21T12:36:32.999Z</v>
+        <v>2026-07-22T07:32:32.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 18:36:17</v>
+        <v>22/07/2026 15:32:17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153343</v>
+        <v>INC000000153422</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F31" t="str">
         <v>ZONA CENTRO</v>
@@ -1385,18 +1385,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-21T12:47:19.000Z</v>
+        <v>2026-07-22T08:15:11.000Z</v>
       </c>
       <c r="I31" t="str">
-        <v>22/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:14:55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1408,39 +1408,39 @@
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F32" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 18:40:06</v>
+        <v>22/07/2026 16:46:27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153353</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F33" t="str">
         <v>ZONA CENTRO</v>
@@ -1449,50 +1449,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-21T13:59:41.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>22/07/2026 19:59:25</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153368</v>
+        <v>INC000000153435</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-21T14:56:44.000Z</v>
+        <v>2026-07-22T09:50:01.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 06:56:28</v>
+        <v>22/07/2026 17:49:45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153382</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,27 +1504,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-21T16:32:55.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>23/07/2026 08:32:39</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153443</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,7 +1536,7 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F36" t="str">
         <v>ZONA CENTRO</v>
@@ -1545,50 +1545,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
+        <v>2026-07-22T10:45:27.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>23/07/2026 09:01:06</v>
+        <v>23/07/2026 16:45:11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153415</v>
+        <v>INC000000153446</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T07:32:32.999Z</v>
+        <v>2026-07-22T10:56:30.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 15:32:17</v>
+        <v>22/07/2026 18:56:14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153422</v>
+        <v>INC000000153449</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,27 +1600,27 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T08:15:11.000Z</v>
+        <v>2026-07-22T10:59:55.999Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>23/07/2026 14:14:55</v>
+        <v>22/07/2026 18:59:40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153427</v>
+        <v>INC000000153454</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,59 +1632,59 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-22T08:42:28.000Z</v>
+        <v>2026-07-22T11:38:33.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 16:42:12</v>
+        <v>23/07/2026 17:38:17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153459</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T11:47:41.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 16:46:27</v>
+        <v>22/07/2026 19:47:25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153466</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,59 +1696,59 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T12:26:58.999Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>22/07/2026 20:26:43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153435</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T09:50:01.000Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 17:49:45</v>
+        <v>22/07/2026 20:31:06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
@@ -1760,27 +1760,27 @@
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153443</v>
+        <v>INC000000153527</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,59 +1792,59 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-22T10:45:27.000Z</v>
+        <v>2026-07-22T11:08:27.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>23/07/2026 16:45:11</v>
+        <v>22/07/2026 19:08:11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153446</v>
+        <v>INC000000153535</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D45" t="str">
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-22T10:56:30.000Z</v>
+        <v>2026-07-22T11:44:00.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>22/07/2026 18:56:14</v>
+        <v>22/07/2026 19:43:44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153449</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1856,7 +1856,7 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F46" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -1865,239 +1865,236 @@
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-22T10:59:55.999Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 18:59:40</v>
+        <v>22/07/2026 19:59:08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153452</v>
+        <v>WO0000000304756</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
+      <c r="E47" t="str">
+        <v>JUAN CAMILO RINCON BLANCO</v>
+      </c>
       <c r="F47" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G47" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-22T11:37:57.000Z</v>
-      </c>
-      <c r="I47" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:56:16.000Z</v>
+      </c>
+      <c r="I47" s="1" t="d">
+        <v>2026-07-22T18:00:16.000Z</v>
       </c>
       <c r="J47" t="str">
-        <v>22/07/2026 19:37:41</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153454</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D48" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E48" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F48" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-22T11:38:33.000Z</v>
-      </c>
-      <c r="I48" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I48" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 17:38:17</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153458</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D49" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E49" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F49" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G49" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-22T11:51:14.000Z</v>
-      </c>
-      <c r="I49" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I49" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J49" t="str">
-        <v>22/07/2026 19:50:58</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153459</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G50" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-22T11:47:41.000Z</v>
-      </c>
-      <c r="I50" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J50" t="str">
-        <v>22/07/2026 19:47:25</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153460</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G51" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-22T11:49:50.000Z</v>
-      </c>
-      <c r="I51" t="str">
-        <v>-</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I51" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 19:49:34</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153505</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G52" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
-      </c>
-      <c r="I52" t="str">
-        <v>-</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I52" s="1" t="d">
+        <v>2026-07-22T19:00:16.000Z</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153506</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G53" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-22T09:01:19.000Z</v>
-      </c>
-      <c r="I53" t="str">
-        <v>-</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J53" t="str">
-        <v>22/07/2026 17:01:03</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153517</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2109,91 +2106,85 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-22T09:42:26.000Z</v>
-      </c>
-      <c r="I54" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 17:42:10</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153527</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G55" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-22T11:08:27.000Z</v>
-      </c>
-      <c r="I55" t="str">
-        <v>-</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J55" t="str">
-        <v>22/07/2026 19:08:11</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153535</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-22T11:44:00.000Z</v>
-      </c>
-      <c r="I56" t="str">
-        <v>-</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I56" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>22/07/2026 19:43:44</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000304422</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2205,27 +2196,27 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G57" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-06T12:24:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I57" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>16/07/2026 12:55</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2237,7 +2228,7 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F58" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2246,111 +2237,108 @@
         <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
       </c>
       <c r="I58" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>-</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000304757</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D59" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G59" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-16T12:39:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I59" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 15:12</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G60" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I60" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000309101</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G61" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I61" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-16T21:59:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>19/08/2026 08:00</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2365,53 +2353,50 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G62" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F63" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I63" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2423,68 +2408,68 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
-        <v>2026-07-22T19:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E65" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G65" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000307614</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2493,27 +2478,30 @@
         <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-14T12:13:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I66" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>13/08/2026 13:14</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F67" t="str">
         <v>ZONA CENTRO</v>
@@ -2522,15 +2510,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J67" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2542,56 +2530,53 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G69" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I69" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J69" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309779</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2603,178 +2588,172 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G70" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
+        <v>2026-07-19T13:12:16.000Z</v>
       </c>
       <c r="I70" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-22T17:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G72" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G73" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000310097</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-21T12:01:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2786,262 +2765,259 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G76" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G77" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000310164</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F78" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-21T11:36:15.999Z</v>
       </c>
       <c r="J78" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>24/07/2026 11:38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D79" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E79" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G79" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I79" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000309424</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-17T11:13:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 11:25</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F82" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I84" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310521</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3053,7 +3029,7 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F85" t="str">
         <v>ZONA CENTRO</v>
@@ -3062,15 +3038,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T22:31:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000309990</v>
+        <v>WO0000000310530</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3091,15 +3067,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T09:34:16.000Z</v>
+        <v>2026-07-22T06:09:15.999Z</v>
       </c>
       <c r="J86" t="str">
-        <v>24/07/2026 09:34</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310026</v>
+        <v>WO0000000310533</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3111,82 +3087,82 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T09:37:16.000Z</v>
+        <v>2026-07-22T06:14:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>24/07/2026 09:37</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310640</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3198,24 +3174,24 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-22T10:26:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>27/07/2026 10:28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310697</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3227,7 +3203,7 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F91" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3236,15 +3212,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-22T12:05:15.999Z</v>
       </c>
       <c r="J91" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>27/07/2026 12:11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310748</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3256,24 +3232,24 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-22T10:39:15.999Z</v>
       </c>
       <c r="J92" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>27/07/2026 10:40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3285,24 +3261,24 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3314,462 +3290,24 @@
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>24/07/2026 11:38</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>WO0000000310240</v>
-      </c>
-      <c r="B95" t="str">
-        <v>No</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="D95" t="str">
-        <v>Media</v>
-      </c>
-      <c r="E95" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
-      </c>
-      <c r="F95" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G95" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H95" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I95" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
-      </c>
-      <c r="J95" t="str">
-        <v>23/07/2026 14:41</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>WO0000000310328</v>
-      </c>
-      <c r="B96" t="str">
-        <v>No</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D96" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E96" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
-      </c>
-      <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G96" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H96" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
-      </c>
-      <c r="J96" t="str">
-        <v>23/07/2026 16:08</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>WO0000000310343</v>
-      </c>
-      <c r="B97" t="str">
-        <v>No</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D97" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E97" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F97" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G97" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H97" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="J97" t="str">
-        <v>24/07/2026 14:55</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>WO0000000310376</v>
-      </c>
-      <c r="B98" t="str">
-        <v>No</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D98" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E98" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
-      </c>
-      <c r="F98" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G98" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H98" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
-      </c>
-      <c r="J98" t="str">
-        <v>24/07/2026 08:38</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>WO0000000310425</v>
-      </c>
-      <c r="B99" t="str">
-        <v>No</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D99" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E99" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F99" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G99" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H99" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
-      </c>
-      <c r="J99" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>WO0000000310452</v>
-      </c>
-      <c r="B100" t="str">
-        <v>No</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D100" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E100" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F100" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G100" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H100" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
-      </c>
-      <c r="J100" t="str">
-        <v>24/07/2026 10:00</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>WO0000000310521</v>
-      </c>
-      <c r="B101" t="str">
-        <v>No</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D101" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E101" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F101" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G101" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H101" s="1" t="d">
-        <v>2026-07-21T22:31:16.000Z</v>
-      </c>
-      <c r="J101" t="str">
-        <v>24/07/2026 10:00</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>WO0000000310530</v>
-      </c>
-      <c r="B102" t="str">
-        <v>No</v>
-      </c>
-      <c r="C102" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D102" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E102" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F102" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G102" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H102" s="1" t="d">
-        <v>2026-07-22T06:09:15.999Z</v>
-      </c>
-      <c r="J102" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>WO0000000310533</v>
-      </c>
-      <c r="B103" t="str">
-        <v>No</v>
-      </c>
-      <c r="C103" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D103" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E103" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F103" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G103" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H103" s="1" t="d">
-        <v>2026-07-22T06:14:16.000Z</v>
-      </c>
-      <c r="J103" t="str">
-        <v>27/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>WO0000000310577</v>
-      </c>
-      <c r="B104" t="str">
-        <v>No</v>
-      </c>
-      <c r="C104" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D104" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E104" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
-      <c r="F104" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
-      </c>
-      <c r="G104" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H104" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
-      </c>
-      <c r="J104" t="str">
-        <v>27/07/2026 08:40</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>WO0000000310630</v>
-      </c>
-      <c r="B105" t="str">
-        <v>No</v>
-      </c>
-      <c r="C105" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E105" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G105" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H105" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
-      </c>
-      <c r="J105" t="str">
-        <v>27/07/2026 09:59</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>WO0000000310640</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D106" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E106" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
-      </c>
-      <c r="F106" t="str">
-        <v>SPT CABECERA CALLE 42</v>
-      </c>
-      <c r="G106" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H106" s="1" t="d">
-        <v>2026-07-22T10:26:16.000Z</v>
-      </c>
-      <c r="J106" t="str">
-        <v>27/07/2026 10:28</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>WO0000000310684</v>
-      </c>
-      <c r="B107" t="str">
-        <v>No</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Media</v>
-      </c>
-      <c r="E107" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G107" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H107" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
-      </c>
-      <c r="J107" t="str">
-        <v>24/07/2026 11:46</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>WO0000000310748</v>
-      </c>
-      <c r="B108" t="str">
-        <v>No</v>
-      </c>
-      <c r="C108" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D108" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E108" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F108" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G108" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H108" s="1" t="d">
-        <v>2026-07-22T10:39:15.999Z</v>
-      </c>
-      <c r="J108" t="str">
-        <v>27/07/2026 10:40</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>WO0000000310781</v>
-      </c>
-      <c r="B109" t="str">
-        <v>No</v>
-      </c>
-      <c r="C109" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D109" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E109" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
-      </c>
-      <c r="F109" t="str">
-        <v>SPT ZONA CENTRO</v>
-      </c>
-      <c r="G109" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H109" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
-      </c>
-      <c r="J109" t="str">
-        <v>27/07/2026 11:33</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,7 +556,7 @@
         <v>2026-07-14T10:57:48.999Z</v>
       </c>
       <c r="I5" t="str">
-        <v>22/07/2026 16:00:00</v>
+        <v>24/07/2026 16:00:00</v>
       </c>
       <c r="J5" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152768</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -777,10 +777,10 @@
         <v>b) 5-10</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-17T10:13:53.999Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152774</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G13" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-17T10:28:03.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>22/07/2026 18:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,19 +832,19 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G14" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 16:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153266</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,16 +864,16 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T17:06:23.000Z</v>
       </c>
       <c r="I15" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -884,51 +884,51 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>-</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J16" t="str">
-        <v>22/07/2026 16:16:33</v>
+        <v>-</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153196</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F17" t="str">
         <v>ZONA CENTRO</v>
@@ -937,42 +937,42 @@
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-21T10:34:43.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J17" t="str">
-        <v>22/07/2026 16:34:27</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153279</v>
       </c>
       <c r="B18" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C18" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F18" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-21T17:06:23.000Z</v>
+        <v>2026-07-22T06:27:48.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,39 +980,39 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>23/07/2026 09:04:44</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,16 +1024,16 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F20" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I20" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -1044,71 +1044,71 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F21" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T06:27:48.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I21" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J21" t="str">
-        <v>22/07/2026 14:27:32</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>23/07/2026 09:01:06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,16 +1120,16 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F23" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153342</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,155 +1152,155 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-21T12:36:32.999Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>22/07/2026 18:36:17</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153343</v>
+        <v>INC000000153435</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-21T12:47:19.000Z</v>
+        <v>2026-07-22T09:50:01.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>22/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>-</v>
+        <v>23/07/2026 15:49:45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F26" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>22/07/2026 18:40:06</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153368</v>
+        <v>INC000000153446</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-21T14:56:44.000Z</v>
+        <v>2026-07-22T10:56:30.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>23/07/2026 06:56:28</v>
+        <v>22/07/2026 18:56:14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153382</v>
+        <v>INC000000153449</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-21T16:32:55.000Z</v>
+        <v>2026-07-22T10:59:55.999Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>23/07/2026 08:32:39</v>
+        <v>22/07/2026 18:59:40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153454</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,7 +1312,7 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F29" t="str">
         <v>ZONA CENTRO</v>
@@ -1321,18 +1321,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
+        <v>2026-07-22T11:38:33.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>23/07/2026 09:01:06</v>
+        <v>23/07/2026 17:38:17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153415</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,27 +1344,27 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F30" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T07:32:32.999Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>22/07/2026 15:32:17</v>
+        <v>23/07/2026 18:31:06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153422</v>
+        <v>INC000000153475</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,7 +1376,7 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F31" t="str">
         <v>ZONA CENTRO</v>
@@ -1385,18 +1385,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T08:15:11.000Z</v>
+        <v>2026-07-22T14:37:01.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>23/07/2026 14:14:55</v>
+        <v>24/07/2026 06:36:45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1408,27 +1408,27 @@
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F32" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>22/07/2026 16:46:27</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153494</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,59 +1440,59 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T16:51:06.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>23/07/2026 09:50:50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153435</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T09:50:01.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>22/07/2026 17:49:45</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153527</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,27 +1504,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T11:08:27.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>22/07/2026 19:08:11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153443</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,27 +1536,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-22T10:45:27.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>23/07/2026 16:45:11</v>
+        <v>22/07/2026 19:59:08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153446</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,27 +1568,27 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T10:56:30.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>22/07/2026 18:56:14</v>
+        <v>23/07/2026 19:10:20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153449</v>
+        <v>INC000000153553</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,27 +1600,27 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T10:59:55.999Z</v>
+        <v>2026-07-22T14:20:42.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>22/07/2026 18:59:40</v>
+        <v>24/07/2026 06:20:26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153454</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,59 +1632,59 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-22T11:38:33.000Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 17:38:17</v>
+        <v>23/07/2026 08:00:45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153459</v>
+        <v>INC000000153565</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T11:47:41.000Z</v>
+        <v>2026-07-22T15:19:57.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>22/07/2026 19:47:25</v>
+        <v>23/07/2026 08:19:41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153466</v>
+        <v>INC000000153571</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,187 +1696,178 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T12:26:58.999Z</v>
+        <v>2026-07-22T16:10:36.999Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>22/07/2026 20:26:43</v>
+        <v>24/07/2026 08:10:21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>22/07/2026 20:31:06</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153505</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D43" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E43" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F43" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
-      </c>
-      <c r="I43" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I43" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153527</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D44" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E44" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-22T11:08:27.000Z</v>
-      </c>
-      <c r="I44" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I44" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J44" t="str">
-        <v>22/07/2026 19:08:11</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153535</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D45" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E45" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>Media</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-22T11:44:00.000Z</v>
-      </c>
-      <c r="I45" t="str">
-        <v>-</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J45" t="str">
-        <v>22/07/2026 19:43:44</v>
+        <v>28/07/2026 15:19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153538</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G46" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
-      </c>
-      <c r="I46" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J46" t="str">
-        <v>22/07/2026 19:59:08</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>WO0000000304756</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1888,27 +1879,27 @@
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F47" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G47" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-16T10:56:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I47" s="1" t="d">
-        <v>2026-07-22T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J47" t="str">
-        <v>-</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1917,62 +1908,59 @@
         <v>Pendiente</v>
       </c>
       <c r="D48" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G48" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I48" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J48" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D49" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G49" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I49" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J49" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1987,53 +1975,50 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G50" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J50" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G51" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I51" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J51" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2045,190 +2030,193 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I52" s="1" t="d">
-        <v>2026-07-22T19:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G53" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I53" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J53" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G54" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I54" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J54" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I55" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J55" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G56" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I56" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G57" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I57" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309162</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F58" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2237,18 +2225,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I58" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-17T09:16:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2260,7 +2245,7 @@
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F59" t="str">
         <v>ZONA CENTRO</v>
@@ -2269,105 +2254,108 @@
         <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="I59" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D60" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E60" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000309101</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-16T21:59:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I61" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>19/08/2026 08:00</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J62" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2379,117 +2367,111 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I64" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J64" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D65" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-18T08:36:15.999Z</v>
       </c>
       <c r="J65" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>27/07/2026 14:32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I66" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J66" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
@@ -2501,114 +2483,111 @@
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F67" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G67" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G68" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000309779</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-19T13:12:16.000Z</v>
-      </c>
-      <c r="I70" s="1" t="d">
-        <v>2026-07-22T17:00:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2620,82 +2599,85 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E72" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2707,24 +2689,24 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J74" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310097</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2736,82 +2718,82 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T12:01:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G76" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310164</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2823,36 +2805,36 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T11:36:15.999Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>24/07/2026 11:38</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F79" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2861,134 +2843,131 @@
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I79" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310697</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-22T12:05:15.999Z</v>
       </c>
       <c r="J80" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>27/07/2026 12:11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J83" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3000,53 +2979,53 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310521</v>
+        <v>WO0000000311007</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T22:31:16.000Z</v>
+        <v>2026-07-22T15:44:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 15:47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310530</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3058,24 +3037,24 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-22T06:09:15.999Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310533</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3087,24 +3066,24 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-22T06:14:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3116,24 +3095,24 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3145,7 +3124,7 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F89" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3154,15 +3133,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310640</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3174,140 +3153,53 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-22T10:26:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>27/07/2026 10:28</v>
+        <v>21/08/2026 16:58</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000311106</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-22T16:38:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>27/07/2026 12:11</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>WO0000000310748</v>
-      </c>
-      <c r="B92" t="str">
-        <v>No</v>
-      </c>
-      <c r="C92" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D92" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E92" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F92" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G92" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H92" s="1" t="d">
-        <v>2026-07-22T10:39:15.999Z</v>
-      </c>
-      <c r="J92" t="str">
-        <v>27/07/2026 10:40</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>WO0000000310781</v>
-      </c>
-      <c r="B93" t="str">
-        <v>No</v>
-      </c>
-      <c r="C93" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D93" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E93" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
-      </c>
-      <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G93" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H93" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
-      </c>
-      <c r="J93" t="str">
-        <v>24/07/2026 13:56</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>WO0000000310805</v>
-      </c>
-      <c r="B94" t="str">
-        <v>No</v>
-      </c>
-      <c r="C94" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D94" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E94" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F94" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G94" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H94" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
-      </c>
-      <c r="J94" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>27/07/2026 16:38</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1236,7 +1236,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153446</v>
+        <v>INC000000153454</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1248,59 +1248,59 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F27" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T10:56:30.000Z</v>
+        <v>2026-07-22T11:38:33.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>22/07/2026 18:56:14</v>
+        <v>23/07/2026 17:38:17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153449</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-22T10:59:55.999Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>22/07/2026 18:59:40</v>
+        <v>23/07/2026 18:31:06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153454</v>
+        <v>INC000000153475</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,7 +1312,7 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F29" t="str">
         <v>ZONA CENTRO</v>
@@ -1321,50 +1321,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-22T11:38:33.000Z</v>
+        <v>2026-07-22T14:37:01.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>23/07/2026 17:38:17</v>
+        <v>24/07/2026 06:36:45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>23/07/2026 18:31:06</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153475</v>
+        <v>INC000000153494</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,39 +1376,39 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>LUIS HERNANDO BELTRAN CORRALES</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T14:37:01.000Z</v>
+        <v>2026-07-22T16:51:06.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>24/07/2026 06:36:45</v>
+        <v>23/07/2026 09:50:50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F32" t="str">
         <v>ZONA CENTRO</v>
@@ -1417,18 +1417,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153494</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,33 +1440,33 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F33" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T16:51:06.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>23/07/2026 09:50:50</v>
+        <v>22/07/2026 19:59:08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
@@ -1481,50 +1481,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>23/07/2026 19:10:20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153527</v>
+        <v>INC000000153553</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T11:08:27.000Z</v>
+        <v>2026-07-22T14:20:42.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>22/07/2026 19:08:11</v>
+        <v>24/07/2026 06:20:26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153565</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,27 +1536,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F36" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-22T15:19:57.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>22/07/2026 19:59:08</v>
+        <v>23/07/2026 08:19:41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153571</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1577,114 +1577,114 @@
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-22T16:10:36.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>23/07/2026 19:10:20</v>
+        <v>24/07/2026 08:10:21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153553</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T14:20:42.000Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>24/07/2026 06:20:26</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153560</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D39" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E39" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G39" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
-      </c>
-      <c r="I39" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I39" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 08:00:45</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153565</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D40" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E40" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G40" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T15:19:57.000Z</v>
-      </c>
-      <c r="I40" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I40" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 08:19:41</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153571</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1693,10 +1693,7 @@
         <v>Asignado</v>
       </c>
       <c r="D41" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E41" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>Media</v>
       </c>
       <c r="F41" t="str">
         <v>ZONA CENTRO</v>
@@ -1705,50 +1702,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T16:10:36.999Z</v>
-      </c>
-      <c r="I41" t="str">
-        <v>-</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J41" t="str">
-        <v>24/07/2026 08:10:21</v>
+        <v>28/07/2026 15:19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153572</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F42" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G42" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
-      </c>
-      <c r="I42" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J42" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
@@ -1757,30 +1748,30 @@
         <v>Pendiente</v>
       </c>
       <c r="D43" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G43" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I43" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J43" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1789,56 +1780,59 @@
         <v>Pendiente</v>
       </c>
       <c r="D44" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G44" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I44" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J44" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>WO0000000305285</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D45" t="str">
-        <v>Media</v>
+        <v>Baja</v>
+      </c>
+      <c r="E45" t="str">
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G45" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J45" t="str">
-        <v>28/07/2026 15:19</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1853,53 +1847,50 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G46" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J46" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G47" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I47" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J47" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1911,178 +1902,181 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I48" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J48" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G49" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I49" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J49" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G50" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I50" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J50" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G51" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I51" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J51" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G52" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I52" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G53" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I53" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J53" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>23/07/2026 08:41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2094,117 +2088,117 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="I54" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J54" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E55" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F55" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I55" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J55" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I56" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G57" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000309162</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2216,117 +2210,111 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-17T09:16:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309657</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G59" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I59" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-17T17:33:15.999Z</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>24/07/2026 08:00</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000309692</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-18T08:36:15.999Z</v>
       </c>
       <c r="J60" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>27/07/2026 14:32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F61" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I61" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J61" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2338,82 +2326,82 @@
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G62" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G63" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000309692</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2425,24 +2413,24 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G65" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-18T08:36:15.999Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>27/07/2026 14:32</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2454,82 +2442,85 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E67" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
+      </c>
+      <c r="I67" s="1" t="d">
+        <v>2026-07-22T20:00:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>23/07/2026 14:41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
@@ -2541,114 +2532,111 @@
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J69" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D72" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2660,53 +2648,53 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310697</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2718,36 +2706,36 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-22T12:05:15.999Z</v>
       </c>
       <c r="J75" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>27/07/2026 12:11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F76" t="str">
         <v>ZONA CENTRO</v>
@@ -2756,44 +2744,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2805,53 +2793,53 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J78" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000311007</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2863,7 +2851,7 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F80" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2872,15 +2860,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-22T15:44:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>27/07/2026 12:11</v>
+        <v>27/07/2026 15:47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
@@ -2892,24 +2880,24 @@
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2921,7 +2909,7 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F82" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2930,15 +2918,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2959,44 +2947,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000311007</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3008,24 +2996,24 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-22T15:44:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J85" t="str">
-        <v>27/07/2026 15:47</v>
+        <v>21/08/2026 16:58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000311106</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3040,166 +3028,21 @@
         <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-22T16:38:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>27/07/2026 15:53</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>WO0000000311019</v>
-      </c>
-      <c r="B87" t="str">
-        <v>No</v>
-      </c>
-      <c r="C87" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D87" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E87" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G87" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H87" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
-      </c>
-      <c r="J87" t="str">
-        <v>27/07/2026 15:56</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>WO0000000311031</v>
-      </c>
-      <c r="B88" t="str">
-        <v>No</v>
-      </c>
-      <c r="C88" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D88" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E88" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G88" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H88" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
-      </c>
-      <c r="J88" t="str">
-        <v>27/07/2026 16:22</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>WO0000000311036</v>
-      </c>
-      <c r="B89" t="str">
-        <v>No</v>
-      </c>
-      <c r="C89" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D89" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E89" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F89" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G89" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H89" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
-      </c>
-      <c r="J89" t="str">
-        <v>27/07/2026 16:27</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>WO0000000311046</v>
-      </c>
-      <c r="B90" t="str">
-        <v>No</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D90" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E90" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
-      </c>
-      <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G90" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H90" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
-      </c>
-      <c r="J90" t="str">
-        <v>21/08/2026 16:58</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>WO0000000311106</v>
-      </c>
-      <c r="B91" t="str">
-        <v>No</v>
-      </c>
-      <c r="C91" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D91" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E91" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
-      </c>
-      <c r="F91" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G91" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H91" s="1" t="d">
-        <v>2026-07-22T16:38:16.000Z</v>
-      </c>
-      <c r="J91" t="str">
         <v>27/07/2026 16:38</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J86"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -628,31 +628,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>INC000000152361</v>
+        <v>INC000000152668</v>
       </c>
       <c r="B8" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C8" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D8" t="str">
         <v>Baja</v>
       </c>
       <c r="E8" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F8" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G8" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H8" s="1" t="d">
-        <v>2026-07-15T12:30:33.000Z</v>
+        <v>2026-07-17T08:56:42.000Z</v>
       </c>
       <c r="I8" t="str">
-        <v>22/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J8" t="str">
         <v>-</v>
@@ -660,31 +660,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000152668</v>
+        <v>INC000000152674</v>
       </c>
       <c r="B9" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C9" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D9" t="str">
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F9" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G9" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-17T08:56:42.000Z</v>
+        <v>2026-07-17T09:17:43.000Z</v>
       </c>
       <c r="I9" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J9" t="str">
         <v>-</v>
@@ -692,7 +692,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000152760</v>
       </c>
       <c r="B10" t="str">
         <v>No</v>
@@ -704,7 +704,7 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F10" t="str">
         <v>ZONA CENTRO</v>
@@ -713,7 +713,7 @@
         <v>b) 5-10</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-17T09:40:00.000Z</v>
       </c>
       <c r="I10" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000152790</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,7 +736,7 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
@@ -745,7 +745,7 @@
         <v>b) 5-10</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-17T11:37:39.000Z</v>
       </c>
       <c r="I11" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,16 +768,16 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G12" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I12" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 16:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,19 +832,19 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>23/07/2026 16:00:00</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153266</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
@@ -864,19 +864,19 @@
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F15" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-21T17:06:23.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J15" t="str">
         <v>-</v>
@@ -884,39 +884,39 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>29/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J16" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,16 +928,16 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F17" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I17" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -948,31 +948,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153279</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B18" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F18" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-22T06:27:48.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I18" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,27 +992,27 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>23/07/2026 09:01:06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,16 +1024,16 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F20" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I20" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -1044,19 +1044,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F21" t="str">
         <v>ZONA CENTRO</v>
@@ -1065,190 +1065,190 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I21" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>-</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 09:01:06</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153454</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F23" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T11:38:33.000Z</v>
       </c>
       <c r="I23" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:38:17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D24" t="str">
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>23/07/2026 18:31:06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153435</v>
+        <v>INC000000153475</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-22T09:50:01.000Z</v>
+        <v>2026-07-22T14:37:01.000Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>23/07/2026 15:49:45</v>
+        <v>24/07/2026 06:36:45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F26" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153454</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F27" t="str">
         <v>ZONA CENTRO</v>
@@ -1257,62 +1257,62 @@
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T11:38:33.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>23/07/2026 17:38:17</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B28" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C28" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>23/07/2026 18:31:06</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153475</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F29" t="str">
         <v>ZONA CENTRO</v>
@@ -1321,18 +1321,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-22T14:37:01.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>24/07/2026 06:36:45</v>
+        <v>23/07/2026 19:10:20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153553</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,27 +1344,27 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T14:20:42.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>24/07/2026 06:20:26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153494</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1375,28 +1375,25 @@
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
-      <c r="E31" t="str">
-        <v>LUIS HERNANDO BELTRAN CORRALES</v>
-      </c>
       <c r="F31" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT REGIONALES</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T16:51:06.000Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>23/07/2026 09:50:50</v>
+        <v>23/07/2026 12:49:07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1417,18 +1414,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,27 +1437,27 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F33" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>22/07/2026 19:59:08</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153580</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1472,27 +1469,27 @@
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-22T19:53:13.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 19:10:20</v>
+        <v>23/07/2026 12:52:57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153553</v>
+        <v>INC000000153583</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,27 +1501,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T14:20:42.000Z</v>
+        <v>2026-07-22T22:09:45.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>24/07/2026 06:20:26</v>
+        <v>23/07/2026 14:00:00</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153565</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,65 +1533,65 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F36" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-22T15:19:57.000Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>23/07/2026 08:19:41</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153571</v>
+        <v>INC000000153587</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-22T16:10:36.999Z</v>
+        <v>2026-07-23T06:42:54.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>24/07/2026 08:10:21</v>
+        <v>23/07/2026 14:42:38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153572</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
@@ -1603,114 +1600,120 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>23/07/2026 14:57:27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153593</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D39" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G39" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I39" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T07:20:03.000Z</v>
+      </c>
+      <c r="I39" t="str">
+        <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>24/07/2026 13:19:47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153594</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D40" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F40" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G40" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I40" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T07:28:45.999Z</v>
+      </c>
+      <c r="I40" t="str">
+        <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>23/07/2026 15:28:30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>WO0000000305285</v>
+        <v>INC000000153599</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D41" t="str">
-        <v>Media</v>
+        <v>Baja</v>
+      </c>
+      <c r="E41" t="str">
+        <v>FREDY ANDRES AVILA VEGA</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA LAGOMAR</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-23T07:49:22.999Z</v>
+      </c>
+      <c r="I41" t="str">
+        <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>28/07/2026 15:19</v>
+        <v>24/07/2026 13:49:07</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
@@ -1722,146 +1725,155 @@
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F42" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G42" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
+      </c>
+      <c r="I42" t="str">
+        <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 10:28:31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G43" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I43" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
+      </c>
+      <c r="I43" t="str">
+        <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>23/07/2026 10:50:38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G44" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I44" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
+      </c>
+      <c r="I44" t="str">
+        <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>23/07/2026 11:18:44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>WO0000000307105</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
       </c>
       <c r="C45" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D45" t="str">
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
+      </c>
+      <c r="I45" t="str">
+        <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>WO0000000307624</v>
+        <v>INC000000153615</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G46" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-23T06:13:55.000Z</v>
+      </c>
+      <c r="I46" t="str">
+        <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>23/07/2026 14:13:39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>WO0000000307703</v>
+        <v>INC000000153616</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1873,94 +1885,97 @@
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G47" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-23T06:34:58.000Z</v>
+      </c>
+      <c r="I47" t="str">
+        <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>23/07/2026 14:34:42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>WO0000000307988</v>
+        <v>INC000000153620</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D48" t="str">
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G48" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I48" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-23T06:51:02.000Z</v>
+      </c>
+      <c r="I48" t="str">
+        <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 14:50:46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000153621</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G49" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I49" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-23T06:56:45.000Z</v>
+      </c>
+      <c r="I49" t="str">
+        <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>23/07/2026 14:56:29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>WO0000000308443</v>
+        <v>INC000000153623</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
@@ -1972,21 +1987,21 @@
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G50" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I50" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-23T07:22:45.000Z</v>
+      </c>
+      <c r="I50" t="str">
+        <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>23/07/2026 15:22:29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -1995,10 +2010,10 @@
         <v>Pendiente</v>
       </c>
       <c r="D51" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E51" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F51" t="str">
         <v>ZONA CENTRO</v>
@@ -2007,137 +2022,137 @@
         <v>b) 5-10</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="I51" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J51" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D52" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E52" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I52" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E53" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>Media</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G53" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J53" t="str">
-        <v>23/07/2026 08:41</v>
+        <v>28/07/2026 15:19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G54" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I54" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J54" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D55" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G55" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I55" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J55" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2149,56 +2164,56 @@
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G56" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I56" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G57" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2210,7 +2225,7 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F58" t="str">
         <v>ZONA CENTRO</v>
@@ -2219,15 +2234,15 @@
         <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000309657</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
@@ -2239,169 +2254,181 @@
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G59" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-17T17:33:15.999Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>24/07/2026 08:00</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000309692</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-18T08:36:15.999Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I60" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>27/07/2026 14:32</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G61" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I61" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G62" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I62" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I63" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000308986</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G64" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-16T17:35:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>23/07/2026 09:42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2413,117 +2440,111 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F66" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I66" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
-        <v>Media</v>
+        <v>Alta</v>
       </c>
       <c r="E67" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
-      </c>
-      <c r="I67" s="1" t="d">
-        <v>2026-07-22T20:00:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>23/07/2026 14:41</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000310328</v>
-      </c>
-      <c r="B68" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>-</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000310343</v>
-      </c>
-      <c r="B69" t="str">
-        <v>No</v>
+        <v>WO0000000309319</v>
       </c>
       <c r="C69" t="str">
         <v>Asignado</v>
@@ -2535,27 +2556,27 @@
         <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-22T10:46:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>-</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
@@ -2567,18 +2588,21 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G70" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I70" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
@@ -2590,30 +2614,30 @@
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F71" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J71" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
@@ -2625,18 +2649,18 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2648,24 +2672,24 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J73" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2677,65 +2701,65 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>27/07/2026 12:11</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F76" t="str">
         <v>ZONA CENTRO</v>
@@ -2744,15 +2768,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
@@ -2764,24 +2788,24 @@
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2793,7 +2817,7 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F78" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2802,218 +2826,218 @@
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E79" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>24/07/2026 14:41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000311007</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-22T15:44:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>27/07/2026 15:47</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J81" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000311106</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3025,24 +3049,430 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F86" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G86" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H86" s="1" t="d">
+        <v>2026-07-22T09:58:16.000Z</v>
+      </c>
+      <c r="J86" t="str">
+        <v>27/07/2026 09:59</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>WO0000000310697</v>
+      </c>
+      <c r="B87" t="str">
+        <v>No</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E87" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F87" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G87" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H87" s="1" t="d">
+        <v>2026-07-22T12:05:15.999Z</v>
+      </c>
+      <c r="J87" t="str">
+        <v>27/07/2026 12:11</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>WO0000000310781</v>
+      </c>
+      <c r="B88" t="str">
+        <v>No</v>
+      </c>
+      <c r="C88" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E88" t="str">
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+      </c>
+      <c r="F88" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G88" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H88" s="1" t="d">
+        <v>2026-07-22T11:28:16.000Z</v>
+      </c>
+      <c r="J88" t="str">
+        <v>24/07/2026 13:56</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>WO0000000310805</v>
+      </c>
+      <c r="B89" t="str">
+        <v>No</v>
+      </c>
+      <c r="C89" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E89" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F89" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G89" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H89" s="1" t="d">
+        <v>2026-07-22T12:04:16.000Z</v>
+      </c>
+      <c r="J89" t="str">
+        <v>27/07/2026 12:06</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>WO0000000310888</v>
+      </c>
+      <c r="B90" t="str">
+        <v>No</v>
+      </c>
+      <c r="C90" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E90" t="str">
         <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F90" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G90" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H90" s="1" t="d">
+        <v>2026-07-22T16:03:15.999Z</v>
+      </c>
+      <c r="J90" t="str">
+        <v>27/07/2026 16:03</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>WO0000000310974</v>
+      </c>
+      <c r="B91" t="str">
+        <v>No</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E91" t="str">
+        <v>NICK STEVE TRIANA LOPEZ</v>
+      </c>
+      <c r="F91" t="str">
+        <v>SPT ZONA OCCIDENTE</v>
+      </c>
+      <c r="G91" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H91" s="1" t="d">
+        <v>2026-07-22T15:04:16.000Z</v>
+      </c>
+      <c r="J91" t="str">
+        <v>27/07/2026 15:18</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>WO0000000311007</v>
+      </c>
+      <c r="B92" t="str">
+        <v>No</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E92" t="str">
+        <v>JUAN CAMILO RINCON BLANCO</v>
+      </c>
+      <c r="F92" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G92" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H92" s="1" t="d">
+        <v>2026-07-22T15:44:16.000Z</v>
+      </c>
+      <c r="J92" t="str">
+        <v>27/07/2026 15:47</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>WO0000000311014</v>
+      </c>
+      <c r="B93" t="str">
+        <v>No</v>
+      </c>
+      <c r="C93" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E93" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F93" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G93" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H93" s="1" t="d">
+        <v>2026-07-22T15:53:16.000Z</v>
+      </c>
+      <c r="J93" t="str">
+        <v>27/07/2026 15:53</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>WO0000000311019</v>
+      </c>
+      <c r="B94" t="str">
+        <v>No</v>
+      </c>
+      <c r="C94" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E94" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F94" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G94" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H94" s="1" t="d">
+        <v>2026-07-22T15:56:16.000Z</v>
+      </c>
+      <c r="J94" t="str">
+        <v>27/07/2026 15:56</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>WO0000000311031</v>
+      </c>
+      <c r="B95" t="str">
+        <v>No</v>
+      </c>
+      <c r="C95" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E95" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F95" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G95" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H95" s="1" t="d">
+        <v>2026-07-22T16:22:16.000Z</v>
+      </c>
+      <c r="J95" t="str">
+        <v>27/07/2026 16:22</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>WO0000000311036</v>
+      </c>
+      <c r="B96" t="str">
+        <v>No</v>
+      </c>
+      <c r="C96" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E96" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F96" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G96" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H96" s="1" t="d">
+        <v>2026-07-22T16:27:16.000Z</v>
+      </c>
+      <c r="J96" t="str">
+        <v>27/07/2026 16:27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>WO0000000311046</v>
+      </c>
+      <c r="B97" t="str">
+        <v>No</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E97" t="str">
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+      </c>
+      <c r="F97" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G97" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H97" s="1" t="d">
+        <v>2026-07-22T16:58:15.999Z</v>
+      </c>
+      <c r="J97" t="str">
+        <v>21/08/2026 16:58</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>WO0000000311080</v>
+      </c>
+      <c r="B98" t="str">
+        <v>No</v>
+      </c>
+      <c r="C98" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E98" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F98" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G98" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H98" s="1" t="d">
+        <v>2026-07-23T07:09:16.000Z</v>
+      </c>
+      <c r="J98" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>WO0000000311145</v>
+      </c>
+      <c r="B99" t="str">
+        <v>No</v>
+      </c>
+      <c r="C99" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E99" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F99" t="str">
         <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
-      <c r="G86" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H86" s="1" t="d">
-        <v>2026-07-22T16:38:16.000Z</v>
-      </c>
-      <c r="J86" t="str">
-        <v>27/07/2026 16:38</v>
+      <c r="G99" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H99" s="1" t="d">
+        <v>2026-07-23T06:11:16.000Z</v>
+      </c>
+      <c r="J99" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>WO0000000311147</v>
+      </c>
+      <c r="B100" t="str">
+        <v>No</v>
+      </c>
+      <c r="C100" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E100" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F100" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G100" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H100" s="1" t="d">
+        <v>2026-07-23T07:04:16.000Z</v>
+      </c>
+      <c r="J100" t="str">
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -986,7 +986,7 @@
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
@@ -1004,10 +1004,10 @@
         <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>-</v>
+        <v>23/07/2026 13:00:00</v>
       </c>
       <c r="J19" t="str">
-        <v>23/07/2026 09:01:06</v>
+        <v>-</v>
       </c>
     </row>
     <row r="20">
@@ -1108,66 +1108,66 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153454</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T11:38:33.000Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>23/07/2026 17:38:17</v>
+        <v>23/07/2026 18:31:06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153468</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D24" t="str">
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T12:36:50.999Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>23/07/2026 18:31:06</v>
+        <v>24/07/2026 14:36:35</v>
       </c>
     </row>
     <row r="25">
@@ -1271,10 +1271,10 @@
         <v>INC000000153538</v>
       </c>
       <c r="B28" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
@@ -1283,7 +1283,7 @@
         <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
@@ -1292,7 +1292,7 @@
         <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I28" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J28" t="str">
         <v>-</v>
@@ -1306,13 +1306,13 @@
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F29" t="str">
         <v>ZONA CENTRO</v>
@@ -1324,10 +1324,10 @@
         <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I29" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J29" t="str">
-        <v>23/07/2026 19:10:20</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30">
@@ -1375,6 +1375,9 @@
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
+      <c r="E31" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
       <c r="F31" t="str">
         <v>SPT REGIONALES</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
@@ -1484,7 +1487,7 @@
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 12:52:57</v>
+        <v>24/07/2026 11:52:57</v>
       </c>
     </row>
     <row r="35">
@@ -1495,7 +1498,7 @@
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
@@ -1617,167 +1620,167 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153593</v>
+        <v>INC000000153594</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T07:20:03.000Z</v>
+        <v>2026-07-23T07:28:45.999Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>24/07/2026 13:19:47</v>
+        <v>23/07/2026 15:28:30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153594</v>
+        <v>INC000000153598</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T07:28:45.999Z</v>
+        <v>2026-07-23T07:48:59.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 15:28:30</v>
+        <v>23/07/2026 15:48:43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153599</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>FREDY ANDRES AVILA VEGA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA LAGOMAR</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-23T07:49:22.999Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
       </c>
       <c r="I41" t="str">
-        <v>-</v>
+        <v>23/07/2026 21:00:00</v>
       </c>
       <c r="J41" t="str">
-        <v>24/07/2026 13:49:07</v>
+        <v>-</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I42" t="str">
-        <v>-</v>
+        <v>23/07/2026 19:00:00</v>
       </c>
       <c r="J42" t="str">
-        <v>23/07/2026 10:28:31</v>
+        <v>-</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I43" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 10:50:38</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1789,27 +1792,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>23/07/2026 11:18:44</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153615</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1821,59 +1824,59 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T06:13:55.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>23/07/2026 14:13:39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153615</v>
+        <v>INC000000153616</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T06:13:55.000Z</v>
+        <v>2026-07-23T06:34:58.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>23/07/2026 14:13:39</v>
+        <v>23/07/2026 14:34:42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153616</v>
+        <v>INC000000153620</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1894,50 +1897,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T06:34:58.000Z</v>
+        <v>2026-07-23T06:51:02.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>23/07/2026 14:34:42</v>
+        <v>23/07/2026 14:50:46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153620</v>
+        <v>INC000000153621</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D48" t="str">
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-23T06:51:02.000Z</v>
+        <v>2026-07-23T06:56:45.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 14:50:46</v>
+        <v>23/07/2026 14:56:29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153621</v>
+        <v>INC000000153623</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1958,18 +1961,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-23T06:56:45.000Z</v>
+        <v>2026-07-23T07:22:45.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>23/07/2026 14:56:29</v>
+        <v>23/07/2026 15:22:29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153623</v>
+        <v>INC000000153629</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1990,82 +1993,82 @@
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-23T07:22:45.000Z</v>
+        <v>2026-07-23T07:57:47.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>23/07/2026 15:22:29</v>
+        <v>23/07/2026 15:57:31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153632</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D51" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F51" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G51" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I51" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T08:00:07.000Z</v>
+      </c>
+      <c r="I51" t="str">
+        <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>23/07/2026 15:59:51</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153633</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D52" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G52" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I52" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T08:02:53.000Z</v>
+      </c>
+      <c r="I52" t="str">
+        <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>23/07/2026 16:02:37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>WO0000000305285</v>
+        <v>INC000000153635</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2074,7 +2077,10 @@
         <v>Asignado</v>
       </c>
       <c r="D53" t="str">
-        <v>Media</v>
+        <v>Baja</v>
+      </c>
+      <c r="E53" t="str">
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F53" t="str">
         <v>ZONA CENTRO</v>
@@ -2083,50 +2089,56 @@
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-23T08:22:59.999Z</v>
+      </c>
+      <c r="I53" t="str">
+        <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>28/07/2026 15:19</v>
+        <v>24/07/2026 14:22:44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153639</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G54" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-23T08:45:27.000Z</v>
+      </c>
+      <c r="I54" t="str">
+        <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 16:45:11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>WO0000000305566</v>
+        <v>INC000000153702</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
@@ -2138,53 +2150,53 @@
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G55" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I55" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-23T08:07:46.999Z</v>
+      </c>
+      <c r="I55" t="str">
+        <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>23/07/2026 16:07:31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000305625</v>
+        <v>INC000000153706</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G56" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I56" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-23T08:30:20.999Z</v>
+      </c>
+      <c r="I56" t="str">
+        <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>23/07/2026 16:30:05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000307105</v>
+        <v>INC000000153707</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2196,82 +2208,91 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G57" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-23T08:30:46.000Z</v>
+      </c>
+      <c r="I57" t="str">
+        <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>23/07/2026 16:30:30</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000307624</v>
+        <v>INC000000153708</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F58" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-23T08:41:34.000Z</v>
+      </c>
+      <c r="I58" t="str">
+        <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 14:41:18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D59" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E59" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G59" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I59" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2280,10 +2301,10 @@
         <v>Pendiente</v>
       </c>
       <c r="D60" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E60" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F60" t="str">
         <v>ZONA CENTRO</v>
@@ -2292,82 +2313,73 @@
         <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="I60" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D61" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E61" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>Media</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I61" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>28/07/2026 15:19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G62" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I62" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2379,56 +2391,59 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I63" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000308986</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-16T17:35:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
+      </c>
+      <c r="I64" s="1" t="d">
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>23/07/2026 09:42</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2440,36 +2455,36 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2478,99 +2493,108 @@
         <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I66" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F67" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G67" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000307988</v>
+      </c>
+      <c r="B68" t="str">
+        <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I68" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>-</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000309319</v>
+        <v>WO0000000308197</v>
+      </c>
+      <c r="B69" t="str">
+        <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G69" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-22T10:46:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I69" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>-</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2582,39 +2606,39 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G70" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
       </c>
       <c r="I70" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F71" t="str">
         <v>ZONA CENTRO</v>
@@ -2623,15 +2647,18 @@
         <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000309436</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
@@ -2643,114 +2670,111 @@
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G72" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F73" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G73" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
+      </c>
+      <c r="I73" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D74" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E74" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310030</v>
-      </c>
-      <c r="B75" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C75" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310060</v>
-      </c>
-      <c r="B76" t="str">
-        <v>No</v>
+        <v>WO0000000309319</v>
       </c>
       <c r="C76" t="str">
         <v>Asignado</v>
@@ -2759,82 +2783,85 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G76" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-22T10:46:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>-</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000309413</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-17T10:55:15.999Z</v>
       </c>
       <c r="J78" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>23/07/2026 10:55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000309436</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
@@ -2843,27 +2870,27 @@
         <v>En curso</v>
       </c>
       <c r="D79" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G79" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
+        <v>2026-07-17T11:38:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>24/07/2026 14:41</v>
+        <v>24/07/2026 15:38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2875,7 +2902,7 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F80" t="str">
         <v>ZONA CENTRO</v>
@@ -2884,73 +2911,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J80" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2971,44 +2998,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000310112</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3020,24 +3047,24 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-21T10:07:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>24/07/2026 10:07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3046,10 +3073,10 @@
         <v>En curso</v>
       </c>
       <c r="D86" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E86" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F86" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3058,131 +3085,131 @@
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>24/07/2026 14:41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>27/07/2026 12:11</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J88" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3194,53 +3221,53 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000311007</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-22T15:44:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>27/07/2026 15:47</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3252,7 +3279,7 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F93" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3261,27 +3288,27 @@
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000310697</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F94" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3290,15 +3317,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-22T12:05:15.999Z</v>
       </c>
       <c r="J94" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>27/07/2026 12:11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3310,24 +3337,24 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3339,7 +3366,7 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F96" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3348,102 +3375,102 @@
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F97" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J97" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311145</v>
+        <v>WO0000000311007</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-23T06:11:16.000Z</v>
+        <v>2026-07-22T15:44:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>27/07/2026 15:47</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311147</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3455,7 +3482,7 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F100" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3464,15 +3491,247 @@
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
+        <v>2026-07-22T15:53:16.000Z</v>
+      </c>
+      <c r="J100" t="str">
+        <v>27/07/2026 15:53</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>WO0000000311019</v>
+      </c>
+      <c r="B101" t="str">
+        <v>No</v>
+      </c>
+      <c r="C101" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E101" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F101" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G101" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H101" s="1" t="d">
+        <v>2026-07-22T15:56:16.000Z</v>
+      </c>
+      <c r="J101" t="str">
+        <v>27/07/2026 15:56</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>WO0000000311031</v>
+      </c>
+      <c r="B102" t="str">
+        <v>No</v>
+      </c>
+      <c r="C102" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E102" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F102" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G102" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H102" s="1" t="d">
+        <v>2026-07-22T16:22:16.000Z</v>
+      </c>
+      <c r="J102" t="str">
+        <v>27/07/2026 16:22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>WO0000000311036</v>
+      </c>
+      <c r="B103" t="str">
+        <v>No</v>
+      </c>
+      <c r="C103" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E103" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F103" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G103" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H103" s="1" t="d">
+        <v>2026-07-22T16:27:16.000Z</v>
+      </c>
+      <c r="J103" t="str">
+        <v>27/07/2026 16:27</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>WO0000000311046</v>
+      </c>
+      <c r="B104" t="str">
+        <v>No</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E104" t="str">
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+      </c>
+      <c r="F104" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G104" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H104" s="1" t="d">
+        <v>2026-07-22T16:58:15.999Z</v>
+      </c>
+      <c r="J104" t="str">
+        <v>21/08/2026 16:58</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>WO0000000311080</v>
+      </c>
+      <c r="B105" t="str">
+        <v>No</v>
+      </c>
+      <c r="C105" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E105" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F105" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G105" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H105" s="1" t="d">
+        <v>2026-07-23T07:09:16.000Z</v>
+      </c>
+      <c r="J105" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>WO0000000311145</v>
+      </c>
+      <c r="B106" t="str">
+        <v>No</v>
+      </c>
+      <c r="C106" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E106" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F106" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G106" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H106" s="1" t="d">
+        <v>2026-07-23T06:11:16.000Z</v>
+      </c>
+      <c r="J106" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>WO0000000311147</v>
+      </c>
+      <c r="B107" t="str">
+        <v>No</v>
+      </c>
+      <c r="C107" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E107" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F107" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G107" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H107" s="1" t="d">
         <v>2026-07-23T07:04:16.000Z</v>
       </c>
-      <c r="J100" t="str">
+      <c r="J107" t="str">
         <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>WO0000000311205</v>
+      </c>
+      <c r="B108" t="str">
+        <v>No</v>
+      </c>
+      <c r="C108" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E108" t="str">
+        <v>SANTIAGO PERDOMO ACERO</v>
+      </c>
+      <c r="F108" t="str">
+        <v>SPT ZONA CENTRO</v>
+      </c>
+      <c r="G108" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H108" s="1" t="d">
+        <v>2026-07-23T08:28:16.000Z</v>
+      </c>
+      <c r="J108" t="str">
+        <v>28/07/2026 08:31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J112"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152790</v>
+        <v>INC000000152896</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,16 +736,16 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F11" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G11" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-17T11:37:39.000Z</v>
+        <v>2026-07-18T10:43:56.000Z</v>
       </c>
       <c r="I11" t="str">
         <v>23/07/2026 18:00:00</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 16:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>23/07/2026 16:00:00</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,7 +832,7 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F14" t="str">
         <v>ZONA CENTRO</v>
@@ -841,10 +841,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>29/07/2026 18:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J14" t="str">
         <v>-</v>
@@ -852,71 +852,71 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J15" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F16" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J16" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>-</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -928,19 +928,19 @@
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F17" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I17" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J17" t="str">
         <v>-</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153385</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,7 +960,7 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F18" t="str">
         <v>ZONA CENTRO</v>
@@ -969,10 +969,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-21T17:01:22.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 13:00:00</v>
       </c>
       <c r="J18" t="str">
         <v>-</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,19 +992,19 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>23/07/2026 13:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J19" t="str">
         <v>-</v>
@@ -1012,39 +1012,39 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F20" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>-</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1056,27 +1056,27 @@
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153467</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1088,27 +1088,27 @@
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T12:35:11.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>23/07/2026 18:31:06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153468</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,27 +1120,27 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T12:36:50.999Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>23/07/2026 18:31:06</v>
+        <v>24/07/2026 14:36:35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153468</v>
+        <v>INC000000153475</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,27 +1152,27 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F24" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T12:36:50.999Z</v>
+        <v>2026-07-22T14:37:01.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>24/07/2026 14:36:35</v>
+        <v>24/07/2026 06:36:45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153475</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
@@ -1184,7 +1184,7 @@
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F25" t="str">
         <v>ZONA CENTRO</v>
@@ -1193,30 +1193,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-22T14:37:01.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>24/07/2026 06:36:45</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F26" t="str">
         <v>ZONA CENTRO</v>
@@ -1225,30 +1225,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F27" t="str">
         <v>ZONA CENTRO</v>
@@ -1257,18 +1257,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>23/07/2026 18:09:27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1280,7 +1280,7 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F28" t="str">
         <v>ZONA CENTRO</v>
@@ -1289,10 +1289,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I28" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J28" t="str">
         <v>-</v>
@@ -1300,39 +1300,39 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153553</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-22T14:20:42.000Z</v>
       </c>
       <c r="I29" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>-</v>
+        <v>24/07/2026 06:20:26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153553</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1344,71 +1344,71 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T14:20:42.000Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>24/07/2026 06:20:26</v>
+        <v>24/07/2026 07:00:45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153560</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F31" t="str">
-        <v>SPT REGIONALES</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>23/07/2026 12:49:07</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153572</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F32" t="str">
         <v>ZONA CENTRO</v>
@@ -1417,18 +1417,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153579</v>
+        <v>INC000000153580</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,91 +1440,91 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T19:01:01.000Z</v>
+        <v>2026-07-22T19:53:13.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>24/07/2026 11:00:45</v>
+        <v>24/07/2026 11:52:57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153580</v>
+        <v>INC000000153583</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F34" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T19:53:13.000Z</v>
+        <v>2026-07-22T22:09:45.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>24/07/2026 11:52:57</v>
+        <v>23/07/2026 14:00:00</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153583</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
       </c>
       <c r="C35" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D35" t="str">
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-22T22:09:45.000Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>23/07/2026 14:00:00</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153586</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,27 +1536,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T06:32:38.000Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>24/07/2026 12:32:22</v>
+        <v>23/07/2026 14:57:27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153587</v>
+        <v>INC000000153594</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,33 +1568,33 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T06:42:54.000Z</v>
+        <v>2026-07-23T07:28:45.999Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>23/07/2026 14:42:38</v>
+        <v>23/07/2026 15:28:30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153589</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
@@ -1609,62 +1609,62 @@
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-23T06:57:43.000Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
       </c>
       <c r="I38" t="str">
-        <v>-</v>
+        <v>23/07/2026 21:00:00</v>
       </c>
       <c r="J38" t="str">
-        <v>23/07/2026 14:57:27</v>
+        <v>-</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153594</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T07:28:45.999Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I39" t="str">
-        <v>-</v>
+        <v>23/07/2026 19:00:00</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 15:28:30</v>
+        <v>-</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153598</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F40" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -1673,146 +1673,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T07:48:59.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I40" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 15:48:43</v>
+        <v>-</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
       </c>
       <c r="I41" t="str">
-        <v>23/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>-</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153615</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-23T06:13:55.000Z</v>
       </c>
       <c r="I42" t="str">
-        <v>23/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:13:39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153616</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-23T06:34:58.000Z</v>
       </c>
       <c r="I43" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:34:42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153620</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T06:51:02.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>23/07/2026 14:50:46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153615</v>
+        <v>INC000000153635</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,91 +1824,91 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T06:13:55.000Z</v>
+        <v>2026-07-23T08:22:59.999Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>23/07/2026 14:13:39</v>
+        <v>24/07/2026 14:22:44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153616</v>
+        <v>INC000000153644</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T06:34:58.000Z</v>
+        <v>2026-07-23T09:37:46.999Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>23/07/2026 14:34:42</v>
+        <v>23/07/2026 17:37:31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153620</v>
+        <v>INC000000153647</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T06:51:02.000Z</v>
+        <v>2026-07-23T09:47:27.999Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>23/07/2026 14:50:46</v>
+        <v>23/07/2026 17:47:12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153621</v>
+        <v>INC000000153648</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,27 +1920,27 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-23T06:56:45.000Z</v>
+        <v>2026-07-23T10:02:06.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 14:56:29</v>
+        <v>23/07/2026 18:01:50</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153623</v>
+        <v>INC000000153649</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,27 +1952,27 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F49" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-23T07:22:45.000Z</v>
+        <v>2026-07-23T10:03:35.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>23/07/2026 15:22:29</v>
+        <v>23/07/2026 18:03:19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153629</v>
+        <v>INC000000153650</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,91 +1984,91 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-23T07:57:47.000Z</v>
+        <v>2026-07-23T10:04:28.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>23/07/2026 15:57:31</v>
+        <v>23/07/2026 18:04:12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153632</v>
+        <v>INC000000153706</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-23T08:00:07.000Z</v>
+        <v>2026-07-23T08:30:20.999Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>23/07/2026 15:59:51</v>
+        <v>23/07/2026 16:30:05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153633</v>
+        <v>INC000000153707</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-23T08:02:53.000Z</v>
+        <v>2026-07-23T08:30:46.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 16:02:37</v>
+        <v>23/07/2026 16:30:30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153635</v>
+        <v>INC000000153708</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2080,7 +2080,7 @@
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F53" t="str">
         <v>ZONA CENTRO</v>
@@ -2089,114 +2089,114 @@
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-23T08:22:59.999Z</v>
+        <v>2026-07-23T08:41:34.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>24/07/2026 14:22:44</v>
+        <v>24/07/2026 14:41:18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153639</v>
+        <v>INC000000153715</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-23T08:45:27.000Z</v>
+        <v>2026-07-23T09:01:56.999Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>23/07/2026 16:45:11</v>
+        <v>23/07/2026 17:01:41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153702</v>
+        <v>INC000000153716</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-23T08:07:46.999Z</v>
+        <v>2026-07-23T09:01:56.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>23/07/2026 16:07:31</v>
+        <v>23/07/2026 17:01:41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153706</v>
+        <v>INC000000153718</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-23T08:30:20.999Z</v>
+        <v>2026-07-23T09:29:29.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 16:30:05</v>
+        <v>23/07/2026 17:29:13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153707</v>
+        <v>INC000000153719</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,27 +2208,27 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-23T08:30:46.000Z</v>
+        <v>2026-07-23T09:17:02.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 16:30:30</v>
+        <v>23/07/2026 17:16:46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153708</v>
+        <v>INC000000153721</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
@@ -2240,91 +2240,91 @@
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-23T08:41:34.000Z</v>
+        <v>2026-07-23T09:27:59.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>24/07/2026 14:41:18</v>
+        <v>23/07/2026 17:27:43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000305248</v>
+        <v>INC000000153726</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G59" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I59" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T09:57:45.999Z</v>
+      </c>
+      <c r="I59" t="str">
+        <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>23/07/2026 17:57:30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D60" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G60" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I60" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
+      </c>
+      <c r="I60" t="str">
+        <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>23/07/2026 17:59:51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000305285</v>
+        <v>INC000000153729</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2333,53 +2333,62 @@
         <v>Asignado</v>
       </c>
       <c r="D61" t="str">
-        <v>Media</v>
+        <v>Baja</v>
+      </c>
+      <c r="E61" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-23T10:07:22.000Z</v>
+      </c>
+      <c r="I61" t="str">
+        <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>28/07/2026 15:19</v>
+        <v>23/07/2026 18:07:06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153730</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G62" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-23T10:06:13.999Z</v>
+      </c>
+      <c r="I62" t="str">
+        <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 18:05:58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2388,30 +2397,30 @@
         <v>Pendiente</v>
       </c>
       <c r="D63" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E63" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
+        <v>2026-07-15T11:49:16.000Z</v>
       </c>
       <c r="I63" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2420,59 +2429,59 @@
         <v>Pendiente</v>
       </c>
       <c r="D64" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E64" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E65" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G65" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>27/07/2026 09:14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2487,50 +2496,53 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G66" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G67" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
+      </c>
+      <c r="I67" s="1" t="d">
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2542,152 +2554,146 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G68" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I68" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G69" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I69" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G70" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I70" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G71" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2699,108 +2705,120 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G73" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
       </c>
       <c r="I73" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D74" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I74" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000308723</v>
+      </c>
+      <c r="B75" t="str">
+        <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I75" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>-</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000309319</v>
+        <v>WO0000000309139</v>
+      </c>
+      <c r="B76" t="str">
+        <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G76" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-22T10:46:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>-</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000309281</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
@@ -2812,7 +2830,7 @@
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F77" t="str">
         <v>ZONA CENTRO</v>
@@ -2821,18 +2839,18 @@
         <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
+        <v>2026-07-17T10:53:16.000Z</v>
       </c>
       <c r="I77" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>22/07/2026 12:53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000309413</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2841,7 +2859,7 @@
         <v>Asignado</v>
       </c>
       <c r="D78" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E78" t="str">
         <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
@@ -2850,105 +2868,102 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-17T10:55:15.999Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>23/07/2026 10:55</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000309436</v>
-      </c>
-      <c r="B79" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G79" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-17T11:38:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>24/07/2026 15:38</v>
+        <v>-</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000309834</v>
-      </c>
-      <c r="B80" t="str">
-        <v>No</v>
+        <v>WO0000000309319</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-22T10:46:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>-</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2960,53 +2975,53 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J82" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
       </c>
       <c r="C83" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D83" t="str">
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310030</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3018,53 +3033,53 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310112</v>
+        <v>WO0000000310060</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T10:07:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>24/07/2026 10:07</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3073,27 +3088,27 @@
         <v>En curso</v>
       </c>
       <c r="D86" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>24/07/2026 14:41</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3102,85 +3117,85 @@
         <v>En curso</v>
       </c>
       <c r="D87" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E87" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 14:41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
       </c>
       <c r="C88" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D88" t="str">
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
       </c>
       <c r="J89" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3192,7 +3207,7 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F90" t="str">
         <v>ZONA CENTRO</v>
@@ -3201,15 +3216,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3230,44 +3245,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3279,30 +3294,30 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
@@ -3317,44 +3332,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>27/07/2026 12:11</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000310697</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F95" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-22T12:05:15.999Z</v>
       </c>
       <c r="J95" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>27/07/2026 12:11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3366,24 +3381,24 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000310789</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3395,65 +3410,65 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>28/07/2026 08:13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311007</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F99" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3462,44 +3477,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-22T15:44:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J99" t="str">
-        <v>27/07/2026 15:47</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000311007</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3511,7 +3526,7 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F101" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3520,15 +3535,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-22T15:44:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>27/07/2026 15:47</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3549,15 +3564,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3578,44 +3593,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F104" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3627,7 +3642,7 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F105" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3636,44 +3651,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000311145</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F106" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-23T06:11:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J106" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>21/08/2026 16:58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000311147</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3685,24 +3700,24 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-23T07:04:16.000Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J107" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000311205</v>
+        <v>WO0000000311080</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3714,24 +3729,140 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-23T08:28:16.000Z</v>
+        <v>2026-07-23T07:09:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>28/07/2026 08:31</v>
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>WO0000000311145</v>
+      </c>
+      <c r="B109" t="str">
+        <v>No</v>
+      </c>
+      <c r="C109" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E109" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F109" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G109" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H109" s="1" t="d">
+        <v>2026-07-23T06:11:16.000Z</v>
+      </c>
+      <c r="J109" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>WO0000000311147</v>
+      </c>
+      <c r="B110" t="str">
+        <v>No</v>
+      </c>
+      <c r="C110" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E110" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F110" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G110" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H110" s="1" t="d">
+        <v>2026-07-23T07:04:16.000Z</v>
+      </c>
+      <c r="J110" t="str">
+        <v>28/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>WO0000000311247</v>
+      </c>
+      <c r="B111" t="str">
+        <v>No</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E111" t="str">
+        <v>GERLYN RENTERIA OROZCO</v>
+      </c>
+      <c r="F111" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G111" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H111" s="1" t="d">
+        <v>2026-07-23T09:42:16.000Z</v>
+      </c>
+      <c r="J111" t="str">
+        <v>28/07/2026 09:42</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WO0000000311253</v>
+      </c>
+      <c r="B112" t="str">
+        <v>No</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E112" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F112" t="str">
+        <v>SPT ESCRITORIO VIRTUAL</v>
+      </c>
+      <c r="G112" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H112" s="1" t="d">
+        <v>2026-07-23T10:08:16.000Z</v>
+      </c>
+      <c r="J112" t="str">
+        <v>28/07/2026 10:10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J112"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -692,7 +692,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000152760</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B10" t="str">
         <v>No</v>
@@ -704,19 +704,19 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F10" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G10" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-17T09:40:00.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I10" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 16:00:00</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000152896</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,19 +736,19 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F11" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G11" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-18T10:43:56.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 16:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,39 +788,39 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153299</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
       </c>
       <c r="C13" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D13" t="str">
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-22T08:16:41.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>29/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J13" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:16:25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153335</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,16 +832,16 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CENTRO MAYOR</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T12:17:03.000Z</v>
       </c>
       <c r="I14" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -852,39 +852,39 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I15" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J15" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>-</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -896,16 +896,16 @@
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F16" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I16" t="str">
         <v>23/07/2026 17:00:00</v>
@@ -916,19 +916,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F17" t="str">
         <v>ZONA CENTRO</v>
@@ -937,94 +937,94 @@
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J17" t="str">
-        <v>-</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153385</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-21T17:01:22.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>23/07/2026 13:00:00</v>
+        <v>-</v>
       </c>
       <c r="J18" t="str">
-        <v>-</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153475</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F19" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T14:37:01.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J19" t="str">
-        <v>-</v>
+        <v>24/07/2026 06:36:45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F20" t="str">
         <v>ZONA CENTRO</v>
@@ -1033,18 +1033,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1056,91 +1056,91 @@
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153467</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T12:35:11.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 18:31:06</v>
+        <v>23/07/2026 18:09:27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153468</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F23" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T12:36:50.999Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I23" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J23" t="str">
-        <v>24/07/2026 14:36:35</v>
+        <v>-</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153475</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,7 +1152,7 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F24" t="str">
         <v>ZONA CENTRO</v>
@@ -1161,30 +1161,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T14:37:01.000Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>24/07/2026 06:36:45</v>
+        <v>24/07/2026 07:00:45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F25" t="str">
         <v>ZONA CENTRO</v>
@@ -1193,30 +1193,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F26" t="str">
         <v>ZONA CENTRO</v>
@@ -1225,18 +1225,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153580</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1248,39 +1248,39 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-22T19:53:13.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>23/07/2026 18:09:27</v>
+        <v>24/07/2026 11:52:57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F28" t="str">
         <v>ZONA CENTRO</v>
@@ -1289,18 +1289,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I28" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>-</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153553</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,123 +1312,123 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-22T14:20:42.000Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>24/07/2026 06:20:26</v>
+        <v>23/07/2026 14:57:27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153560</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F30" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
       </c>
       <c r="I30" t="str">
-        <v>-</v>
+        <v>23/07/2026 21:00:00</v>
       </c>
       <c r="J30" t="str">
-        <v>24/07/2026 07:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153572</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I31" t="str">
-        <v>-</v>
+        <v>23/07/2026 19:00:00</v>
       </c>
       <c r="J31" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>-</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153579</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F32" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T19:01:01.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I32" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J32" t="str">
-        <v>24/07/2026 11:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153580</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,59 +1440,59 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T19:53:13.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>24/07/2026 11:52:57</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153583</v>
+        <v>INC000000153615</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-22T22:09:45.000Z</v>
+        <v>2026-07-23T06:13:55.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 14:00:00</v>
+        <v>23/07/2026 14:13:39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153586</v>
+        <v>INC000000153635</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1513,18 +1513,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-23T06:32:38.000Z</v>
+        <v>2026-07-23T08:22:59.999Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>24/07/2026 12:32:22</v>
+        <v>24/07/2026 14:22:44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153589</v>
+        <v>INC000000153647</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,155 +1536,155 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F36" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T06:57:43.000Z</v>
+        <v>2026-07-23T09:47:27.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>23/07/2026 14:57:27</v>
+        <v>23/07/2026 17:47:12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153594</v>
+        <v>INC000000153648</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
       </c>
       <c r="C37" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D37" t="str">
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T07:28:45.999Z</v>
+        <v>2026-07-23T10:02:06.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>23/07/2026 15:28:30</v>
+        <v>23/07/2026 18:01:50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153649</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-23T10:03:35.000Z</v>
       </c>
       <c r="I38" t="str">
-        <v>23/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:03:19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153650</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-23T10:04:28.000Z</v>
       </c>
       <c r="I39" t="str">
-        <v>23/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:04:12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153652</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-23T10:10:09.000Z</v>
       </c>
       <c r="I40" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:09:53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153657</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1696,27 +1696,27 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T10:35:40.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>23/07/2026 18:35:24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153615</v>
+        <v>INC000000153658</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
@@ -1728,91 +1728,91 @@
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-23T06:13:55.000Z</v>
+        <v>2026-07-23T10:24:06.999Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>23/07/2026 14:13:39</v>
+        <v>24/07/2026 16:23:51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153616</v>
+        <v>INC000000153661</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-23T06:34:58.000Z</v>
+        <v>2026-07-23T10:52:03.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 14:34:42</v>
+        <v>23/07/2026 18:51:47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153620</v>
+        <v>INC000000153667</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
       </c>
       <c r="C44" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D44" t="str">
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-23T06:51:02.000Z</v>
+        <v>2026-07-23T11:32:49.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>23/07/2026 14:50:46</v>
+        <v>24/07/2026 17:32:33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153635</v>
+        <v>INC000000153669</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,91 +1824,91 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T08:22:59.999Z</v>
+        <v>2026-07-23T11:30:05.999Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>24/07/2026 14:22:44</v>
+        <v>23/07/2026 19:29:50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153644</v>
+        <v>INC000000153672</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T09:37:46.999Z</v>
+        <v>2026-07-23T11:45:48.999Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>23/07/2026 17:37:31</v>
+        <v>23/07/2026 19:45:33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153647</v>
+        <v>INC000000153673</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T09:47:27.999Z</v>
+        <v>2026-07-23T11:57:31.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>23/07/2026 17:47:12</v>
+        <v>23/07/2026 19:57:15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153648</v>
+        <v>INC000000153677</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,27 +1920,27 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-23T10:02:06.000Z</v>
+        <v>2026-07-23T12:19:22.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 18:01:50</v>
+        <v>23/07/2026 20:19:06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153649</v>
+        <v>INC000000153708</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,27 +1952,27 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F49" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G49" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-23T10:03:35.000Z</v>
+        <v>2026-07-23T08:41:34.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>23/07/2026 18:03:19</v>
+        <v>24/07/2026 14:41:18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153650</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,91 +1984,91 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-23T10:04:28.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>23/07/2026 18:04:12</v>
+        <v>23/07/2026 17:59:51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153706</v>
+        <v>INC000000153730</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-23T08:30:20.999Z</v>
+        <v>2026-07-23T10:06:13.999Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>23/07/2026 16:30:05</v>
+        <v>23/07/2026 18:05:58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153707</v>
+        <v>INC000000153733</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-23T08:30:46.000Z</v>
+        <v>2026-07-23T10:30:57.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 16:30:30</v>
+        <v>24/07/2026 16:30:41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153708</v>
+        <v>INC000000153738</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2080,91 +2080,91 @@
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-23T08:41:34.000Z</v>
+        <v>2026-07-23T11:13:56.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>24/07/2026 14:41:18</v>
+        <v>24/07/2026 17:13:40</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153715</v>
+        <v>INC000000153741</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-23T09:01:56.999Z</v>
+        <v>2026-07-23T11:24:06.999Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>23/07/2026 17:01:41</v>
+        <v>24/07/2026 17:23:51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153716</v>
+        <v>INC000000153746</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-23T09:01:56.999Z</v>
+        <v>2026-07-23T11:45:11.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>23/07/2026 17:01:41</v>
+        <v>23/07/2026 19:44:55</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153718</v>
+        <v>INC000000153749</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2176,155 +2176,155 @@
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-23T09:29:29.000Z</v>
+        <v>2026-07-23T11:44:11.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 17:29:13</v>
+        <v>23/07/2026 19:43:55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153719</v>
+        <v>INC000000153751</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D57" t="str">
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-23T09:17:02.000Z</v>
+        <v>2026-07-23T12:20:01.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 17:16:46</v>
+        <v>23/07/2026 20:19:45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153721</v>
+        <v>INC000000153759</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-23T09:27:59.000Z</v>
+        <v>2026-07-23T12:05:41.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>23/07/2026 17:27:43</v>
+        <v>24/07/2026 18:05:25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153726</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D59" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E59" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G59" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-23T09:57:45.999Z</v>
-      </c>
-      <c r="I59" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I59" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>23/07/2026 17:57:30</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153727</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D60" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E60" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-23T10:00:07.000Z</v>
-      </c>
-      <c r="I60" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I60" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>23/07/2026 17:59:51</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153729</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2333,10 +2333,10 @@
         <v>Asignado</v>
       </c>
       <c r="D61" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E61" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F61" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2345,50 +2345,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-23T10:07:22.000Z</v>
-      </c>
-      <c r="I61" t="str">
-        <v>-</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>23/07/2026 18:07:06</v>
+        <v>27/07/2026 09:14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153730</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F62" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G62" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-23T10:06:13.999Z</v>
-      </c>
-      <c r="I62" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>23/07/2026 18:05:58</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000305566</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2397,30 +2391,30 @@
         <v>Pendiente</v>
       </c>
       <c r="D63" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
+        <v>2026-07-08T11:28:16.000Z</v>
       </c>
       <c r="I63" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T17:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>17/07/2026 13:49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2429,59 +2423,59 @@
         <v>Pendiente</v>
       </c>
       <c r="D64" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000305285</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D65" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>27/07/2026 09:14</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2496,53 +2490,50 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G67" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I67" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2554,358 +2545,355 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I68" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G69" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I69" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F70" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G70" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I70" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G72" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D73" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E73" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G73" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I73" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000308443</v>
-      </c>
-      <c r="B74" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C74" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F74" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I74" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>-</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000308723</v>
-      </c>
-      <c r="B75" t="str">
-        <v>No</v>
+        <v>WO0000000309319</v>
       </c>
       <c r="C75" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F75" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G75" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I75" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-22T10:46:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I76" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000309281</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F77" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-17T10:53:16.000Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J77" t="str">
-        <v>22/07/2026 12:53</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000310028</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F78" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000310030</v>
+      </c>
+      <c r="B79" t="str">
+        <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>-</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000309319</v>
+        <v>WO0000000310060</v>
+      </c>
+      <c r="B80" t="str">
+        <v>No</v>
       </c>
       <c r="C80" t="str">
         <v>Asignado</v>
@@ -2914,56 +2902,53 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-22T10:46:16.000Z</v>
+        <v>2026-07-21T10:46:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>-</v>
+        <v>20/08/2026 10:46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000310111</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G81" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I81" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-21T10:05:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>24/07/2026 10:05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310240</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2972,27 +2957,27 @@
         <v>En curso</v>
       </c>
       <c r="D82" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E82" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F82" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T14:23:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 14:41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -3004,53 +2989,56 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-31T18:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3062,7 +3050,7 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F85" t="str">
         <v>ZONA CENTRO</v>
@@ -3071,73 +3059,76 @@
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D87" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
+      </c>
+      <c r="I87" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>24/07/2026 14:41</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3149,24 +3140,24 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F88" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3178,36 +3169,36 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F90" t="str">
         <v>ZONA CENTRO</v>
@@ -3216,73 +3207,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310789</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>28/07/2026 08:13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3294,65 +3285,65 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J93" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000310697</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F95" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3361,15 +3352,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-22T12:05:15.999Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>27/07/2026 12:11</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
@@ -3381,24 +3372,24 @@
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000310789</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
@@ -3410,24 +3401,24 @@
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>28/07/2026 08:13</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3439,7 +3430,7 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F98" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3448,73 +3439,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J99" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>21/08/2026 16:58</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J100" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311007</v>
+        <v>WO0000000311080</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3526,7 +3517,7 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F101" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3535,15 +3526,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-22T15:44:16.000Z</v>
+        <v>2026-07-23T07:09:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>27/07/2026 15:47</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000311145</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3555,24 +3546,24 @@
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-23T06:11:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000311147</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3584,7 +3575,7 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F103" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3593,56 +3584,56 @@
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-23T07:04:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000311247</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-23T09:42:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>28/07/2026 09:42</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000311264</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F105" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3651,73 +3642,73 @@
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-23T10:27:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>28/07/2026 10:27</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000311266</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F106" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-23T10:29:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>28/07/2026 10:29</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000311055</v>
+        <v>WO0000000311330</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
       </c>
       <c r="C107" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D107" t="str">
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-22T17:40:15.999Z</v>
+        <v>2026-07-23T11:09:15.999Z</v>
       </c>
       <c r="J107" t="str">
-        <v>28/07/2026 09:27</v>
+        <v>28/07/2026 11:09</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000311341</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3729,7 +3720,7 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F108" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3738,131 +3729,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-23T11:35:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>28/07/2026 11:36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000311145</v>
+        <v>WO0000000311358</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-23T06:11:16.000Z</v>
+        <v>2026-07-23T12:22:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>28/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>WO0000000311147</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-      <c r="C110" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E110" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F110" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G110" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H110" s="1" t="d">
-        <v>2026-07-23T07:04:16.000Z</v>
-      </c>
-      <c r="J110" t="str">
-        <v>28/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>WO0000000311247</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E111" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
-      </c>
-      <c r="F111" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G111" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H111" s="1" t="d">
-        <v>2026-07-23T09:42:16.000Z</v>
-      </c>
-      <c r="J111" t="str">
-        <v>28/07/2026 09:42</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>WO0000000311253</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E112" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F112" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
-      </c>
-      <c r="G112" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H112" s="1" t="d">
-        <v>2026-07-23T10:08:16.000Z</v>
-      </c>
-      <c r="J112" t="str">
-        <v>28/07/2026 10:10</v>
+        <v>28/07/2026 12:22</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -660,39 +660,39 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000152674</v>
+        <v>INC000000153092</v>
       </c>
       <c r="B9" t="str">
         <v>No</v>
       </c>
       <c r="C9" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D9" t="str">
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F9" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G9" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-17T09:17:43.000Z</v>
+        <v>2026-07-21T10:16:49.000Z</v>
       </c>
       <c r="I9" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J9" t="str">
-        <v>-</v>
+        <v>23/07/2026 14:28:19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B10" t="str">
         <v>No</v>
@@ -704,19 +704,19 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F10" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G10" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I10" t="str">
-        <v>23/07/2026 16:00:00</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,7 +736,7 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
@@ -745,10 +745,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I11" t="str">
-        <v>29/07/2026 18:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,7 +768,7 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F12" t="str">
         <v>ZONA CENTRO</v>
@@ -777,10 +777,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,135 +788,135 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000153299</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
       </c>
       <c r="C13" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D13" t="str">
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F13" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-22T08:16:41.000Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J13" t="str">
-        <v>23/07/2026 14:16:25</v>
+        <v>-</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153335</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
       </c>
       <c r="C14" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D14" t="str">
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>KAREN JULIETH ALVARADO ALVAREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F14" t="str">
-        <v>SPT CABECERA CENTRO MAYOR</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-21T12:17:03.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I14" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J14" t="str">
-        <v>-</v>
+        <v>23/07/2026 15:04:17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>-</v>
       </c>
       <c r="J15" t="str">
-        <v>-</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153490</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
       <c r="E16" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F16" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T15:48:35.999Z</v>
       </c>
       <c r="I16" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J16" t="str">
-        <v>-</v>
+        <v>24/07/2026 07:48:20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153505</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
@@ -937,62 +937,62 @@
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T08:54:06.000Z</v>
       </c>
       <c r="I17" t="str">
         <v>-</v>
       </c>
       <c r="J17" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>23/07/2026 14:53:50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153538</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T11:59:23.999Z</v>
       </c>
       <c r="I18" t="str">
         <v>-</v>
       </c>
       <c r="J18" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>23/07/2026 18:09:27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153475</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
       </c>
       <c r="C19" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D19" t="str">
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F19" t="str">
         <v>ZONA CENTRO</v>
@@ -1001,18 +1001,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-22T14:37:01.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I19" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J19" t="str">
-        <v>24/07/2026 06:36:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1024,7 +1024,7 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F20" t="str">
         <v>ZONA CENTRO</v>
@@ -1033,18 +1033,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
       </c>
       <c r="J20" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>24/07/2026 07:00:45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153572</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1065,18 +1065,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T16:23:52.000Z</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
       </c>
       <c r="J21" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>24/07/2026 08:23:36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
@@ -1088,7 +1088,7 @@
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F22" t="str">
         <v>ZONA CENTRO</v>
@@ -1097,50 +1097,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>23/07/2026 18:09:27</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153580</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D23" t="str">
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-22T19:53:13.000Z</v>
       </c>
       <c r="I23" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>-</v>
+        <v>24/07/2026 11:52:57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153560</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1152,7 +1152,7 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F24" t="str">
         <v>ZONA CENTRO</v>
@@ -1161,24 +1161,24 @@
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
       </c>
       <c r="J24" t="str">
-        <v>24/07/2026 07:00:45</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153572</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
@@ -1187,120 +1187,120 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>23/07/2026 14:57:27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153579</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F26" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T19:01:01.000Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
       </c>
       <c r="I26" t="str">
-        <v>-</v>
+        <v>23/07/2026 21:00:00</v>
       </c>
       <c r="J26" t="str">
-        <v>24/07/2026 11:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153580</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F27" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T19:53:13.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I27" t="str">
-        <v>-</v>
+        <v>23/07/2026 19:00:00</v>
       </c>
       <c r="J27" t="str">
-        <v>24/07/2026 11:52:57</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153586</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F28" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-23T06:32:38.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I28" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J28" t="str">
-        <v>24/07/2026 12:32:22</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153589</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,51 +1312,51 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F29" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-23T06:57:43.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>23/07/2026 14:57:27</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153615</v>
       </c>
       <c r="B30" t="str">
-        <v>No</v>
+        <v>Si</v>
       </c>
       <c r="C30" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F30" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-23T06:13:55.000Z</v>
       </c>
       <c r="I30" t="str">
-        <v>23/07/2026 21:00:00</v>
+        <v>-</v>
       </c>
       <c r="J30" t="str">
         <v>-</v>
@@ -1364,71 +1364,71 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153635</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F31" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-23T08:22:59.999Z</v>
       </c>
       <c r="I31" t="str">
-        <v>23/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>-</v>
+        <v>24/07/2026 14:22:44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153647</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F32" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-23T09:47:27.999Z</v>
       </c>
       <c r="I32" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>-</v>
+        <v>23/07/2026 17:47:12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153649</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1440,27 +1440,27 @@
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F33" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T10:03:35.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>23/07/2026 18:03:19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153615</v>
+        <v>INC000000153652</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1481,18 +1481,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-23T06:13:55.000Z</v>
+        <v>2026-07-23T10:10:09.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 14:13:39</v>
+        <v>23/07/2026 18:09:53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153635</v>
+        <v>INC000000153657</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,27 +1504,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-23T08:22:59.999Z</v>
+        <v>2026-07-23T10:35:40.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>24/07/2026 14:22:44</v>
+        <v>23/07/2026 18:35:24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153647</v>
+        <v>INC000000153658</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,27 +1536,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F36" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T09:47:27.999Z</v>
+        <v>2026-07-23T10:24:06.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>23/07/2026 17:47:12</v>
+        <v>24/07/2026 16:23:51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153648</v>
+        <v>INC000000153661</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,27 +1568,27 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T10:02:06.000Z</v>
+        <v>2026-07-23T10:52:03.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>23/07/2026 18:01:50</v>
+        <v>23/07/2026 18:51:47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153649</v>
+        <v>INC000000153669</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,27 +1600,27 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-23T10:03:35.000Z</v>
+        <v>2026-07-23T11:30:05.999Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>23/07/2026 18:03:19</v>
+        <v>23/07/2026 19:29:50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153650</v>
+        <v>INC000000153676</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,27 +1632,27 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T10:04:28.000Z</v>
+        <v>2026-07-23T12:13:53.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 18:04:12</v>
+        <v>23/07/2026 20:13:37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153652</v>
+        <v>INC000000153677</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1664,27 +1664,27 @@
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T10:10:09.000Z</v>
+        <v>2026-07-23T12:19:22.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 18:09:53</v>
+        <v>23/07/2026 20:19:06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153657</v>
+        <v>INC000000153679</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1695,28 +1695,25 @@
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
-      <c r="E41" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
-      </c>
       <c r="F41" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-23T10:35:40.000Z</v>
+        <v>2026-07-23T12:42:49.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>23/07/2026 18:35:24</v>
+        <v>23/07/2026 20:42:33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153658</v>
+        <v>INC000000153684</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
@@ -1728,59 +1725,59 @@
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F42" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-23T10:24:06.999Z</v>
+        <v>2026-07-23T12:52:08.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>24/07/2026 16:23:51</v>
+        <v>23/07/2026 20:51:52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153661</v>
+        <v>INC000000153708</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-23T10:52:03.000Z</v>
+        <v>2026-07-23T08:41:34.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>23/07/2026 18:51:47</v>
+        <v>24/07/2026 14:41:18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153667</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,27 +1789,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-23T11:32:49.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>24/07/2026 17:32:33</v>
+        <v>23/07/2026 17:59:51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153669</v>
+        <v>INC000000153733</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,91 +1821,91 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T11:30:05.999Z</v>
+        <v>2026-07-23T10:30:57.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>23/07/2026 19:29:50</v>
+        <v>24/07/2026 16:30:41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153672</v>
+        <v>INC000000153738</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
       </c>
       <c r="C46" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D46" t="str">
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T11:45:48.999Z</v>
+        <v>2026-07-23T11:13:56.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>23/07/2026 19:45:33</v>
+        <v>24/07/2026 17:13:40</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153673</v>
+        <v>INC000000153741</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T11:57:31.000Z</v>
+        <v>2026-07-23T11:24:06.999Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>23/07/2026 19:57:15</v>
+        <v>24/07/2026 17:23:51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153677</v>
+        <v>INC000000153746</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,7 +1917,7 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F48" t="str">
         <v>SPT ZONA CENTRO</v>
@@ -1929,18 +1926,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-23T12:19:22.000Z</v>
+        <v>2026-07-23T11:45:11.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 20:19:06</v>
+        <v>23/07/2026 19:44:55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153708</v>
+        <v>INC000000153748</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1952,7 +1949,7 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F49" t="str">
         <v>ZONA CENTRO</v>
@@ -1961,18 +1958,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-23T08:41:34.000Z</v>
+        <v>2026-07-23T11:44:08.000Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>24/07/2026 14:41:18</v>
+        <v>24/07/2026 17:43:52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153727</v>
+        <v>INC000000153751</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
@@ -1984,27 +1981,27 @@
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-23T10:00:07.000Z</v>
+        <v>2026-07-23T12:20:01.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>23/07/2026 17:59:51</v>
+        <v>24/07/2026 18:19:45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153730</v>
+        <v>INC000000153756</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,27 +2013,27 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-23T10:06:13.999Z</v>
+        <v>2026-07-23T12:00:45.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>23/07/2026 18:05:58</v>
+        <v>23/07/2026 20:00:29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153733</v>
+        <v>INC000000153767</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,27 +2045,27 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-23T10:30:57.000Z</v>
+        <v>2026-07-23T12:53:01.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>24/07/2026 16:30:41</v>
+        <v>23/07/2026 20:52:45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153738</v>
+        <v>INC000000153769</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
@@ -2083,24 +2080,24 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-23T11:13:56.000Z</v>
+        <v>2026-07-23T12:56:52.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>24/07/2026 17:13:40</v>
+        <v>23/07/2026 20:56:36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153741</v>
+        <v>INC000000153770</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2112,27 +2109,27 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F54" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-23T11:24:06.999Z</v>
+        <v>2026-07-23T12:59:05.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>24/07/2026 17:23:51</v>
+        <v>23/07/2026 20:58:49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153746</v>
+        <v>INC000000153775</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,155 +2141,149 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-23T11:45:11.000Z</v>
+        <v>2026-07-23T13:56:57.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>23/07/2026 19:44:55</v>
+        <v>24/07/2026 19:56:41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153749</v>
+        <v>WO0000000305248</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D56" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E56" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F56" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-23T11:44:11.000Z</v>
-      </c>
-      <c r="I56" t="str">
-        <v>-</v>
+        <v>2026-07-15T11:49:16.000Z</v>
+      </c>
+      <c r="I56" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>23/07/2026 19:43:55</v>
+        <v>22/07/2026 15:49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153751</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D57" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E57" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G57" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-23T12:20:01.000Z</v>
-      </c>
-      <c r="I57" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I57" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 20:19:45</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153759</v>
+        <v>WO0000000305285</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
-        <v>Baja</v>
+        <v>Media</v>
       </c>
       <c r="E58" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-23T12:05:41.000Z</v>
-      </c>
-      <c r="I58" t="str">
-        <v>-</v>
+        <v>2026-07-22T15:19:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>24/07/2026 18:05:25</v>
+        <v>27/07/2026 09:14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G59" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I59" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000305625</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2301,59 +2292,59 @@
         <v>Pendiente</v>
       </c>
       <c r="D60" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G60" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-08T10:09:16.000Z</v>
       </c>
       <c r="I60" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-23T19:00:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>21/07/2026 08:30</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000305285</v>
+        <v>WO0000000307105</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JEFFERSON ESCOBAR ALDANA</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G61" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-11T15:38:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>27/07/2026 09:14</v>
+        <v>13/08/2026 08:00</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
@@ -2368,53 +2359,50 @@
         <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000305566</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G63" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-08T11:28:16.000Z</v>
-      </c>
-      <c r="I63" s="1" t="d">
-        <v>2026-07-23T17:00:16.000Z</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>17/07/2026 13:49</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2426,283 +2414,277 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I65" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G66" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I66" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I67" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G68" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I68" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E69" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I69" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000308443</v>
-      </c>
-      <c r="B70" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F70" t="str">
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G70" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I70" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>-</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000308723</v>
-      </c>
-      <c r="B71" t="str">
-        <v>No</v>
+        <v>WO0000000309319</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G71" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-22T10:46:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>-</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-23T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D73" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F73" t="str">
         <v>ZONA CENTRO</v>
@@ -2711,192 +2693,198 @@
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J73" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000310028</v>
+      </c>
+      <c r="B74" t="str">
+        <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-21T09:40:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>-</v>
+        <v>24/07/2026 09:40</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000309319</v>
+        <v>WO0000000310030</v>
+      </c>
+      <c r="B75" t="str">
+        <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-22T10:46:16.000Z</v>
+        <v>2026-07-21T09:41:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>-</v>
+        <v>24/07/2026 09:41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000310328</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F76" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G76" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I76" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-21T14:08:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>23/07/2026 16:08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F77" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-31T18:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000310060</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
@@ -2911,15 +2899,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T10:46:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
+      </c>
+      <c r="I80" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>20/08/2026 10:46</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310111</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
@@ -2931,24 +2922,24 @@
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-21T10:05:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>24/07/2026 10:05</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310240</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2957,10 +2948,10 @@
         <v>En curso</v>
       </c>
       <c r="D82" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F82" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2969,15 +2960,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-21T14:23:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>24/07/2026 14:41</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2989,7 +2980,7 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F83" t="str">
         <v>ZONA CENTRO</v>
@@ -2998,137 +2989,131 @@
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000310789</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="I84" s="1" t="d">
-        <v>2026-07-31T18:00:16.000Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>28/07/2026 08:13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000310805</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F85" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-22T12:04:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>27/07/2026 12:06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F86" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J86" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
-      </c>
-      <c r="I87" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3140,24 +3125,24 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3169,7 +3154,7 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F89" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3178,15 +3163,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3198,24 +3183,24 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000310789</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3227,53 +3212,53 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>28/07/2026 08:13</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F92" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J92" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>21/08/2026 16:58</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3285,53 +3270,53 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J93" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000311080</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
       </c>
       <c r="C94" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
       </c>
       <c r="E94" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F94" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G94" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-23T07:09:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000311147</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3343,7 +3328,7 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F95" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3352,56 +3337,56 @@
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-23T07:04:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000311247</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-23T09:42:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>28/07/2026 09:42</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000311264</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F97" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3410,15 +3395,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-23T10:27:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>28/07/2026 10:27</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000311266</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3430,24 +3415,24 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-23T10:29:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>28/07/2026 10:29</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000311358</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3459,7 +3444,7 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F99" t="str">
         <v>ZONA CENTRO</v>
@@ -3468,15 +3453,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-23T12:22:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>28/07/2026 12:22</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311055</v>
+        <v>WO0000000311385</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3488,24 +3473,24 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-22T17:40:15.999Z</v>
+        <v>2026-07-23T13:45:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>28/07/2026 09:27</v>
+        <v>28/07/2026 13:47</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000311387</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3526,15 +3511,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-23T13:53:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>28/07/2026 13:55</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311145</v>
+        <v>WO0000000311444</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3549,224 +3534,21 @@
         <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-23T06:11:16.000Z</v>
+        <v>2026-07-23T13:49:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>28/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>WO0000000311147</v>
-      </c>
-      <c r="B103" t="str">
-        <v>No</v>
-      </c>
-      <c r="C103" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D103" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E103" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F103" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G103" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H103" s="1" t="d">
-        <v>2026-07-23T07:04:16.000Z</v>
-      </c>
-      <c r="J103" t="str">
-        <v>28/07/2026 08:00</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>WO0000000311247</v>
-      </c>
-      <c r="B104" t="str">
-        <v>No</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D104" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E104" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
-      </c>
-      <c r="F104" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G104" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H104" s="1" t="d">
-        <v>2026-07-23T09:42:16.000Z</v>
-      </c>
-      <c r="J104" t="str">
-        <v>28/07/2026 09:42</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>WO0000000311264</v>
-      </c>
-      <c r="B105" t="str">
-        <v>No</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E105" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
-      </c>
-      <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G105" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H105" s="1" t="d">
-        <v>2026-07-23T10:27:16.000Z</v>
-      </c>
-      <c r="J105" t="str">
-        <v>28/07/2026 10:27</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>WO0000000311266</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No</v>
-      </c>
-      <c r="C106" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D106" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E106" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
-      </c>
-      <c r="F106" t="str">
-        <v>SPT CABECERA KENNEDY</v>
-      </c>
-      <c r="G106" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H106" s="1" t="d">
-        <v>2026-07-23T10:29:16.000Z</v>
-      </c>
-      <c r="J106" t="str">
-        <v>28/07/2026 10:29</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>WO0000000311330</v>
-      </c>
-      <c r="B107" t="str">
-        <v>No</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E107" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
-      </c>
-      <c r="F107" t="str">
-        <v>SPT CABECERA SUBA</v>
-      </c>
-      <c r="G107" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H107" s="1" t="d">
-        <v>2026-07-23T11:09:15.999Z</v>
-      </c>
-      <c r="J107" t="str">
-        <v>28/07/2026 11:09</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>WO0000000311341</v>
-      </c>
-      <c r="B108" t="str">
-        <v>No</v>
-      </c>
-      <c r="C108" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D108" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E108" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
-      </c>
-      <c r="F108" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G108" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H108" s="1" t="d">
-        <v>2026-07-23T11:35:16.000Z</v>
-      </c>
-      <c r="J108" t="str">
-        <v>28/07/2026 11:36</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>WO0000000311358</v>
-      </c>
-      <c r="B109" t="str">
-        <v>No</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Asignado</v>
-      </c>
-      <c r="D109" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E109" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
-      </c>
-      <c r="F109" t="str">
-        <v>ZONA CENTRO</v>
-      </c>
-      <c r="G109" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H109" s="1" t="d">
-        <v>2026-07-23T12:22:16.000Z</v>
-      </c>
-      <c r="J109" t="str">
-        <v>28/07/2026 12:22</v>
+        <v>28/07/2026 13:50</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J114"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -620,7 +620,7 @@
         <v>2026-07-15T09:19:18.000Z</v>
       </c>
       <c r="I7" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>24/07/2026 18:00:00</v>
       </c>
       <c r="J7" t="str">
         <v>-</v>
@@ -660,39 +660,39 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>INC000000153092</v>
+        <v>INC000000153267</v>
       </c>
       <c r="B9" t="str">
         <v>No</v>
       </c>
       <c r="C9" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D9" t="str">
         <v>Baja</v>
       </c>
       <c r="E9" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F9" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G9" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H9" s="1" t="d">
-        <v>2026-07-21T10:16:49.000Z</v>
+        <v>2026-07-21T17:05:00.000Z</v>
       </c>
       <c r="I9" t="str">
-        <v>-</v>
+        <v>29/07/2026 18:00:00</v>
       </c>
       <c r="J9" t="str">
-        <v>23/07/2026 14:28:19</v>
+        <v>-</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INC000000153267</v>
+        <v>INC000000153271</v>
       </c>
       <c r="B10" t="str">
         <v>No</v>
@@ -704,7 +704,7 @@
         <v>Baja</v>
       </c>
       <c r="E10" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F10" t="str">
         <v>ZONA CENTRO</v>
@@ -713,10 +713,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H10" s="1" t="d">
-        <v>2026-07-21T17:05:00.000Z</v>
+        <v>2026-07-21T19:01:09.000Z</v>
       </c>
       <c r="I10" t="str">
-        <v>29/07/2026 18:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J10" t="str">
         <v>-</v>
@@ -724,7 +724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INC000000153271</v>
+        <v>INC000000153344</v>
       </c>
       <c r="B11" t="str">
         <v>No</v>
@@ -736,7 +736,7 @@
         <v>Baja</v>
       </c>
       <c r="E11" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F11" t="str">
         <v>ZONA CENTRO</v>
@@ -745,10 +745,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H11" s="1" t="d">
-        <v>2026-07-21T19:01:09.000Z</v>
+        <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I11" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>23/07/2026 18:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000153344</v>
+        <v>INC000000153431</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F12" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-21T12:40:21.999Z</v>
+        <v>2026-07-22T08:46:43.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>23/07/2026 17:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,19 +800,19 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F13" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G13" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I13" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>24/07/2026 21:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153442</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,59 +832,59 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T10:41:27.000Z</v>
       </c>
       <c r="I14" t="str">
         <v>-</v>
       </c>
       <c r="J14" t="str">
-        <v>23/07/2026 15:04:17</v>
+        <v>23/07/2026 16:41:11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F15" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G15" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I15" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J15" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>-</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153490</v>
+        <v>INC000000153560</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
@@ -895,40 +895,37 @@
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
-      <c r="E16" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
-      </c>
       <c r="F16" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA LAGOMAR</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-22T15:48:35.999Z</v>
+        <v>2026-07-22T15:01:01.000Z</v>
       </c>
       <c r="I16" t="str">
         <v>-</v>
       </c>
       <c r="J16" t="str">
-        <v>24/07/2026 07:48:20</v>
+        <v>24/07/2026 07:00:45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153505</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F17" t="str">
         <v>ZONA CENTRO</v>
@@ -937,18 +934,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-22T08:54:06.000Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I17" t="str">
         <v>-</v>
       </c>
       <c r="J17" t="str">
-        <v>23/07/2026 14:53:50</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153538</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -960,7 +957,7 @@
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F18" t="str">
         <v>ZONA CENTRO</v>
@@ -969,18 +966,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-22T11:59:23.999Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I18" t="str">
         <v>-</v>
       </c>
       <c r="J18" t="str">
-        <v>23/07/2026 18:09:27</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -992,19 +989,19 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F19" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I19" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>28/07/2026 21:00:00</v>
       </c>
       <c r="J19" t="str">
         <v>-</v>
@@ -1012,103 +1009,103 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153560</v>
+        <v>INC000000153603</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D20" t="str">
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F20" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
+        <v>2026-07-22T17:28:47.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>-</v>
+        <v>23/07/2026 21:00:00</v>
       </c>
       <c r="J20" t="str">
-        <v>24/07/2026 07:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153572</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D21" t="str">
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F21" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T16:23:52.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I21" t="str">
-        <v>-</v>
+        <v>23/07/2026 19:00:00</v>
       </c>
       <c r="J21" t="str">
-        <v>24/07/2026 08:23:36</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153579</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F22" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T19:01:01.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I22" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:00:00</v>
       </c>
       <c r="J22" t="str">
-        <v>24/07/2026 11:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153580</v>
+        <v>INC000000153609</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1120,91 +1117,91 @@
         <v>Baja</v>
       </c>
       <c r="E23" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F23" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G23" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T19:53:13.000Z</v>
+        <v>2026-07-22T19:59:33.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>24/07/2026 11:52:57</v>
+        <v>24/07/2026 11:59:17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153586</v>
+        <v>INC000000153647</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D24" t="str">
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F24" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-23T06:32:38.000Z</v>
+        <v>2026-07-23T09:47:27.999Z</v>
       </c>
       <c r="I24" t="str">
-        <v>-</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J24" t="str">
-        <v>24/07/2026 12:32:22</v>
+        <v>-</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153589</v>
+        <v>INC000000153649</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F25" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-23T06:57:43.000Z</v>
+        <v>2026-07-23T10:03:35.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>-</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J25" t="str">
-        <v>23/07/2026 14:57:27</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153652</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1216,19 +1213,19 @@
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F26" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-23T10:10:09.000Z</v>
       </c>
       <c r="I26" t="str">
-        <v>23/07/2026 21:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J26" t="str">
         <v>-</v>
@@ -1236,51 +1233,51 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153657</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D27" t="str">
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F27" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-23T10:35:40.000Z</v>
       </c>
       <c r="I27" t="str">
-        <v>23/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:35:24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153661</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F28" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -1289,18 +1286,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-23T10:52:03.000Z</v>
       </c>
       <c r="I28" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>-</v>
+        <v>23/07/2026 18:51:47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153677</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1321,21 +1318,21 @@
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T12:19:22.000Z</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
       </c>
       <c r="J29" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>24/07/2026 18:19:06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153615</v>
+        <v>INC000000153679</v>
       </c>
       <c r="B30" t="str">
-        <v>Si</v>
+        <v>No</v>
       </c>
       <c r="C30" t="str">
         <v>Asignado</v>
@@ -1344,27 +1341,27 @@
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F30" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA ORIENTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-23T06:13:55.000Z</v>
+        <v>2026-07-23T12:42:49.000Z</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>-</v>
+        <v>23/07/2026 20:42:33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153635</v>
+        <v>INC000000153684</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1376,27 +1373,27 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-23T08:22:59.999Z</v>
+        <v>2026-07-23T12:52:08.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>24/07/2026 14:22:44</v>
+        <v>23/07/2026 20:51:52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153647</v>
+        <v>INC000000153724</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1408,33 +1405,33 @@
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
       </c>
       <c r="F32" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-23T09:47:27.999Z</v>
+        <v>2026-07-23T09:49:33.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>23/07/2026 17:47:12</v>
+        <v>23/07/2026 17:49:17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153649</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
@@ -1449,18 +1446,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-23T10:03:35.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
       </c>
       <c r="I33" t="str">
-        <v>-</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J33" t="str">
-        <v>23/07/2026 18:03:19</v>
+        <v>-</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153652</v>
+        <v>INC000000153733</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1472,27 +1469,27 @@
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F34" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G34" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-23T10:10:09.000Z</v>
+        <v>2026-07-23T10:30:57.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>23/07/2026 18:09:53</v>
+        <v>24/07/2026 16:30:41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153657</v>
+        <v>INC000000153738</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1504,27 +1501,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F35" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-23T10:35:40.000Z</v>
+        <v>2026-07-23T11:13:56.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>23/07/2026 18:35:24</v>
+        <v>24/07/2026 17:13:40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153658</v>
+        <v>INC000000153741</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1536,27 +1533,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T10:24:06.999Z</v>
+        <v>2026-07-23T11:24:06.999Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>24/07/2026 16:23:51</v>
+        <v>24/07/2026 17:23:51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153661</v>
+        <v>INC000000153748</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,27 +1565,27 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F37" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T10:52:03.000Z</v>
+        <v>2026-07-23T11:44:08.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>23/07/2026 18:51:47</v>
+        <v>24/07/2026 17:43:52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153669</v>
+        <v>INC000000153751</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1600,27 +1597,27 @@
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F38" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-23T11:30:05.999Z</v>
+        <v>2026-07-23T12:20:01.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>23/07/2026 19:29:50</v>
+        <v>24/07/2026 18:19:45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153676</v>
+        <v>INC000000153756</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1632,27 +1629,27 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T12:13:53.000Z</v>
+        <v>2026-07-23T12:00:45.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 20:13:37</v>
+        <v>23/07/2026 20:00:29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153677</v>
+        <v>INC000000153767</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1664,7 +1661,7 @@
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F40" t="str">
         <v>SPT ZONA CENTRO</v>
@@ -1673,18 +1670,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T12:19:22.000Z</v>
+        <v>2026-07-23T12:53:01.000Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 20:19:06</v>
+        <v>23/07/2026 20:52:45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153679</v>
+        <v>INC000000153769</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1695,89 +1692,92 @@
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
+      <c r="E41" t="str">
+        <v>NICK STEVE TRIANA LOPEZ</v>
+      </c>
       <c r="F41" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-23T12:42:49.000Z</v>
+        <v>2026-07-23T12:56:52.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>23/07/2026 20:42:33</v>
+        <v>23/07/2026 20:56:36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153684</v>
+        <v>INC000000153770</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-23T12:52:08.000Z</v>
+        <v>2026-07-23T12:59:05.000Z</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>23/07/2026 20:51:52</v>
+        <v>23/07/2026 20:58:49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153708</v>
+        <v>INC000000153775</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-23T08:41:34.000Z</v>
+        <v>2026-07-23T13:56:57.000Z</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>24/07/2026 14:41:18</v>
+        <v>24/07/2026 19:56:41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153727</v>
+        <v>INC000000153777</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1789,27 +1789,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-23T10:00:07.000Z</v>
+        <v>2026-07-23T14:12:45.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>23/07/2026 17:59:51</v>
+        <v>24/07/2026 07:12:29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153733</v>
+        <v>INC000000153781</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1821,27 +1821,27 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F45" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T10:30:57.000Z</v>
+        <v>2026-07-23T14:52:02.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>24/07/2026 16:30:41</v>
+        <v>24/07/2026 07:51:46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153738</v>
+        <v>INC000000153785</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1853,27 +1853,27 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T11:13:56.000Z</v>
+        <v>2026-07-23T15:07:27.999Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>24/07/2026 17:13:40</v>
+        <v>25/07/2026 07:07:12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153741</v>
+        <v>INC000000153789</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1885,359 +1885,341 @@
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F47" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T11:24:06.999Z</v>
+        <v>2026-07-23T15:37:32.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>24/07/2026 17:23:51</v>
+        <v>24/07/2026 08:37:16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153746</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D48" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E48" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G48" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-23T11:45:11.000Z</v>
-      </c>
-      <c r="I48" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I48" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 19:44:55</v>
+        <v>23/07/2026 13:33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153748</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
       </c>
       <c r="C49" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D49" t="str">
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G49" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-23T11:44:08.000Z</v>
-      </c>
-      <c r="I49" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J49" t="str">
-        <v>24/07/2026 17:43:52</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153751</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F50" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G50" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-23T12:20:01.000Z</v>
-      </c>
-      <c r="I50" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J50" t="str">
-        <v>24/07/2026 18:19:45</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153756</v>
+        <v>WO0000000307703</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
       </c>
       <c r="C51" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D51" t="str">
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G51" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-23T12:00:45.000Z</v>
-      </c>
-      <c r="I51" t="str">
-        <v>-</v>
+        <v>2026-07-14T14:27:16.000Z</v>
       </c>
       <c r="J51" t="str">
-        <v>23/07/2026 20:00:29</v>
+        <v>24/07/2026 16:18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153767</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G52" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-23T12:53:01.000Z</v>
-      </c>
-      <c r="I52" t="str">
-        <v>-</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I52" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J52" t="str">
-        <v>23/07/2026 20:52:45</v>
+        <v>21/07/2026 09:38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153769</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G53" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-23T12:56:52.000Z</v>
-      </c>
-      <c r="I53" t="str">
-        <v>-</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I53" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J53" t="str">
-        <v>23/07/2026 20:56:36</v>
+        <v>17/07/2026 14:53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153770</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G54" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-23T12:59:05.000Z</v>
-      </c>
-      <c r="I54" t="str">
-        <v>-</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I54" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J54" t="str">
-        <v>23/07/2026 20:58:49</v>
+        <v>21/07/2026 16:31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153775</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G55" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-23T13:56:57.000Z</v>
-      </c>
-      <c r="I55" t="str">
-        <v>-</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I55" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J55" t="str">
-        <v>24/07/2026 19:56:41</v>
+        <v>21/07/2026 12:49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000305248</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G56" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-15T11:49:16.000Z</v>
-      </c>
-      <c r="I56" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J56" t="str">
-        <v>22/07/2026 15:49</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
       </c>
       <c r="C57" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D57" t="str">
         <v>Alta</v>
       </c>
       <c r="E57" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F57" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G57" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I57" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J57" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000305285</v>
-      </c>
-      <c r="B58" t="str">
-        <v>No</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="C58" t="str">
         <v>Asignado</v>
       </c>
       <c r="D58" t="str">
-        <v>Media</v>
+        <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F58" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2246,163 +2228,166 @@
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-22T15:19:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>27/07/2026 09:14</v>
+        <v>-</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G59" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I59" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>23/07/2026 10:48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000305625</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-08T10:09:16.000Z</v>
-      </c>
-      <c r="I60" s="1" t="d">
-        <v>2026-07-23T19:00:16.000Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J60" t="str">
-        <v>21/07/2026 08:30</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000307105</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>JEFFERSON ESCOBAR ALDANA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-11T15:38:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
+      </c>
+      <c r="I61" s="1" t="d">
+        <v>2026-07-31T18:00:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>13/08/2026 08:00</v>
+        <v>24/07/2026 14:55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F62" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G62" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 08:38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000307703</v>
+        <v>WO0000000310425</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G63" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-21T17:12:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>27/07/2026 08:00</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2420,27 +2405,27 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
         <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>24/07/2026 10:00</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000310577</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
@@ -2449,30 +2434,27 @@
         <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G65" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I65" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-22T08:38:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>27/07/2026 08:40</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000308443</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D66" t="str">
         <v>Baja</v>
@@ -2484,53 +2466,47 @@
         <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G66" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I66" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000308723</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F67" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G67" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I67" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000309139</v>
+        <v>WO0000000310789</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2542,53 +2518,56 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G68" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>28/07/2026 08:13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000309315</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D69" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J69" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000310974</v>
+      </c>
+      <c r="B70" t="str">
+        <v>No</v>
       </c>
       <c r="C70" t="str">
         <v>Asignado</v>
@@ -2597,33 +2576,36 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>-</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000309319</v>
+        <v>WO0000000311014</v>
+      </c>
+      <c r="B71" t="str">
+        <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F71" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2632,47 +2614,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-22T10:46:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>-</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F72" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G72" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I72" s="1" t="d">
-        <v>2026-07-23T18:00:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2684,24 +2663,24 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G73" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310028</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2713,24 +2692,24 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-21T09:40:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>24/07/2026 09:40</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310030</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2742,24 +2721,24 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>CARLOS IVAN CUCANCHON CARRILLO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-21T09:41:16.000Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J75" t="str">
-        <v>24/07/2026 09:41</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310328</v>
+        <v>WO0000000311080</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2771,68 +2750,65 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G76" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-21T14:08:16.000Z</v>
+        <v>2026-07-23T07:09:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>23/07/2026 16:08</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000311147</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="I77" s="1" t="d">
-        <v>2026-07-31T18:00:16.000Z</v>
+        <v>2026-07-23T07:04:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>28/07/2026 08:00</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000311247</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F78" t="str">
         <v>ZONA CENTRO</v>
@@ -2841,15 +2817,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-23T09:42:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>28/07/2026 09:42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000311264</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
@@ -2861,85 +2837,82 @@
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F79" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G79" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-23T10:27:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>28/07/2026 10:27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000311266</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D80" t="str">
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F80" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
-      </c>
-      <c r="I80" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-23T10:29:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>28/07/2026 10:29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000311358</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F81" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-23T12:22:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>28/07/2026 12:22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000311385</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
@@ -2951,7 +2924,7 @@
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F82" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2960,15 +2933,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-23T13:45:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>28/07/2026 13:47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000311387</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2980,24 +2953,24 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F83" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-23T13:53:16.000Z</v>
       </c>
       <c r="J83" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>28/07/2026 13:55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000310789</v>
+        <v>WO0000000311397</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -3009,24 +2982,24 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
+        <v>2026-07-23T14:23:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>28/07/2026 08:13</v>
+        <v>28/07/2026 14:25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000310805</v>
+        <v>WO0000000311400</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
@@ -3038,7 +3011,7 @@
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F85" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3047,15 +3020,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-22T12:04:16.000Z</v>
+        <v>2026-07-23T14:26:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>27/07/2026 12:06</v>
+        <v>28/07/2026 14:28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000311444</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3067,7 +3040,7 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F86" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3076,15 +3049,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-23T13:49:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>28/07/2026 13:50</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000311457</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3096,24 +3069,24 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-23T14:35:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>28/07/2026 14:42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000311459</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3125,7 +3098,7 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F88" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3134,15 +3107,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-23T14:43:15.999Z</v>
       </c>
       <c r="J88" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>28/07/2026 14:45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000311464</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
@@ -3154,7 +3127,7 @@
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F89" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3163,15 +3136,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-23T14:47:15.999Z</v>
       </c>
       <c r="J89" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>28/07/2026 14:50</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000311469</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3183,7 +3156,7 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F90" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3192,15 +3165,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-23T15:02:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>28/07/2026 15:05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000311471</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
@@ -3212,7 +3185,7 @@
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F91" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3221,15 +3194,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-23T15:06:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>28/07/2026 15:08</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000311476</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3250,15 +3223,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-23T15:24:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>21/08/2026 16:58</v>
+        <v>24/08/2026 15:24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000311055</v>
+        <v>WO0000000311478</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
@@ -3270,24 +3243,24 @@
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-22T17:40:15.999Z</v>
+        <v>2026-07-23T15:16:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>28/07/2026 09:27</v>
+        <v>28/07/2026 15:18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000311480</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3308,15 +3281,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-23T15:19:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>28/07/2026 15:21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000311147</v>
+        <v>WO0000000311485</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3337,56 +3310,56 @@
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-23T07:04:16.000Z</v>
+        <v>2026-07-23T15:26:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>28/07/2026 15:28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000311247</v>
+        <v>WO0000000311492</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-23T09:42:16.000Z</v>
+        <v>2026-07-23T15:33:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>28/07/2026 09:42</v>
+        <v>28/07/2026 15:35</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000311264</v>
+        <v>WO0000000311493</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F97" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3395,15 +3368,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-23T10:27:16.000Z</v>
+        <v>2026-07-23T15:36:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>28/07/2026 10:27</v>
+        <v>28/07/2026 15:38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000311266</v>
+        <v>WO0000000311498</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3415,53 +3388,53 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-23T10:29:16.000Z</v>
+        <v>2026-07-23T15:41:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>28/07/2026 10:29</v>
+        <v>28/07/2026 15:42</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311358</v>
+        <v>WO0000000311499</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
       </c>
       <c r="C99" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D99" t="str">
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F99" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-23T12:22:16.000Z</v>
+        <v>2026-07-23T15:43:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>28/07/2026 12:22</v>
+        <v>28/07/2026 15:45</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311385</v>
+        <v>WO0000000311502</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3482,15 +3455,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-23T13:45:16.000Z</v>
+        <v>2026-07-23T14:29:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>28/07/2026 13:47</v>
+        <v>28/07/2026 14:32</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311387</v>
+        <v>WO0000000311505</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3511,15 +3484,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-23T13:53:16.000Z</v>
+        <v>2026-07-23T14:35:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>28/07/2026 13:55</v>
+        <v>28/07/2026 14:37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311444</v>
+        <v>WO0000000311507</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3540,15 +3513,363 @@
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-23T13:49:16.000Z</v>
+        <v>2026-07-23T14:40:15.999Z</v>
       </c>
       <c r="J102" t="str">
-        <v>28/07/2026 13:50</v>
+        <v>28/07/2026 14:41</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>WO0000000311514</v>
+      </c>
+      <c r="B103" t="str">
+        <v>No</v>
+      </c>
+      <c r="C103" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E103" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F103" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G103" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H103" s="1" t="d">
+        <v>2026-07-23T14:54:15.999Z</v>
+      </c>
+      <c r="J103" t="str">
+        <v>28/07/2026 14:56</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>WO0000000311518</v>
+      </c>
+      <c r="B104" t="str">
+        <v>No</v>
+      </c>
+      <c r="C104" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E104" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F104" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G104" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H104" s="1" t="d">
+        <v>2026-07-23T14:57:16.000Z</v>
+      </c>
+      <c r="J104" t="str">
+        <v>28/07/2026 14:58</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>WO0000000311520</v>
+      </c>
+      <c r="B105" t="str">
+        <v>No</v>
+      </c>
+      <c r="C105" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E105" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F105" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G105" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H105" s="1" t="d">
+        <v>2026-07-23T14:59:16.000Z</v>
+      </c>
+      <c r="J105" t="str">
+        <v>28/07/2026 15:01</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>WO0000000311525</v>
+      </c>
+      <c r="B106" t="str">
+        <v>No</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E106" t="str">
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+      </c>
+      <c r="F106" t="str">
+        <v>ZONA CENTRO</v>
+      </c>
+      <c r="G106" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H106" s="1" t="d">
+        <v>2026-07-23T15:09:15.999Z</v>
+      </c>
+      <c r="J106" t="str">
+        <v>28/07/2026 15:09</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>WO0000000311526</v>
+      </c>
+      <c r="B107" t="str">
+        <v>No</v>
+      </c>
+      <c r="C107" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E107" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F107" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G107" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H107" s="1" t="d">
+        <v>2026-07-23T15:11:16.000Z</v>
+      </c>
+      <c r="J107" t="str">
+        <v>28/07/2026 15:12</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>WO0000000311528</v>
+      </c>
+      <c r="B108" t="str">
+        <v>No</v>
+      </c>
+      <c r="C108" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E108" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F108" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G108" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H108" s="1" t="d">
+        <v>2026-07-23T15:14:16.000Z</v>
+      </c>
+      <c r="J108" t="str">
+        <v>28/07/2026 15:15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>WO0000000311530</v>
+      </c>
+      <c r="B109" t="str">
+        <v>No</v>
+      </c>
+      <c r="C109" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E109" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F109" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G109" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H109" s="1" t="d">
+        <v>2026-07-23T15:22:16.000Z</v>
+      </c>
+      <c r="J109" t="str">
+        <v>28/07/2026 15:24</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>WO0000000311532</v>
+      </c>
+      <c r="B110" t="str">
+        <v>No</v>
+      </c>
+      <c r="C110" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E110" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F110" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G110" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H110" s="1" t="d">
+        <v>2026-07-23T15:30:16.000Z</v>
+      </c>
+      <c r="J110" t="str">
+        <v>28/07/2026 15:32</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>WO0000000311536</v>
+      </c>
+      <c r="B111" t="str">
+        <v>No</v>
+      </c>
+      <c r="C111" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E111" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F111" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G111" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H111" s="1" t="d">
+        <v>2026-07-23T15:38:16.000Z</v>
+      </c>
+      <c r="J111" t="str">
+        <v>28/07/2026 15:40</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WO0000000311539</v>
+      </c>
+      <c r="B112" t="str">
+        <v>No</v>
+      </c>
+      <c r="C112" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E112" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F112" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G112" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H112" s="1" t="d">
+        <v>2026-07-23T15:46:16.000Z</v>
+      </c>
+      <c r="J112" t="str">
+        <v>28/07/2026 15:48</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>WO0000000311604</v>
+      </c>
+      <c r="B113" t="str">
+        <v>No</v>
+      </c>
+      <c r="C113" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E113" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F113" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G113" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H113" s="1" t="d">
+        <v>2026-07-23T15:49:16.000Z</v>
+      </c>
+      <c r="J113" t="str">
+        <v>28/07/2026 15:50</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>WO0000000311606</v>
+      </c>
+      <c r="B114" t="str">
+        <v>No</v>
+      </c>
+      <c r="C114" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E114" t="str">
+        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+      </c>
+      <c r="F114" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G114" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H114" s="1" t="d">
+        <v>2026-07-23T15:51:16.000Z</v>
+      </c>
+      <c r="J114" t="str">
+        <v>28/07/2026 15:53</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -748,7 +748,7 @@
         <v>2026-07-21T12:40:21.999Z</v>
       </c>
       <c r="I11" t="str">
-        <v>23/07/2026 18:00:00</v>
+        <v>24/07/2026 18:00:00</v>
       </c>
       <c r="J11" t="str">
         <v>-</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>INC000000153431</v>
+        <v>INC000000153433</v>
       </c>
       <c r="B12" t="str">
         <v>No</v>
@@ -768,19 +768,19 @@
         <v>Baja</v>
       </c>
       <c r="E12" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F12" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G12" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H12" s="1" t="d">
-        <v>2026-07-22T08:46:43.000Z</v>
+        <v>2026-07-22T09:04:33.000Z</v>
       </c>
       <c r="I12" t="str">
-        <v>23/07/2026 17:00:00</v>
+        <v>24/07/2026 21:00:00</v>
       </c>
       <c r="J12" t="str">
         <v>-</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>INC000000153433</v>
+        <v>INC000000153548</v>
       </c>
       <c r="B13" t="str">
         <v>No</v>
@@ -800,7 +800,7 @@
         <v>Baja</v>
       </c>
       <c r="E13" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F13" t="str">
         <v>ZONA CENTRO</v>
@@ -809,10 +809,10 @@
         <v>a) 0-4</v>
       </c>
       <c r="H13" s="1" t="d">
-        <v>2026-07-22T09:04:33.000Z</v>
+        <v>2026-07-22T13:10:35.999Z</v>
       </c>
       <c r="I13" t="str">
-        <v>24/07/2026 21:00:00</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J13" t="str">
         <v>-</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>INC000000153442</v>
+        <v>INC000000153579</v>
       </c>
       <c r="B14" t="str">
         <v>No</v>
@@ -832,39 +832,39 @@
         <v>Baja</v>
       </c>
       <c r="E14" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F14" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G14" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H14" s="1" t="d">
-        <v>2026-07-22T10:41:27.000Z</v>
+        <v>2026-07-22T19:01:01.000Z</v>
       </c>
       <c r="I14" t="str">
         <v>-</v>
       </c>
       <c r="J14" t="str">
-        <v>23/07/2026 16:41:11</v>
+        <v>24/07/2026 11:00:45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>INC000000153548</v>
+        <v>INC000000153586</v>
       </c>
       <c r="B15" t="str">
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
       </c>
       <c r="E15" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F15" t="str">
         <v>ZONA CENTRO</v>
@@ -873,111 +873,114 @@
         <v>a) 0-4</v>
       </c>
       <c r="H15" s="1" t="d">
-        <v>2026-07-22T13:10:35.999Z</v>
+        <v>2026-07-23T06:32:38.000Z</v>
       </c>
       <c r="I15" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J15" t="str">
-        <v>-</v>
+        <v>24/07/2026 12:32:22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>INC000000153560</v>
+        <v>INC000000153589</v>
       </c>
       <c r="B16" t="str">
         <v>No</v>
       </c>
       <c r="C16" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D16" t="str">
         <v>Baja</v>
       </c>
+      <c r="E16" t="str">
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+      </c>
       <c r="F16" t="str">
-        <v>ZONA LAGOMAR</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G16" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H16" s="1" t="d">
-        <v>2026-07-22T15:01:01.000Z</v>
+        <v>2026-07-23T06:57:43.000Z</v>
       </c>
       <c r="I16" t="str">
-        <v>-</v>
+        <v>28/07/2026 21:00:00</v>
       </c>
       <c r="J16" t="str">
-        <v>24/07/2026 07:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>INC000000153579</v>
+        <v>INC000000153605</v>
       </c>
       <c r="B17" t="str">
         <v>No</v>
       </c>
       <c r="C17" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D17" t="str">
         <v>Baja</v>
       </c>
       <c r="E17" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F17" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G17" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H17" s="1" t="d">
-        <v>2026-07-22T19:01:01.000Z</v>
+        <v>2026-07-22T17:50:54.000Z</v>
       </c>
       <c r="I17" t="str">
-        <v>-</v>
+        <v>27/07/2026 19:00:00</v>
       </c>
       <c r="J17" t="str">
-        <v>24/07/2026 11:00:45</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>INC000000153586</v>
+        <v>INC000000153607</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
       </c>
       <c r="C18" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D18" t="str">
         <v>Baja</v>
       </c>
       <c r="E18" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F18" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G18" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H18" s="1" t="d">
-        <v>2026-07-23T06:32:38.000Z</v>
+        <v>2026-07-22T18:19:00.000Z</v>
       </c>
       <c r="I18" t="str">
-        <v>-</v>
+        <v>24/07/2026 20:00:00</v>
       </c>
       <c r="J18" t="str">
-        <v>24/07/2026 12:32:22</v>
+        <v>-</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>INC000000153589</v>
+        <v>INC000000153647</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -989,19 +992,19 @@
         <v>Baja</v>
       </c>
       <c r="E19" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F19" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G19" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H19" s="1" t="d">
-        <v>2026-07-23T06:57:43.000Z</v>
+        <v>2026-07-23T09:47:27.999Z</v>
       </c>
       <c r="I19" t="str">
-        <v>28/07/2026 21:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J19" t="str">
         <v>-</v>
@@ -1009,7 +1012,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INC000000153603</v>
+        <v>INC000000153649</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -1021,19 +1024,19 @@
         <v>Baja</v>
       </c>
       <c r="E20" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F20" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G20" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H20" s="1" t="d">
-        <v>2026-07-22T17:28:47.000Z</v>
+        <v>2026-07-23T10:03:35.000Z</v>
       </c>
       <c r="I20" t="str">
-        <v>23/07/2026 21:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J20" t="str">
         <v>-</v>
@@ -1041,7 +1044,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INC000000153605</v>
+        <v>INC000000153652</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -1053,19 +1056,19 @@
         <v>Baja</v>
       </c>
       <c r="E21" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F21" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G21" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H21" s="1" t="d">
-        <v>2026-07-22T17:50:54.000Z</v>
+        <v>2026-07-23T10:10:09.000Z</v>
       </c>
       <c r="I21" t="str">
-        <v>23/07/2026 19:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J21" t="str">
         <v>-</v>
@@ -1073,39 +1076,39 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>INC000000153607</v>
+        <v>INC000000153657</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
       </c>
       <c r="E22" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F22" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G22" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H22" s="1" t="d">
-        <v>2026-07-22T18:19:00.000Z</v>
+        <v>2026-07-23T10:35:40.000Z</v>
       </c>
       <c r="I22" t="str">
-        <v>23/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J22" t="str">
-        <v>-</v>
+        <v>24/07/2026 16:35:24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>INC000000153609</v>
+        <v>INC000000153677</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -1126,18 +1129,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H23" s="1" t="d">
-        <v>2026-07-22T19:59:33.000Z</v>
+        <v>2026-07-23T12:19:22.000Z</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
       </c>
       <c r="J23" t="str">
-        <v>24/07/2026 11:59:17</v>
+        <v>24/07/2026 18:19:06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>INC000000153647</v>
+        <v>INC000000153679</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
@@ -1149,16 +1152,16 @@
         <v>Baja</v>
       </c>
       <c r="E24" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F24" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G24" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H24" s="1" t="d">
-        <v>2026-07-23T09:47:27.999Z</v>
+        <v>2026-07-23T12:42:49.000Z</v>
       </c>
       <c r="I24" t="str">
         <v>24/07/2026 17:00:00</v>
@@ -1169,39 +1172,39 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153649</v>
+        <v>INC000000153684</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F25" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-23T10:03:35.000Z</v>
+        <v>2026-07-23T12:52:08.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>24/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J25" t="str">
-        <v>-</v>
+        <v>24/07/2026 18:51:52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153652</v>
+        <v>INC000000153696</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1213,19 +1216,19 @@
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F26" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-23T10:10:09.000Z</v>
+        <v>2026-07-23T16:05:54.000Z</v>
       </c>
       <c r="I26" t="str">
-        <v>24/07/2026 17:00:00</v>
+        <v>24/07/2026 20:00:00</v>
       </c>
       <c r="J26" t="str">
         <v>-</v>
@@ -1233,7 +1236,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153657</v>
+        <v>INC000000153698</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1245,27 +1248,27 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F27" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-23T10:35:40.000Z</v>
+        <v>2026-07-23T16:40:30.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>23/07/2026 18:35:24</v>
+        <v>24/07/2026 09:40:14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153661</v>
+        <v>INC000000153699</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
@@ -1277,91 +1280,91 @@
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-23T10:52:03.000Z</v>
+        <v>2026-07-23T16:36:59.000Z</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
       </c>
       <c r="J28" t="str">
-        <v>23/07/2026 18:51:47</v>
+        <v>24/07/2026 09:36:43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153677</v>
+        <v>INC000000153724</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D29" t="str">
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
       </c>
       <c r="F29" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-23T12:19:22.000Z</v>
+        <v>2026-07-23T09:49:33.000Z</v>
       </c>
       <c r="I29" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J29" t="str">
-        <v>24/07/2026 18:19:06</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153679</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F30" t="str">
-        <v>SPT ZONA ORIENTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-23T12:42:49.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
       </c>
       <c r="I30" t="str">
-        <v>-</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J30" t="str">
-        <v>23/07/2026 20:42:33</v>
+        <v>-</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153684</v>
+        <v>INC000000153733</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1373,27 +1376,27 @@
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F31" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-23T12:52:08.000Z</v>
+        <v>2026-07-23T10:30:57.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>23/07/2026 20:51:52</v>
+        <v>24/07/2026 16:30:41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153724</v>
+        <v>INC000000153738</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1405,59 +1408,59 @@
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F32" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-23T09:49:33.000Z</v>
+        <v>2026-07-23T11:13:56.000Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>23/07/2026 17:49:17</v>
+        <v>24/07/2026 17:13:40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153727</v>
+        <v>INC000000153741</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
       </c>
       <c r="E33" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F33" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G33" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-23T10:00:07.000Z</v>
+        <v>2026-07-23T11:24:06.999Z</v>
       </c>
       <c r="I33" t="str">
-        <v>24/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>-</v>
+        <v>24/07/2026 17:23:51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153733</v>
+        <v>INC000000153748</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1478,18 +1481,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-23T10:30:57.000Z</v>
+        <v>2026-07-23T11:44:08.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>24/07/2026 16:30:41</v>
+        <v>24/07/2026 17:43:52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153738</v>
+        <v>INC000000153751</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1501,27 +1504,27 @@
         <v>Baja</v>
       </c>
       <c r="E35" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F35" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G35" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-23T11:13:56.000Z</v>
+        <v>2026-07-23T12:20:01.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>24/07/2026 17:13:40</v>
+        <v>24/07/2026 18:19:45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153741</v>
+        <v>INC000000153756</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1533,27 +1536,27 @@
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T11:24:06.999Z</v>
+        <v>2026-07-23T12:00:45.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>24/07/2026 17:23:51</v>
+        <v>24/07/2026 18:00:29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153748</v>
+        <v>INC000000153767</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1565,7 +1568,7 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F37" t="str">
         <v>ZONA CENTRO</v>
@@ -1574,50 +1577,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T11:44:08.000Z</v>
+        <v>2026-07-23T12:53:01.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>24/07/2026 17:43:52</v>
+        <v>24/07/2026 18:52:45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153751</v>
+        <v>INC000000153769</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-23T12:20:01.000Z</v>
+        <v>2026-07-23T12:56:52.000Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>24/07/2026 18:19:45</v>
+        <v>24/07/2026 18:56:36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153756</v>
+        <v>INC000000153775</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
@@ -1629,27 +1632,27 @@
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F39" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T12:00:45.000Z</v>
+        <v>2026-07-23T13:56:57.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>23/07/2026 20:00:29</v>
+        <v>24/07/2026 19:56:41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153767</v>
+        <v>INC000000153785</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
@@ -1661,27 +1664,27 @@
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F40" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T12:53:01.000Z</v>
+        <v>2026-07-23T15:07:27.999Z</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
       </c>
       <c r="J40" t="str">
-        <v>23/07/2026 20:52:45</v>
+        <v>25/07/2026 07:07:12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153769</v>
+        <v>INC000000153793</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
@@ -1693,91 +1696,91 @@
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-23T12:56:52.000Z</v>
+        <v>2026-07-23T16:03:19.000Z</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>23/07/2026 20:56:36</v>
+        <v>24/07/2026 09:58:38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153770</v>
+        <v>INC000000153794</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-23T12:59:05.000Z</v>
+        <v>2026-07-23T16:21:06.999Z</v>
       </c>
       <c r="I42" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J42" t="str">
-        <v>23/07/2026 20:58:49</v>
+        <v>-</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153775</v>
+        <v>INC000000153796</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F43" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-23T13:56:57.000Z</v>
+        <v>2026-07-23T16:55:29.999Z</v>
       </c>
       <c r="I43" t="str">
-        <v>-</v>
+        <v>24/07/2026 20:00:00</v>
       </c>
       <c r="J43" t="str">
-        <v>24/07/2026 19:56:41</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153777</v>
+        <v>INC000000153802</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1798,18 +1801,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-23T14:12:45.000Z</v>
+        <v>2026-07-23T17:11:07.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>24/07/2026 07:12:29</v>
+        <v>24/07/2026 10:10:51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153781</v>
+        <v>INC000000153806</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1821,27 +1824,27 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>SANTIAGO PERDOMO ACERO</v>
       </c>
       <c r="F45" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G45" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T14:52:02.000Z</v>
+        <v>2026-07-23T17:43:20.000Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>24/07/2026 07:51:46</v>
+        <v>25/07/2026 09:43:04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153785</v>
+        <v>INC000000153807</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1853,27 +1856,27 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T15:07:27.999Z</v>
+        <v>2026-07-23T17:13:51.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>25/07/2026 07:07:12</v>
+        <v>24/07/2026 10:13:35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153789</v>
+        <v>INC000000153811</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
@@ -1885,59 +1888,59 @@
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F47" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T15:37:32.000Z</v>
+        <v>2026-07-23T22:49:22.999Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>24/07/2026 08:37:16</v>
+        <v>27/07/2026 06:00:00</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153813</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
       </c>
       <c r="C48" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D48" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F48" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G48" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I48" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-24T06:01:01.000Z</v>
+      </c>
+      <c r="I48" t="str">
+        <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>23/07/2026 13:33</v>
+        <v>24/07/2026 14:00:45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153815</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1949,53 +1952,59 @@
         <v>Baja</v>
       </c>
       <c r="E49" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F49" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G49" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-24T06:15:58.000Z</v>
+      </c>
+      <c r="I49" t="str">
+        <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>24/07/2026 14:15:42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>WO0000000307624</v>
+        <v>INC000000153818</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F50" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G50" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-24T06:32:03.000Z</v>
+      </c>
+      <c r="I50" t="str">
+        <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 14:31:47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>WO0000000307703</v>
+        <v>INC000000153821</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2007,181 +2016,187 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G51" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-14T14:27:16.000Z</v>
+        <v>2026-07-24T06:51:17.999Z</v>
+      </c>
+      <c r="I51" t="str">
+        <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>24/07/2026 16:18</v>
+        <v>24/07/2026 14:51:02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>WO0000000307988</v>
+        <v>INC000000153822</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
       </c>
       <c r="C52" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D52" t="str">
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F52" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G52" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I52" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-24T06:51:19.000Z</v>
+      </c>
+      <c r="I52" t="str">
+        <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>21/07/2026 09:38</v>
+        <v>24/07/2026 14:51:03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000153907</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>DIEGO ARTURO ROMERO CALDERON</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA LAGOMAR</v>
       </c>
       <c r="G53" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I53" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-23T19:54:55.000Z</v>
+      </c>
+      <c r="I53" t="str">
+        <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>17/07/2026 14:53</v>
+        <v>25/07/2026 11:54:39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>WO0000000308443</v>
+        <v>INC000000153909</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
       </c>
       <c r="C54" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D54" t="str">
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G54" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I54" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-23T22:33:57.000Z</v>
+      </c>
+      <c r="I54" t="str">
+        <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>21/07/2026 16:31</v>
+        <v>24/07/2026 14:00:00</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000153912</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
       </c>
       <c r="C55" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D55" t="str">
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F55" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G55" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I55" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-24T06:13:18.000Z</v>
+      </c>
+      <c r="I55" t="str">
+        <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>21/07/2026 12:49</v>
+        <v>24/07/2026 14:13:02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000153913</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G56" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-24T06:10:35.000Z</v>
+      </c>
+      <c r="I56" t="str">
+        <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>27/07/2026 06:10:19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>WO0000000309315</v>
+        <v>INC000000153915</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2190,85 +2205,91 @@
         <v>Asignado</v>
       </c>
       <c r="D57" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F57" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-24T06:17:56.000Z</v>
+      </c>
+      <c r="I57" t="str">
+        <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>24/07/2026 14:17:40</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000309318</v>
+        <v>WO0000000305253</v>
+      </c>
+      <c r="B58" t="str">
+        <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D58" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E58" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G58" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I58" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J58" t="str">
-        <v>-</v>
+        <v>27/07/2026 10:03</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000309411</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G59" t="str">
-        <v>b) 5-10</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I59" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J59" t="str">
-        <v>23/07/2026 10:48</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000309834</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2280,24 +2301,24 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F60" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G60" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J60" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000310343</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
@@ -2309,85 +2330,91 @@
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F61" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G61" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I61" s="1" t="d">
-        <v>2026-07-31T18:00:16.000Z</v>
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J61" t="str">
-        <v>24/07/2026 14:55</v>
+        <v>24/07/2026 09:38</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000310376</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
       <c r="E62" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F62" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G62" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I62" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J62" t="str">
-        <v>24/07/2026 08:38</v>
+        <v>24/07/2026 10:19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000310425</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-21T17:12:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I63" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J63" t="str">
-        <v>27/07/2026 08:00</v>
+        <v>28/07/2026 13:47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
@@ -2399,27 +2426,27 @@
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F64" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="I64" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J64" t="str">
-        <v>24/07/2026 10:00</v>
+        <v>24/07/2026 10:31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000310577</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2431,111 +2458,117 @@
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F65" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G65" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-22T08:38:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J65" t="str">
-        <v>27/07/2026 08:40</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
       </c>
       <c r="C66" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D66" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E66" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F66" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J66" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F67" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
+      </c>
+      <c r="I67" s="1" t="d">
+        <v>2026-07-27T17:00:16.000Z</v>
       </c>
       <c r="J67" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>28/07/2026 16:59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000310789</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G68" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I68" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J68" t="str">
-        <v>28/07/2026 08:13</v>
+        <v>24/07/2026 15:25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
@@ -2547,111 +2580,120 @@
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J69" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
+      </c>
+      <c r="I70" s="1" t="d">
+        <v>2026-07-31T18:00:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>27/07/2026 12:17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F71" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
+      </c>
+      <c r="I71" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>-</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
       </c>
       <c r="C72" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
         <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F72" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
+      </c>
+      <c r="I72" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>24/07/2026 14:50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2663,7 +2705,7 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F73" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2672,15 +2714,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2692,24 +2734,24 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F74" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000311055</v>
+        <v>WO0000000310789</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2721,24 +2763,24 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>ANDRES ALBERTO JUTINICO VELA</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT CABECERA SUBA</v>
       </c>
       <c r="G75" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-22T17:40:15.999Z</v>
+        <v>2026-07-22T11:38:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>28/07/2026 09:27</v>
+        <v>28/07/2026 08:13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000311080</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
@@ -2750,7 +2792,7 @@
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F76" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2759,44 +2801,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-23T07:09:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J76" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000311147</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G77" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-23T07:04:16.000Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>28/07/2026 08:00</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000311247</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
@@ -2808,36 +2850,36 @@
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F78" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G78" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-23T09:42:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>28/07/2026 09:42</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000311264</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
       </c>
       <c r="C79" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D79" t="str">
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F79" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2846,15 +2888,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-23T10:27:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>28/07/2026 10:27</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000311266</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
@@ -2866,82 +2908,82 @@
         <v>Baja</v>
       </c>
       <c r="E80" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-23T10:29:16.000Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>28/07/2026 10:29</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000311358</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F81" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G81" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-23T12:22:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>28/07/2026 12:22</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000311385</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
       </c>
       <c r="E82" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F82" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-23T13:45:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J82" t="str">
-        <v>28/07/2026 13:47</v>
+        <v>27/07/2026 15:34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000311387</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2953,24 +2995,24 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-23T13:53:16.000Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J83" t="str">
-        <v>28/07/2026 13:55</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000311397</v>
+        <v>WO0000000311247</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
@@ -2982,36 +3024,36 @@
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F84" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-23T14:23:16.000Z</v>
+        <v>2026-07-23T09:42:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>28/07/2026 14:25</v>
+        <v>28/07/2026 09:42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000311400</v>
+        <v>WO0000000311264</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F85" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3020,15 +3062,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-23T14:26:16.000Z</v>
+        <v>2026-07-23T10:27:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>28/07/2026 14:28</v>
+        <v>28/07/2026 10:27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000311444</v>
+        <v>WO0000000311266</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
@@ -3040,24 +3082,24 @@
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-23T13:49:16.000Z</v>
+        <v>2026-07-23T10:29:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>28/07/2026 13:50</v>
+        <v>28/07/2026 10:29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000311457</v>
+        <v>WO0000000311358</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
@@ -3069,24 +3111,24 @@
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F87" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-23T14:35:16.000Z</v>
+        <v>2026-07-23T12:22:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>28/07/2026 14:42</v>
+        <v>28/07/2026 12:22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000311459</v>
+        <v>WO0000000311457</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3098,7 +3140,7 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F88" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3107,102 +3149,102 @@
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-23T14:43:15.999Z</v>
+        <v>2026-07-23T14:35:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>28/07/2026 14:45</v>
+        <v>28/07/2026 14:42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000311464</v>
+        <v>WO0000000311476</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F89" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-23T14:47:15.999Z</v>
+        <v>2026-07-23T15:24:16.000Z</v>
       </c>
       <c r="J89" t="str">
-        <v>28/07/2026 14:50</v>
+        <v>24/08/2026 15:24</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000311469</v>
+        <v>WO0000000311525</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
       </c>
       <c r="C90" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D90" t="str">
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F90" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-23T15:02:15.999Z</v>
+        <v>2026-07-23T15:09:15.999Z</v>
       </c>
       <c r="J90" t="str">
-        <v>28/07/2026 15:05</v>
+        <v>28/07/2026 15:09</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000311471</v>
+        <v>WO0000000311546</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F91" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-23T15:06:16.000Z</v>
+        <v>2026-07-23T15:57:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>28/07/2026 15:08</v>
+        <v>28/07/2026 15:57</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000311476</v>
+        <v>WO0000000311566</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
@@ -3214,7 +3256,7 @@
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F92" t="str">
         <v>ZONA CENTRO</v>
@@ -3223,44 +3265,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-23T15:24:16.000Z</v>
+        <v>2026-07-23T16:54:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>24/08/2026 15:24</v>
+        <v>28/07/2026 16:54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000311478</v>
+        <v>WO0000000311569</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F93" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-23T15:16:16.000Z</v>
+        <v>2026-07-23T17:07:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>28/07/2026 15:18</v>
+        <v>25/08/2026 08:00</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000311480</v>
+        <v>WO0000000311573</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3270,9 +3312,6 @@
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
-      </c>
-      <c r="E94" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
       </c>
       <c r="F94" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3281,15 +3320,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-23T15:19:16.000Z</v>
+        <v>2026-07-23T17:26:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>28/07/2026 15:21</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000311485</v>
+        <v>WO0000000311586</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
@@ -3301,111 +3340,111 @@
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-23T15:26:16.000Z</v>
+        <v>2026-07-23T19:44:16.000Z</v>
       </c>
       <c r="J95" t="str">
-        <v>28/07/2026 15:28</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000311492</v>
+        <v>WO0000000311612</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F96" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-23T15:33:16.000Z</v>
+        <v>2026-07-23T16:15:16.000Z</v>
       </c>
       <c r="J96" t="str">
-        <v>28/07/2026 15:35</v>
+        <v>28/07/2026 16:15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000311493</v>
+        <v>WO0000000311616</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F97" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G97" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-23T15:36:16.000Z</v>
+        <v>2026-07-23T16:27:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>28/07/2026 15:38</v>
+        <v>28/07/2026 16:27</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000311498</v>
+        <v>WO0000000311619</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
       </c>
       <c r="C98" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D98" t="str">
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F98" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-23T15:41:16.000Z</v>
+        <v>2026-07-23T16:41:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>28/07/2026 15:42</v>
+        <v>28/07/2026 16:41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311499</v>
+        <v>WO0000000311656</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3417,24 +3456,24 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-23T15:43:16.000Z</v>
+        <v>2026-07-24T06:05:15.999Z</v>
       </c>
       <c r="J99" t="str">
-        <v>28/07/2026 15:45</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311502</v>
+        <v>WO0000000311659</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
@@ -3446,7 +3485,7 @@
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F100" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3455,15 +3494,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-23T14:29:16.000Z</v>
+        <v>2026-07-24T06:39:15.999Z</v>
       </c>
       <c r="J100" t="str">
-        <v>28/07/2026 14:32</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311505</v>
+        <v>WO0000000311662</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3475,7 +3514,7 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F101" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3484,15 +3523,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-23T14:35:16.000Z</v>
+        <v>2026-07-24T06:47:15.999Z</v>
       </c>
       <c r="J101" t="str">
-        <v>28/07/2026 14:37</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311507</v>
+        <v>WO0000000311667</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
@@ -3504,7 +3543,7 @@
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F102" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3513,15 +3552,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-23T14:40:15.999Z</v>
+        <v>2026-07-24T07:05:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>28/07/2026 14:41</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000311514</v>
+        <v>WO0000000311701</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
@@ -3533,7 +3572,7 @@
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F103" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3542,15 +3581,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-23T14:54:15.999Z</v>
+        <v>2026-07-24T06:42:16.000Z</v>
       </c>
       <c r="J103" t="str">
-        <v>28/07/2026 14:56</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000311518</v>
+        <v>WO0000000311702</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
@@ -3562,7 +3601,7 @@
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F104" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3571,15 +3610,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-23T14:57:16.000Z</v>
+        <v>2026-07-24T06:44:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>28/07/2026 14:58</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000311520</v>
+        <v>WO0000000311704</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
@@ -3591,7 +3630,7 @@
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F105" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3600,44 +3639,44 @@
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-23T14:59:16.000Z</v>
+        <v>2026-07-24T06:50:15.999Z</v>
       </c>
       <c r="J105" t="str">
-        <v>28/07/2026 15:01</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000311525</v>
+        <v>WO0000000311705</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
       </c>
       <c r="C106" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D106" t="str">
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F106" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G106" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-23T15:09:15.999Z</v>
+        <v>2026-07-24T06:53:16.000Z</v>
       </c>
       <c r="J106" t="str">
-        <v>28/07/2026 15:09</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000311526</v>
+        <v>WO0000000311706</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3649,7 +3688,7 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F107" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3658,15 +3697,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-23T15:11:16.000Z</v>
+        <v>2026-07-24T06:55:16.000Z</v>
       </c>
       <c r="J107" t="str">
-        <v>28/07/2026 15:12</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000311528</v>
+        <v>WO0000000311710</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
@@ -3678,7 +3717,7 @@
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F108" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3687,15 +3726,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-23T15:14:16.000Z</v>
+        <v>2026-07-24T06:59:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>28/07/2026 15:15</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000311530</v>
+        <v>WO0000000311713</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
@@ -3707,7 +3746,7 @@
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F109" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3716,15 +3755,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-23T15:22:16.000Z</v>
+        <v>2026-07-24T07:01:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>28/07/2026 15:24</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000311532</v>
+        <v>WO0000000311715</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
@@ -3736,7 +3775,7 @@
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F110" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3745,15 +3784,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-23T15:30:16.000Z</v>
+        <v>2026-07-24T07:07:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>28/07/2026 15:32</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000311536</v>
+        <v>WO0000000311716</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3765,7 +3804,7 @@
         <v>Baja</v>
       </c>
       <c r="E111" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F111" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3774,102 +3813,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-23T15:38:16.000Z</v>
+        <v>2026-07-24T07:10:15.999Z</v>
       </c>
       <c r="J111" t="str">
-        <v>28/07/2026 15:40</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>WO0000000311539</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-      <c r="C112" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E112" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F112" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G112" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H112" s="1" t="d">
-        <v>2026-07-23T15:46:16.000Z</v>
-      </c>
-      <c r="J112" t="str">
-        <v>28/07/2026 15:48</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>WO0000000311604</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-      <c r="C113" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E113" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F113" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G113" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H113" s="1" t="d">
-        <v>2026-07-23T15:49:16.000Z</v>
-      </c>
-      <c r="J113" t="str">
-        <v>28/07/2026 15:50</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>WO0000000311606</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-      <c r="C114" t="str">
-        <v>En curso</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Baja</v>
-      </c>
-      <c r="E114" t="str">
-        <v>JULIAN HUMBERTO MOLINA BERNAL</v>
-      </c>
-      <c r="F114" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
-      </c>
-      <c r="G114" t="str">
-        <v>a) 0-4</v>
-      </c>
-      <c r="H114" s="1" t="d">
-        <v>2026-07-23T15:51:16.000Z</v>
-      </c>
-      <c r="J114" t="str">
-        <v>28/07/2026 15:53</v>
+        <v>29/07/2026 08:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J128"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1178,7 +1178,7 @@
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
@@ -1370,7 +1370,7 @@
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
@@ -1466,7 +1466,7 @@
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
@@ -1690,7 +1690,7 @@
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
@@ -1699,7 +1699,7 @@
         <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F41" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
@@ -1711,7 +1711,7 @@
         <v>-</v>
       </c>
       <c r="J41" t="str">
-        <v>24/07/2026 09:58:38</v>
+        <v>25/07/2026 08:03:03</v>
       </c>
     </row>
     <row r="42">
@@ -1792,10 +1792,10 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F44" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
@@ -1807,7 +1807,7 @@
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>24/07/2026 10:10:51</v>
+        <v>25/07/2026 09:10:51</v>
       </c>
     </row>
     <row r="45">
@@ -1824,7 +1824,7 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>SANTIAGO PERDOMO ACERO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F45" t="str">
         <v>ZONA CENTRO</v>
@@ -1839,7 +1839,7 @@
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>25/07/2026 09:43:04</v>
+        <v>27/07/2026 07:30:29</v>
       </c>
     </row>
     <row r="46">
@@ -2068,39 +2068,39 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153907</v>
+        <v>INC000000153823</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>DIEGO ARTURO ROMERO CALDERON</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F53" t="str">
-        <v>ZONA LAGOMAR</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-23T19:54:55.000Z</v>
+        <v>2026-07-24T06:56:46.000Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>25/07/2026 11:54:39</v>
+        <v>24/07/2026 14:56:30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153909</v>
+        <v>INC000000153824</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2112,7 +2112,7 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F54" t="str">
         <v>SPT CABECERA CALLE 26</v>
@@ -2121,18 +2121,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-23T22:33:57.000Z</v>
+        <v>2026-07-24T07:14:28.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>24/07/2026 14:00:00</v>
+        <v>24/07/2026 15:14:12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153912</v>
+        <v>INC000000153826</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,59 +2144,59 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-24T06:13:18.000Z</v>
+        <v>2026-07-24T07:27:52.999Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>24/07/2026 14:13:02</v>
+        <v>24/07/2026 15:27:37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153913</v>
+        <v>INC000000153827</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
       </c>
       <c r="C56" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D56" t="str">
         <v>Baja</v>
       </c>
       <c r="E56" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F56" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G56" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-24T06:10:35.000Z</v>
+        <v>2026-07-24T07:28:17.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>27/07/2026 06:10:19</v>
+        <v>24/07/2026 15:28:01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153915</v>
+        <v>INC000000153828</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,7 +2208,7 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F57" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2217,265 +2217,271 @@
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-24T06:17:56.000Z</v>
+        <v>2026-07-24T07:29:17.000Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>24/07/2026 14:17:40</v>
+        <v>24/07/2026 15:29:01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WO0000000305253</v>
+        <v>INC000000153829</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D58" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F58" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G58" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
-      </c>
-      <c r="I58" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-24T07:34:05.000Z</v>
+      </c>
+      <c r="I58" t="str">
+        <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>27/07/2026 10:03</v>
+        <v>24/07/2026 15:33:49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>WO0000000305335</v>
+        <v>INC000000153830</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DAVID ESTEBAN DIAZ LLANOS</v>
       </c>
       <c r="F59" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 42</v>
       </c>
       <c r="G59" t="str">
-        <v>c) 11-30</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-24T07:43:41.000Z</v>
+      </c>
+      <c r="I59" t="str">
+        <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>24/07/2026 15:43:25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WO0000000307624</v>
+        <v>INC000000153833</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
       </c>
       <c r="C60" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D60" t="str">
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F60" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G60" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-24T07:52:37.999Z</v>
+      </c>
+      <c r="I60" t="str">
+        <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>24/07/2026 15:52:22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WO0000000307988</v>
+        <v>INC000000153834</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G61" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
-      </c>
-      <c r="I61" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-24T07:52:04.000Z</v>
+      </c>
+      <c r="I61" t="str">
+        <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>24/07/2026 09:38</v>
+        <v>27/07/2026 07:51:48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WO0000000308197</v>
+        <v>INC000000153837</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
-      <c r="E62" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
-      </c>
       <c r="F62" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G62" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I62" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-24T08:16:27.000Z</v>
+      </c>
+      <c r="I62" t="str">
+        <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>24/07/2026 10:19</v>
+        <v>24/07/2026 16:16:11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WO0000000308443</v>
+        <v>INC000000153907</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
       </c>
       <c r="C63" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D63" t="str">
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>FREDY ANDRES AVILA VEGA</v>
       </c>
       <c r="F63" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA LAGOMAR</v>
       </c>
       <c r="G63" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-15T15:46:16.000Z</v>
-      </c>
-      <c r="I63" s="1" t="d">
-        <v>2026-07-24T17:00:16.000Z</v>
+        <v>2026-07-23T19:54:55.000Z</v>
+      </c>
+      <c r="I63" t="str">
+        <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>28/07/2026 13:47</v>
+        <v>27/07/2026 07:46:06</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WO0000000308723</v>
+        <v>INC000000153909</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
       </c>
       <c r="F64" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G64" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-16T10:49:16.000Z</v>
-      </c>
-      <c r="I64" s="1" t="d">
-        <v>2026-07-30T17:00:16.000Z</v>
+        <v>2026-07-23T22:33:57.000Z</v>
+      </c>
+      <c r="I64" t="str">
+        <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>24/07/2026 10:31</v>
+        <v>24/07/2026 14:00:00</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WO0000000309139</v>
+        <v>INC000000153912</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
       </c>
       <c r="C65" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D65" t="str">
         <v>Baja</v>
       </c>
       <c r="E65" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F65" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G65" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-17T08:29:16.000Z</v>
+        <v>2026-07-24T06:13:18.000Z</v>
+      </c>
+      <c r="I65" t="str">
+        <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>27/07/2026 16:47</v>
+        <v>24/07/2026 14:13:02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>WO0000000309315</v>
+        <v>INC000000153913</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2484,10 +2490,10 @@
         <v>Asignado</v>
       </c>
       <c r="D66" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F66" t="str">
         <v>ZONA CENTRO</v>
@@ -2496,21 +2502,24 @@
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-21T15:30:16.000Z</v>
+        <v>2026-07-24T06:10:35.000Z</v>
+      </c>
+      <c r="I66" t="str">
+        <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>28/07/2026 10:30</v>
+        <v>27/07/2026 06:10:19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WO0000000309318</v>
+        <v>INC000000153915</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
@@ -2525,143 +2534,146 @@
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-22T10:44:16.000Z</v>
-      </c>
-      <c r="I67" s="1" t="d">
-        <v>2026-07-27T17:00:16.000Z</v>
+        <v>2026-07-24T06:17:56.000Z</v>
+      </c>
+      <c r="I67" t="str">
+        <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>28/07/2026 16:59</v>
+        <v>24/07/2026 14:17:40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WO0000000309411</v>
+        <v>INC000000153916</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
       </c>
       <c r="C68" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D68" t="str">
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F68" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G68" t="str">
-        <v>b) 5-10</v>
+        <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-17T10:48:15.999Z</v>
-      </c>
-      <c r="I68" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-24T06:26:57.000Z</v>
+      </c>
+      <c r="I68" t="str">
+        <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>24/07/2026 15:25</v>
+        <v>24/07/2026 14:26:41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WO0000000309834</v>
+        <v>INC000000153917</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D69" t="str">
         <v>Baja</v>
       </c>
       <c r="E69" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F69" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G69" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-19T11:09:15.999Z</v>
+        <v>2026-07-24T06:43:42.999Z</v>
+      </c>
+      <c r="I69" t="str">
+        <v>-</v>
       </c>
       <c r="J69" t="str">
-        <v>27/07/2026 12:00</v>
+        <v>24/07/2026 14:43:27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WO0000000310343</v>
+        <v>INC000000153919</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
       </c>
       <c r="C70" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D70" t="str">
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G70" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-21T14:47:15.999Z</v>
-      </c>
-      <c r="I70" s="1" t="d">
-        <v>2026-07-31T18:00:16.000Z</v>
+        <v>2026-07-24T07:28:12.000Z</v>
+      </c>
+      <c r="I70" t="str">
+        <v>-</v>
       </c>
       <c r="J70" t="str">
-        <v>27/07/2026 12:17</v>
+        <v>24/07/2026 15:27:56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>WO0000000310376</v>
+        <v>INC000000153923</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G71" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-21T15:38:16.000Z</v>
-      </c>
-      <c r="I71" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+        <v>2026-07-24T08:08:50.999Z</v>
+      </c>
+      <c r="I71" t="str">
+        <v>-</v>
       </c>
       <c r="J71" t="str">
-        <v>-</v>
+        <v>27/07/2026 08:08:35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000310452</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
@@ -2670,30 +2682,30 @@
         <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E72" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F72" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G72" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-21T22:40:16.000Z</v>
+        <v>2026-07-16T09:33:16.000Z</v>
       </c>
       <c r="I72" s="1" t="d">
         <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>24/07/2026 14:50</v>
+        <v>27/07/2026 10:03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000310630</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
@@ -2705,24 +2717,24 @@
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F73" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G73" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-22T09:58:16.000Z</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>27/07/2026 09:59</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000310781</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
@@ -2734,140 +2746,152 @@
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F74" t="str">
         <v>ZONA CENTRO</v>
       </c>
       <c r="G74" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-22T11:28:16.000Z</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>24/07/2026 13:56</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000310789</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
       </c>
       <c r="C75" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D75" t="str">
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>ANDRES ALBERTO JUTINICO VELA</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F75" t="str">
-        <v>SPT CABECERA SUBA</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G75" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-22T11:38:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
+      </c>
+      <c r="I75" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>28/07/2026 08:13</v>
+        <v>24/07/2026 09:38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000310888</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F76" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G76" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-22T16:03:15.999Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I76" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J76" t="str">
-        <v>27/07/2026 16:03</v>
+        <v>24/07/2026 10:19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WO0000000310974</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B77" t="str">
         <v>No</v>
       </c>
       <c r="C77" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D77" t="str">
         <v>Baja</v>
       </c>
       <c r="E77" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F77" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G77" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H77" s="1" t="d">
-        <v>2026-07-22T15:04:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I77" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J77" t="str">
-        <v>27/07/2026 15:18</v>
+        <v>28/07/2026 13:47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WO0000000311014</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B78" t="str">
         <v>No</v>
       </c>
       <c r="C78" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D78" t="str">
         <v>Baja</v>
       </c>
       <c r="E78" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F78" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G78" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H78" s="1" t="d">
-        <v>2026-07-22T15:53:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
+      </c>
+      <c r="I78" s="1" t="d">
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J78" t="str">
-        <v>27/07/2026 15:53</v>
+        <v>24/07/2026 10:31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WO0000000311019</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B79" t="str">
         <v>No</v>
@@ -2879,65 +2903,65 @@
         <v>Baja</v>
       </c>
       <c r="E79" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F79" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G79" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H79" s="1" t="d">
-        <v>2026-07-22T15:56:16.000Z</v>
+        <v>2026-07-17T08:29:16.000Z</v>
       </c>
       <c r="J79" t="str">
-        <v>27/07/2026 15:56</v>
+        <v>27/07/2026 16:47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>WO0000000311031</v>
+        <v>WO0000000309315</v>
       </c>
       <c r="B80" t="str">
         <v>No</v>
       </c>
       <c r="C80" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D80" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E80" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F80" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G80" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H80" s="1" t="d">
-        <v>2026-07-22T16:22:16.000Z</v>
+        <v>2026-07-21T15:30:16.000Z</v>
       </c>
       <c r="J80" t="str">
-        <v>27/07/2026 16:22</v>
+        <v>28/07/2026 10:30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>WO0000000311036</v>
+        <v>WO0000000309318</v>
       </c>
       <c r="B81" t="str">
         <v>No</v>
       </c>
       <c r="C81" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D81" t="str">
         <v>Baja</v>
       </c>
       <c r="E81" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F81" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -2946,21 +2970,24 @@
         <v>a) 0-4</v>
       </c>
       <c r="H81" s="1" t="d">
-        <v>2026-07-22T16:27:16.000Z</v>
+        <v>2026-07-22T10:44:16.000Z</v>
+      </c>
+      <c r="I81" s="1" t="d">
+        <v>2026-07-27T17:00:16.000Z</v>
       </c>
       <c r="J81" t="str">
-        <v>27/07/2026 16:27</v>
+        <v>28/07/2026 16:59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>WO0000000311046</v>
+        <v>WO0000000309411</v>
       </c>
       <c r="B82" t="str">
         <v>No</v>
       </c>
       <c r="C82" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D82" t="str">
         <v>Baja</v>
@@ -2972,18 +2999,21 @@
         <v>ZONA CENTRO</v>
       </c>
       <c r="G82" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H82" s="1" t="d">
-        <v>2026-07-22T16:58:15.999Z</v>
+        <v>2026-07-17T10:48:15.999Z</v>
+      </c>
+      <c r="I82" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J82" t="str">
-        <v>27/07/2026 15:34</v>
+        <v>24/07/2026 15:25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>WO0000000311055</v>
+        <v>WO0000000309834</v>
       </c>
       <c r="B83" t="str">
         <v>No</v>
@@ -2995,140 +3025,149 @@
         <v>Baja</v>
       </c>
       <c r="E83" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F83" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G83" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H83" s="1" t="d">
-        <v>2026-07-22T17:40:15.999Z</v>
+        <v>2026-07-19T11:09:15.999Z</v>
       </c>
       <c r="J83" t="str">
-        <v>28/07/2026 09:27</v>
+        <v>27/07/2026 12:00</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>WO0000000311247</v>
+        <v>WO0000000310343</v>
       </c>
       <c r="B84" t="str">
         <v>No</v>
       </c>
       <c r="C84" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D84" t="str">
         <v>Baja</v>
       </c>
       <c r="E84" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F84" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA CENTRO</v>
       </c>
       <c r="G84" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H84" s="1" t="d">
-        <v>2026-07-23T09:42:16.000Z</v>
+        <v>2026-07-21T14:47:15.999Z</v>
+      </c>
+      <c r="I84" s="1" t="d">
+        <v>2026-07-31T18:00:16.000Z</v>
       </c>
       <c r="J84" t="str">
-        <v>28/07/2026 09:42</v>
+        <v>27/07/2026 12:17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>WO0000000311264</v>
+        <v>WO0000000310376</v>
       </c>
       <c r="B85" t="str">
         <v>No</v>
       </c>
       <c r="C85" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D85" t="str">
         <v>Baja</v>
       </c>
       <c r="E85" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F85" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G85" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H85" s="1" t="d">
-        <v>2026-07-23T10:27:16.000Z</v>
+        <v>2026-07-21T15:38:16.000Z</v>
+      </c>
+      <c r="I85" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J85" t="str">
-        <v>28/07/2026 10:27</v>
+        <v>-</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>WO0000000311266</v>
+        <v>WO0000000310452</v>
       </c>
       <c r="B86" t="str">
         <v>No</v>
       </c>
       <c r="C86" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D86" t="str">
         <v>Baja</v>
       </c>
       <c r="E86" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F86" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G86" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H86" s="1" t="d">
-        <v>2026-07-23T10:29:16.000Z</v>
+        <v>2026-07-21T22:40:16.000Z</v>
+      </c>
+      <c r="I86" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J86" t="str">
-        <v>28/07/2026 10:29</v>
+        <v>24/07/2026 14:50</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>WO0000000311358</v>
+        <v>WO0000000310630</v>
       </c>
       <c r="B87" t="str">
         <v>No</v>
       </c>
       <c r="C87" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D87" t="str">
         <v>Baja</v>
       </c>
       <c r="E87" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F87" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G87" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H87" s="1" t="d">
-        <v>2026-07-23T12:22:16.000Z</v>
+        <v>2026-07-22T09:58:16.000Z</v>
       </c>
       <c r="J87" t="str">
-        <v>28/07/2026 12:22</v>
+        <v>27/07/2026 09:59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>WO0000000311457</v>
+        <v>WO0000000310781</v>
       </c>
       <c r="B88" t="str">
         <v>No</v>
@@ -3140,53 +3179,53 @@
         <v>Baja</v>
       </c>
       <c r="E88" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F88" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G88" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H88" s="1" t="d">
-        <v>2026-07-23T14:35:16.000Z</v>
+        <v>2026-07-22T11:28:16.000Z</v>
       </c>
       <c r="J88" t="str">
-        <v>28/07/2026 14:42</v>
+        <v>24/07/2026 13:56</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>WO0000000311476</v>
+        <v>WO0000000310888</v>
       </c>
       <c r="B89" t="str">
         <v>No</v>
       </c>
       <c r="C89" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D89" t="str">
         <v>Baja</v>
       </c>
       <c r="E89" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F89" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G89" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H89" s="1" t="d">
-        <v>2026-07-23T15:24:16.000Z</v>
+        <v>2026-07-22T16:03:15.999Z</v>
       </c>
       <c r="J89" t="str">
-        <v>24/08/2026 15:24</v>
+        <v>27/07/2026 16:03</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>WO0000000311525</v>
+        <v>WO0000000310974</v>
       </c>
       <c r="B90" t="str">
         <v>No</v>
@@ -3198,111 +3237,111 @@
         <v>Baja</v>
       </c>
       <c r="E90" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F90" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G90" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H90" s="1" t="d">
-        <v>2026-07-23T15:09:15.999Z</v>
+        <v>2026-07-22T15:04:16.000Z</v>
       </c>
       <c r="J90" t="str">
-        <v>28/07/2026 15:09</v>
+        <v>27/07/2026 15:18</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>WO0000000311546</v>
+        <v>WO0000000311014</v>
       </c>
       <c r="B91" t="str">
         <v>No</v>
       </c>
       <c r="C91" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D91" t="str">
         <v>Baja</v>
       </c>
       <c r="E91" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F91" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G91" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H91" s="1" t="d">
-        <v>2026-07-23T15:57:16.000Z</v>
+        <v>2026-07-22T15:53:16.000Z</v>
       </c>
       <c r="J91" t="str">
-        <v>28/07/2026 15:57</v>
+        <v>27/07/2026 15:53</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>WO0000000311566</v>
+        <v>WO0000000311019</v>
       </c>
       <c r="B92" t="str">
         <v>No</v>
       </c>
       <c r="C92" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D92" t="str">
         <v>Baja</v>
       </c>
       <c r="E92" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F92" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G92" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H92" s="1" t="d">
-        <v>2026-07-23T16:54:16.000Z</v>
+        <v>2026-07-22T15:56:16.000Z</v>
       </c>
       <c r="J92" t="str">
-        <v>28/07/2026 16:54</v>
+        <v>27/07/2026 15:56</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>WO0000000311569</v>
+        <v>WO0000000311031</v>
       </c>
       <c r="B93" t="str">
         <v>No</v>
       </c>
       <c r="C93" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D93" t="str">
         <v>Baja</v>
       </c>
       <c r="E93" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F93" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G93" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H93" s="1" t="d">
-        <v>2026-07-23T17:07:16.000Z</v>
+        <v>2026-07-22T16:22:16.000Z</v>
       </c>
       <c r="J93" t="str">
-        <v>25/08/2026 08:00</v>
+        <v>27/07/2026 16:22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>WO0000000311573</v>
+        <v>WO0000000311036</v>
       </c>
       <c r="B94" t="str">
         <v>No</v>
@@ -3312,6 +3351,9 @@
       </c>
       <c r="D94" t="str">
         <v>Baja</v>
+      </c>
+      <c r="E94" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F94" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3320,85 +3362,85 @@
         <v>a) 0-4</v>
       </c>
       <c r="H94" s="1" t="d">
-        <v>2026-07-23T17:26:16.000Z</v>
+        <v>2026-07-22T16:27:16.000Z</v>
       </c>
       <c r="J94" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>27/07/2026 16:27</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>WO0000000311586</v>
+        <v>WO0000000311046</v>
       </c>
       <c r="B95" t="str">
         <v>No</v>
       </c>
       <c r="C95" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D95" t="str">
         <v>Baja</v>
       </c>
       <c r="E95" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F95" t="str">
-        <v>SPT CABECERA CARRERA 60</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G95" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H95" s="1" t="d">
-        <v>2026-07-23T19:44:16.000Z</v>
+        <v>2026-07-22T16:58:15.999Z</v>
       </c>
       <c r="J95" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>27/07/2026 15:34</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>WO0000000311612</v>
+        <v>WO0000000311055</v>
       </c>
       <c r="B96" t="str">
         <v>No</v>
       </c>
       <c r="C96" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D96" t="str">
         <v>Baja</v>
       </c>
       <c r="E96" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F96" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G96" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H96" s="1" t="d">
-        <v>2026-07-23T16:15:16.000Z</v>
+        <v>2026-07-22T17:40:15.999Z</v>
       </c>
       <c r="J96" t="str">
-        <v>28/07/2026 16:15</v>
+        <v>28/07/2026 09:27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>WO0000000311616</v>
+        <v>WO0000000311247</v>
       </c>
       <c r="B97" t="str">
         <v>No</v>
       </c>
       <c r="C97" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D97" t="str">
         <v>Baja</v>
       </c>
       <c r="E97" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F97" t="str">
         <v>ZONA CENTRO</v>
@@ -3407,15 +3449,15 @@
         <v>a) 0-4</v>
       </c>
       <c r="H97" s="1" t="d">
-        <v>2026-07-23T16:27:16.000Z</v>
+        <v>2026-07-23T09:42:16.000Z</v>
       </c>
       <c r="J97" t="str">
-        <v>28/07/2026 16:27</v>
+        <v>28/07/2026 09:42</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WO0000000311619</v>
+        <v>WO0000000311264</v>
       </c>
       <c r="B98" t="str">
         <v>No</v>
@@ -3427,24 +3469,24 @@
         <v>Baja</v>
       </c>
       <c r="E98" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F98" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G98" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H98" s="1" t="d">
-        <v>2026-07-23T16:41:16.000Z</v>
+        <v>2026-07-23T10:27:16.000Z</v>
       </c>
       <c r="J98" t="str">
-        <v>28/07/2026 16:41</v>
+        <v>28/07/2026 10:27</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WO0000000311656</v>
+        <v>WO0000000311266</v>
       </c>
       <c r="B99" t="str">
         <v>No</v>
@@ -3456,53 +3498,53 @@
         <v>Baja</v>
       </c>
       <c r="E99" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F99" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G99" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H99" s="1" t="d">
-        <v>2026-07-24T06:05:15.999Z</v>
+        <v>2026-07-23T10:29:16.000Z</v>
       </c>
       <c r="J99" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 10:29</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WO0000000311659</v>
+        <v>WO0000000311358</v>
       </c>
       <c r="B100" t="str">
         <v>No</v>
       </c>
       <c r="C100" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D100" t="str">
         <v>Baja</v>
       </c>
       <c r="E100" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F100" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G100" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H100" s="1" t="d">
-        <v>2026-07-24T06:39:15.999Z</v>
+        <v>2026-07-23T12:22:16.000Z</v>
       </c>
       <c r="J100" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 12:22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WO0000000311662</v>
+        <v>WO0000000311457</v>
       </c>
       <c r="B101" t="str">
         <v>No</v>
@@ -3514,7 +3556,7 @@
         <v>Baja</v>
       </c>
       <c r="E101" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F101" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3523,131 +3565,131 @@
         <v>a) 0-4</v>
       </c>
       <c r="H101" s="1" t="d">
-        <v>2026-07-24T06:47:15.999Z</v>
+        <v>2026-07-23T14:35:16.000Z</v>
       </c>
       <c r="J101" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 14:42</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>WO0000000311667</v>
+        <v>WO0000000311476</v>
       </c>
       <c r="B102" t="str">
         <v>No</v>
       </c>
       <c r="C102" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D102" t="str">
         <v>Baja</v>
       </c>
       <c r="E102" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F102" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G102" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H102" s="1" t="d">
-        <v>2026-07-24T07:05:16.000Z</v>
+        <v>2026-07-23T15:24:16.000Z</v>
       </c>
       <c r="J102" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>24/08/2026 15:24</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>WO0000000311701</v>
+        <v>WO0000000311525</v>
       </c>
       <c r="B103" t="str">
         <v>No</v>
       </c>
       <c r="C103" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D103" t="str">
         <v>Baja</v>
       </c>
       <c r="E103" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F103" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G103" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H103" s="1" t="d">
-        <v>2026-07-24T06:42:16.000Z</v>
+        <v>2026-07-23T15:09:15.999Z</v>
       </c>
       <c r="J103" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 15:09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>WO0000000311702</v>
+        <v>WO0000000311546</v>
       </c>
       <c r="B104" t="str">
         <v>No</v>
       </c>
       <c r="C104" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D104" t="str">
         <v>Baja</v>
       </c>
       <c r="E104" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F104" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G104" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H104" s="1" t="d">
-        <v>2026-07-24T06:44:16.000Z</v>
+        <v>2026-07-23T15:57:16.000Z</v>
       </c>
       <c r="J104" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 15:57</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>WO0000000311704</v>
+        <v>WO0000000311566</v>
       </c>
       <c r="B105" t="str">
         <v>No</v>
       </c>
       <c r="C105" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D105" t="str">
         <v>Baja</v>
       </c>
       <c r="E105" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F105" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G105" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H105" s="1" t="d">
-        <v>2026-07-24T06:50:15.999Z</v>
+        <v>2026-07-23T16:54:16.000Z</v>
       </c>
       <c r="J105" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 16:54</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>WO0000000311705</v>
+        <v>WO0000000311573</v>
       </c>
       <c r="B106" t="str">
         <v>No</v>
@@ -3659,7 +3701,7 @@
         <v>Baja</v>
       </c>
       <c r="E106" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F106" t="str">
         <v>SPT CABECERA CARRERA 69</v>
@@ -3668,7 +3710,7 @@
         <v>a) 0-4</v>
       </c>
       <c r="H106" s="1" t="d">
-        <v>2026-07-24T06:53:16.000Z</v>
+        <v>2026-07-23T17:26:16.000Z</v>
       </c>
       <c r="J106" t="str">
         <v>29/07/2026 08:00</v>
@@ -3676,7 +3718,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>WO0000000311706</v>
+        <v>WO0000000311586</v>
       </c>
       <c r="B107" t="str">
         <v>No</v>
@@ -3688,16 +3730,16 @@
         <v>Baja</v>
       </c>
       <c r="E107" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F107" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT CABECERA CARRERA 60</v>
       </c>
       <c r="G107" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H107" s="1" t="d">
-        <v>2026-07-24T06:55:16.000Z</v>
+        <v>2026-07-23T19:44:16.000Z</v>
       </c>
       <c r="J107" t="str">
         <v>29/07/2026 08:00</v>
@@ -3705,94 +3747,94 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>WO0000000311710</v>
+        <v>WO0000000311612</v>
       </c>
       <c r="B108" t="str">
         <v>No</v>
       </c>
       <c r="C108" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D108" t="str">
         <v>Baja</v>
       </c>
       <c r="E108" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F108" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G108" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H108" s="1" t="d">
-        <v>2026-07-24T06:59:16.000Z</v>
+        <v>2026-07-23T16:15:16.000Z</v>
       </c>
       <c r="J108" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 16:15</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WO0000000311713</v>
+        <v>WO0000000311616</v>
       </c>
       <c r="B109" t="str">
         <v>No</v>
       </c>
       <c r="C109" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D109" t="str">
         <v>Baja</v>
       </c>
       <c r="E109" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F109" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G109" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H109" s="1" t="d">
-        <v>2026-07-24T07:01:16.000Z</v>
+        <v>2026-07-23T16:27:16.000Z</v>
       </c>
       <c r="J109" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 16:27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WO0000000311715</v>
+        <v>WO0000000311619</v>
       </c>
       <c r="B110" t="str">
         <v>No</v>
       </c>
       <c r="C110" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D110" t="str">
         <v>Baja</v>
       </c>
       <c r="E110" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F110" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G110" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H110" s="1" t="d">
-        <v>2026-07-24T07:07:16.000Z</v>
+        <v>2026-07-23T16:41:16.000Z</v>
       </c>
       <c r="J110" t="str">
-        <v>29/07/2026 08:00</v>
+        <v>28/07/2026 16:41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>WO0000000311716</v>
+        <v>WO0000000311659</v>
       </c>
       <c r="B111" t="str">
         <v>No</v>
@@ -3813,15 +3855,505 @@
         <v>a) 0-4</v>
       </c>
       <c r="H111" s="1" t="d">
-        <v>2026-07-24T07:10:15.999Z</v>
+        <v>2026-07-24T06:39:15.999Z</v>
       </c>
       <c r="J111" t="str">
         <v>29/07/2026 08:00</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WO0000000311662</v>
+      </c>
+      <c r="B112" t="str">
+        <v>No</v>
+      </c>
+      <c r="C112" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E112" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F112" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G112" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H112" s="1" t="d">
+        <v>2026-07-24T06:47:15.999Z</v>
+      </c>
+      <c r="J112" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>WO0000000311667</v>
+      </c>
+      <c r="B113" t="str">
+        <v>No</v>
+      </c>
+      <c r="C113" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E113" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F113" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G113" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H113" s="1" t="d">
+        <v>2026-07-24T07:05:16.000Z</v>
+      </c>
+      <c r="J113" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>WO0000000311671</v>
+      </c>
+      <c r="B114" t="str">
+        <v>No</v>
+      </c>
+      <c r="C114" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="F114" t="str">
+        <v>SPT CABECERA CALLE 42</v>
+      </c>
+      <c r="G114" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H114" s="1" t="d">
+        <v>2026-07-24T07:54:16.000Z</v>
+      </c>
+      <c r="J114" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>WO0000000311676</v>
+      </c>
+      <c r="B115" t="str">
+        <v>No</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E115" t="str">
+        <v>JEISON ANDRES REYES ROMERO</v>
+      </c>
+      <c r="F115" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G115" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H115" s="1" t="d">
+        <v>2026-07-24T08:19:16.000Z</v>
+      </c>
+      <c r="J115" t="str">
+        <v>29/07/2026 08:19</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>WO0000000311677</v>
+      </c>
+      <c r="B116" t="str">
+        <v>No</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E116" t="str">
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+      </c>
+      <c r="F116" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G116" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H116" s="1" t="d">
+        <v>2026-07-24T08:23:16.000Z</v>
+      </c>
+      <c r="J116" t="str">
+        <v>29/07/2026 08:23</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>WO0000000311701</v>
+      </c>
+      <c r="B117" t="str">
+        <v>No</v>
+      </c>
+      <c r="C117" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E117" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F117" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G117" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H117" s="1" t="d">
+        <v>2026-07-24T06:42:16.000Z</v>
+      </c>
+      <c r="J117" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>WO0000000311702</v>
+      </c>
+      <c r="B118" t="str">
+        <v>No</v>
+      </c>
+      <c r="C118" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E118" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F118" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G118" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H118" s="1" t="d">
+        <v>2026-07-24T06:44:16.000Z</v>
+      </c>
+      <c r="J118" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>WO0000000311704</v>
+      </c>
+      <c r="B119" t="str">
+        <v>No</v>
+      </c>
+      <c r="C119" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E119" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F119" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G119" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H119" s="1" t="d">
+        <v>2026-07-24T06:50:15.999Z</v>
+      </c>
+      <c r="J119" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>WO0000000311705</v>
+      </c>
+      <c r="B120" t="str">
+        <v>No</v>
+      </c>
+      <c r="C120" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E120" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F120" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G120" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H120" s="1" t="d">
+        <v>2026-07-24T06:53:16.000Z</v>
+      </c>
+      <c r="J120" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>WO0000000311706</v>
+      </c>
+      <c r="B121" t="str">
+        <v>No</v>
+      </c>
+      <c r="C121" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E121" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F121" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G121" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H121" s="1" t="d">
+        <v>2026-07-24T06:55:16.000Z</v>
+      </c>
+      <c r="J121" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>WO0000000311710</v>
+      </c>
+      <c r="B122" t="str">
+        <v>No</v>
+      </c>
+      <c r="C122" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E122" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F122" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G122" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H122" s="1" t="d">
+        <v>2026-07-24T06:59:16.000Z</v>
+      </c>
+      <c r="J122" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>WO0000000311713</v>
+      </c>
+      <c r="B123" t="str">
+        <v>No</v>
+      </c>
+      <c r="C123" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E123" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F123" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G123" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H123" s="1" t="d">
+        <v>2026-07-24T07:01:16.000Z</v>
+      </c>
+      <c r="J123" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>WO0000000311715</v>
+      </c>
+      <c r="B124" t="str">
+        <v>No</v>
+      </c>
+      <c r="C124" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E124" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F124" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G124" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H124" s="1" t="d">
+        <v>2026-07-24T07:07:16.000Z</v>
+      </c>
+      <c r="J124" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>WO0000000311716</v>
+      </c>
+      <c r="B125" t="str">
+        <v>No</v>
+      </c>
+      <c r="C125" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E125" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F125" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G125" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H125" s="1" t="d">
+        <v>2026-07-24T07:10:15.999Z</v>
+      </c>
+      <c r="J125" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>WO0000000311717</v>
+      </c>
+      <c r="B126" t="str">
+        <v>No</v>
+      </c>
+      <c r="C126" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E126" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F126" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G126" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H126" s="1" t="d">
+        <v>2026-07-24T07:13:15.999Z</v>
+      </c>
+      <c r="J126" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>WO0000000311720</v>
+      </c>
+      <c r="B127" t="str">
+        <v>No</v>
+      </c>
+      <c r="C127" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E127" t="str">
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+      </c>
+      <c r="F127" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G127" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H127" s="1" t="d">
+        <v>2026-07-24T07:16:16.000Z</v>
+      </c>
+      <c r="J127" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>WO0000000311739</v>
+      </c>
+      <c r="B128" t="str">
+        <v>No</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Asignado</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E128" t="str">
+        <v>JUAN CAMILO RINCON BLANCO</v>
+      </c>
+      <c r="F128" t="str">
+        <v>SPT CABECERA CARRERA 69</v>
+      </c>
+      <c r="G128" t="str">
+        <v>a) 0-4</v>
+      </c>
+      <c r="H128" s="1" t="d">
+        <v>2026-07-24T07:58:15.999Z</v>
+      </c>
+      <c r="J128" t="str">
+        <v>29/07/2026 08:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J125"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -858,7 +858,7 @@
         <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D15" t="str">
         <v>Baja</v>
@@ -1082,7 +1082,7 @@
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D22" t="str">
         <v>Baja</v>
@@ -1172,71 +1172,71 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>INC000000153684</v>
+        <v>INC000000153696</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D25" t="str">
         <v>Baja</v>
       </c>
       <c r="E25" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F25" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G25" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H25" s="1" t="d">
-        <v>2026-07-23T12:52:08.000Z</v>
+        <v>2026-07-23T16:05:54.000Z</v>
       </c>
       <c r="I25" t="str">
-        <v>-</v>
+        <v>24/07/2026 20:00:00</v>
       </c>
       <c r="J25" t="str">
-        <v>24/07/2026 18:51:52</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>INC000000153696</v>
+        <v>INC000000153698</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D26" t="str">
         <v>Baja</v>
       </c>
       <c r="E26" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F26" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G26" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H26" s="1" t="d">
-        <v>2026-07-23T16:05:54.000Z</v>
+        <v>2026-07-23T16:40:30.000Z</v>
       </c>
       <c r="I26" t="str">
-        <v>24/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J26" t="str">
-        <v>-</v>
+        <v>24/07/2026 09:40:14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>INC000000153698</v>
+        <v>INC000000153699</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
@@ -1248,59 +1248,59 @@
         <v>Baja</v>
       </c>
       <c r="E27" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F27" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G27" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H27" s="1" t="d">
-        <v>2026-07-23T16:40:30.000Z</v>
+        <v>2026-07-23T16:36:59.000Z</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
       </c>
       <c r="J27" t="str">
-        <v>24/07/2026 09:40:14</v>
+        <v>24/07/2026 09:36:43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>INC000000153699</v>
+        <v>INC000000153724</v>
       </c>
       <c r="B28" t="str">
         <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D28" t="str">
         <v>Baja</v>
       </c>
       <c r="E28" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
       </c>
       <c r="F28" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G28" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H28" s="1" t="d">
-        <v>2026-07-23T16:36:59.000Z</v>
+        <v>2026-07-23T09:49:33.000Z</v>
       </c>
       <c r="I28" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J28" t="str">
-        <v>24/07/2026 09:36:43</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>INC000000153724</v>
+        <v>INC000000153727</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1312,19 +1312,19 @@
         <v>Baja</v>
       </c>
       <c r="E29" t="str">
-        <v>DANIEL ALFONSO MENDOZA BARBOSA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F29" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G29" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H29" s="1" t="d">
-        <v>2026-07-23T09:49:33.000Z</v>
+        <v>2026-07-23T10:00:07.000Z</v>
       </c>
       <c r="I29" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>24/07/2026 17:00:00</v>
       </c>
       <c r="J29" t="str">
         <v>-</v>
@@ -1332,109 +1332,109 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>INC000000153727</v>
+        <v>INC000000153733</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D30" t="str">
         <v>Baja</v>
       </c>
       <c r="E30" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F30" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G30" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H30" s="1" t="d">
-        <v>2026-07-23T10:00:07.000Z</v>
+        <v>2026-07-23T10:30:57.000Z</v>
       </c>
       <c r="I30" t="str">
-        <v>24/07/2026 17:00:00</v>
+        <v>-</v>
       </c>
       <c r="J30" t="str">
-        <v>-</v>
+        <v>24/07/2026 16:30:41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>INC000000153733</v>
+        <v>INC000000153738</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
       </c>
       <c r="C31" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D31" t="str">
         <v>Baja</v>
       </c>
       <c r="E31" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F31" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G31" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H31" s="1" t="d">
-        <v>2026-07-23T10:30:57.000Z</v>
+        <v>2026-07-23T11:13:56.000Z</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
       </c>
       <c r="J31" t="str">
-        <v>24/07/2026 16:30:41</v>
+        <v>24/07/2026 17:13:40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>INC000000153738</v>
+        <v>INC000000153741</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
       </c>
       <c r="C32" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D32" t="str">
         <v>Baja</v>
       </c>
       <c r="E32" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
       </c>
       <c r="F32" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G32" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H32" s="1" t="d">
-        <v>2026-07-23T11:13:56.000Z</v>
+        <v>2026-07-23T11:24:06.999Z</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
       </c>
       <c r="J32" t="str">
-        <v>24/07/2026 17:13:40</v>
+        <v>24/07/2026 17:23:51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>INC000000153741</v>
+        <v>INC000000153748</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
       </c>
       <c r="C33" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D33" t="str">
         <v>Baja</v>
@@ -1449,30 +1449,30 @@
         <v>a) 0-4</v>
       </c>
       <c r="H33" s="1" t="d">
-        <v>2026-07-23T11:24:06.999Z</v>
+        <v>2026-07-23T11:44:08.000Z</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
       </c>
       <c r="J33" t="str">
-        <v>24/07/2026 17:23:51</v>
+        <v>24/07/2026 17:43:52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>INC000000153748</v>
+        <v>INC000000153751</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
       </c>
       <c r="C34" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D34" t="str">
         <v>Baja</v>
       </c>
       <c r="E34" t="str">
-        <v>ANDERSON JULIAN RATIVA RAMIREZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F34" t="str">
         <v>ZONA CENTRO</v>
@@ -1481,18 +1481,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H34" s="1" t="d">
-        <v>2026-07-23T11:44:08.000Z</v>
+        <v>2026-07-23T12:20:01.000Z</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
       </c>
       <c r="J34" t="str">
-        <v>24/07/2026 17:43:52</v>
+        <v>24/07/2026 18:19:45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>INC000000153751</v>
+        <v>INC000000153767</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1513,50 +1513,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H35" s="1" t="d">
-        <v>2026-07-23T12:20:01.000Z</v>
+        <v>2026-07-23T12:53:01.000Z</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
       </c>
       <c r="J35" t="str">
-        <v>24/07/2026 18:19:45</v>
+        <v>24/07/2026 18:52:45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>INC000000153756</v>
+        <v>INC000000153769</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
       </c>
       <c r="C36" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D36" t="str">
         <v>Baja</v>
       </c>
       <c r="E36" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F36" t="str">
-        <v>ZONA NORTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G36" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H36" s="1" t="d">
-        <v>2026-07-23T12:00:45.000Z</v>
+        <v>2026-07-23T12:56:52.000Z</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
       </c>
       <c r="J36" t="str">
-        <v>24/07/2026 18:00:29</v>
+        <v>24/07/2026 18:56:36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>INC000000153767</v>
+        <v>INC000000153775</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1568,219 +1568,219 @@
         <v>Baja</v>
       </c>
       <c r="E37" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F37" t="str">
-        <v>ZONA CENTRO</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G37" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H37" s="1" t="d">
-        <v>2026-07-23T12:53:01.000Z</v>
+        <v>2026-07-23T13:56:57.000Z</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
       </c>
       <c r="J37" t="str">
-        <v>24/07/2026 18:52:45</v>
+        <v>24/07/2026 19:56:41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>INC000000153769</v>
+        <v>INC000000153785</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
       </c>
       <c r="C38" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D38" t="str">
         <v>Baja</v>
       </c>
       <c r="E38" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F38" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G38" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H38" s="1" t="d">
-        <v>2026-07-23T12:56:52.000Z</v>
+        <v>2026-07-23T15:07:27.999Z</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
       </c>
       <c r="J38" t="str">
-        <v>24/07/2026 18:56:36</v>
+        <v>25/07/2026 07:07:12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>INC000000153775</v>
+        <v>INC000000153793</v>
       </c>
       <c r="B39" t="str">
         <v>No</v>
       </c>
       <c r="C39" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D39" t="str">
         <v>Baja</v>
       </c>
       <c r="E39" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F39" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NORTE</v>
       </c>
       <c r="G39" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H39" s="1" t="d">
-        <v>2026-07-23T13:56:57.000Z</v>
+        <v>2026-07-23T16:03:19.000Z</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
       </c>
       <c r="J39" t="str">
-        <v>24/07/2026 19:56:41</v>
+        <v>25/07/2026 08:03:03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>INC000000153785</v>
+        <v>INC000000153794</v>
       </c>
       <c r="B40" t="str">
         <v>No</v>
       </c>
       <c r="C40" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D40" t="str">
         <v>Baja</v>
       </c>
       <c r="E40" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F40" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G40" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H40" s="1" t="d">
-        <v>2026-07-23T15:07:27.999Z</v>
+        <v>2026-07-23T16:21:06.999Z</v>
       </c>
       <c r="I40" t="str">
-        <v>-</v>
+        <v>24/07/2026 19:00:00</v>
       </c>
       <c r="J40" t="str">
-        <v>25/07/2026 07:07:12</v>
+        <v>-</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>INC000000153793</v>
+        <v>INC000000153796</v>
       </c>
       <c r="B41" t="str">
         <v>No</v>
       </c>
       <c r="C41" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D41" t="str">
         <v>Baja</v>
       </c>
       <c r="E41" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>JOSE ARLEY SANCHEZ COLORADO</v>
       </c>
       <c r="F41" t="str">
-        <v>ZONA NORTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G41" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H41" s="1" t="d">
-        <v>2026-07-23T16:03:19.000Z</v>
+        <v>2026-07-23T16:55:29.999Z</v>
       </c>
       <c r="I41" t="str">
-        <v>-</v>
+        <v>24/07/2026 20:00:00</v>
       </c>
       <c r="J41" t="str">
-        <v>25/07/2026 08:03:03</v>
+        <v>-</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>INC000000153794</v>
+        <v>INC000000153802</v>
       </c>
       <c r="B42" t="str">
         <v>No</v>
       </c>
       <c r="C42" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D42" t="str">
         <v>Baja</v>
       </c>
       <c r="E42" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F42" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G42" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H42" s="1" t="d">
-        <v>2026-07-23T16:21:06.999Z</v>
+        <v>2026-07-23T17:11:07.000Z</v>
       </c>
       <c r="I42" t="str">
-        <v>24/07/2026 19:00:00</v>
+        <v>-</v>
       </c>
       <c r="J42" t="str">
-        <v>-</v>
+        <v>25/07/2026 09:10:51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>INC000000153796</v>
+        <v>INC000000153806</v>
       </c>
       <c r="B43" t="str">
         <v>No</v>
       </c>
       <c r="C43" t="str">
-        <v>Pendiente</v>
+        <v>Asignado</v>
       </c>
       <c r="D43" t="str">
         <v>Baja</v>
       </c>
       <c r="E43" t="str">
-        <v>JOSE ARLEY SANCHEZ COLORADO</v>
+        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
       </c>
       <c r="F43" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G43" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H43" s="1" t="d">
-        <v>2026-07-23T16:55:29.999Z</v>
+        <v>2026-07-23T17:43:20.000Z</v>
       </c>
       <c r="I43" t="str">
-        <v>24/07/2026 20:00:00</v>
+        <v>-</v>
       </c>
       <c r="J43" t="str">
-        <v>-</v>
+        <v>27/07/2026 07:30:29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>INC000000153802</v>
+        <v>INC000000153807</v>
       </c>
       <c r="B44" t="str">
         <v>No</v>
@@ -1792,27 +1792,27 @@
         <v>Baja</v>
       </c>
       <c r="E44" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F44" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G44" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H44" s="1" t="d">
-        <v>2026-07-23T17:11:07.000Z</v>
+        <v>2026-07-23T17:13:51.000Z</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
       </c>
       <c r="J44" t="str">
-        <v>25/07/2026 09:10:51</v>
+        <v>24/07/2026 10:13:35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>INC000000153806</v>
+        <v>INC000000153811</v>
       </c>
       <c r="B45" t="str">
         <v>No</v>
@@ -1824,7 +1824,7 @@
         <v>Baja</v>
       </c>
       <c r="E45" t="str">
-        <v>MIGUEL JOSE NUÑEZ MARQUEZ</v>
+        <v>DILAN SAMIR LOPEZ ARAUJO</v>
       </c>
       <c r="F45" t="str">
         <v>ZONA CENTRO</v>
@@ -1833,18 +1833,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H45" s="1" t="d">
-        <v>2026-07-23T17:43:20.000Z</v>
+        <v>2026-07-23T22:49:22.999Z</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
       </c>
       <c r="J45" t="str">
-        <v>27/07/2026 07:30:29</v>
+        <v>27/07/2026 06:00:00</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>INC000000153807</v>
+        <v>INC000000153813</v>
       </c>
       <c r="B46" t="str">
         <v>No</v>
@@ -1856,59 +1856,59 @@
         <v>Baja</v>
       </c>
       <c r="E46" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F46" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT ZONA OCCIDENTE</v>
       </c>
       <c r="G46" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H46" s="1" t="d">
-        <v>2026-07-23T17:13:51.000Z</v>
+        <v>2026-07-24T06:01:01.000Z</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
       </c>
       <c r="J46" t="str">
-        <v>24/07/2026 10:13:35</v>
+        <v>24/07/2026 14:00:45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>INC000000153811</v>
+        <v>INC000000153815</v>
       </c>
       <c r="B47" t="str">
         <v>No</v>
       </c>
       <c r="C47" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D47" t="str">
         <v>Baja</v>
       </c>
       <c r="E47" t="str">
-        <v>DILAN SAMIR LOPEZ ARAUJO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F47" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G47" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H47" s="1" t="d">
-        <v>2026-07-23T22:49:22.999Z</v>
+        <v>2026-07-24T06:15:58.000Z</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
       </c>
       <c r="J47" t="str">
-        <v>27/07/2026 06:00:00</v>
+        <v>24/07/2026 14:15:42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>INC000000153813</v>
+        <v>INC000000153818</v>
       </c>
       <c r="B48" t="str">
         <v>No</v>
@@ -1920,27 +1920,27 @@
         <v>Baja</v>
       </c>
       <c r="E48" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>MARIA FERNANDA PEREIRA BUENO</v>
       </c>
       <c r="F48" t="str">
-        <v>SPT ZONA OCCIDENTE</v>
+        <v>SPT CABECERA CALLE 94</v>
       </c>
       <c r="G48" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H48" s="1" t="d">
-        <v>2026-07-24T06:01:01.000Z</v>
+        <v>2026-07-24T06:32:03.000Z</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
       </c>
       <c r="J48" t="str">
-        <v>24/07/2026 14:00:45</v>
+        <v>24/07/2026 14:31:47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>INC000000153815</v>
+        <v>INC000000153821</v>
       </c>
       <c r="B49" t="str">
         <v>No</v>
@@ -1961,50 +1961,50 @@
         <v>a) 0-4</v>
       </c>
       <c r="H49" s="1" t="d">
-        <v>2026-07-24T06:15:58.000Z</v>
+        <v>2026-07-24T06:51:17.999Z</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
       </c>
       <c r="J49" t="str">
-        <v>24/07/2026 14:15:42</v>
+        <v>24/07/2026 14:51:02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>INC000000153818</v>
+        <v>INC000000153822</v>
       </c>
       <c r="B50" t="str">
         <v>No</v>
       </c>
       <c r="C50" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D50" t="str">
         <v>Baja</v>
       </c>
       <c r="E50" t="str">
-        <v>MARIA FERNANDA PEREIRA BUENO</v>
+        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
       </c>
       <c r="F50" t="str">
-        <v>SPT CABECERA CALLE 94</v>
+        <v>SPT CABECERA 1 MAYO</v>
       </c>
       <c r="G50" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H50" s="1" t="d">
-        <v>2026-07-24T06:32:03.000Z</v>
+        <v>2026-07-24T06:51:19.000Z</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
       </c>
       <c r="J50" t="str">
-        <v>24/07/2026 14:31:47</v>
+        <v>24/07/2026 14:51:03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>INC000000153821</v>
+        <v>INC000000153823</v>
       </c>
       <c r="B51" t="str">
         <v>No</v>
@@ -2016,27 +2016,27 @@
         <v>Baja</v>
       </c>
       <c r="E51" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F51" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G51" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H51" s="1" t="d">
-        <v>2026-07-24T06:51:17.999Z</v>
+        <v>2026-07-24T06:56:46.000Z</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
       </c>
       <c r="J51" t="str">
-        <v>24/07/2026 14:51:02</v>
+        <v>24/07/2026 14:56:30</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>INC000000153822</v>
+        <v>INC000000153824</v>
       </c>
       <c r="B52" t="str">
         <v>No</v>
@@ -2048,59 +2048,59 @@
         <v>Baja</v>
       </c>
       <c r="E52" t="str">
-        <v>PEDRO ANTONIO SARMIENTO PEREZ</v>
+        <v>DANIEL CAMILO BARRERO GALINDO</v>
       </c>
       <c r="F52" t="str">
-        <v>SPT CABECERA 1 MAYO</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G52" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H52" s="1" t="d">
-        <v>2026-07-24T06:51:19.000Z</v>
+        <v>2026-07-24T07:14:28.000Z</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
       </c>
       <c r="J52" t="str">
-        <v>24/07/2026 14:51:03</v>
+        <v>24/07/2026 15:14:12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>INC000000153823</v>
+        <v>INC000000153826</v>
       </c>
       <c r="B53" t="str">
         <v>No</v>
       </c>
       <c r="C53" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D53" t="str">
         <v>Baja</v>
       </c>
       <c r="E53" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F53" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G53" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H53" s="1" t="d">
-        <v>2026-07-24T06:56:46.000Z</v>
+        <v>2026-07-24T07:27:52.999Z</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
       </c>
       <c r="J53" t="str">
-        <v>24/07/2026 14:56:30</v>
+        <v>24/07/2026 15:27:37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>INC000000153824</v>
+        <v>INC000000153827</v>
       </c>
       <c r="B54" t="str">
         <v>No</v>
@@ -2112,27 +2112,27 @@
         <v>Baja</v>
       </c>
       <c r="E54" t="str">
-        <v>DANIEL CAMILO BARRERO GALINDO</v>
+        <v>ALLISSON MAURICIO MORENO PABON</v>
       </c>
       <c r="F54" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>SPT CABECERA KENNEDY</v>
       </c>
       <c r="G54" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H54" s="1" t="d">
-        <v>2026-07-24T07:14:28.000Z</v>
+        <v>2026-07-24T07:28:17.000Z</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
       </c>
       <c r="J54" t="str">
-        <v>24/07/2026 15:14:12</v>
+        <v>24/07/2026 15:28:01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>INC000000153826</v>
+        <v>INC000000153828</v>
       </c>
       <c r="B55" t="str">
         <v>No</v>
@@ -2144,27 +2144,27 @@
         <v>Baja</v>
       </c>
       <c r="E55" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F55" t="str">
-        <v>SPT ZONA SURORIENTE</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G55" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H55" s="1" t="d">
-        <v>2026-07-24T07:27:52.999Z</v>
+        <v>2026-07-24T07:29:17.000Z</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
       </c>
       <c r="J55" t="str">
-        <v>24/07/2026 15:27:37</v>
+        <v>24/07/2026 15:29:01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>INC000000153827</v>
+        <v>INC000000153829</v>
       </c>
       <c r="B56" t="str">
         <v>No</v>
@@ -2185,18 +2185,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H56" s="1" t="d">
-        <v>2026-07-24T07:28:17.000Z</v>
+        <v>2026-07-24T07:34:05.000Z</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
       </c>
       <c r="J56" t="str">
-        <v>24/07/2026 15:28:01</v>
+        <v>24/07/2026 15:33:49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>INC000000153828</v>
+        <v>INC000000153833</v>
       </c>
       <c r="B57" t="str">
         <v>No</v>
@@ -2208,91 +2208,91 @@
         <v>Baja</v>
       </c>
       <c r="E57" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
       </c>
       <c r="F57" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ZONA NORTE</v>
       </c>
       <c r="G57" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H57" s="1" t="d">
-        <v>2026-07-24T07:29:17.000Z</v>
+        <v>2026-07-24T07:52:37.999Z</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
       </c>
       <c r="J57" t="str">
-        <v>24/07/2026 15:29:01</v>
+        <v>24/07/2026 15:52:22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>INC000000153829</v>
+        <v>INC000000153834</v>
       </c>
       <c r="B58" t="str">
         <v>No</v>
       </c>
       <c r="C58" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D58" t="str">
         <v>Baja</v>
       </c>
       <c r="E58" t="str">
-        <v>ALLISSON MAURICIO MORENO PABON</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F58" t="str">
-        <v>SPT CABECERA KENNEDY</v>
+        <v>ZONA SURORIENTE</v>
       </c>
       <c r="G58" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H58" s="1" t="d">
-        <v>2026-07-24T07:34:05.000Z</v>
+        <v>2026-07-24T07:52:04.000Z</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
       </c>
       <c r="J58" t="str">
-        <v>24/07/2026 15:33:49</v>
+        <v>27/07/2026 07:51:48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>INC000000153830</v>
+        <v>INC000000153837</v>
       </c>
       <c r="B59" t="str">
         <v>No</v>
       </c>
       <c r="C59" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D59" t="str">
         <v>Baja</v>
       </c>
       <c r="E59" t="str">
-        <v>DAVID ESTEBAN DIAZ LLANOS</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F59" t="str">
-        <v>SPT CABECERA CALLE 42</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G59" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H59" s="1" t="d">
-        <v>2026-07-24T07:43:41.000Z</v>
+        <v>2026-07-24T08:16:27.000Z</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
       </c>
       <c r="J59" t="str">
-        <v>24/07/2026 15:43:25</v>
+        <v>24/07/2026 16:16:11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>INC000000153833</v>
+        <v>INC000000153838</v>
       </c>
       <c r="B60" t="str">
         <v>No</v>
@@ -2304,88 +2304,91 @@
         <v>Baja</v>
       </c>
       <c r="E60" t="str">
-        <v>EDWIN ALEXIS PATIÑO TEJEDOR</v>
+        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
       </c>
       <c r="F60" t="str">
-        <v>SPT ZONA NORTE</v>
+        <v>SPT ZONA SURORIENTE</v>
       </c>
       <c r="G60" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H60" s="1" t="d">
-        <v>2026-07-24T07:52:37.999Z</v>
+        <v>2026-07-24T08:18:57.000Z</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
       </c>
       <c r="J60" t="str">
-        <v>24/07/2026 15:52:22</v>
+        <v>24/07/2026 16:18:41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>INC000000153834</v>
+        <v>INC000000153907</v>
       </c>
       <c r="B61" t="str">
         <v>No</v>
       </c>
       <c r="C61" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D61" t="str">
         <v>Baja</v>
       </c>
       <c r="E61" t="str">
-        <v>MICHAEL STEVEN FRAILE GOMEZ</v>
+        <v>FREDY ANDRES AVILA VEGA</v>
       </c>
       <c r="F61" t="str">
-        <v>ZONA SURORIENTE</v>
+        <v>ZONA LAGOMAR</v>
       </c>
       <c r="G61" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H61" s="1" t="d">
-        <v>2026-07-24T07:52:04.000Z</v>
+        <v>2026-07-23T19:54:55.000Z</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
       </c>
       <c r="J61" t="str">
-        <v>27/07/2026 07:51:48</v>
+        <v>27/07/2026 07:46:06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>INC000000153837</v>
+        <v>INC000000153909</v>
       </c>
       <c r="B62" t="str">
         <v>No</v>
       </c>
       <c r="C62" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D62" t="str">
         <v>Baja</v>
       </c>
+      <c r="E62" t="str">
+        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+      </c>
       <c r="F62" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>SPT CABECERA CALLE 26</v>
       </c>
       <c r="G62" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H62" s="1" t="d">
-        <v>2026-07-24T08:16:27.000Z</v>
+        <v>2026-07-23T22:33:57.000Z</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
       </c>
       <c r="J62" t="str">
-        <v>24/07/2026 16:16:11</v>
+        <v>24/07/2026 14:00:00</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>INC000000153907</v>
+        <v>INC000000153912</v>
       </c>
       <c r="B63" t="str">
         <v>No</v>
@@ -2397,59 +2400,59 @@
         <v>Baja</v>
       </c>
       <c r="E63" t="str">
-        <v>FREDY ANDRES AVILA VEGA</v>
+        <v>JUAN CAMILO RINCON BLANCO</v>
       </c>
       <c r="F63" t="str">
-        <v>ZONA LAGOMAR</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G63" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H63" s="1" t="d">
-        <v>2026-07-23T19:54:55.000Z</v>
+        <v>2026-07-24T06:13:18.000Z</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
       </c>
       <c r="J63" t="str">
-        <v>27/07/2026 07:46:06</v>
+        <v>24/07/2026 14:13:02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>INC000000153909</v>
+        <v>INC000000153913</v>
       </c>
       <c r="B64" t="str">
         <v>No</v>
       </c>
       <c r="C64" t="str">
-        <v>En curso</v>
+        <v>Asignado</v>
       </c>
       <c r="D64" t="str">
         <v>Baja</v>
       </c>
       <c r="E64" t="str">
-        <v>CAMILO ANDRES GONZALEZ NARVAEZ</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F64" t="str">
-        <v>SPT CABECERA CALLE 26</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G64" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H64" s="1" t="d">
-        <v>2026-07-23T22:33:57.000Z</v>
+        <v>2026-07-24T06:10:35.000Z</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
       </c>
       <c r="J64" t="str">
-        <v>24/07/2026 14:00:00</v>
+        <v>27/07/2026 06:10:19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>INC000000153912</v>
+        <v>INC000000153915</v>
       </c>
       <c r="B65" t="str">
         <v>No</v>
@@ -2470,18 +2473,18 @@
         <v>a) 0-4</v>
       </c>
       <c r="H65" s="1" t="d">
-        <v>2026-07-24T06:13:18.000Z</v>
+        <v>2026-07-24T06:17:56.000Z</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
       </c>
       <c r="J65" t="str">
-        <v>24/07/2026 14:13:02</v>
+        <v>24/07/2026 14:17:40</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>INC000000153913</v>
+        <v>INC000000153917</v>
       </c>
       <c r="B66" t="str">
         <v>No</v>
@@ -2493,59 +2496,59 @@
         <v>Baja</v>
       </c>
       <c r="E66" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F66" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G66" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H66" s="1" t="d">
-        <v>2026-07-24T06:10:35.000Z</v>
+        <v>2026-07-24T06:43:42.999Z</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
       </c>
       <c r="J66" t="str">
-        <v>27/07/2026 06:10:19</v>
+        <v>24/07/2026 14:43:27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>INC000000153915</v>
+        <v>INC000000153919</v>
       </c>
       <c r="B67" t="str">
         <v>No</v>
       </c>
       <c r="C67" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D67" t="str">
         <v>Baja</v>
       </c>
       <c r="E67" t="str">
-        <v>JUAN CAMILO RINCON BLANCO</v>
+        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
       </c>
       <c r="F67" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>SPT ESCRITORIO VIRTUAL</v>
       </c>
       <c r="G67" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H67" s="1" t="d">
-        <v>2026-07-24T06:17:56.000Z</v>
+        <v>2026-07-24T07:28:12.000Z</v>
       </c>
       <c r="I67" t="str">
         <v>-</v>
       </c>
       <c r="J67" t="str">
-        <v>24/07/2026 14:17:40</v>
+        <v>24/07/2026 15:27:56</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>INC000000153916</v>
+        <v>INC000000153923</v>
       </c>
       <c r="B68" t="str">
         <v>No</v>
@@ -2557,59 +2560,59 @@
         <v>Baja</v>
       </c>
       <c r="E68" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>JEISON ANDRES REYES ROMERO</v>
       </c>
       <c r="F68" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA ORIENTE</v>
       </c>
       <c r="G68" t="str">
         <v>a) 0-4</v>
       </c>
       <c r="H68" s="1" t="d">
-        <v>2026-07-24T06:26:57.000Z</v>
+        <v>2026-07-24T08:08:50.999Z</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
       </c>
       <c r="J68" t="str">
-        <v>24/07/2026 14:26:41</v>
+        <v>27/07/2026 08:08:35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>INC000000153917</v>
+        <v>WO0000000305253</v>
       </c>
       <c r="B69" t="str">
         <v>No</v>
       </c>
       <c r="C69" t="str">
-        <v>Asignado</v>
+        <v>Pendiente</v>
       </c>
       <c r="D69" t="str">
-        <v>Baja</v>
+        <v>Alta</v>
       </c>
       <c r="E69" t="str">
-        <v>IVAN FELIPE GARCIA MANRIQUE</v>
+        <v>GERLYN RENTERIA OROZCO</v>
       </c>
       <c r="F69" t="str">
-        <v>SPT CABECERA CARRERA 69</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G69" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H69" s="1" t="d">
-        <v>2026-07-24T06:43:42.999Z</v>
-      </c>
-      <c r="I69" t="str">
-        <v>-</v>
+        <v>2026-07-16T09:33:16.000Z</v>
+      </c>
+      <c r="I69" s="1" t="d">
+        <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J69" t="str">
-        <v>24/07/2026 14:43:27</v>
+        <v>27/07/2026 10:03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>INC000000153919</v>
+        <v>WO0000000305335</v>
       </c>
       <c r="B70" t="str">
         <v>No</v>
@@ -2621,59 +2624,53 @@
         <v>Baja</v>
       </c>
       <c r="E70" t="str">
-        <v>FABIAN JESSID PASTRANA AGUIRRE</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F70" t="str">
-        <v>SPT ESCRITORIO VIRTUAL</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G70" t="str">
-        <v>a) 0-4</v>
+        <v>c) 11-30</v>
       </c>
       <c r="H70" s="1" t="d">
-        <v>2026-07-24T07:28:12.000Z</v>
-      </c>
-      <c r="I70" t="str">
-        <v>-</v>
+        <v>2026-07-08T07:01:16.000Z</v>
       </c>
       <c r="J70" t="str">
-        <v>24/07/2026 15:27:56</v>
+        <v>14/08/2026 13:09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>INC000000153923</v>
+        <v>WO0000000307624</v>
       </c>
       <c r="B71" t="str">
         <v>No</v>
       </c>
       <c r="C71" t="str">
-        <v>Asignado</v>
+        <v>En curso</v>
       </c>
       <c r="D71" t="str">
         <v>Baja</v>
       </c>
       <c r="E71" t="str">
-        <v>JEISON ANDRES REYES ROMERO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F71" t="str">
-        <v>ZONA ORIENTE</v>
+        <v>ZONA CENTRO</v>
       </c>
       <c r="G71" t="str">
-        <v>a) 0-4</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H71" s="1" t="d">
-        <v>2026-07-24T08:08:50.999Z</v>
-      </c>
-      <c r="I71" t="str">
-        <v>-</v>
+        <v>2026-07-14T12:23:16.000Z</v>
       </c>
       <c r="J71" t="str">
-        <v>27/07/2026 08:08:35</v>
+        <v>13/08/2026 12:23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>WO0000000305253</v>
+        <v>WO0000000307988</v>
       </c>
       <c r="B72" t="str">
         <v>No</v>
@@ -2682,10 +2679,10 @@
         <v>Pendiente</v>
       </c>
       <c r="D72" t="str">
-        <v>Alta</v>
+        <v>Baja</v>
       </c>
       <c r="E72" t="str">
-        <v>GERLYN RENTERIA OROZCO</v>
+        <v>KEVIN ALEXIS GARCIA GUARACA</v>
       </c>
       <c r="F72" t="str">
         <v>ZONA CENTRO</v>
@@ -2694,76 +2691,82 @@
         <v>b) 5-10</v>
       </c>
       <c r="H72" s="1" t="d">
-        <v>2026-07-16T09:33:16.000Z</v>
+        <v>2026-07-15T09:38:16.000Z</v>
       </c>
       <c r="I72" s="1" t="d">
         <v>2026-07-24T18:00:16.000Z</v>
       </c>
       <c r="J72" t="str">
-        <v>27/07/2026 10:03</v>
+        <v>24/07/2026 09:38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WO0000000305335</v>
+        <v>WO0000000308197</v>
       </c>
       <c r="B73" t="str">
         <v>No</v>
       </c>
       <c r="C73" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D73" t="str">
         <v>Baja</v>
       </c>
       <c r="E73" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F73" t="str">
-        <v>ZONA OCCIDENTE</v>
+        <v>ZONA NOROCCIDENTE</v>
       </c>
       <c r="G73" t="str">
-        <v>c) 11-30</v>
+        <v>b) 5-10</v>
       </c>
       <c r="H73" s="1" t="d">
-        <v>2026-07-08T07:01:16.000Z</v>
+        <v>2026-07-15T12:53:16.000Z</v>
+      </c>
+      <c r="I73" s="1" t="d">
+        <v>2026-07-27T18:00:16.000Z</v>
       </c>
       <c r="J73" t="str">
-        <v>14/08/2026 13:09</v>
+        <v>24/07/2026 10:19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WO0000000307624</v>
+        <v>WO0000000308443</v>
       </c>
       <c r="B74" t="str">
         <v>No</v>
       </c>
       <c r="C74" t="str">
-        <v>En curso</v>
+        <v>Pendiente</v>
       </c>
       <c r="D74" t="str">
         <v>Baja</v>
       </c>
       <c r="E74" t="str">
-        <v>NICK STEVE TRIANA LOPEZ</v>
+        <v>IVAN FELIPE GARCIA MANRIQUE</v>
       </c>
       <c r="F74" t="str">
-        <v>ZONA CENTRO</v>
+        <v>SPT CABECERA CARRERA 69</v>
       </c>
       <c r="G74" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H74" s="1" t="d">
-        <v>2026-07-14T12:23:16.000Z</v>
+        <v>2026-07-15T15:46:16.000Z</v>
+      </c>
+      <c r="I74" s="1" t="d">
+        <v>2026-07-24T17:00:16.000Z</v>
       </c>
       <c r="J74" t="str">
-        <v>13/08/2026 12:23</v>
+        <v>28/07/2026 13:47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WO0000000307988</v>
+        <v>WO0000000308723</v>
       </c>
       <c r="B75" t="str">
         <v>No</v>
@@ -2775,7 +2778,7 @@
         <v>Baja</v>
       </c>
       <c r="E75" t="str">
-        <v>KEVIN ALEXIS GARCIA GUARACA</v>
+        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
       </c>
       <c r="F75" t="str">
         <v>ZONA CENTRO</v>
@@ -2784,82 +2787,76 @@
         <v>b) 5-10</v>
       </c>
       <c r="H75" s="1" t="d">
-        <v>2026-07-15T09:38:16.000Z</v>
+        <v>2026-07-16T10:49:16.000Z</v>
       </c>
       <c r="I75" s="1" t="d">
-        <v>2026-07-24T18:00:16.000Z</v>
+        <v>2026-07-30T17:00:16.000Z</v>
       </c>
       <c r="J75" t="str">
-        <v>24/07/2026 09:38</v>
+        <v>24/07/2026 10:31</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WO0000000308197</v>
+        <v>WO0000000309139</v>
       </c>
       <c r="B76" t="str">
         <v>No</v>
       </c>
       <c r="C76" t="str">
-        <v>Pendiente</v>
+        <v>En curso</v>
       </c>
       <c r="D76" t="str">
         <v>Baja</v>
       </c>
       <c r="E76" t="str">
-        <v>DANIEL ALEJANDRO BORDA MESTIZO</v>
+        <v>NICK STEVE TRIANA LOPEZ</v>
       </c>
       <c r="F76" t="str">
-        <v>ZONA NOROCCIDENTE</v>
+        <v>ZONA OCCIDENTE</v>
       </c>
       <c r="G76" t="str">
         <v>b) 5-10</v>
       </c>
       <c r="H76" s="1" t="d">
-        <v>2026-07-15T12:53:16.000Z</v>
-      </c>
-      <c r="I76" s="1" t="d">
-        <v>2026-07-27T18:00:16.000Z</v>
+